--- a/quizzes/peinture-15e.xlsx
+++ b/quizzes/peinture-15e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB4D682-7202-47C2-96E6-29ECA5082C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A62597-A848-475C-8A7E-3D8D9EC03BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2632" uniqueCount="1340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2606" uniqueCount="1340">
   <si>
     <t>Image</t>
   </si>
@@ -4578,7 +4578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S196"/>
+  <dimension ref="A1:S194"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="59.140625" style="30" customWidth="1"/>
@@ -12049,7 +12049,7 @@
     </row>
     <row r="146" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="15" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>993</v>
@@ -12066,28 +12066,28 @@
         <v>996</v>
       </c>
       <c r="H146" s="7" t="s">
-        <v>809</v>
+        <v>999</v>
       </c>
       <c r="I146" s="7" t="s">
-        <v>203</v>
+        <v>32</v>
       </c>
       <c r="J146" s="7" t="s">
-        <v>204</v>
+        <v>33</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="M146" s="8"/>
-      <c r="N146" s="8"/>
+        <v>1000</v>
+      </c>
+      <c r="M146" s="7"/>
+      <c r="N146" s="7"/>
       <c r="O146" s="7" t="s">
         <v>345</v>
       </c>
       <c r="P146" s="7" t="s">
-        <v>355</v>
+        <v>1001</v>
       </c>
       <c r="Q146" s="7" t="s">
-        <v>997</v>
+        <v>1002</v>
       </c>
       <c r="R146" s="7" t="s">
         <v>190</v>
@@ -12098,7 +12098,7 @@
     </row>
     <row r="147" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="15" t="s">
-        <v>998</v>
+        <v>1007</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>993</v>
@@ -12115,17 +12115,17 @@
         <v>996</v>
       </c>
       <c r="H147" s="7" t="s">
-        <v>999</v>
+        <v>1008</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>32</v>
+        <v>698</v>
       </c>
       <c r="J147" s="7" t="s">
-        <v>33</v>
+        <v>699</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="8" t="s">
-        <v>1000</v>
+        <v>1009</v>
       </c>
       <c r="M147" s="7"/>
       <c r="N147" s="7"/>
@@ -12133,10 +12133,10 @@
         <v>345</v>
       </c>
       <c r="P147" s="7" t="s">
-        <v>1001</v>
+        <v>377</v>
       </c>
       <c r="Q147" s="7" t="s">
-        <v>1002</v>
+        <v>1010</v>
       </c>
       <c r="R147" s="7" t="s">
         <v>190</v>
@@ -12147,7 +12147,7 @@
     </row>
     <row r="148" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="15" t="s">
-        <v>1003</v>
+        <v>1011</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>993</v>
@@ -12164,28 +12164,28 @@
         <v>996</v>
       </c>
       <c r="H148" s="7" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="I148" s="7" t="s">
-        <v>330</v>
+        <v>1013</v>
       </c>
       <c r="J148" s="7" t="s">
-        <v>331</v>
+        <v>1014</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="8" t="s">
-        <v>1005</v>
+        <v>1015</v>
       </c>
       <c r="M148" s="7"/>
       <c r="N148" s="7"/>
       <c r="O148" s="7" t="s">
-        <v>345</v>
+        <v>187</v>
       </c>
       <c r="P148" s="7" t="s">
-        <v>765</v>
+        <v>451</v>
       </c>
       <c r="Q148" s="7" t="s">
-        <v>1006</v>
+        <v>1016</v>
       </c>
       <c r="R148" s="7" t="s">
         <v>190</v>
@@ -12196,7 +12196,7 @@
     </row>
     <row r="149" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="15" t="s">
-        <v>1007</v>
+        <v>1017</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>993</v>
@@ -12213,17 +12213,17 @@
         <v>996</v>
       </c>
       <c r="H149" s="7" t="s">
-        <v>1008</v>
+        <v>1018</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>698</v>
+        <v>330</v>
       </c>
       <c r="J149" s="7" t="s">
-        <v>699</v>
+        <v>331</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="8" t="s">
-        <v>1009</v>
+        <v>1019</v>
       </c>
       <c r="M149" s="7"/>
       <c r="N149" s="7"/>
@@ -12231,10 +12231,10 @@
         <v>345</v>
       </c>
       <c r="P149" s="7" t="s">
-        <v>377</v>
+        <v>576</v>
       </c>
       <c r="Q149" s="7" t="s">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="R149" s="7" t="s">
         <v>190</v>
@@ -12245,7 +12245,7 @@
     </row>
     <row r="150" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="15" t="s">
-        <v>1011</v>
+        <v>1021</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>993</v>
@@ -12262,28 +12262,30 @@
         <v>996</v>
       </c>
       <c r="H150" s="7" t="s">
-        <v>1012</v>
+        <v>1022</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>1013</v>
+        <v>1023</v>
       </c>
       <c r="J150" s="7" t="s">
-        <v>1014</v>
-      </c>
-      <c r="K150" s="7"/>
+        <v>1024</v>
+      </c>
+      <c r="K150" s="7" t="s">
+        <v>1025</v>
+      </c>
       <c r="L150" s="8" t="s">
-        <v>1015</v>
+        <v>1026</v>
       </c>
       <c r="M150" s="7"/>
       <c r="N150" s="7"/>
       <c r="O150" s="7" t="s">
-        <v>187</v>
+        <v>1027</v>
       </c>
       <c r="P150" s="7" t="s">
-        <v>451</v>
+        <v>355</v>
       </c>
       <c r="Q150" s="7" t="s">
-        <v>1016</v>
+        <v>1028</v>
       </c>
       <c r="R150" s="7" t="s">
         <v>190</v>
@@ -12294,7 +12296,7 @@
     </row>
     <row r="151" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="15" t="s">
-        <v>1017</v>
+        <v>1029</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>993</v>
@@ -12311,17 +12313,17 @@
         <v>996</v>
       </c>
       <c r="H151" s="7" t="s">
-        <v>1018</v>
+        <v>485</v>
       </c>
       <c r="I151" s="7" t="s">
-        <v>330</v>
+        <v>645</v>
       </c>
       <c r="J151" s="7" t="s">
-        <v>331</v>
+        <v>646</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="8" t="s">
-        <v>1019</v>
+        <v>1030</v>
       </c>
       <c r="M151" s="7"/>
       <c r="N151" s="7"/>
@@ -12329,10 +12331,10 @@
         <v>345</v>
       </c>
       <c r="P151" s="7" t="s">
-        <v>576</v>
+        <v>1031</v>
       </c>
       <c r="Q151" s="7" t="s">
-        <v>1020</v>
+        <v>1032</v>
       </c>
       <c r="R151" s="7" t="s">
         <v>190</v>
@@ -12343,7 +12345,7 @@
     </row>
     <row r="152" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="15" t="s">
-        <v>1021</v>
+        <v>1033</v>
       </c>
       <c r="B152" s="7" t="s">
         <v>993</v>
@@ -12360,30 +12362,28 @@
         <v>996</v>
       </c>
       <c r="H152" s="7" t="s">
-        <v>1022</v>
+        <v>1034</v>
       </c>
       <c r="I152" s="7" t="s">
-        <v>1023</v>
+        <v>25</v>
       </c>
       <c r="J152" s="7" t="s">
-        <v>1024</v>
-      </c>
-      <c r="K152" s="7" t="s">
-        <v>1025</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="K152" s="7"/>
       <c r="L152" s="8" t="s">
-        <v>1026</v>
+        <v>1035</v>
       </c>
       <c r="M152" s="7"/>
       <c r="N152" s="7"/>
       <c r="O152" s="7" t="s">
-        <v>1027</v>
+        <v>345</v>
       </c>
       <c r="P152" s="7" t="s">
-        <v>355</v>
+        <v>1036</v>
       </c>
       <c r="Q152" s="7" t="s">
-        <v>1028</v>
+        <v>1037</v>
       </c>
       <c r="R152" s="7" t="s">
         <v>190</v>
@@ -12394,7 +12394,7 @@
     </row>
     <row r="153" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="15" t="s">
-        <v>1029</v>
+        <v>1038</v>
       </c>
       <c r="B153" s="7" t="s">
         <v>993</v>
@@ -12411,17 +12411,17 @@
         <v>996</v>
       </c>
       <c r="H153" s="7" t="s">
-        <v>485</v>
+        <v>1039</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>645</v>
+        <v>304</v>
       </c>
       <c r="J153" s="7" t="s">
-        <v>646</v>
+        <v>305</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="8" t="s">
-        <v>1030</v>
+        <v>376</v>
       </c>
       <c r="M153" s="7"/>
       <c r="N153" s="7"/>
@@ -12429,10 +12429,10 @@
         <v>345</v>
       </c>
       <c r="P153" s="7" t="s">
-        <v>1031</v>
+        <v>750</v>
       </c>
       <c r="Q153" s="7" t="s">
-        <v>1032</v>
+        <v>568</v>
       </c>
       <c r="R153" s="7" t="s">
         <v>190</v>
@@ -12442,8 +12442,8 @@
       </c>
     </row>
     <row r="154" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="15" t="s">
-        <v>1033</v>
+      <c r="A154" s="23" t="s">
+        <v>1040</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>993</v>
@@ -12460,17 +12460,17 @@
         <v>996</v>
       </c>
       <c r="H154" s="7" t="s">
-        <v>1034</v>
+        <v>999</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J154" s="7" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="8" t="s">
-        <v>1035</v>
+        <v>1000</v>
       </c>
       <c r="M154" s="7"/>
       <c r="N154" s="7"/>
@@ -12478,10 +12478,10 @@
         <v>345</v>
       </c>
       <c r="P154" s="7" t="s">
-        <v>1036</v>
+        <v>1001</v>
       </c>
       <c r="Q154" s="7" t="s">
-        <v>1037</v>
+        <v>1002</v>
       </c>
       <c r="R154" s="7" t="s">
         <v>190</v>
@@ -12490,9 +12490,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:19" s="26" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="15" t="s">
-        <v>1038</v>
+        <v>1003</v>
       </c>
       <c r="B155" s="7" t="s">
         <v>993</v>
@@ -12509,17 +12509,17 @@
         <v>996</v>
       </c>
       <c r="H155" s="7" t="s">
-        <v>1039</v>
+        <v>1004</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="J155" s="7" t="s">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="8" t="s">
-        <v>376</v>
+        <v>1005</v>
       </c>
       <c r="M155" s="7"/>
       <c r="N155" s="7"/>
@@ -12527,10 +12527,10 @@
         <v>345</v>
       </c>
       <c r="P155" s="7" t="s">
-        <v>750</v>
+        <v>765</v>
       </c>
       <c r="Q155" s="7" t="s">
-        <v>568</v>
+        <v>1006</v>
       </c>
       <c r="R155" s="7" t="s">
         <v>190</v>
@@ -12539,362 +12539,358 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="23" t="s">
-        <v>1040</v>
-      </c>
-      <c r="B156" s="7" t="s">
-        <v>993</v>
-      </c>
-      <c r="C156" s="7" t="s">
-        <v>994</v>
-      </c>
-      <c r="D156" s="7"/>
-      <c r="E156" s="7"/>
-      <c r="F156" s="7" t="s">
-        <v>995</v>
-      </c>
-      <c r="G156" s="7" t="s">
-        <v>996</v>
-      </c>
-      <c r="H156" s="7" t="s">
-        <v>999</v>
-      </c>
-      <c r="I156" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="J156" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="K156" s="7"/>
-      <c r="L156" s="8" t="s">
-        <v>1000</v>
-      </c>
-      <c r="M156" s="7"/>
-      <c r="N156" s="7"/>
-      <c r="O156" s="7" t="s">
+    <row r="156" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="18" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B156" s="12" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C156" s="12" t="s">
+        <v>839</v>
+      </c>
+      <c r="D156" s="12" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E156" s="12" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F156" s="12" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G156" s="12" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H156" s="12" t="s">
+        <v>1303</v>
+      </c>
+      <c r="I156" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J156" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K156" s="12" t="s">
+        <v>1304</v>
+      </c>
+      <c r="L156" s="13" t="s">
+        <v>1305</v>
+      </c>
+      <c r="M156" s="13"/>
+      <c r="N156" s="13" t="s">
+        <v>1306</v>
+      </c>
+      <c r="O156" s="12" t="s">
+        <v>1307</v>
+      </c>
+      <c r="P156" s="12">
+        <v>240</v>
+      </c>
+      <c r="Q156" s="12">
+        <v>223</v>
+      </c>
+      <c r="R156" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="S156" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="18" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B157" s="12" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C157" s="12" t="s">
+        <v>839</v>
+      </c>
+      <c r="D157" s="12" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E157" s="12" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F157" s="12" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G157" s="12" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H157" s="12" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I157" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J157" s="12" t="s">
+        <v>1309</v>
+      </c>
+      <c r="K157" s="12" t="s">
+        <v>1310</v>
+      </c>
+      <c r="L157" s="13" t="s">
+        <v>1311</v>
+      </c>
+      <c r="M157" s="13" t="s">
+        <v>1312</v>
+      </c>
+      <c r="N157" s="13" t="s">
+        <v>1313</v>
+      </c>
+      <c r="O157" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="P157" s="12">
+        <v>190</v>
+      </c>
+      <c r="Q157" s="12">
+        <v>122</v>
+      </c>
+      <c r="R157" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="S157" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="158" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="15" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D158" s="1"/>
+      <c r="E158" s="1"/>
+      <c r="F158" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="H158" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="J158" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K158" s="1"/>
+      <c r="L158" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="M158" s="2"/>
+      <c r="N158" s="2"/>
+      <c r="O158" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="P156" s="7" t="s">
-        <v>1001</v>
-      </c>
-      <c r="Q156" s="7" t="s">
-        <v>1002</v>
-      </c>
-      <c r="R156" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="S156" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157" spans="1:19" s="26" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="15" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B157" s="7" t="s">
-        <v>993</v>
-      </c>
-      <c r="C157" s="7" t="s">
-        <v>994</v>
-      </c>
-      <c r="D157" s="7"/>
-      <c r="E157" s="7"/>
-      <c r="F157" s="7" t="s">
-        <v>995</v>
-      </c>
-      <c r="G157" s="7" t="s">
-        <v>996</v>
-      </c>
-      <c r="H157" s="7" t="s">
-        <v>1004</v>
-      </c>
-      <c r="I157" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="J157" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="K157" s="7"/>
-      <c r="L157" s="8" t="s">
-        <v>1005</v>
-      </c>
-      <c r="M157" s="7"/>
-      <c r="N157" s="7"/>
-      <c r="O157" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="P157" s="7" t="s">
-        <v>765</v>
-      </c>
-      <c r="Q157" s="7" t="s">
-        <v>1006</v>
-      </c>
-      <c r="R157" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="S157" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="18" t="s">
-        <v>1314</v>
-      </c>
-      <c r="B158" s="12" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C158" s="12" t="s">
-        <v>839</v>
-      </c>
-      <c r="D158" s="12" t="s">
-        <v>1042</v>
-      </c>
-      <c r="E158" s="12" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F158" s="12" t="s">
-        <v>1043</v>
-      </c>
-      <c r="G158" s="12" t="s">
-        <v>1044</v>
-      </c>
-      <c r="H158" s="12" t="s">
-        <v>1303</v>
-      </c>
-      <c r="I158" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="J158" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="K158" s="12" t="s">
-        <v>1304</v>
-      </c>
-      <c r="L158" s="13" t="s">
-        <v>1305</v>
-      </c>
-      <c r="M158" s="13"/>
-      <c r="N158" s="13" t="s">
-        <v>1306</v>
-      </c>
-      <c r="O158" s="12" t="s">
-        <v>1307</v>
-      </c>
-      <c r="P158" s="12">
-        <v>240</v>
-      </c>
-      <c r="Q158" s="12">
-        <v>223</v>
-      </c>
-      <c r="R158" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="S158" s="12">
+      <c r="P158" s="1"/>
+      <c r="Q158" s="1"/>
+      <c r="R158" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="S158" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:19" s="29" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="18" t="s">
-        <v>1315</v>
-      </c>
-      <c r="B159" s="12" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C159" s="12" t="s">
-        <v>839</v>
-      </c>
-      <c r="D159" s="12" t="s">
-        <v>1042</v>
-      </c>
-      <c r="E159" s="12" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F159" s="12" t="s">
-        <v>1043</v>
-      </c>
-      <c r="G159" s="12" t="s">
-        <v>1044</v>
-      </c>
-      <c r="H159" s="12" t="s">
-        <v>1308</v>
-      </c>
-      <c r="I159" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="J159" s="12" t="s">
-        <v>1309</v>
-      </c>
-      <c r="K159" s="12" t="s">
-        <v>1310</v>
+        <v>1294</v>
+      </c>
+      <c r="B159" s="19" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C159" s="19" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D159" s="19"/>
+      <c r="E159" s="19"/>
+      <c r="F159" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G159" s="19" t="s">
+        <v>571</v>
+      </c>
+      <c r="H159" s="16" t="s">
+        <v>1295</v>
+      </c>
+      <c r="I159" s="16" t="s">
+        <v>1296</v>
+      </c>
+      <c r="J159" s="16" t="s">
+        <v>1297</v>
+      </c>
+      <c r="K159" s="20" t="s">
+        <v>1298</v>
       </c>
       <c r="L159" s="13" t="s">
-        <v>1311</v>
-      </c>
-      <c r="M159" s="13" t="s">
-        <v>1312</v>
-      </c>
-      <c r="N159" s="13" t="s">
-        <v>1313</v>
-      </c>
-      <c r="O159" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="P159" s="12">
-        <v>190</v>
-      </c>
-      <c r="Q159" s="12">
-        <v>122</v>
-      </c>
-      <c r="R159" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="S159" s="16">
+        <v>1299</v>
+      </c>
+      <c r="M159" s="20"/>
+      <c r="N159" s="20" t="s">
+        <v>1300</v>
+      </c>
+      <c r="O159" s="16" t="s">
+        <v>554</v>
+      </c>
+      <c r="P159" s="20" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Q159" s="20">
+        <v>27</v>
+      </c>
+      <c r="R159" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="S159" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="160" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="15" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>1047</v>
-      </c>
-      <c r="D160" s="1"/>
-      <c r="E160" s="1"/>
-      <c r="F160" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G160" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="H160" s="1" t="s">
-        <v>1048</v>
-      </c>
-      <c r="I160" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="J160" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="K160" s="1"/>
-      <c r="L160" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="M160" s="2"/>
-      <c r="N160" s="2"/>
-      <c r="O160" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="P160" s="1"/>
-      <c r="Q160" s="1"/>
-      <c r="R160" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="S160" s="1">
+        <v>1051</v>
+      </c>
+      <c r="B160" s="12" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C160" s="12" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D160" s="12"/>
+      <c r="E160" s="12"/>
+      <c r="F160" s="12" t="s">
+        <v>801</v>
+      </c>
+      <c r="G160" s="12" t="s">
+        <v>1054</v>
+      </c>
+      <c r="H160" s="12" t="s">
+        <v>1055</v>
+      </c>
+      <c r="I160" s="12" t="s">
+        <v>1056</v>
+      </c>
+      <c r="J160" s="12" t="s">
+        <v>1057</v>
+      </c>
+      <c r="K160" s="12"/>
+      <c r="L160" s="13" t="s">
+        <v>1058</v>
+      </c>
+      <c r="M160" s="13"/>
+      <c r="N160" s="13"/>
+      <c r="O160" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P160" s="12" t="s">
+        <v>1059</v>
+      </c>
+      <c r="Q160" s="12" t="s">
+        <v>1060</v>
+      </c>
+      <c r="R160" s="12" t="s">
+        <v>807</v>
+      </c>
+      <c r="S160" s="12">
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="1:19" s="29" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="18" t="s">
-        <v>1294</v>
-      </c>
-      <c r="B161" s="19" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C161" s="19" t="s">
-        <v>1047</v>
-      </c>
-      <c r="D161" s="19"/>
-      <c r="E161" s="19"/>
-      <c r="F161" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G161" s="19" t="s">
-        <v>571</v>
+    <row r="161" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="15" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B161" s="16" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C161" s="16" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D161" s="14"/>
+      <c r="E161" s="14"/>
+      <c r="F161" s="12" t="s">
+        <v>801</v>
+      </c>
+      <c r="G161" s="12" t="s">
+        <v>1054</v>
       </c>
       <c r="H161" s="16" t="s">
-        <v>1295</v>
+        <v>809</v>
       </c>
       <c r="I161" s="16" t="s">
-        <v>1296</v>
+        <v>1056</v>
       </c>
       <c r="J161" s="16" t="s">
-        <v>1297</v>
-      </c>
-      <c r="K161" s="20" t="s">
-        <v>1298</v>
-      </c>
+        <v>1062</v>
+      </c>
+      <c r="K161" s="17"/>
       <c r="L161" s="13" t="s">
-        <v>1299</v>
-      </c>
-      <c r="M161" s="20"/>
-      <c r="N161" s="20" t="s">
-        <v>1300</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="M161" s="17"/>
+      <c r="N161" s="17"/>
       <c r="O161" s="16" t="s">
-        <v>554</v>
-      </c>
-      <c r="P161" s="20" t="s">
-        <v>1301</v>
-      </c>
-      <c r="Q161" s="20">
-        <v>27</v>
-      </c>
-      <c r="R161" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="S161" s="1">
+        <v>412</v>
+      </c>
+      <c r="P161" s="17"/>
+      <c r="Q161" s="17"/>
+      <c r="R161" s="16" t="s">
+        <v>807</v>
+      </c>
+      <c r="S161" s="16">
         <v>3</v>
       </c>
     </row>
     <row r="162" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="15" t="s">
-        <v>1051</v>
+        <v>1063</v>
       </c>
       <c r="B162" s="12" t="s">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="C162" s="12" t="s">
-        <v>1053</v>
-      </c>
-      <c r="D162" s="12"/>
-      <c r="E162" s="12"/>
+        <v>394</v>
+      </c>
+      <c r="D162" s="12" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E162" s="12" t="s">
+        <v>1065</v>
+      </c>
       <c r="F162" s="12" t="s">
-        <v>801</v>
+        <v>1066</v>
       </c>
       <c r="G162" s="12" t="s">
-        <v>1054</v>
+        <v>457</v>
       </c>
       <c r="H162" s="12" t="s">
-        <v>1055</v>
+        <v>956</v>
       </c>
       <c r="I162" s="12" t="s">
-        <v>1056</v>
+        <v>840</v>
       </c>
       <c r="J162" s="12" t="s">
-        <v>1057</v>
+        <v>1067</v>
       </c>
       <c r="K162" s="12"/>
       <c r="L162" s="13" t="s">
-        <v>1058</v>
+        <v>1068</v>
       </c>
       <c r="M162" s="13"/>
       <c r="N162" s="13"/>
       <c r="O162" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="P162" s="12" t="s">
-        <v>1059</v>
-      </c>
-      <c r="Q162" s="12" t="s">
-        <v>1060</v>
-      </c>
+      <c r="P162" s="12"/>
+      <c r="Q162" s="12"/>
       <c r="R162" s="12" t="s">
-        <v>807</v>
+        <v>29</v>
       </c>
       <c r="S162" s="12">
         <v>3</v>
@@ -12902,44 +12898,48 @@
     </row>
     <row r="163" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="15" t="s">
-        <v>1061</v>
+        <v>1069</v>
       </c>
       <c r="B163" s="16" t="s">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="C163" s="16" t="s">
-        <v>1053</v>
-      </c>
-      <c r="D163" s="14"/>
-      <c r="E163" s="14"/>
+        <v>394</v>
+      </c>
+      <c r="D163" s="12" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E163" s="12" t="s">
+        <v>1065</v>
+      </c>
       <c r="F163" s="12" t="s">
-        <v>801</v>
+        <v>1066</v>
       </c>
       <c r="G163" s="12" t="s">
-        <v>1054</v>
+        <v>457</v>
       </c>
       <c r="H163" s="16" t="s">
-        <v>809</v>
+        <v>1070</v>
       </c>
       <c r="I163" s="16" t="s">
-        <v>1056</v>
+        <v>1071</v>
       </c>
       <c r="J163" s="16" t="s">
-        <v>1062</v>
+        <v>1072</v>
       </c>
       <c r="K163" s="17"/>
       <c r="L163" s="13" t="s">
-        <v>543</v>
+        <v>846</v>
       </c>
       <c r="M163" s="17"/>
       <c r="N163" s="17"/>
       <c r="O163" s="16" t="s">
-        <v>412</v>
+        <v>109</v>
       </c>
       <c r="P163" s="17"/>
       <c r="Q163" s="17"/>
       <c r="R163" s="16" t="s">
-        <v>807</v>
+        <v>29</v>
       </c>
       <c r="S163" s="16">
         <v>3</v>
@@ -12947,43 +12947,41 @@
     </row>
     <row r="164" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="15" t="s">
-        <v>1063</v>
+        <v>1073</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>1064</v>
+        <v>1074</v>
       </c>
       <c r="C164" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="D164" s="12" t="s">
-        <v>1065</v>
-      </c>
-      <c r="E164" s="12" t="s">
-        <v>1065</v>
-      </c>
+        <v>1075</v>
+      </c>
+      <c r="D164" s="12"/>
+      <c r="E164" s="12"/>
       <c r="F164" s="12" t="s">
-        <v>1066</v>
+        <v>1076</v>
       </c>
       <c r="G164" s="12" t="s">
-        <v>457</v>
+        <v>1077</v>
       </c>
       <c r="H164" s="12" t="s">
-        <v>956</v>
+        <v>1078</v>
       </c>
       <c r="I164" s="12" t="s">
-        <v>840</v>
+        <v>122</v>
       </c>
       <c r="J164" s="12" t="s">
-        <v>1067</v>
+        <v>1079</v>
       </c>
       <c r="K164" s="12"/>
       <c r="L164" s="13" t="s">
-        <v>1068</v>
+        <v>1080</v>
       </c>
       <c r="M164" s="13"/>
-      <c r="N164" s="13"/>
+      <c r="N164" s="13" t="s">
+        <v>1081</v>
+      </c>
       <c r="O164" s="12" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="P164" s="12"/>
       <c r="Q164" s="12"/>
@@ -12995,39 +12993,35 @@
       </c>
     </row>
     <row r="165" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="15" t="s">
-        <v>1069</v>
+      <c r="A165" s="18" t="s">
+        <v>1302</v>
       </c>
       <c r="B165" s="16" t="s">
-        <v>1064</v>
+        <v>1074</v>
       </c>
       <c r="C165" s="16" t="s">
-        <v>394</v>
-      </c>
-      <c r="D165" s="12" t="s">
-        <v>1065</v>
-      </c>
-      <c r="E165" s="12" t="s">
-        <v>1065</v>
-      </c>
+        <v>1075</v>
+      </c>
+      <c r="D165" s="14"/>
+      <c r="E165" s="14"/>
       <c r="F165" s="12" t="s">
-        <v>1066</v>
+        <v>1076</v>
       </c>
       <c r="G165" s="12" t="s">
-        <v>457</v>
+        <v>1077</v>
       </c>
       <c r="H165" s="16" t="s">
-        <v>1070</v>
+        <v>1082</v>
       </c>
       <c r="I165" s="16" t="s">
-        <v>1071</v>
+        <v>86</v>
       </c>
       <c r="J165" s="16" t="s">
-        <v>1072</v>
+        <v>87</v>
       </c>
       <c r="K165" s="17"/>
       <c r="L165" s="13" t="s">
-        <v>846</v>
+        <v>332</v>
       </c>
       <c r="M165" s="17"/>
       <c r="N165" s="17"/>
@@ -13043,101 +13037,119 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="15" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B166" s="12" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C166" s="12" t="s">
-        <v>1075</v>
-      </c>
-      <c r="D166" s="12"/>
-      <c r="E166" s="12"/>
-      <c r="F166" s="12" t="s">
-        <v>1076</v>
-      </c>
-      <c r="G166" s="12" t="s">
-        <v>1077</v>
-      </c>
-      <c r="H166" s="12" t="s">
-        <v>1078</v>
-      </c>
-      <c r="I166" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="J166" s="12" t="s">
-        <v>1079</v>
-      </c>
-      <c r="K166" s="12"/>
-      <c r="L166" s="13" t="s">
-        <v>1080</v>
-      </c>
-      <c r="M166" s="13"/>
-      <c r="N166" s="13" t="s">
-        <v>1081</v>
-      </c>
-      <c r="O166" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="P166" s="12"/>
-      <c r="Q166" s="12"/>
-      <c r="R166" s="12" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D166" s="1"/>
+      <c r="E166" s="1"/>
+      <c r="F166" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H166" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="I166" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J166" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K166" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L166" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="M166" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="N166" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="O166" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="P166" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Q166" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="R166" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="S166" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="167" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="18" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B167" s="16" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C167" s="16" t="s">
-        <v>1075</v>
-      </c>
-      <c r="D167" s="14"/>
-      <c r="E167" s="14"/>
-      <c r="F167" s="12" t="s">
-        <v>1076</v>
-      </c>
-      <c r="G167" s="12" t="s">
-        <v>1077</v>
-      </c>
-      <c r="H167" s="16" t="s">
-        <v>1082</v>
-      </c>
-      <c r="I167" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="J167" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="K167" s="17"/>
-      <c r="L167" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="M167" s="17"/>
-      <c r="N167" s="17"/>
-      <c r="O167" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="P167" s="17"/>
-      <c r="Q167" s="17"/>
-      <c r="R167" s="16" t="s">
+      <c r="S166" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="23" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D167" s="1"/>
+      <c r="E167" s="1"/>
+      <c r="F167" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H167" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="I167" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J167" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K167" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L167" s="5" t="s">
+        <v>1097</v>
+      </c>
+      <c r="M167" s="5" t="s">
+        <v>1090</v>
+      </c>
+      <c r="N167" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="O167" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="P167" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="Q167" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="R167" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="S167" s="16">
-        <v>3</v>
+      <c r="S167" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="15" t="s">
-        <v>1083</v>
+      <c r="A168" s="23" t="s">
+        <v>1101</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>1084</v>
@@ -13154,7 +13166,7 @@
         <v>1087</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>279</v>
+        <v>669</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>44</v>
@@ -13165,23 +13177,23 @@
       <c r="K168" s="1" t="s">
         <v>1088</v>
       </c>
-      <c r="L168" s="2" t="s">
-        <v>1089</v>
-      </c>
-      <c r="M168" s="2" t="s">
+      <c r="L168" s="5" t="s">
+        <v>1102</v>
+      </c>
+      <c r="M168" s="5" t="s">
         <v>1090</v>
       </c>
-      <c r="N168" s="2" t="s">
-        <v>1091</v>
+      <c r="N168" s="1" t="s">
+        <v>1103</v>
       </c>
       <c r="O168" s="1" t="s">
-        <v>1092</v>
+        <v>459</v>
       </c>
       <c r="P168" s="1" t="s">
-        <v>1093</v>
+        <v>1104</v>
       </c>
       <c r="Q168" s="1" t="s">
-        <v>1094</v>
+        <v>1105</v>
       </c>
       <c r="R168" s="1" t="s">
         <v>29</v>
@@ -13191,8 +13203,8 @@
       </c>
     </row>
     <row r="169" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="23" t="s">
-        <v>1095</v>
+      <c r="A169" s="15" t="s">
+        <v>1106</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>1084</v>
@@ -13209,7 +13221,7 @@
         <v>1087</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>1096</v>
+        <v>1107</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>44</v>
@@ -13221,22 +13233,22 @@
         <v>1088</v>
       </c>
       <c r="L169" s="5" t="s">
-        <v>1097</v>
+        <v>1108</v>
       </c>
       <c r="M169" s="5" t="s">
         <v>1090</v>
       </c>
       <c r="N169" s="1" t="s">
-        <v>1098</v>
+        <v>1109</v>
       </c>
       <c r="O169" s="1" t="s">
         <v>459</v>
       </c>
       <c r="P169" s="1" t="s">
-        <v>1099</v>
+        <v>480</v>
       </c>
       <c r="Q169" s="1" t="s">
-        <v>1100</v>
+        <v>585</v>
       </c>
       <c r="R169" s="1" t="s">
         <v>29</v>
@@ -13246,8 +13258,8 @@
       </c>
     </row>
     <row r="170" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="23" t="s">
-        <v>1101</v>
+      <c r="A170" s="15" t="s">
+        <v>1110</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>1084</v>
@@ -13264,7 +13276,7 @@
         <v>1087</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>669</v>
+        <v>689</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>44</v>
@@ -13276,22 +13288,22 @@
         <v>1088</v>
       </c>
       <c r="L170" s="5" t="s">
-        <v>1102</v>
+        <v>1111</v>
       </c>
       <c r="M170" s="5" t="s">
         <v>1090</v>
       </c>
       <c r="N170" s="1" t="s">
-        <v>1103</v>
+        <v>1112</v>
       </c>
       <c r="O170" s="1" t="s">
         <v>459</v>
       </c>
       <c r="P170" s="1" t="s">
-        <v>1104</v>
+        <v>480</v>
       </c>
       <c r="Q170" s="1" t="s">
-        <v>1105</v>
+        <v>1113</v>
       </c>
       <c r="R170" s="1" t="s">
         <v>29</v>
@@ -13302,7 +13314,7 @@
     </row>
     <row r="171" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="15" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>1084</v>
@@ -13330,23 +13342,23 @@
       <c r="K171" s="1" t="s">
         <v>1088</v>
       </c>
-      <c r="L171" s="5" t="s">
-        <v>1108</v>
-      </c>
-      <c r="M171" s="5" t="s">
+      <c r="L171" s="24" t="s">
+        <v>1115</v>
+      </c>
+      <c r="M171" s="24" t="s">
         <v>1090</v>
       </c>
       <c r="N171" s="1" t="s">
-        <v>1109</v>
+        <v>1116</v>
       </c>
       <c r="O171" s="1" t="s">
         <v>459</v>
       </c>
       <c r="P171" s="1" t="s">
-        <v>480</v>
+        <v>1117</v>
       </c>
       <c r="Q171" s="1" t="s">
-        <v>585</v>
+        <v>1118</v>
       </c>
       <c r="R171" s="1" t="s">
         <v>29</v>
@@ -13357,7 +13369,7 @@
     </row>
     <row r="172" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="15" t="s">
-        <v>1110</v>
+        <v>1119</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>1084</v>
@@ -13385,23 +13397,23 @@
       <c r="K172" s="1" t="s">
         <v>1088</v>
       </c>
-      <c r="L172" s="5" t="s">
-        <v>1111</v>
-      </c>
-      <c r="M172" s="5" t="s">
+      <c r="L172" s="24" t="s">
+        <v>1120</v>
+      </c>
+      <c r="M172" s="24" t="s">
         <v>1090</v>
       </c>
       <c r="N172" s="1" t="s">
-        <v>1112</v>
+        <v>1121</v>
       </c>
       <c r="O172" s="1" t="s">
         <v>459</v>
       </c>
       <c r="P172" s="1" t="s">
-        <v>480</v>
+        <v>1122</v>
       </c>
       <c r="Q172" s="1" t="s">
-        <v>1113</v>
+        <v>1123</v>
       </c>
       <c r="R172" s="1" t="s">
         <v>29</v>
@@ -13412,7 +13424,7 @@
     </row>
     <row r="173" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="15" t="s">
-        <v>1114</v>
+        <v>1124</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>1084</v>
@@ -13429,7 +13441,7 @@
         <v>1087</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>1107</v>
+        <v>1125</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>44</v>
@@ -13438,25 +13450,25 @@
         <v>45</v>
       </c>
       <c r="K173" s="1" t="s">
-        <v>1088</v>
+        <v>1126</v>
       </c>
       <c r="L173" s="24" t="s">
-        <v>1115</v>
+        <v>1127</v>
       </c>
       <c r="M173" s="24" t="s">
-        <v>1090</v>
+        <v>1128</v>
       </c>
       <c r="N173" s="1" t="s">
-        <v>1116</v>
+        <v>1129</v>
       </c>
       <c r="O173" s="1" t="s">
-        <v>459</v>
+        <v>286</v>
       </c>
       <c r="P173" s="1" t="s">
-        <v>1117</v>
+        <v>1130</v>
       </c>
       <c r="Q173" s="1" t="s">
-        <v>1118</v>
+        <v>738</v>
       </c>
       <c r="R173" s="1" t="s">
         <v>29</v>
@@ -13467,7 +13479,7 @@
     </row>
     <row r="174" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="15" t="s">
-        <v>1119</v>
+        <v>1131</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>1084</v>
@@ -13484,34 +13496,32 @@
         <v>1087</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>689</v>
+        <v>771</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>44</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>45</v>
+        <v>1132</v>
       </c>
       <c r="K174" s="1" t="s">
-        <v>1088</v>
+        <v>1133</v>
       </c>
       <c r="L174" s="24" t="s">
-        <v>1120</v>
-      </c>
-      <c r="M174" s="24" t="s">
-        <v>1090</v>
-      </c>
+        <v>1134</v>
+      </c>
+      <c r="M174" s="24"/>
       <c r="N174" s="1" t="s">
-        <v>1121</v>
+        <v>1135</v>
       </c>
       <c r="O174" s="1" t="s">
-        <v>459</v>
+        <v>345</v>
       </c>
       <c r="P174" s="1" t="s">
-        <v>1122</v>
+        <v>1136</v>
       </c>
       <c r="Q174" s="1" t="s">
-        <v>1123</v>
+        <v>1137</v>
       </c>
       <c r="R174" s="1" t="s">
         <v>29</v>
@@ -13522,7 +13532,7 @@
     </row>
     <row r="175" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="15" t="s">
-        <v>1124</v>
+        <v>1138</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>1084</v>
@@ -13539,34 +13549,32 @@
         <v>1087</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>1125</v>
+        <v>771</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>44</v>
+        <v>683</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>45</v>
+        <v>1050</v>
       </c>
       <c r="K175" s="1" t="s">
-        <v>1126</v>
+        <v>1139</v>
       </c>
       <c r="L175" s="24" t="s">
-        <v>1127</v>
-      </c>
-      <c r="M175" s="24" t="s">
-        <v>1128</v>
-      </c>
+        <v>1140</v>
+      </c>
+      <c r="M175" s="24"/>
       <c r="N175" s="1" t="s">
-        <v>1129</v>
+        <v>1141</v>
       </c>
       <c r="O175" s="1" t="s">
-        <v>286</v>
+        <v>345</v>
       </c>
       <c r="P175" s="1" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="Q175" s="1" t="s">
-        <v>738</v>
+        <v>1143</v>
       </c>
       <c r="R175" s="1" t="s">
         <v>29</v>
@@ -13575,51 +13583,51 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="15" t="s">
-        <v>1131</v>
+    <row r="176" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="25" t="s">
+        <v>1144</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>1084</v>
+        <v>1145</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>1085</v>
-      </c>
-      <c r="D176" s="1"/>
-      <c r="E176" s="1"/>
-      <c r="F176" s="1" t="s">
-        <v>1086</v>
-      </c>
-      <c r="G176" s="1" t="s">
-        <v>1087</v>
-      </c>
-      <c r="H176" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="I176" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J176" s="1" t="s">
-        <v>1132</v>
-      </c>
-      <c r="K176" s="1" t="s">
-        <v>1133</v>
-      </c>
-      <c r="L176" s="24" t="s">
-        <v>1134</v>
-      </c>
-      <c r="M176" s="24"/>
-      <c r="N176" s="1" t="s">
-        <v>1135</v>
-      </c>
-      <c r="O176" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="P176" s="1" t="s">
-        <v>1136</v>
-      </c>
-      <c r="Q176" s="1" t="s">
-        <v>1137</v>
+        <v>1146</v>
+      </c>
+      <c r="D176" s="6"/>
+      <c r="E176" s="6"/>
+      <c r="F176" s="6">
+        <v>1452</v>
+      </c>
+      <c r="G176" s="6">
+        <v>1517</v>
+      </c>
+      <c r="H176" s="6" t="s">
+        <v>1147</v>
+      </c>
+      <c r="I176" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J176" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="K176" s="6" t="s">
+        <v>1148</v>
+      </c>
+      <c r="L176" s="6" t="s">
+        <v>648</v>
+      </c>
+      <c r="M176" s="6"/>
+      <c r="N176" s="6" t="s">
+        <v>1149</v>
+      </c>
+      <c r="O176" s="6" t="s">
+        <v>951</v>
+      </c>
+      <c r="P176" s="6" t="s">
+        <v>1150</v>
+      </c>
+      <c r="Q176" s="6" t="s">
+        <v>1151</v>
       </c>
       <c r="R176" s="1" t="s">
         <v>29</v>
@@ -13628,51 +13636,51 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="15" t="s">
-        <v>1138</v>
+    <row r="177" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="25" t="s">
+        <v>1152</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>1084</v>
+        <v>1145</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>1085</v>
-      </c>
-      <c r="D177" s="1"/>
-      <c r="E177" s="1"/>
-      <c r="F177" s="1" t="s">
-        <v>1086</v>
-      </c>
-      <c r="G177" s="1" t="s">
-        <v>1087</v>
-      </c>
-      <c r="H177" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="I177" s="1" t="s">
-        <v>683</v>
-      </c>
-      <c r="J177" s="1" t="s">
-        <v>1050</v>
-      </c>
-      <c r="K177" s="1" t="s">
-        <v>1139</v>
-      </c>
-      <c r="L177" s="24" t="s">
-        <v>1140</v>
-      </c>
-      <c r="M177" s="24"/>
-      <c r="N177" s="1" t="s">
-        <v>1141</v>
-      </c>
-      <c r="O177" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="P177" s="1" t="s">
-        <v>1142</v>
-      </c>
-      <c r="Q177" s="1" t="s">
-        <v>1143</v>
+        <v>1146</v>
+      </c>
+      <c r="D177" s="6"/>
+      <c r="E177" s="6"/>
+      <c r="F177" s="6">
+        <v>1452</v>
+      </c>
+      <c r="G177" s="6">
+        <v>1517</v>
+      </c>
+      <c r="H177" s="6" t="s">
+        <v>1153</v>
+      </c>
+      <c r="I177" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="J177" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="K177" s="6" t="s">
+        <v>1154</v>
+      </c>
+      <c r="L177" s="6" t="s">
+        <v>1155</v>
+      </c>
+      <c r="M177" s="6"/>
+      <c r="N177" s="6" t="s">
+        <v>1156</v>
+      </c>
+      <c r="O177" s="6" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P177" s="6" t="s">
+        <v>1158</v>
+      </c>
+      <c r="Q177" s="6" t="s">
+        <v>1159</v>
       </c>
       <c r="R177" s="1" t="s">
         <v>29</v>
@@ -13683,7 +13691,7 @@
     </row>
     <row r="178" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="25" t="s">
-        <v>1144</v>
+        <v>1160</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>1145</v>
@@ -13691,7 +13699,7 @@
       <c r="C178" s="1" t="s">
         <v>1146</v>
       </c>
-      <c r="D178" s="6"/>
+      <c r="D178" s="3"/>
       <c r="E178" s="6"/>
       <c r="F178" s="6">
         <v>1452</v>
@@ -13700,32 +13708,32 @@
         <v>1517</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>1147</v>
+        <v>1161</v>
       </c>
       <c r="I178" s="6" t="s">
-        <v>25</v>
+        <v>1162</v>
       </c>
       <c r="J178" s="6" t="s">
-        <v>154</v>
+        <v>1163</v>
       </c>
       <c r="K178" s="6" t="s">
-        <v>1148</v>
+        <v>1164</v>
       </c>
       <c r="L178" s="6" t="s">
-        <v>648</v>
+        <v>1165</v>
       </c>
       <c r="M178" s="6"/>
       <c r="N178" s="6" t="s">
-        <v>1149</v>
+        <v>1166</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>951</v>
+        <v>1167</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>1150</v>
+        <v>1168</v>
       </c>
       <c r="Q178" s="6" t="s">
-        <v>1151</v>
+        <v>1169</v>
       </c>
       <c r="R178" s="1" t="s">
         <v>29</v>
@@ -13736,7 +13744,7 @@
     </row>
     <row r="179" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="25" t="s">
-        <v>1152</v>
+        <v>1170</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>1145</v>
@@ -13753,32 +13761,32 @@
         <v>1517</v>
       </c>
       <c r="H179" s="6" t="s">
-        <v>1153</v>
+        <v>1171</v>
       </c>
       <c r="I179" s="6" t="s">
-        <v>645</v>
+        <v>25</v>
       </c>
       <c r="J179" s="6" t="s">
-        <v>646</v>
+        <v>154</v>
       </c>
       <c r="K179" s="6" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="L179" s="6" t="s">
-        <v>1155</v>
+        <v>1172</v>
       </c>
       <c r="M179" s="6"/>
       <c r="N179" s="6" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="O179" s="6" t="s">
-        <v>1157</v>
+        <v>345</v>
       </c>
       <c r="P179" s="6" t="s">
-        <v>1158</v>
+        <v>1174</v>
       </c>
       <c r="Q179" s="6" t="s">
-        <v>1159</v>
+        <v>1175</v>
       </c>
       <c r="R179" s="1" t="s">
         <v>29</v>
@@ -13789,7 +13797,7 @@
     </row>
     <row r="180" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="25" t="s">
-        <v>1160</v>
+        <v>1176</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>1145</v>
@@ -13797,7 +13805,7 @@
       <c r="C180" s="1" t="s">
         <v>1146</v>
       </c>
-      <c r="D180" s="3"/>
+      <c r="D180" s="6"/>
       <c r="E180" s="6"/>
       <c r="F180" s="6">
         <v>1452</v>
@@ -13806,32 +13814,32 @@
         <v>1517</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>1161</v>
+        <v>1177</v>
       </c>
       <c r="I180" s="6" t="s">
-        <v>1162</v>
+        <v>861</v>
       </c>
       <c r="J180" s="6" t="s">
-        <v>1163</v>
+        <v>270</v>
       </c>
       <c r="K180" s="6" t="s">
-        <v>1164</v>
+        <v>862</v>
       </c>
       <c r="L180" s="6" t="s">
-        <v>1165</v>
+        <v>1178</v>
       </c>
       <c r="M180" s="6"/>
       <c r="N180" s="6" t="s">
-        <v>1166</v>
+        <v>1179</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>1167</v>
+        <v>1180</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>1168</v>
+        <v>1181</v>
       </c>
       <c r="Q180" s="6" t="s">
-        <v>1169</v>
+        <v>1182</v>
       </c>
       <c r="R180" s="1" t="s">
         <v>29</v>
@@ -13842,7 +13850,7 @@
     </row>
     <row r="181" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="25" t="s">
-        <v>1170</v>
+        <v>1183</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>1145</v>
@@ -13859,32 +13867,32 @@
         <v>1517</v>
       </c>
       <c r="H181" s="6" t="s">
-        <v>1171</v>
+        <v>1184</v>
       </c>
       <c r="I181" s="6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J181" s="6" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="K181" s="6" t="s">
-        <v>1148</v>
+        <v>1185</v>
       </c>
       <c r="L181" s="6" t="s">
-        <v>1172</v>
+        <v>1186</v>
       </c>
       <c r="M181" s="6"/>
       <c r="N181" s="6" t="s">
-        <v>1173</v>
+        <v>1187</v>
       </c>
       <c r="O181" s="6" t="s">
-        <v>345</v>
+        <v>1188</v>
       </c>
       <c r="P181" s="6" t="s">
-        <v>1174</v>
+        <v>1189</v>
       </c>
       <c r="Q181" s="6" t="s">
-        <v>1175</v>
+        <v>1190</v>
       </c>
       <c r="R181" s="1" t="s">
         <v>29</v>
@@ -13893,9 +13901,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="25" t="s">
-        <v>1176</v>
+    <row r="182" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="23" t="s">
+        <v>1191</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>1145</v>
@@ -13912,32 +13920,32 @@
         <v>1517</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>1177</v>
+        <v>1192</v>
       </c>
       <c r="I182" s="6" t="s">
-        <v>861</v>
+        <v>122</v>
       </c>
       <c r="J182" s="6" t="s">
-        <v>270</v>
+        <v>1193</v>
       </c>
       <c r="K182" s="6" t="s">
-        <v>862</v>
+        <v>1194</v>
       </c>
       <c r="L182" s="6" t="s">
-        <v>1178</v>
+        <v>1195</v>
       </c>
       <c r="M182" s="6"/>
       <c r="N182" s="6" t="s">
-        <v>1179</v>
+        <v>1196</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>1180</v>
+        <v>1197</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>1181</v>
-      </c>
-      <c r="Q182" s="6" t="s">
-        <v>1182</v>
+        <v>1198</v>
+      </c>
+      <c r="Q182" s="6">
+        <v>32</v>
       </c>
       <c r="R182" s="1" t="s">
         <v>29</v>
@@ -13946,9 +13954,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="25" t="s">
-        <v>1183</v>
+    <row r="183" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="23" t="s">
+        <v>1199</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>1145</v>
@@ -13965,32 +13973,32 @@
         <v>1517</v>
       </c>
       <c r="H183" s="6" t="s">
-        <v>1184</v>
+        <v>1200</v>
       </c>
       <c r="I183" s="6" t="s">
-        <v>32</v>
+        <v>1201</v>
       </c>
       <c r="J183" s="6" t="s">
-        <v>33</v>
+        <v>1202</v>
       </c>
       <c r="K183" s="6" t="s">
-        <v>1185</v>
+        <v>36</v>
       </c>
       <c r="L183" s="6" t="s">
-        <v>1186</v>
+        <v>1203</v>
       </c>
       <c r="M183" s="6"/>
       <c r="N183" s="6" t="s">
-        <v>1187</v>
+        <v>1204</v>
       </c>
       <c r="O183" s="6" t="s">
-        <v>1188</v>
+        <v>1205</v>
       </c>
       <c r="P183" s="6" t="s">
-        <v>1189</v>
+        <v>1206</v>
       </c>
       <c r="Q183" s="6" t="s">
-        <v>1190</v>
+        <v>1207</v>
       </c>
       <c r="R183" s="1" t="s">
         <v>29</v>
@@ -14000,8 +14008,8 @@
       </c>
     </row>
     <row r="184" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="23" t="s">
-        <v>1191</v>
+      <c r="A184" s="25" t="s">
+        <v>1208</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>1145</v>
@@ -14018,32 +14026,32 @@
         <v>1517</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="I184" s="6" t="s">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="J184" s="6" t="s">
-        <v>1193</v>
+        <v>33</v>
       </c>
       <c r="K184" s="6" t="s">
-        <v>1194</v>
+        <v>1210</v>
       </c>
       <c r="L184" s="6" t="s">
-        <v>1195</v>
+        <v>1211</v>
       </c>
       <c r="M184" s="6"/>
       <c r="N184" s="6" t="s">
-        <v>1196</v>
+        <v>1211</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>1197</v>
+        <v>1205</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>1198</v>
-      </c>
-      <c r="Q184" s="6">
-        <v>32</v>
+        <v>1212</v>
+      </c>
+      <c r="Q184" s="6" t="s">
+        <v>1213</v>
       </c>
       <c r="R184" s="1" t="s">
         <v>29</v>
@@ -14053,8 +14061,8 @@
       </c>
     </row>
     <row r="185" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="23" t="s">
-        <v>1199</v>
+      <c r="A185" s="25" t="s">
+        <v>1214</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>1145</v>
@@ -14071,32 +14079,32 @@
         <v>1517</v>
       </c>
       <c r="H185" s="6" t="s">
-        <v>1200</v>
+        <v>1215</v>
       </c>
       <c r="I185" s="6" t="s">
-        <v>1201</v>
+        <v>122</v>
       </c>
       <c r="J185" s="6" t="s">
-        <v>1202</v>
+        <v>1216</v>
       </c>
       <c r="K185" s="6" t="s">
-        <v>36</v>
+        <v>1217</v>
       </c>
       <c r="L185" s="6" t="s">
-        <v>1203</v>
+        <v>64</v>
       </c>
       <c r="M185" s="6"/>
       <c r="N185" s="6" t="s">
-        <v>1204</v>
+        <v>1218</v>
       </c>
       <c r="O185" s="6" t="s">
-        <v>1205</v>
+        <v>1219</v>
       </c>
       <c r="P185" s="6" t="s">
-        <v>1206</v>
+        <v>1220</v>
       </c>
       <c r="Q185" s="6" t="s">
-        <v>1207</v>
+        <v>1221</v>
       </c>
       <c r="R185" s="1" t="s">
         <v>29</v>
@@ -14106,50 +14114,52 @@
       </c>
     </row>
     <row r="186" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="25" t="s">
-        <v>1208</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>1145</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>1146</v>
-      </c>
-      <c r="D186" s="6"/>
-      <c r="E186" s="6"/>
-      <c r="F186" s="6">
-        <v>1452</v>
-      </c>
-      <c r="G186" s="6">
-        <v>1517</v>
+      <c r="A186" s="15" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D186" s="3"/>
+      <c r="E186" s="3"/>
+      <c r="F186" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>1226</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>1209</v>
+        <v>1227</v>
       </c>
       <c r="I186" s="6" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J186" s="6" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="K186" s="6" t="s">
-        <v>1210</v>
+        <v>1228</v>
       </c>
       <c r="L186" s="6" t="s">
-        <v>1211</v>
-      </c>
-      <c r="M186" s="6"/>
+        <v>1229</v>
+      </c>
+      <c r="M186" s="6" t="s">
+        <v>1230</v>
+      </c>
       <c r="N186" s="6" t="s">
-        <v>1211</v>
+        <v>1231</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>1205</v>
-      </c>
-      <c r="P186" s="6" t="s">
-        <v>1212</v>
-      </c>
-      <c r="Q186" s="6" t="s">
-        <v>1213</v>
+        <v>109</v>
+      </c>
+      <c r="P186" s="6">
+        <v>167</v>
+      </c>
+      <c r="Q186" s="6">
+        <v>87</v>
       </c>
       <c r="R186" s="1" t="s">
         <v>29</v>
@@ -14159,50 +14169,50 @@
       </c>
     </row>
     <row r="187" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="25" t="s">
-        <v>1214</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>1145</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>1146</v>
-      </c>
-      <c r="D187" s="6"/>
-      <c r="E187" s="6"/>
-      <c r="F187" s="6">
-        <v>1452</v>
-      </c>
-      <c r="G187" s="6">
-        <v>1517</v>
+      <c r="A187" s="15" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C187" s="6" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D187" s="3"/>
+      <c r="E187" s="3"/>
+      <c r="F187" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>1226</v>
       </c>
       <c r="H187" s="6" t="s">
-        <v>1215</v>
+        <v>296</v>
       </c>
       <c r="I187" s="6" t="s">
-        <v>122</v>
+        <v>25</v>
       </c>
       <c r="J187" s="6" t="s">
-        <v>1216</v>
+        <v>79</v>
       </c>
       <c r="K187" s="6" t="s">
-        <v>1217</v>
+        <v>1228</v>
       </c>
       <c r="L187" s="6" t="s">
-        <v>64</v>
+        <v>1172</v>
       </c>
       <c r="M187" s="6"/>
       <c r="N187" s="6" t="s">
-        <v>1218</v>
+        <v>1173</v>
       </c>
       <c r="O187" s="6" t="s">
-        <v>1219</v>
-      </c>
-      <c r="P187" s="6" t="s">
-        <v>1220</v>
-      </c>
-      <c r="Q187" s="6" t="s">
-        <v>1221</v>
+        <v>109</v>
+      </c>
+      <c r="P187" s="6">
+        <v>111</v>
+      </c>
+      <c r="Q187" s="6">
+        <v>134</v>
       </c>
       <c r="R187" s="1" t="s">
         <v>29</v>
@@ -14213,7 +14223,7 @@
     </row>
     <row r="188" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="15" t="s">
-        <v>1222</v>
+        <v>1233</v>
       </c>
       <c r="B188" s="6" t="s">
         <v>1223</v>
@@ -14230,7 +14240,7 @@
         <v>1226</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>1227</v>
+        <v>1234</v>
       </c>
       <c r="I188" s="6" t="s">
         <v>25</v>
@@ -14242,22 +14252,20 @@
         <v>1228</v>
       </c>
       <c r="L188" s="6" t="s">
-        <v>1229</v>
-      </c>
-      <c r="M188" s="6" t="s">
-        <v>1230</v>
-      </c>
+        <v>1235</v>
+      </c>
+      <c r="M188" s="6"/>
       <c r="N188" s="6" t="s">
-        <v>1231</v>
+        <v>1236</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="P188" s="6">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="Q188" s="6">
-        <v>87</v>
+        <v>314</v>
       </c>
       <c r="R188" s="1" t="s">
         <v>29</v>
@@ -14268,7 +14276,7 @@
     </row>
     <row r="189" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="15" t="s">
-        <v>1232</v>
+        <v>1237</v>
       </c>
       <c r="B189" s="6" t="s">
         <v>1223</v>
@@ -14285,7 +14293,7 @@
         <v>1226</v>
       </c>
       <c r="H189" s="6" t="s">
-        <v>296</v>
+        <v>268</v>
       </c>
       <c r="I189" s="6" t="s">
         <v>25</v>
@@ -14297,20 +14305,20 @@
         <v>1228</v>
       </c>
       <c r="L189" s="6" t="s">
-        <v>1172</v>
+        <v>1238</v>
       </c>
       <c r="M189" s="6"/>
       <c r="N189" s="6" t="s">
-        <v>1173</v>
+        <v>1239</v>
       </c>
       <c r="O189" s="6" t="s">
-        <v>109</v>
+        <v>1240</v>
       </c>
       <c r="P189" s="6">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="Q189" s="6">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="R189" s="1" t="s">
         <v>29</v>
@@ -14321,7 +14329,7 @@
     </row>
     <row r="190" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="15" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="B190" s="6" t="s">
         <v>1223</v>
@@ -14338,32 +14346,34 @@
         <v>1226</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>1234</v>
+        <v>268</v>
       </c>
       <c r="I190" s="6" t="s">
-        <v>25</v>
+        <v>269</v>
       </c>
       <c r="J190" s="6" t="s">
-        <v>79</v>
+        <v>270</v>
       </c>
       <c r="K190" s="6" t="s">
-        <v>1228</v>
+        <v>971</v>
       </c>
       <c r="L190" s="6" t="s">
-        <v>1235</v>
-      </c>
-      <c r="M190" s="6"/>
+        <v>1242</v>
+      </c>
+      <c r="M190" s="6" t="s">
+        <v>1243</v>
+      </c>
       <c r="N190" s="6" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>159</v>
+        <v>66</v>
       </c>
       <c r="P190" s="6">
-        <v>203</v>
+        <v>348</v>
       </c>
       <c r="Q190" s="6">
-        <v>314</v>
+        <v>558</v>
       </c>
       <c r="R190" s="1" t="s">
         <v>29</v>
@@ -14374,7 +14384,7 @@
     </row>
     <row r="191" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="15" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="B191" s="6" t="s">
         <v>1223</v>
@@ -14391,32 +14401,32 @@
         <v>1226</v>
       </c>
       <c r="H191" s="6" t="s">
-        <v>268</v>
+        <v>1246</v>
       </c>
       <c r="I191" s="6" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="J191" s="6" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K191" s="6" t="s">
-        <v>1228</v>
+        <v>112</v>
       </c>
       <c r="L191" s="6" t="s">
-        <v>1238</v>
+        <v>1247</v>
       </c>
       <c r="M191" s="6"/>
       <c r="N191" s="6" t="s">
-        <v>1239</v>
+        <v>1248</v>
       </c>
       <c r="O191" s="6" t="s">
-        <v>1240</v>
+        <v>1249</v>
       </c>
       <c r="P191" s="6">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="Q191" s="6">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="R191" s="1" t="s">
         <v>29</v>
@@ -14427,7 +14437,7 @@
     </row>
     <row r="192" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="15" t="s">
-        <v>1241</v>
+        <v>1250</v>
       </c>
       <c r="B192" s="6" t="s">
         <v>1223</v>
@@ -14444,34 +14454,32 @@
         <v>1226</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>268</v>
+        <v>1251</v>
       </c>
       <c r="I192" s="6" t="s">
-        <v>269</v>
+        <v>25</v>
       </c>
       <c r="J192" s="6" t="s">
-        <v>270</v>
+        <v>79</v>
       </c>
       <c r="K192" s="6" t="s">
-        <v>971</v>
+        <v>1228</v>
       </c>
       <c r="L192" s="6" t="s">
-        <v>1242</v>
-      </c>
-      <c r="M192" s="6" t="s">
-        <v>1243</v>
-      </c>
+        <v>1252</v>
+      </c>
+      <c r="M192" s="6"/>
       <c r="N192" s="6" t="s">
-        <v>1244</v>
+        <v>1253</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="P192" s="6">
-        <v>348</v>
+        <v>150</v>
       </c>
       <c r="Q192" s="6">
-        <v>558</v>
+        <v>156</v>
       </c>
       <c r="R192" s="1" t="s">
         <v>29</v>
@@ -14482,7 +14490,7 @@
     </row>
     <row r="193" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="15" t="s">
-        <v>1245</v>
+        <v>1254</v>
       </c>
       <c r="B193" s="6" t="s">
         <v>1223</v>
@@ -14499,32 +14507,32 @@
         <v>1226</v>
       </c>
       <c r="H193" s="6" t="s">
-        <v>1246</v>
+        <v>1255</v>
       </c>
       <c r="I193" s="6" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="J193" s="6" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K193" s="6" t="s">
-        <v>112</v>
+        <v>1228</v>
       </c>
       <c r="L193" s="6" t="s">
-        <v>1247</v>
+        <v>1256</v>
       </c>
       <c r="M193" s="6"/>
       <c r="N193" s="6" t="s">
-        <v>1248</v>
+        <v>1257</v>
       </c>
       <c r="O193" s="6" t="s">
-        <v>1249</v>
+        <v>109</v>
       </c>
       <c r="P193" s="6">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="Q193" s="6">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="R193" s="1" t="s">
         <v>29</v>
@@ -14535,158 +14543,52 @@
     </row>
     <row r="194" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="15" t="s">
-        <v>1250</v>
-      </c>
-      <c r="B194" s="6" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>1223</v>
       </c>
-      <c r="C194" s="6" t="s">
+      <c r="C194" s="1" t="s">
         <v>1224</v>
       </c>
-      <c r="D194" s="3"/>
-      <c r="E194" s="3"/>
+      <c r="D194" s="1"/>
+      <c r="E194" s="1"/>
       <c r="F194" s="1" t="s">
         <v>1225</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>1226</v>
       </c>
-      <c r="H194" s="6" t="s">
-        <v>1251</v>
-      </c>
-      <c r="I194" s="6" t="s">
+      <c r="H194" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="I194" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J194" s="6" t="s">
+      <c r="J194" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="K194" s="6" t="s">
-        <v>1228</v>
-      </c>
-      <c r="L194" s="6" t="s">
-        <v>1252</v>
-      </c>
-      <c r="M194" s="6"/>
-      <c r="N194" s="6" t="s">
-        <v>1253</v>
-      </c>
-      <c r="O194" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P194" s="6">
-        <v>150</v>
-      </c>
-      <c r="Q194" s="6">
-        <v>156</v>
+      <c r="K194" s="1"/>
+      <c r="L194" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="M194" s="2"/>
+      <c r="N194" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="O194" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="P194" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="Q194" s="1" t="s">
+        <v>1263</v>
       </c>
       <c r="R194" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S194" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="15" t="s">
-        <v>1254</v>
-      </c>
-      <c r="B195" s="6" t="s">
-        <v>1223</v>
-      </c>
-      <c r="C195" s="6" t="s">
-        <v>1224</v>
-      </c>
-      <c r="D195" s="3"/>
-      <c r="E195" s="3"/>
-      <c r="F195" s="1" t="s">
-        <v>1225</v>
-      </c>
-      <c r="G195" s="1" t="s">
-        <v>1226</v>
-      </c>
-      <c r="H195" s="6" t="s">
-        <v>1255</v>
-      </c>
-      <c r="I195" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J195" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K195" s="6" t="s">
-        <v>1228</v>
-      </c>
-      <c r="L195" s="6" t="s">
-        <v>1256</v>
-      </c>
-      <c r="M195" s="6"/>
-      <c r="N195" s="6" t="s">
-        <v>1257</v>
-      </c>
-      <c r="O195" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P195" s="6">
-        <v>62</v>
-      </c>
-      <c r="Q195" s="6">
-        <v>91</v>
-      </c>
-      <c r="R195" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S195" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="15" t="s">
-        <v>1258</v>
-      </c>
-      <c r="B196" s="1" t="s">
-        <v>1223</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>1224</v>
-      </c>
-      <c r="D196" s="1"/>
-      <c r="E196" s="1"/>
-      <c r="F196" s="1" t="s">
-        <v>1225</v>
-      </c>
-      <c r="G196" s="1" t="s">
-        <v>1226</v>
-      </c>
-      <c r="H196" s="1" t="s">
-        <v>1259</v>
-      </c>
-      <c r="I196" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J196" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K196" s="1"/>
-      <c r="L196" s="2" t="s">
-        <v>1260</v>
-      </c>
-      <c r="M196" s="2"/>
-      <c r="N196" s="2" t="s">
-        <v>1261</v>
-      </c>
-      <c r="O196" s="1" t="s">
-        <v>1092</v>
-      </c>
-      <c r="P196" s="1" t="s">
-        <v>1262</v>
-      </c>
-      <c r="Q196" s="1" t="s">
-        <v>1263</v>
-      </c>
-      <c r="R196" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S196" s="1">
         <v>1</v>
       </c>
     </row>
@@ -14827,66 +14729,64 @@
     <hyperlink ref="A142" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
     <hyperlink ref="A143" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
     <hyperlink ref="A144" r:id="rId135" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="A145" r:id="rId136" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="A146" r:id="rId137" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="A147" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="A148" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="A149" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="A150" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="A151" r:id="rId142" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="A152" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="A153" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="A154" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="A155" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="A156" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="A157" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="A160" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="A162" r:id="rId150" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="A163" r:id="rId151" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="A164" r:id="rId152" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="A165" r:id="rId153" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="A166" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="A168" r:id="rId155" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="A169" r:id="rId156" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="A170" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="A171" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="A172" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="A173" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="A174" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="A175" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="A176" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="A177" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="A178" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="A179" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="A180" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="A181" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="A182" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="A183" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="A184" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="A185" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="A186" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="A187" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="A188" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="A189" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="A190" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="A191" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="A192" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="A193" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="A194" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="A195" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="A196" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="A122" r:id="rId184" xr:uid="{5387F726-DCFD-4836-AE7E-7DC737AD9B52}"/>
-    <hyperlink ref="A126" r:id="rId185" xr:uid="{2DD984AB-7E65-440E-990B-3DEB390F5232}"/>
-    <hyperlink ref="A127" r:id="rId186" xr:uid="{C1D5EDB1-0DBC-460B-BFE8-8A64BA531FE9}"/>
-    <hyperlink ref="A129" r:id="rId187" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0b/Paolo_Uccello_%E2%80%94_The_Decisive_Attack_of_Micheletto_Attendolo_at_San_Romano.jpg/1280px-Paolo_Uccello_%E2%80%94_The_Decisive_Attack_of_Micheletto_Attendolo_at_San_Romano.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8568C58D-9F0D-448F-A287-7E73E21239CF}"/>
-    <hyperlink ref="A51" r:id="rId188" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Beato_angelico_e_lorenzo_monaco%2C_pala_di_santa_trinita_%28deposizione_e_santi%29%2C_ante_1432%2C_01.jpg/1920px-Beato_angelico_e_lorenzo_monaco%2C_pala_di_santa_trinita_%28deposizione_e_santi%29%2C_ante_1432%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9A5901B2-A8C7-4333-8C93-3BA24B441446}"/>
-    <hyperlink ref="A161" r:id="rId189" xr:uid="{66FFDBF1-519C-4A74-8049-39696640DDD4}"/>
-    <hyperlink ref="A167" r:id="rId190" xr:uid="{C484BA40-5873-4062-BAC8-9BEE869078E5}"/>
-    <hyperlink ref="A158" r:id="rId191" xr:uid="{F646FB71-58FB-457D-8A7A-0FB460CB78F9}"/>
-    <hyperlink ref="A159" r:id="rId192" xr:uid="{2E363D48-40BE-441E-AC26-10AFA79ECF4B}"/>
-    <hyperlink ref="A102" r:id="rId193" xr:uid="{FA3B3813-9FCD-4BF6-BB3B-DA6B2910415D}"/>
-    <hyperlink ref="A93" r:id="rId194" xr:uid="{F9194648-35D5-46AD-8B7C-6F8007C9A92F}"/>
-    <hyperlink ref="A95" r:id="rId195" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5e/Apocalypse_figur%C3%A9e_des_ducs_de_Savoie_-_Escorial_E_Vit.5_-_Adoration_of_the_lamb2.jpg/960px-Apocalypse_figur%C3%A9e_des_ducs_de_Savoie_-_Escorial_E_Vit.5_-_Adoration_of_the_lamb2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{05264A43-B26E-4B7D-98A2-6DA5DE2DB650}"/>
+    <hyperlink ref="A145" r:id="rId136" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="A146" r:id="rId137" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="A147" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="A148" r:id="rId139" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="A149" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="A150" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="A151" r:id="rId142" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="A152" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="A153" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="A154" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="A155" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="A158" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="A160" r:id="rId148" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="A161" r:id="rId149" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="A162" r:id="rId150" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="A163" r:id="rId151" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="A164" r:id="rId152" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="A166" r:id="rId153" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="A167" r:id="rId154" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="A168" r:id="rId155" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="A169" r:id="rId156" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="A170" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="A171" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="A172" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="A173" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="A174" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="A175" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="A176" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="A177" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="A178" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="A179" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="A180" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="A181" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="A182" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="A183" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="A184" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="A185" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="A186" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="A187" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="A188" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="A189" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="A190" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="A191" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="A192" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="A193" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="A194" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="A122" r:id="rId182" xr:uid="{5387F726-DCFD-4836-AE7E-7DC737AD9B52}"/>
+    <hyperlink ref="A126" r:id="rId183" xr:uid="{2DD984AB-7E65-440E-990B-3DEB390F5232}"/>
+    <hyperlink ref="A127" r:id="rId184" xr:uid="{C1D5EDB1-0DBC-460B-BFE8-8A64BA531FE9}"/>
+    <hyperlink ref="A129" r:id="rId185" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0b/Paolo_Uccello_%E2%80%94_The_Decisive_Attack_of_Micheletto_Attendolo_at_San_Romano.jpg/1280px-Paolo_Uccello_%E2%80%94_The_Decisive_Attack_of_Micheletto_Attendolo_at_San_Romano.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8568C58D-9F0D-448F-A287-7E73E21239CF}"/>
+    <hyperlink ref="A51" r:id="rId186" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Beato_angelico_e_lorenzo_monaco%2C_pala_di_santa_trinita_%28deposizione_e_santi%29%2C_ante_1432%2C_01.jpg/1920px-Beato_angelico_e_lorenzo_monaco%2C_pala_di_santa_trinita_%28deposizione_e_santi%29%2C_ante_1432%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9A5901B2-A8C7-4333-8C93-3BA24B441446}"/>
+    <hyperlink ref="A159" r:id="rId187" xr:uid="{66FFDBF1-519C-4A74-8049-39696640DDD4}"/>
+    <hyperlink ref="A165" r:id="rId188" xr:uid="{C484BA40-5873-4062-BAC8-9BEE869078E5}"/>
+    <hyperlink ref="A156" r:id="rId189" xr:uid="{F646FB71-58FB-457D-8A7A-0FB460CB78F9}"/>
+    <hyperlink ref="A157" r:id="rId190" xr:uid="{2E363D48-40BE-441E-AC26-10AFA79ECF4B}"/>
+    <hyperlink ref="A102" r:id="rId191" xr:uid="{FA3B3813-9FCD-4BF6-BB3B-DA6B2910415D}"/>
+    <hyperlink ref="A93" r:id="rId192" xr:uid="{F9194648-35D5-46AD-8B7C-6F8007C9A92F}"/>
+    <hyperlink ref="A95" r:id="rId193" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5e/Apocalypse_figur%C3%A9e_des_ducs_de_Savoie_-_Escorial_E_Vit.5_-_Adoration_of_the_lamb2.jpg/960px-Apocalypse_figur%C3%A9e_des_ducs_de_Savoie_-_Escorial_E_Vit.5_-_Adoration_of_the_lamb2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{05264A43-B26E-4B7D-98A2-6DA5DE2DB650}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-15e.xlsx
+++ b/quizzes/peinture-15e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A62597-A848-475C-8A7E-3D8D9EC03BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C607AA8-C605-4C02-AA8A-8A487E73EA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2606" uniqueCount="1340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2606" uniqueCount="1341">
   <si>
     <t>Image</t>
   </si>
@@ -4040,6 +4040,9 @@
   </si>
   <si>
     <t>"L'Adoration de l'Agneau"</t>
+  </si>
+  <si>
+    <t>137 cm</t>
   </si>
 </sst>
 </file>
@@ -4201,7 +4204,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4232,6 +4235,7 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4581,88 +4585,88 @@
   <dimension ref="A1:S194"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59.140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="12" style="31" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="31" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="5.85546875" style="32" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" style="31" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="31" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" style="31" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="31" customWidth="1"/>
-    <col min="10" max="10" width="32.85546875" style="31" customWidth="1"/>
-    <col min="11" max="11" width="7.85546875" style="31" customWidth="1"/>
-    <col min="12" max="12" width="30.28515625" style="31" customWidth="1"/>
-    <col min="13" max="13" width="5.140625" style="31" customWidth="1"/>
-    <col min="14" max="14" width="18.85546875" style="31" customWidth="1"/>
-    <col min="15" max="15" width="15" style="31" customWidth="1"/>
-    <col min="16" max="16" width="10" style="31" customWidth="1"/>
-    <col min="17" max="17" width="7.42578125" style="31" customWidth="1"/>
-    <col min="18" max="18" width="9.140625" style="31" customWidth="1"/>
-    <col min="19" max="19" width="8.85546875" style="31" customWidth="1"/>
+    <col min="1" max="1" width="59.140625" style="31" customWidth="1"/>
+    <col min="2" max="2" width="12" style="32" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" style="32" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="5.85546875" style="33" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" style="32" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="32" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" style="32" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="32" customWidth="1"/>
+    <col min="10" max="10" width="32.85546875" style="32" customWidth="1"/>
+    <col min="11" max="11" width="7.85546875" style="32" customWidth="1"/>
+    <col min="12" max="12" width="30.28515625" style="32" customWidth="1"/>
+    <col min="13" max="13" width="5.140625" style="32" customWidth="1"/>
+    <col min="14" max="14" width="18.85546875" style="32" customWidth="1"/>
+    <col min="15" max="15" width="15" style="32" customWidth="1"/>
+    <col min="16" max="16" width="10" style="32" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" style="32" customWidth="1"/>
+    <col min="18" max="18" width="9.140625" style="32" customWidth="1"/>
+    <col min="19" max="19" width="8.85546875" style="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="K1" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="L1" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="22" t="s">
+      <c r="M1" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="N1" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="22" t="s">
+      <c r="O1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="22" t="s">
+      <c r="P1" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="22" t="s">
+      <c r="Q1" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="22" t="s">
+      <c r="R1" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="22" t="s">
+      <c r="S1" s="23" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -4706,8 +4710,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+    <row r="3" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="24" t="s">
         <v>30</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -4759,8 +4763,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+    <row r="4" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
         <v>39</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -4812,8 +4816,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="23" t="s">
+    <row r="5" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="24" t="s">
         <v>50</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -4865,8 +4869,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+    <row r="6" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -4918,8 +4922,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="23" t="s">
+    <row r="7" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="24" t="s">
         <v>67</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -4973,8 +4977,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="26" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+    <row r="8" spans="1:19" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
         <v>74</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -5026,8 +5030,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:19" s="26" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
+    <row r="9" spans="1:19" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="24" t="s">
         <v>84</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -5079,8 +5083,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+    <row r="10" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
         <v>93</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -5126,8 +5130,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="23" t="s">
+    <row r="11" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -5179,8 +5183,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="23" t="s">
+    <row r="12" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="24" t="s">
         <v>110</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -5232,8 +5236,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
+    <row r="13" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="24" t="s">
         <v>116</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -5285,8 +5289,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="23" t="s">
+    <row r="14" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="24" t="s">
         <v>120</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -5338,8 +5342,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="23" t="s">
+    <row r="15" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -5393,8 +5397,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+    <row r="16" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="24" t="s">
         <v>132</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -5446,8 +5450,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="23" t="s">
+    <row r="17" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="24" t="s">
         <v>141</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -5499,8 +5503,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="23" t="s">
+    <row r="18" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="24" t="s">
         <v>149</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -5554,8 +5558,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="23" t="s">
+    <row r="19" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="24" t="s">
         <v>161</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -5607,8 +5611,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="23" t="s">
+    <row r="20" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="24" t="s">
         <v>167</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -5660,8 +5664,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
+    <row r="21" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="24" t="s">
         <v>175</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -5713,8 +5717,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+    <row r="22" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
         <v>179</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -5762,8 +5766,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="23" t="s">
+    <row r="23" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="24" t="s">
         <v>191</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -5815,8 +5819,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
+    <row r="24" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
         <v>197</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -5870,8 +5874,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="23" t="s">
+    <row r="25" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="24" t="s">
         <v>211</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -5923,8 +5927,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
+    <row r="26" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
         <v>218</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -5976,8 +5980,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="23" t="s">
+    <row r="27" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="24" t="s">
         <v>226</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -6029,8 +6033,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
+    <row r="28" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="16" t="s">
         <v>231</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -6082,8 +6086,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="23" t="s">
+    <row r="29" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="24" t="s">
         <v>241</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -6135,8 +6139,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
+    <row r="30" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="16" t="s">
         <v>245</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -6188,8 +6192,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="23" t="s">
+    <row r="31" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="24" t="s">
         <v>254</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -6241,8 +6245,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="15" t="s">
+    <row r="32" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="16" t="s">
         <v>263</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -6296,8 +6300,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="23" t="s">
+    <row r="33" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="24" t="s">
         <v>275</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -6351,8 +6355,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="23" t="s">
+    <row r="34" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="24" t="s">
         <v>276</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -6406,8 +6410,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
+    <row r="35" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="16" t="s">
         <v>287</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -6461,8 +6465,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
+    <row r="36" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="16" t="s">
         <v>293</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -6514,8 +6518,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="23" t="s">
+    <row r="37" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
         <v>303</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -6569,8 +6573,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
+    <row r="38" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
         <v>311</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -6624,8 +6628,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="23" t="s">
+    <row r="39" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24" t="s">
         <v>322</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -6677,8 +6681,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="23" t="s">
+    <row r="40" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="24" t="s">
         <v>325</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -6724,8 +6728,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
+    <row r="41" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="16" t="s">
         <v>334</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -6773,8 +6777,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="15" t="s">
+    <row r="42" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="16" t="s">
         <v>339</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -6822,8 +6826,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="15" t="s">
+    <row r="43" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="16" t="s">
         <v>349</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -6871,8 +6875,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="15" t="s">
+    <row r="44" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="16" t="s">
         <v>356</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -6916,8 +6920,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="15" t="s">
+    <row r="45" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="16" t="s">
         <v>363</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -6961,8 +6965,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="15" t="s">
+    <row r="46" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="16" t="s">
         <v>368</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -7006,8 +7010,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="15" t="s">
+    <row r="47" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="16" t="s">
         <v>375</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -7051,8 +7055,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="15" t="s">
+    <row r="48" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="16" t="s">
         <v>379</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -7102,8 +7106,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="15" t="s">
+    <row r="49" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="16" t="s">
         <v>388</v>
       </c>
       <c r="B49" s="10" t="s">
@@ -7151,534 +7155,534 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="15" t="s">
+    <row r="50" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="16" t="s">
         <v>392</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="13" t="s">
         <v>393</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="E50" s="12" t="s">
+      <c r="E50" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="F50" s="12" t="s">
+      <c r="F50" s="13" t="s">
         <v>396</v>
       </c>
-      <c r="G50" s="12" t="s">
+      <c r="G50" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="H50" s="12" t="s">
+      <c r="H50" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="I50" s="12" t="s">
+      <c r="I50" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="J50" s="12" t="s">
+      <c r="J50" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="K50" s="12" t="s">
+      <c r="K50" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="L50" s="13" t="s">
+      <c r="L50" s="14" t="s">
         <v>401</v>
       </c>
-      <c r="M50" s="13" t="s">
+      <c r="M50" s="14" t="s">
         <v>402</v>
       </c>
-      <c r="N50" s="13" t="s">
+      <c r="N50" s="14" t="s">
         <v>403</v>
       </c>
-      <c r="O50" s="12" t="s">
+      <c r="O50" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="P50" s="12" t="s">
+      <c r="P50" s="13" t="s">
         <v>404</v>
       </c>
-      <c r="Q50" s="12" t="s">
+      <c r="Q50" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="R50" s="12" t="s">
+      <c r="R50" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="S50" s="12">
+      <c r="S50" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="18" t="s">
+    <row r="51" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="19" t="s">
         <v>1293</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B51" s="17" t="s">
         <v>393</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C51" s="17" t="s">
         <v>394</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="E51" s="12" t="s">
+      <c r="E51" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="F51" s="12" t="s">
+      <c r="F51" s="13" t="s">
         <v>396</v>
       </c>
-      <c r="G51" s="12" t="s">
+      <c r="G51" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="H51" s="16" t="s">
+      <c r="H51" s="17" t="s">
         <v>406</v>
       </c>
-      <c r="I51" s="16" t="s">
+      <c r="I51" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="J51" s="16" t="s">
+      <c r="J51" s="17" t="s">
         <v>407</v>
       </c>
-      <c r="K51" s="17" t="s">
+      <c r="K51" s="18" t="s">
         <v>408</v>
       </c>
-      <c r="L51" s="13" t="s">
+      <c r="L51" s="14" t="s">
         <v>409</v>
       </c>
-      <c r="M51" s="17" t="s">
+      <c r="M51" s="18" t="s">
         <v>410</v>
       </c>
-      <c r="N51" s="17" t="s">
+      <c r="N51" s="18" t="s">
         <v>411</v>
       </c>
-      <c r="O51" s="16" t="s">
+      <c r="O51" s="17" t="s">
         <v>412</v>
       </c>
-      <c r="P51" s="16" t="s">
+      <c r="P51" s="17" t="s">
         <v>413</v>
       </c>
-      <c r="Q51" s="16" t="s">
+      <c r="Q51" s="17" t="s">
         <v>414</v>
       </c>
-      <c r="R51" s="16" t="s">
+      <c r="R51" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S51" s="16">
+      <c r="S51" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="15" t="s">
+    <row r="52" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="16" t="s">
         <v>415</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="17" t="s">
         <v>393</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C52" s="17" t="s">
         <v>394</v>
       </c>
-      <c r="D52" s="16" t="s">
+      <c r="D52" s="17" t="s">
         <v>395</v>
       </c>
-      <c r="E52" s="16" t="s">
+      <c r="E52" s="17" t="s">
         <v>395</v>
       </c>
-      <c r="F52" s="16" t="s">
+      <c r="F52" s="17" t="s">
         <v>396</v>
       </c>
-      <c r="G52" s="16" t="s">
+      <c r="G52" s="17" t="s">
         <v>397</v>
       </c>
-      <c r="H52" s="16" t="s">
+      <c r="H52" s="17" t="s">
         <v>416</v>
       </c>
-      <c r="I52" s="16" t="s">
+      <c r="I52" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="J52" s="16" t="s">
+      <c r="J52" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="K52" s="16" t="s">
+      <c r="K52" s="17" t="s">
         <v>417</v>
       </c>
-      <c r="L52" s="13" t="s">
+      <c r="L52" s="14" t="s">
         <v>418</v>
       </c>
-      <c r="M52" s="14"/>
-      <c r="N52" s="16" t="s">
+      <c r="M52" s="15"/>
+      <c r="N52" s="17" t="s">
         <v>419</v>
       </c>
-      <c r="O52" s="16" t="s">
+      <c r="O52" s="17" t="s">
         <v>260</v>
       </c>
-      <c r="P52" s="16" t="s">
+      <c r="P52" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="Q52" s="16" t="s">
+      <c r="Q52" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="R52" s="16" t="s">
+      <c r="R52" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S52" s="16">
+      <c r="S52" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="15" t="s">
+    <row r="53" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="16" t="s">
         <v>421</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="B53" s="17" t="s">
         <v>393</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C53" s="17" t="s">
         <v>394</v>
       </c>
-      <c r="D53" s="16" t="s">
+      <c r="D53" s="17" t="s">
         <v>395</v>
       </c>
-      <c r="E53" s="16" t="s">
+      <c r="E53" s="17" t="s">
         <v>395</v>
       </c>
-      <c r="F53" s="16" t="s">
+      <c r="F53" s="17" t="s">
         <v>396</v>
       </c>
-      <c r="G53" s="16" t="s">
+      <c r="G53" s="17" t="s">
         <v>397</v>
       </c>
-      <c r="H53" s="16" t="s">
+      <c r="H53" s="17" t="s">
         <v>422</v>
       </c>
-      <c r="I53" s="16" t="s">
+      <c r="I53" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="J53" s="16" t="s">
+      <c r="J53" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="K53" s="16" t="s">
+      <c r="K53" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="L53" s="13" t="s">
+      <c r="L53" s="14" t="s">
         <v>353</v>
       </c>
-      <c r="M53" s="14"/>
-      <c r="N53" s="16" t="s">
+      <c r="M53" s="15"/>
+      <c r="N53" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="O53" s="16" t="s">
+      <c r="O53" s="17" t="s">
         <v>423</v>
       </c>
-      <c r="P53" s="16" t="s">
+      <c r="P53" s="17" t="s">
         <v>424</v>
       </c>
-      <c r="Q53" s="16" t="s">
+      <c r="Q53" s="17" t="s">
         <v>425</v>
       </c>
-      <c r="R53" s="16" t="s">
+      <c r="R53" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S53" s="16">
+      <c r="S53" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="15" t="s">
+    <row r="54" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="16" t="s">
         <v>426</v>
       </c>
-      <c r="B54" s="12" t="s">
+      <c r="B54" s="13" t="s">
         <v>427</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12" t="s">
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13" t="s">
         <v>428</v>
       </c>
-      <c r="G54" s="12" t="s">
+      <c r="G54" s="13" t="s">
         <v>429</v>
       </c>
-      <c r="H54" s="12" t="s">
+      <c r="H54" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="I54" s="12" t="s">
+      <c r="I54" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="J54" s="12" t="s">
+      <c r="J54" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="K54" s="12"/>
-      <c r="L54" s="13" t="s">
+      <c r="K54" s="13"/>
+      <c r="L54" s="14" t="s">
         <v>431</v>
       </c>
-      <c r="M54" s="13"/>
-      <c r="N54" s="13" t="s">
+      <c r="M54" s="14"/>
+      <c r="N54" s="14" t="s">
         <v>432</v>
       </c>
-      <c r="O54" s="12" t="s">
+      <c r="O54" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="P54" s="12" t="s">
+      <c r="P54" s="13" t="s">
         <v>433</v>
       </c>
-      <c r="Q54" s="12" t="s">
+      <c r="Q54" s="13" t="s">
         <v>434</v>
       </c>
-      <c r="R54" s="12" t="s">
+      <c r="R54" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="S54" s="12">
+      <c r="S54" s="13">
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="15" t="s">
+    <row r="55" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="16" t="s">
         <v>435</v>
       </c>
-      <c r="B55" s="16" t="s">
+      <c r="B55" s="17" t="s">
         <v>427</v>
       </c>
-      <c r="C55" s="16" t="s">
+      <c r="C55" s="17" t="s">
         <v>381</v>
       </c>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="12" t="s">
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="13" t="s">
         <v>428</v>
       </c>
-      <c r="G55" s="12" t="s">
+      <c r="G55" s="13" t="s">
         <v>429</v>
       </c>
-      <c r="H55" s="16" t="s">
+      <c r="H55" s="17" t="s">
         <v>436</v>
       </c>
-      <c r="I55" s="16" t="s">
+      <c r="I55" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="J55" s="16" t="s">
+      <c r="J55" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="K55" s="14"/>
-      <c r="L55" s="13" t="s">
+      <c r="K55" s="15"/>
+      <c r="L55" s="14" t="s">
         <v>353</v>
       </c>
-      <c r="M55" s="14"/>
-      <c r="N55" s="14"/>
-      <c r="O55" s="16" t="s">
+      <c r="M55" s="15"/>
+      <c r="N55" s="15"/>
+      <c r="O55" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="P55" s="16" t="s">
+      <c r="P55" s="17" t="s">
         <v>355</v>
       </c>
-      <c r="Q55" s="16" t="s">
+      <c r="Q55" s="17" t="s">
         <v>437</v>
       </c>
-      <c r="R55" s="16" t="s">
+      <c r="R55" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S55" s="16">
+      <c r="S55" s="17">
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="15" t="s">
+    <row r="56" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="16" t="s">
         <v>438</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="13" t="s">
         <v>439</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="13" t="s">
         <v>440</v>
       </c>
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12" t="s">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13" t="s">
         <v>441</v>
       </c>
-      <c r="G56" s="12" t="s">
+      <c r="G56" s="13" t="s">
         <v>442</v>
       </c>
-      <c r="H56" s="12" t="s">
+      <c r="H56" s="13" t="s">
         <v>443</v>
       </c>
-      <c r="I56" s="12" t="s">
+      <c r="I56" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="J56" s="12" t="s">
+      <c r="J56" s="13" t="s">
         <v>444</v>
       </c>
-      <c r="K56" s="12"/>
-      <c r="L56" s="13" t="s">
+      <c r="K56" s="13"/>
+      <c r="L56" s="14" t="s">
         <v>445</v>
       </c>
-      <c r="M56" s="13"/>
-      <c r="N56" s="13" t="s">
+      <c r="M56" s="14"/>
+      <c r="N56" s="14" t="s">
         <v>446</v>
       </c>
-      <c r="O56" s="12" t="s">
+      <c r="O56" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="P56" s="12"/>
-      <c r="Q56" s="12"/>
-      <c r="R56" s="12" t="s">
+      <c r="P56" s="13"/>
+      <c r="Q56" s="13"/>
+      <c r="R56" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="S56" s="12">
+      <c r="S56" s="13">
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="15" t="s">
+    <row r="57" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="16" t="s">
         <v>447</v>
       </c>
-      <c r="B57" s="16" t="s">
+      <c r="B57" s="17" t="s">
         <v>439</v>
       </c>
-      <c r="C57" s="16" t="s">
+      <c r="C57" s="17" t="s">
         <v>440</v>
       </c>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="12" t="s">
+      <c r="D57" s="15"/>
+      <c r="E57" s="15"/>
+      <c r="F57" s="13" t="s">
         <v>441</v>
       </c>
-      <c r="G57" s="12" t="s">
+      <c r="G57" s="13" t="s">
         <v>442</v>
       </c>
-      <c r="H57" s="16" t="s">
+      <c r="H57" s="17" t="s">
         <v>448</v>
       </c>
-      <c r="I57" s="16" t="s">
+      <c r="I57" s="17" t="s">
         <v>449</v>
       </c>
-      <c r="J57" s="16" t="s">
+      <c r="J57" s="17" t="s">
         <v>450</v>
       </c>
-      <c r="K57" s="14"/>
-      <c r="L57" s="13" t="s">
+      <c r="K57" s="15"/>
+      <c r="L57" s="14" t="s">
         <v>418</v>
       </c>
-      <c r="M57" s="14"/>
-      <c r="N57" s="14"/>
-      <c r="O57" s="16" t="s">
+      <c r="M57" s="15"/>
+      <c r="N57" s="15"/>
+      <c r="O57" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="P57" s="16" t="s">
+      <c r="P57" s="17" t="s">
         <v>451</v>
       </c>
-      <c r="Q57" s="16" t="s">
+      <c r="Q57" s="17" t="s">
         <v>452</v>
       </c>
-      <c r="R57" s="16" t="s">
+      <c r="R57" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S57" s="16">
+      <c r="S57" s="17">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="15" t="s">
+    <row r="58" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="16" t="s">
         <v>453</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="B58" s="13" t="s">
         <v>454</v>
       </c>
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="13" t="s">
         <v>455</v>
       </c>
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12" t="s">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13" t="s">
         <v>456</v>
       </c>
-      <c r="G58" s="12" t="s">
+      <c r="G58" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="H58" s="12" t="s">
+      <c r="H58" s="13" t="s">
         <v>457</v>
       </c>
-      <c r="I58" s="12" t="s">
+      <c r="I58" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="J58" s="12" t="s">
+      <c r="J58" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="K58" s="12"/>
-      <c r="L58" s="13" t="s">
+      <c r="K58" s="13"/>
+      <c r="L58" s="14" t="s">
         <v>458</v>
       </c>
-      <c r="M58" s="13"/>
-      <c r="N58" s="13"/>
-      <c r="O58" s="12" t="s">
+      <c r="M58" s="14"/>
+      <c r="N58" s="14"/>
+      <c r="O58" s="13" t="s">
         <v>459</v>
       </c>
-      <c r="P58" s="12" t="s">
+      <c r="P58" s="13" t="s">
         <v>460</v>
       </c>
-      <c r="Q58" s="12" t="s">
+      <c r="Q58" s="13" t="s">
         <v>461</v>
       </c>
-      <c r="R58" s="12" t="s">
+      <c r="R58" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="S58" s="12">
+      <c r="S58" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="15" t="s">
+    <row r="59" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="16" t="s">
         <v>462</v>
       </c>
-      <c r="B59" s="16" t="s">
+      <c r="B59" s="17" t="s">
         <v>454</v>
       </c>
-      <c r="C59" s="16" t="s">
+      <c r="C59" s="17" t="s">
         <v>455</v>
       </c>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="12" t="s">
+      <c r="D59" s="15"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="13" t="s">
         <v>456</v>
       </c>
-      <c r="G59" s="12" t="s">
+      <c r="G59" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="H59" s="16" t="s">
+      <c r="H59" s="17" t="s">
         <v>463</v>
       </c>
-      <c r="I59" s="16" t="s">
+      <c r="I59" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J59" s="16" t="s">
+      <c r="J59" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="K59" s="14"/>
-      <c r="L59" s="13" t="s">
+      <c r="K59" s="15"/>
+      <c r="L59" s="14" t="s">
         <v>464</v>
       </c>
-      <c r="M59" s="14"/>
-      <c r="N59" s="14"/>
-      <c r="O59" s="16" t="s">
+      <c r="M59" s="15"/>
+      <c r="N59" s="15"/>
+      <c r="O59" s="17" t="s">
         <v>286</v>
       </c>
-      <c r="P59" s="16" t="s">
+      <c r="P59" s="17" t="s">
         <v>465</v>
       </c>
-      <c r="Q59" s="16" t="s">
+      <c r="Q59" s="17" t="s">
         <v>466</v>
       </c>
-      <c r="R59" s="16" t="s">
+      <c r="R59" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S59" s="16">
+      <c r="S59" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="15" t="s">
+    <row r="60" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="16" t="s">
         <v>467</v>
       </c>
       <c r="B60" s="1" t="s">
@@ -7728,151 +7732,151 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="15" t="s">
+    <row r="61" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="16" t="s">
         <v>476</v>
       </c>
-      <c r="B61" s="16" t="s">
+      <c r="B61" s="17" t="s">
         <v>454</v>
       </c>
-      <c r="C61" s="16" t="s">
+      <c r="C61" s="17" t="s">
         <v>468</v>
       </c>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="12" t="s">
+      <c r="D61" s="15"/>
+      <c r="E61" s="15"/>
+      <c r="F61" s="13" t="s">
         <v>469</v>
       </c>
-      <c r="G61" s="12" t="s">
+      <c r="G61" s="13" t="s">
         <v>470</v>
       </c>
-      <c r="H61" s="16" t="s">
+      <c r="H61" s="17" t="s">
         <v>477</v>
       </c>
-      <c r="I61" s="16" t="s">
+      <c r="I61" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="J61" s="16" t="s">
+      <c r="J61" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="K61" s="17"/>
-      <c r="L61" s="13" t="s">
+      <c r="K61" s="18"/>
+      <c r="L61" s="14" t="s">
         <v>478</v>
       </c>
-      <c r="M61" s="17"/>
-      <c r="N61" s="17"/>
-      <c r="O61" s="16" t="s">
+      <c r="M61" s="18"/>
+      <c r="N61" s="18"/>
+      <c r="O61" s="17" t="s">
         <v>479</v>
       </c>
-      <c r="P61" s="16" t="s">
+      <c r="P61" s="17" t="s">
         <v>480</v>
       </c>
-      <c r="Q61" s="16" t="s">
+      <c r="Q61" s="17" t="s">
         <v>481</v>
       </c>
-      <c r="R61" s="16" t="s">
+      <c r="R61" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S61" s="16">
+      <c r="S61" s="17">
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="15" t="s">
+    <row r="62" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="16" t="s">
         <v>482</v>
       </c>
-      <c r="B62" s="12" t="s">
+      <c r="B62" s="13" t="s">
         <v>483</v>
       </c>
-      <c r="C62" s="12" t="s">
+      <c r="C62" s="13" t="s">
         <v>484</v>
       </c>
-      <c r="D62" s="12"/>
-      <c r="E62" s="12"/>
-      <c r="F62" s="12" t="s">
+      <c r="D62" s="13"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13" t="s">
         <v>485</v>
       </c>
-      <c r="G62" s="12" t="s">
+      <c r="G62" s="13" t="s">
         <v>486</v>
       </c>
-      <c r="H62" s="12" t="s">
+      <c r="H62" s="13" t="s">
         <v>487</v>
       </c>
-      <c r="I62" s="12" t="s">
+      <c r="I62" s="13" t="s">
         <v>488</v>
       </c>
-      <c r="J62" s="12" t="s">
+      <c r="J62" s="13" t="s">
         <v>489</v>
       </c>
-      <c r="K62" s="12"/>
-      <c r="L62" s="13" t="s">
+      <c r="K62" s="13"/>
+      <c r="L62" s="14" t="s">
         <v>490</v>
       </c>
-      <c r="M62" s="13"/>
-      <c r="N62" s="13"/>
-      <c r="O62" s="12" t="s">
+      <c r="M62" s="14"/>
+      <c r="N62" s="14"/>
+      <c r="O62" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="P62" s="12"/>
-      <c r="Q62" s="12"/>
-      <c r="R62" s="12" t="s">
+      <c r="P62" s="13"/>
+      <c r="Q62" s="13"/>
+      <c r="R62" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="S62" s="12">
+      <c r="S62" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="15" t="s">
+    <row r="63" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="16" t="s">
         <v>491</v>
       </c>
-      <c r="B63" s="16" t="s">
+      <c r="B63" s="17" t="s">
         <v>483</v>
       </c>
-      <c r="C63" s="16" t="s">
+      <c r="C63" s="17" t="s">
         <v>484</v>
       </c>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="12" t="s">
+      <c r="D63" s="15"/>
+      <c r="E63" s="15"/>
+      <c r="F63" s="13" t="s">
         <v>485</v>
       </c>
-      <c r="G63" s="12" t="s">
+      <c r="G63" s="13" t="s">
         <v>486</v>
       </c>
-      <c r="H63" s="16" t="s">
+      <c r="H63" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="I63" s="16" t="s">
+      <c r="I63" s="17" t="s">
         <v>492</v>
       </c>
-      <c r="J63" s="16" t="s">
+      <c r="J63" s="17" t="s">
         <v>493</v>
       </c>
-      <c r="K63" s="17"/>
-      <c r="L63" s="13" t="s">
+      <c r="K63" s="18"/>
+      <c r="L63" s="14" t="s">
         <v>494</v>
       </c>
-      <c r="M63" s="17"/>
-      <c r="N63" s="17"/>
-      <c r="O63" s="16" t="s">
+      <c r="M63" s="18"/>
+      <c r="N63" s="18"/>
+      <c r="O63" s="17" t="s">
         <v>345</v>
       </c>
-      <c r="P63" s="16" t="s">
+      <c r="P63" s="17" t="s">
         <v>495</v>
       </c>
-      <c r="Q63" s="16" t="s">
+      <c r="Q63" s="17" t="s">
         <v>496</v>
       </c>
-      <c r="R63" s="16" t="s">
+      <c r="R63" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="S63" s="16">
+      <c r="S63" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="15" t="s">
+    <row r="64" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="16" t="s">
         <v>497</v>
       </c>
       <c r="B64" s="1" t="s">
@@ -7922,803 +7926,803 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="15" t="s">
+    <row r="65" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="16" t="s">
         <v>507</v>
       </c>
-      <c r="B65" s="16" t="s">
+      <c r="B65" s="17" t="s">
         <v>498</v>
       </c>
-      <c r="C65" s="16" t="s">
+      <c r="C65" s="17" t="s">
         <v>455</v>
       </c>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
+      <c r="D65" s="15"/>
+      <c r="E65" s="15"/>
       <c r="F65" s="1" t="s">
         <v>135</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="H65" s="16" t="s">
+      <c r="H65" s="17" t="s">
         <v>508</v>
       </c>
-      <c r="I65" s="16" t="s">
+      <c r="I65" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="J65" s="16" t="s">
+      <c r="J65" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="K65" s="16" t="s">
+      <c r="K65" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="L65" s="13" t="s">
+      <c r="L65" s="14" t="s">
         <v>509</v>
       </c>
-      <c r="M65" s="17"/>
-      <c r="N65" s="16" t="s">
+      <c r="M65" s="18"/>
+      <c r="N65" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="O65" s="16" t="s">
+      <c r="O65" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="P65" s="16" t="s">
+      <c r="P65" s="17" t="s">
         <v>510</v>
       </c>
-      <c r="Q65" s="16" t="s">
+      <c r="Q65" s="17" t="s">
         <v>511</v>
       </c>
-      <c r="R65" s="16" t="s">
+      <c r="R65" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S65" s="16">
+      <c r="S65" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="15" t="s">
+    <row r="66" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="16" t="s">
         <v>512</v>
       </c>
-      <c r="B66" s="16" t="s">
+      <c r="B66" s="17" t="s">
         <v>498</v>
       </c>
-      <c r="C66" s="16" t="s">
+      <c r="C66" s="17" t="s">
         <v>455</v>
       </c>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
+      <c r="D66" s="15"/>
+      <c r="E66" s="15"/>
       <c r="F66" s="1" t="s">
         <v>135</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="H66" s="16" t="s">
+      <c r="H66" s="17" t="s">
         <v>364</v>
       </c>
-      <c r="I66" s="16" t="s">
+      <c r="I66" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="J66" s="16" t="s">
+      <c r="J66" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="K66" s="16" t="s">
+      <c r="K66" s="17" t="s">
         <v>513</v>
       </c>
-      <c r="L66" s="13" t="s">
+      <c r="L66" s="14" t="s">
         <v>514</v>
       </c>
-      <c r="M66" s="17"/>
-      <c r="N66" s="16" t="s">
+      <c r="M66" s="18"/>
+      <c r="N66" s="17" t="s">
         <v>515</v>
       </c>
-      <c r="O66" s="16" t="s">
+      <c r="O66" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="P66" s="16" t="s">
+      <c r="P66" s="17" t="s">
         <v>516</v>
       </c>
-      <c r="Q66" s="16" t="s">
+      <c r="Q66" s="17" t="s">
         <v>517</v>
       </c>
-      <c r="R66" s="16" t="s">
+      <c r="R66" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S66" s="16">
+      <c r="S66" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="15" t="s">
+    <row r="67" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="16" t="s">
         <v>518</v>
       </c>
-      <c r="B67" s="16" t="s">
+      <c r="B67" s="17" t="s">
         <v>498</v>
       </c>
-      <c r="C67" s="16" t="s">
+      <c r="C67" s="17" t="s">
         <v>455</v>
       </c>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
+      <c r="D67" s="15"/>
+      <c r="E67" s="15"/>
       <c r="F67" s="1" t="s">
         <v>135</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="H67" s="16" t="s">
+      <c r="H67" s="17" t="s">
         <v>519</v>
       </c>
-      <c r="I67" s="16" t="s">
+      <c r="I67" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J67" s="16" t="s">
+      <c r="J67" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="K67" s="16" t="s">
+      <c r="K67" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="L67" s="13" t="s">
+      <c r="L67" s="14" t="s">
         <v>520</v>
       </c>
-      <c r="M67" s="17"/>
-      <c r="N67" s="16" t="s">
+      <c r="M67" s="18"/>
+      <c r="N67" s="17" t="s">
         <v>521</v>
       </c>
-      <c r="O67" s="16" t="s">
+      <c r="O67" s="17" t="s">
         <v>522</v>
       </c>
-      <c r="P67" s="16" t="s">
+      <c r="P67" s="17" t="s">
         <v>523</v>
       </c>
-      <c r="Q67" s="16" t="s">
+      <c r="Q67" s="17" t="s">
         <v>390</v>
       </c>
-      <c r="R67" s="16" t="s">
+      <c r="R67" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S67" s="16">
+      <c r="S67" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="15" t="s">
+    <row r="68" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="16" t="s">
         <v>524</v>
       </c>
-      <c r="B68" s="16" t="s">
+      <c r="B68" s="17" t="s">
         <v>498</v>
       </c>
-      <c r="C68" s="16" t="s">
+      <c r="C68" s="17" t="s">
         <v>455</v>
       </c>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
+      <c r="D68" s="15"/>
+      <c r="E68" s="15"/>
       <c r="F68" s="1" t="s">
         <v>135</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="H68" s="16" t="s">
+      <c r="H68" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="I68" s="16" t="s">
+      <c r="I68" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J68" s="16" t="s">
+      <c r="J68" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="K68" s="16" t="s">
+      <c r="K68" s="17" t="s">
         <v>525</v>
       </c>
-      <c r="L68" s="13" t="s">
+      <c r="L68" s="14" t="s">
         <v>526</v>
       </c>
-      <c r="M68" s="17"/>
-      <c r="N68" s="16" t="s">
+      <c r="M68" s="18"/>
+      <c r="N68" s="17" t="s">
         <v>527</v>
       </c>
-      <c r="O68" s="16" t="s">
+      <c r="O68" s="17" t="s">
         <v>522</v>
       </c>
-      <c r="P68" s="16" t="s">
+      <c r="P68" s="17" t="s">
         <v>528</v>
       </c>
-      <c r="Q68" s="16" t="s">
+      <c r="Q68" s="17" t="s">
         <v>529</v>
       </c>
-      <c r="R68" s="16" t="s">
+      <c r="R68" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S68" s="16">
+      <c r="S68" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="15" t="s">
+    <row r="69" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="16" t="s">
         <v>530</v>
       </c>
-      <c r="B69" s="16" t="s">
+      <c r="B69" s="17" t="s">
         <v>498</v>
       </c>
-      <c r="C69" s="16" t="s">
+      <c r="C69" s="17" t="s">
         <v>455</v>
       </c>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
+      <c r="D69" s="15"/>
+      <c r="E69" s="15"/>
       <c r="F69" s="1" t="s">
         <v>135</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="H69" s="16" t="s">
+      <c r="H69" s="17" t="s">
         <v>531</v>
       </c>
-      <c r="I69" s="16" t="s">
+      <c r="I69" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="J69" s="16" t="s">
+      <c r="J69" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="K69" s="16" t="s">
+      <c r="K69" s="17" t="s">
         <v>532</v>
       </c>
-      <c r="L69" s="13" t="s">
+      <c r="L69" s="14" t="s">
         <v>533</v>
       </c>
-      <c r="M69" s="17"/>
-      <c r="N69" s="16" t="s">
+      <c r="M69" s="18"/>
+      <c r="N69" s="17" t="s">
         <v>534</v>
       </c>
-      <c r="O69" s="16" t="s">
+      <c r="O69" s="17" t="s">
         <v>522</v>
       </c>
-      <c r="P69" s="16" t="s">
+      <c r="P69" s="17" t="s">
         <v>535</v>
       </c>
-      <c r="Q69" s="16" t="s">
+      <c r="Q69" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="R69" s="16" t="s">
+      <c r="R69" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S69" s="16">
+      <c r="S69" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="15" t="s">
+    <row r="70" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="16" t="s">
         <v>536</v>
       </c>
-      <c r="B70" s="12" t="s">
+      <c r="B70" s="13" t="s">
         <v>537</v>
       </c>
-      <c r="C70" s="12" t="s">
+      <c r="C70" s="13" t="s">
         <v>538</v>
       </c>
-      <c r="D70" s="12"/>
-      <c r="E70" s="12"/>
-      <c r="F70" s="12" t="s">
+      <c r="D70" s="13"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="G70" s="12" t="s">
+      <c r="G70" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="H70" s="12" t="s">
+      <c r="H70" s="13" t="s">
         <v>539</v>
       </c>
-      <c r="I70" s="12" t="s">
+      <c r="I70" s="13" t="s">
         <v>540</v>
       </c>
-      <c r="J70" s="12" t="s">
+      <c r="J70" s="13" t="s">
         <v>541</v>
       </c>
-      <c r="K70" s="12" t="s">
+      <c r="K70" s="13" t="s">
         <v>542</v>
       </c>
-      <c r="L70" s="13" t="s">
+      <c r="L70" s="14" t="s">
         <v>543</v>
       </c>
-      <c r="M70" s="13"/>
-      <c r="N70" s="13" t="s">
+      <c r="M70" s="14"/>
+      <c r="N70" s="14" t="s">
         <v>544</v>
       </c>
-      <c r="O70" s="12" t="s">
+      <c r="O70" s="13" t="s">
         <v>545</v>
       </c>
-      <c r="P70" s="12" t="s">
+      <c r="P70" s="13" t="s">
         <v>546</v>
       </c>
-      <c r="Q70" s="12" t="s">
+      <c r="Q70" s="13" t="s">
         <v>547</v>
       </c>
-      <c r="R70" s="12" t="s">
+      <c r="R70" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="S70" s="12">
+      <c r="S70" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="15" t="s">
+    <row r="71" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="16" t="s">
         <v>548</v>
       </c>
-      <c r="B71" s="16" t="s">
+      <c r="B71" s="17" t="s">
         <v>537</v>
       </c>
-      <c r="C71" s="16" t="s">
+      <c r="C71" s="17" t="s">
         <v>538</v>
       </c>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="12" t="s">
+      <c r="D71" s="15"/>
+      <c r="E71" s="15"/>
+      <c r="F71" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="G71" s="12" t="s">
+      <c r="G71" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="H71" s="16" t="s">
+      <c r="H71" s="17" t="s">
         <v>549</v>
       </c>
-      <c r="I71" s="16" t="s">
+      <c r="I71" s="17" t="s">
         <v>492</v>
       </c>
-      <c r="J71" s="16" t="s">
+      <c r="J71" s="17" t="s">
         <v>550</v>
       </c>
-      <c r="K71" s="16" t="s">
+      <c r="K71" s="17" t="s">
         <v>551</v>
       </c>
-      <c r="L71" s="13" t="s">
+      <c r="L71" s="14" t="s">
         <v>552</v>
       </c>
-      <c r="M71" s="14"/>
-      <c r="N71" s="16" t="s">
+      <c r="M71" s="15"/>
+      <c r="N71" s="17" t="s">
         <v>553</v>
       </c>
-      <c r="O71" s="16" t="s">
+      <c r="O71" s="17" t="s">
         <v>554</v>
       </c>
-      <c r="P71" s="16" t="s">
+      <c r="P71" s="17" t="s">
         <v>555</v>
       </c>
-      <c r="Q71" s="16" t="s">
+      <c r="Q71" s="17" t="s">
         <v>556</v>
       </c>
-      <c r="R71" s="16" t="s">
+      <c r="R71" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="S71" s="16">
+      <c r="S71" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="15" t="s">
+    <row r="72" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="16" t="s">
         <v>557</v>
       </c>
-      <c r="B72" s="16" t="s">
+      <c r="B72" s="17" t="s">
         <v>537</v>
       </c>
-      <c r="C72" s="16" t="s">
+      <c r="C72" s="17" t="s">
         <v>538</v>
       </c>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="12" t="s">
+      <c r="D72" s="15"/>
+      <c r="E72" s="15"/>
+      <c r="F72" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="G72" s="12" t="s">
+      <c r="G72" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="H72" s="16" t="s">
+      <c r="H72" s="17" t="s">
         <v>457</v>
       </c>
-      <c r="I72" s="16" t="s">
+      <c r="I72" s="17" t="s">
         <v>558</v>
       </c>
-      <c r="J72" s="16" t="s">
+      <c r="J72" s="17" t="s">
         <v>559</v>
       </c>
-      <c r="K72" s="16" t="s">
+      <c r="K72" s="17" t="s">
         <v>560</v>
       </c>
-      <c r="L72" s="13" t="s">
+      <c r="L72" s="14" t="s">
         <v>561</v>
       </c>
-      <c r="M72" s="14"/>
-      <c r="N72" s="16" t="s">
+      <c r="M72" s="15"/>
+      <c r="N72" s="17" t="s">
         <v>562</v>
       </c>
-      <c r="O72" s="16" t="s">
+      <c r="O72" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="P72" s="16" t="s">
+      <c r="P72" s="17" t="s">
         <v>510</v>
       </c>
-      <c r="Q72" s="16" t="s">
+      <c r="Q72" s="17" t="s">
         <v>563</v>
       </c>
-      <c r="R72" s="16" t="s">
+      <c r="R72" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="S72" s="16">
+      <c r="S72" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="15" t="s">
+    <row r="73" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="16" t="s">
         <v>564</v>
       </c>
-      <c r="B73" s="16" t="s">
+      <c r="B73" s="17" t="s">
         <v>537</v>
       </c>
-      <c r="C73" s="16" t="s">
+      <c r="C73" s="17" t="s">
         <v>538</v>
       </c>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="12" t="s">
+      <c r="D73" s="15"/>
+      <c r="E73" s="15"/>
+      <c r="F73" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="G73" s="12" t="s">
+      <c r="G73" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="H73" s="16" t="s">
+      <c r="H73" s="17" t="s">
         <v>565</v>
       </c>
-      <c r="I73" s="16" t="s">
+      <c r="I73" s="17" t="s">
         <v>492</v>
       </c>
-      <c r="J73" s="16" t="s">
+      <c r="J73" s="17" t="s">
         <v>550</v>
       </c>
-      <c r="K73" s="16" t="s">
+      <c r="K73" s="17" t="s">
         <v>551</v>
       </c>
-      <c r="L73" s="13" t="s">
+      <c r="L73" s="14" t="s">
         <v>566</v>
       </c>
-      <c r="M73" s="14"/>
-      <c r="N73" s="16" t="s">
+      <c r="M73" s="15"/>
+      <c r="N73" s="17" t="s">
         <v>567</v>
       </c>
-      <c r="O73" s="16" t="s">
+      <c r="O73" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="P73" s="16" t="s">
+      <c r="P73" s="17" t="s">
         <v>568</v>
       </c>
-      <c r="Q73" s="16" t="s">
+      <c r="Q73" s="17" t="s">
         <v>569</v>
       </c>
-      <c r="R73" s="16" t="s">
+      <c r="R73" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="S73" s="16">
+      <c r="S73" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="15" t="s">
+    <row r="74" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="16" t="s">
         <v>570</v>
       </c>
-      <c r="B74" s="16" t="s">
+      <c r="B74" s="17" t="s">
         <v>537</v>
       </c>
-      <c r="C74" s="16" t="s">
+      <c r="C74" s="17" t="s">
         <v>538</v>
       </c>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="12" t="s">
+      <c r="D74" s="15"/>
+      <c r="E74" s="15"/>
+      <c r="F74" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="G74" s="12" t="s">
+      <c r="G74" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="H74" s="16" t="s">
+      <c r="H74" s="17" t="s">
         <v>571</v>
       </c>
-      <c r="I74" s="16" t="s">
+      <c r="I74" s="17" t="s">
         <v>492</v>
       </c>
-      <c r="J74" s="16" t="s">
+      <c r="J74" s="17" t="s">
         <v>550</v>
       </c>
-      <c r="K74" s="16" t="s">
+      <c r="K74" s="17" t="s">
         <v>551</v>
       </c>
-      <c r="L74" s="13" t="s">
+      <c r="L74" s="14" t="s">
         <v>572</v>
       </c>
-      <c r="M74" s="14"/>
-      <c r="N74" s="16" t="s">
+      <c r="M74" s="15"/>
+      <c r="N74" s="17" t="s">
         <v>573</v>
       </c>
-      <c r="O74" s="16" t="s">
+      <c r="O74" s="17" t="s">
         <v>574</v>
       </c>
-      <c r="P74" s="16" t="s">
+      <c r="P74" s="17" t="s">
         <v>575</v>
       </c>
-      <c r="Q74" s="16" t="s">
+      <c r="Q74" s="17" t="s">
         <v>576</v>
       </c>
-      <c r="R74" s="16" t="s">
+      <c r="R74" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="S74" s="16">
+      <c r="S74" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="15" t="s">
+    <row r="75" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="16" t="s">
         <v>577</v>
       </c>
-      <c r="B75" s="12" t="s">
+      <c r="B75" s="13" t="s">
         <v>578</v>
       </c>
-      <c r="C75" s="12" t="s">
+      <c r="C75" s="13" t="s">
         <v>579</v>
       </c>
-      <c r="D75" s="12"/>
-      <c r="E75" s="12"/>
-      <c r="F75" s="12" t="s">
+      <c r="D75" s="13"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="G75" s="12" t="s">
+      <c r="G75" s="13" t="s">
         <v>580</v>
       </c>
-      <c r="H75" s="12" t="s">
+      <c r="H75" s="13" t="s">
         <v>581</v>
       </c>
-      <c r="I75" s="12" t="s">
+      <c r="I75" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="J75" s="12" t="s">
+      <c r="J75" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="K75" s="12" t="s">
+      <c r="K75" s="13" t="s">
         <v>582</v>
       </c>
-      <c r="L75" s="13" t="s">
+      <c r="L75" s="14" t="s">
         <v>583</v>
       </c>
-      <c r="M75" s="13"/>
-      <c r="N75" s="13" t="s">
+      <c r="M75" s="14"/>
+      <c r="N75" s="14" t="s">
         <v>584</v>
       </c>
-      <c r="O75" s="12" t="s">
+      <c r="O75" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="P75" s="12" t="s">
+      <c r="P75" s="13" t="s">
         <v>585</v>
       </c>
-      <c r="Q75" s="12" t="s">
+      <c r="Q75" s="13" t="s">
         <v>586</v>
       </c>
-      <c r="R75" s="12" t="s">
+      <c r="R75" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="S75" s="12">
+      <c r="S75" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="15" t="s">
+    <row r="76" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="16" t="s">
         <v>587</v>
       </c>
-      <c r="B76" s="16" t="s">
+      <c r="B76" s="17" t="s">
         <v>578</v>
       </c>
-      <c r="C76" s="16" t="s">
+      <c r="C76" s="17" t="s">
         <v>579</v>
       </c>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="12" t="s">
+      <c r="D76" s="15"/>
+      <c r="E76" s="15"/>
+      <c r="F76" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="G76" s="12" t="s">
+      <c r="G76" s="13" t="s">
         <v>580</v>
       </c>
-      <c r="H76" s="16" t="s">
+      <c r="H76" s="17" t="s">
         <v>588</v>
       </c>
-      <c r="I76" s="16" t="s">
+      <c r="I76" s="17" t="s">
         <v>330</v>
       </c>
-      <c r="J76" s="16" t="s">
+      <c r="J76" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="K76" s="16" t="s">
+      <c r="K76" s="17" t="s">
         <v>560</v>
       </c>
-      <c r="L76" s="13" t="s">
+      <c r="L76" s="14" t="s">
         <v>589</v>
       </c>
-      <c r="M76" s="14"/>
-      <c r="N76" s="16" t="s">
+      <c r="M76" s="15"/>
+      <c r="N76" s="17" t="s">
         <v>590</v>
       </c>
-      <c r="O76" s="16" t="s">
+      <c r="O76" s="17" t="s">
         <v>554</v>
       </c>
-      <c r="P76" s="16" t="s">
+      <c r="P76" s="17" t="s">
         <v>591</v>
       </c>
-      <c r="Q76" s="16" t="s">
+      <c r="Q76" s="17" t="s">
         <v>592</v>
       </c>
-      <c r="R76" s="16" t="s">
+      <c r="R76" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="S76" s="16">
+      <c r="S76" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="15" t="s">
+    <row r="77" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="16" t="s">
         <v>593</v>
       </c>
-      <c r="B77" s="16" t="s">
+      <c r="B77" s="17" t="s">
         <v>578</v>
       </c>
-      <c r="C77" s="16" t="s">
+      <c r="C77" s="17" t="s">
         <v>579</v>
       </c>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="12" t="s">
+      <c r="D77" s="15"/>
+      <c r="E77" s="15"/>
+      <c r="F77" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="G77" s="12" t="s">
+      <c r="G77" s="13" t="s">
         <v>580</v>
       </c>
-      <c r="H77" s="16" t="s">
+      <c r="H77" s="17" t="s">
         <v>594</v>
       </c>
-      <c r="I77" s="16" t="s">
+      <c r="I77" s="17" t="s">
         <v>595</v>
       </c>
-      <c r="J77" s="16" t="s">
+      <c r="J77" s="17" t="s">
         <v>596</v>
       </c>
-      <c r="K77" s="16" t="s">
+      <c r="K77" s="17" t="s">
         <v>597</v>
       </c>
-      <c r="L77" s="13" t="s">
+      <c r="L77" s="14" t="s">
         <v>598</v>
       </c>
-      <c r="M77" s="14"/>
-      <c r="N77" s="16" t="s">
+      <c r="M77" s="15"/>
+      <c r="N77" s="17" t="s">
         <v>599</v>
       </c>
-      <c r="O77" s="16" t="s">
+      <c r="O77" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="P77" s="16" t="s">
+      <c r="P77" s="17" t="s">
         <v>495</v>
       </c>
-      <c r="Q77" s="16" t="s">
+      <c r="Q77" s="17" t="s">
         <v>505</v>
       </c>
-      <c r="R77" s="16" t="s">
+      <c r="R77" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="S77" s="16">
+      <c r="S77" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="15" t="s">
+    <row r="78" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="16" t="s">
         <v>600</v>
       </c>
-      <c r="B78" s="16" t="s">
+      <c r="B78" s="17" t="s">
         <v>578</v>
       </c>
-      <c r="C78" s="16" t="s">
+      <c r="C78" s="17" t="s">
         <v>579</v>
       </c>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="12" t="s">
+      <c r="D78" s="15"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="G78" s="12" t="s">
+      <c r="G78" s="13" t="s">
         <v>580</v>
       </c>
-      <c r="H78" s="16" t="s">
+      <c r="H78" s="17" t="s">
         <v>500</v>
       </c>
-      <c r="I78" s="16" t="s">
+      <c r="I78" s="17" t="s">
         <v>492</v>
       </c>
-      <c r="J78" s="16" t="s">
+      <c r="J78" s="17" t="s">
         <v>493</v>
       </c>
-      <c r="K78" s="16" t="s">
+      <c r="K78" s="17" t="s">
         <v>601</v>
       </c>
-      <c r="L78" s="13" t="s">
+      <c r="L78" s="14" t="s">
         <v>602</v>
       </c>
-      <c r="M78" s="14"/>
-      <c r="N78" s="16" t="s">
+      <c r="M78" s="15"/>
+      <c r="N78" s="17" t="s">
         <v>603</v>
       </c>
-      <c r="O78" s="16" t="s">
+      <c r="O78" s="17" t="s">
         <v>554</v>
       </c>
-      <c r="P78" s="16" t="s">
+      <c r="P78" s="17" t="s">
         <v>604</v>
       </c>
-      <c r="Q78" s="16" t="s">
+      <c r="Q78" s="17" t="s">
         <v>605</v>
       </c>
-      <c r="R78" s="16" t="s">
+      <c r="R78" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="S78" s="16">
+      <c r="S78" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="15" t="s">
+    <row r="79" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="16" t="s">
         <v>606</v>
       </c>
-      <c r="B79" s="16" t="s">
+      <c r="B79" s="17" t="s">
         <v>578</v>
       </c>
-      <c r="C79" s="16" t="s">
+      <c r="C79" s="17" t="s">
         <v>579</v>
       </c>
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="12" t="s">
+      <c r="D79" s="15"/>
+      <c r="E79" s="15"/>
+      <c r="F79" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="G79" s="12" t="s">
+      <c r="G79" s="13" t="s">
         <v>580</v>
       </c>
-      <c r="H79" s="16" t="s">
+      <c r="H79" s="17" t="s">
         <v>500</v>
       </c>
-      <c r="I79" s="16" t="s">
+      <c r="I79" s="17" t="s">
         <v>330</v>
       </c>
-      <c r="J79" s="16" t="s">
+      <c r="J79" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="K79" s="16" t="s">
+      <c r="K79" s="17" t="s">
         <v>560</v>
       </c>
-      <c r="L79" s="13" t="s">
+      <c r="L79" s="14" t="s">
         <v>607</v>
       </c>
-      <c r="M79" s="14"/>
-      <c r="N79" s="16" t="s">
+      <c r="M79" s="15"/>
+      <c r="N79" s="17" t="s">
         <v>608</v>
       </c>
-      <c r="O79" s="16" t="s">
+      <c r="O79" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="P79" s="16" t="s">
+      <c r="P79" s="17" t="s">
         <v>609</v>
       </c>
-      <c r="Q79" s="16" t="s">
+      <c r="Q79" s="17" t="s">
         <v>610</v>
       </c>
-      <c r="R79" s="16" t="s">
+      <c r="R79" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="S79" s="16">
+      <c r="S79" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="15" t="s">
+    <row r="80" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="16" t="s">
         <v>611</v>
       </c>
       <c r="B80" s="1" t="s">
@@ -8766,8 +8770,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="15" t="s">
+    <row r="81" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="16" t="s">
         <v>620</v>
       </c>
       <c r="B81" s="1" t="s">
@@ -8819,8 +8823,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="15" t="s">
+    <row r="82" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="16" t="s">
         <v>627</v>
       </c>
       <c r="B82" s="1" t="s">
@@ -8872,8 +8876,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="15" t="s">
+    <row r="83" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="16" t="s">
         <v>634</v>
       </c>
       <c r="B83" s="1" t="s">
@@ -8925,8 +8929,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="15" t="s">
+    <row r="84" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="16" t="s">
         <v>639</v>
       </c>
       <c r="B84" s="1" t="s">
@@ -8978,8 +8982,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="15" t="s">
+    <row r="85" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="16" t="s">
         <v>643</v>
       </c>
       <c r="B85" s="1" t="s">
@@ -9031,8 +9035,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="15" t="s">
+    <row r="86" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="16" t="s">
         <v>651</v>
       </c>
       <c r="B86" s="1" t="s">
@@ -9084,8 +9088,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="15" t="s">
+    <row r="87" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="16" t="s">
         <v>654</v>
       </c>
       <c r="B87" s="1" t="s">
@@ -9137,8 +9141,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="23" t="s">
+    <row r="88" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="24" t="s">
         <v>657</v>
       </c>
       <c r="B88" s="1" t="s">
@@ -9190,8 +9194,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="15" t="s">
+    <row r="89" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="16" t="s">
         <v>662</v>
       </c>
       <c r="B89" s="1" t="s">
@@ -9243,98 +9247,98 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="15" t="s">
+    <row r="90" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="16" t="s">
         <v>665</v>
       </c>
-      <c r="B90" s="12" t="s">
+      <c r="B90" s="13" t="s">
         <v>666</v>
       </c>
-      <c r="C90" s="12" t="s">
+      <c r="C90" s="13" t="s">
         <v>667</v>
       </c>
-      <c r="D90" s="12"/>
-      <c r="E90" s="12"/>
-      <c r="F90" s="12" t="s">
+      <c r="D90" s="13"/>
+      <c r="E90" s="13"/>
+      <c r="F90" s="13" t="s">
         <v>668</v>
       </c>
-      <c r="G90" s="12" t="s">
+      <c r="G90" s="13" t="s">
         <v>669</v>
       </c>
-      <c r="H90" s="12" t="s">
+      <c r="H90" s="13" t="s">
         <v>670</v>
       </c>
-      <c r="I90" s="12" t="s">
+      <c r="I90" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="J90" s="12" t="s">
+      <c r="J90" s="13" t="s">
         <v>671</v>
       </c>
-      <c r="K90" s="12"/>
-      <c r="L90" s="13" t="s">
+      <c r="K90" s="13"/>
+      <c r="L90" s="14" t="s">
         <v>672</v>
       </c>
-      <c r="M90" s="13"/>
-      <c r="N90" s="13"/>
-      <c r="O90" s="12" t="s">
+      <c r="M90" s="14"/>
+      <c r="N90" s="14"/>
+      <c r="O90" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="P90" s="12"/>
-      <c r="Q90" s="12"/>
-      <c r="R90" s="12" t="s">
+      <c r="P90" s="13"/>
+      <c r="Q90" s="13"/>
+      <c r="R90" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="S90" s="12">
+      <c r="S90" s="13">
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="15" t="s">
+    <row r="91" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="16" t="s">
         <v>673</v>
       </c>
-      <c r="B91" s="16" t="s">
+      <c r="B91" s="17" t="s">
         <v>666</v>
       </c>
-      <c r="C91" s="16" t="s">
+      <c r="C91" s="17" t="s">
         <v>667</v>
       </c>
-      <c r="D91" s="14"/>
-      <c r="E91" s="14"/>
-      <c r="F91" s="12" t="s">
+      <c r="D91" s="15"/>
+      <c r="E91" s="15"/>
+      <c r="F91" s="13" t="s">
         <v>668</v>
       </c>
-      <c r="G91" s="12" t="s">
+      <c r="G91" s="13" t="s">
         <v>669</v>
       </c>
-      <c r="H91" s="16" t="s">
+      <c r="H91" s="17" t="s">
         <v>674</v>
       </c>
-      <c r="I91" s="16" t="s">
+      <c r="I91" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="J91" s="16" t="s">
+      <c r="J91" s="17" t="s">
         <v>675</v>
       </c>
-      <c r="K91" s="14"/>
-      <c r="L91" s="13" t="s">
+      <c r="K91" s="15"/>
+      <c r="L91" s="14" t="s">
         <v>676</v>
       </c>
-      <c r="M91" s="14"/>
-      <c r="N91" s="14"/>
-      <c r="O91" s="16" t="s">
+      <c r="M91" s="15"/>
+      <c r="N91" s="15"/>
+      <c r="O91" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="P91" s="14"/>
-      <c r="Q91" s="14"/>
-      <c r="R91" s="16" t="s">
+      <c r="P91" s="15"/>
+      <c r="Q91" s="15"/>
+      <c r="R91" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="S91" s="16">
+      <c r="S91" s="17">
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="15" t="s">
+    <row r="92" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="16" t="s">
         <v>677</v>
       </c>
       <c r="B92" s="1" t="s">
@@ -9378,8 +9382,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="18" t="s">
+    <row r="93" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="19" t="s">
         <v>1329</v>
       </c>
       <c r="B93" s="1" t="s">
@@ -9431,8 +9435,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="15" t="s">
+    <row r="94" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="16" t="s">
         <v>687</v>
       </c>
       <c r="B94" s="1" t="s">
@@ -9482,8 +9486,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="18" t="s">
+    <row r="95" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="19" t="s">
         <v>1338</v>
       </c>
       <c r="B95" s="1" t="s">
@@ -9533,8 +9537,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="15" t="s">
+    <row r="96" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="16" t="s">
         <v>693</v>
       </c>
       <c r="B96" s="1" t="s">
@@ -9582,8 +9586,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="23" t="s">
+    <row r="97" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="24" t="s">
         <v>703</v>
       </c>
       <c r="B97" s="1" t="s">
@@ -9631,8 +9635,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="23" t="s">
+    <row r="98" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="24" t="s">
         <v>707</v>
       </c>
       <c r="B98" s="1" t="s">
@@ -9682,8 +9686,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="23" t="s">
+    <row r="99" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="24" t="s">
         <v>712</v>
       </c>
       <c r="B99" s="1" t="s">
@@ -9733,8 +9737,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="23" t="s">
+    <row r="100" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="24" t="s">
         <v>717</v>
       </c>
       <c r="B100" s="1" t="s">
@@ -9784,104 +9788,104 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="15" t="s">
+    <row r="101" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="16" t="s">
         <v>723</v>
       </c>
-      <c r="B101" s="12" t="s">
+      <c r="B101" s="13" t="s">
         <v>678</v>
       </c>
-      <c r="C101" s="12" t="s">
+      <c r="C101" s="13" t="s">
         <v>724</v>
       </c>
-      <c r="D101" s="12"/>
-      <c r="E101" s="12"/>
-      <c r="F101" s="12" t="s">
+      <c r="D101" s="13"/>
+      <c r="E101" s="13"/>
+      <c r="F101" s="13" t="s">
         <v>725</v>
       </c>
-      <c r="G101" s="12" t="s">
+      <c r="G101" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="H101" s="12" t="s">
+      <c r="H101" s="13" t="s">
         <v>726</v>
       </c>
-      <c r="I101" s="12" t="s">
+      <c r="I101" s="13" t="s">
         <v>727</v>
       </c>
-      <c r="J101" s="12" t="s">
+      <c r="J101" s="13" t="s">
         <v>728</v>
       </c>
-      <c r="K101" s="12"/>
-      <c r="L101" s="13" t="s">
+      <c r="K101" s="13"/>
+      <c r="L101" s="14" t="s">
         <v>729</v>
       </c>
-      <c r="M101" s="13"/>
-      <c r="N101" s="13"/>
-      <c r="O101" s="12"/>
-      <c r="P101" s="12"/>
-      <c r="Q101" s="12"/>
-      <c r="R101" s="12" t="s">
+      <c r="M101" s="14"/>
+      <c r="N101" s="14"/>
+      <c r="O101" s="13"/>
+      <c r="P101" s="13"/>
+      <c r="Q101" s="13"/>
+      <c r="R101" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="S101" s="12">
+      <c r="S101" s="13">
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="18" t="s">
+    <row r="102" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="19" t="s">
         <v>1322</v>
       </c>
-      <c r="B102" s="12" t="s">
+      <c r="B102" s="13" t="s">
         <v>678</v>
       </c>
-      <c r="C102" s="12" t="s">
+      <c r="C102" s="13" t="s">
         <v>724</v>
       </c>
-      <c r="D102" s="12"/>
-      <c r="E102" s="12"/>
-      <c r="F102" s="12" t="s">
+      <c r="D102" s="13"/>
+      <c r="E102" s="13"/>
+      <c r="F102" s="13" t="s">
         <v>725</v>
       </c>
-      <c r="G102" s="12" t="s">
+      <c r="G102" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="H102" s="12" t="s">
+      <c r="H102" s="13" t="s">
         <v>1316</v>
       </c>
-      <c r="I102" s="12" t="s">
+      <c r="I102" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="J102" s="12" t="s">
+      <c r="J102" s="13" t="s">
         <v>1317</v>
       </c>
-      <c r="K102" s="12" t="s">
+      <c r="K102" s="13" t="s">
         <v>1318</v>
       </c>
       <c r="L102" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="M102" s="13"/>
-      <c r="N102" s="13" t="s">
+      <c r="M102" s="14"/>
+      <c r="N102" s="14" t="s">
         <v>1319</v>
       </c>
-      <c r="O102" s="12" t="s">
+      <c r="O102" s="13" t="s">
         <v>1320</v>
       </c>
-      <c r="P102" s="12" t="s">
+      <c r="P102" s="13" t="s">
         <v>1321</v>
       </c>
-      <c r="Q102" s="12">
+      <c r="Q102" s="13">
         <v>18</v>
       </c>
-      <c r="R102" s="12" t="s">
+      <c r="R102" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="S102" s="12">
+      <c r="S102" s="13">
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="15" t="s">
+    <row r="103" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="16" t="s">
         <v>730</v>
       </c>
       <c r="B103" s="1" t="s">
@@ -9933,8 +9937,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="15" t="s">
+    <row r="104" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="16" t="s">
         <v>740</v>
       </c>
       <c r="B104" s="1" t="s">
@@ -9982,8 +9986,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="15" t="s">
+    <row r="105" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="16" t="s">
         <v>745</v>
       </c>
       <c r="B105" s="1" t="s">
@@ -10035,8 +10039,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="15" t="s">
+    <row r="106" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="16" t="s">
         <v>751</v>
       </c>
       <c r="B106" s="1" t="s">
@@ -10088,8 +10092,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="15" t="s">
+    <row r="107" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="16" t="s">
         <v>757</v>
       </c>
       <c r="B107" s="1" t="s">
@@ -10141,8 +10145,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="15" t="s">
+    <row r="108" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="16" t="s">
         <v>767</v>
       </c>
       <c r="B108" s="1" t="s">
@@ -10194,8 +10198,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="15" t="s">
+    <row r="109" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="16" t="s">
         <v>770</v>
       </c>
       <c r="B109" s="1" t="s">
@@ -10247,8 +10251,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="15" t="s">
+    <row r="110" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="16" t="s">
         <v>778</v>
       </c>
       <c r="B110" s="1" t="s">
@@ -10300,8 +10304,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="15" t="s">
+    <row r="111" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="16" t="s">
         <v>784</v>
       </c>
       <c r="B111" s="1" t="s">
@@ -10353,8 +10357,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="15" t="s">
+    <row r="112" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="16" t="s">
         <v>791</v>
       </c>
       <c r="B112" s="1" t="s">
@@ -10406,8 +10410,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="15" t="s">
+    <row r="113" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="16" t="s">
         <v>798</v>
       </c>
       <c r="B113" s="7" t="s">
@@ -10455,8 +10459,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="15" t="s">
+    <row r="114" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="16" t="s">
         <v>808</v>
       </c>
       <c r="B114" s="10" t="s">
@@ -10500,8 +10504,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="15" t="s">
+    <row r="115" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="16" t="s">
         <v>811</v>
       </c>
       <c r="B115" s="7" t="s">
@@ -10545,8 +10549,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="15" t="s">
+    <row r="116" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="16" t="s">
         <v>819</v>
       </c>
       <c r="B116" s="10" t="s">
@@ -10594,8 +10598,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="15" t="s">
+    <row r="117" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="16" t="s">
         <v>823</v>
       </c>
       <c r="B117" s="7" t="s">
@@ -10647,8 +10651,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="15" t="s">
+    <row r="118" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="16" t="s">
         <v>833</v>
       </c>
       <c r="B118" s="10" t="s">
@@ -10702,8 +10706,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="15" t="s">
+    <row r="119" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="16" t="s">
         <v>837</v>
       </c>
       <c r="B119" s="7" t="s">
@@ -10749,8 +10753,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:19" s="27" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="15" t="s">
+    <row r="120" spans="1:19" s="28" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="16" t="s">
         <v>844</v>
       </c>
       <c r="B120" s="10" t="s">
@@ -10798,8 +10802,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="15" t="s">
+    <row r="121" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="16" t="s">
         <v>849</v>
       </c>
       <c r="B121" s="7" t="s">
@@ -10849,8 +10853,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="122" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="18" t="s">
+    <row r="122" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="19" t="s">
         <v>1266</v>
       </c>
       <c r="B122" s="10" t="s">
@@ -10902,8 +10906,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="15" t="s">
+    <row r="123" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="16" t="s">
         <v>863</v>
       </c>
       <c r="B123" s="7" t="s">
@@ -10947,8 +10951,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="15" t="s">
+    <row r="124" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="16" t="s">
         <v>872</v>
       </c>
       <c r="B124" s="10" t="s">
@@ -10992,8 +10996,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="15" t="s">
+    <row r="125" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="16" t="s">
         <v>875</v>
       </c>
       <c r="B125" s="1" t="s">
@@ -11033,8 +11037,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="18" t="s">
+    <row r="126" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="19" t="s">
         <v>1280</v>
       </c>
       <c r="B126" s="1" t="s">
@@ -11075,931 +11079,931 @@
       <c r="Q126" s="1">
         <v>91</v>
       </c>
-      <c r="R126" s="16" t="s">
+      <c r="R126" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S126" s="16">
+      <c r="S126" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="18" t="s">
+    <row r="127" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="19" t="s">
         <v>1290</v>
       </c>
-      <c r="B127" s="12" t="s">
+      <c r="B127" s="13" t="s">
         <v>884</v>
       </c>
-      <c r="C127" s="12" t="s">
+      <c r="C127" s="13" t="s">
         <v>885</v>
       </c>
-      <c r="D127" s="12"/>
-      <c r="E127" s="12"/>
-      <c r="F127" s="12" t="s">
+      <c r="D127" s="13"/>
+      <c r="E127" s="13"/>
+      <c r="F127" s="13" t="s">
         <v>886</v>
       </c>
-      <c r="G127" s="12" t="s">
+      <c r="G127" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="H127" s="12" t="s">
+      <c r="H127" s="13" t="s">
         <v>897</v>
       </c>
-      <c r="I127" s="12" t="s">
+      <c r="I127" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="J127" s="12" t="s">
+      <c r="J127" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="K127" s="12" t="s">
+      <c r="K127" s="13" t="s">
         <v>898</v>
       </c>
-      <c r="L127" s="13" t="s">
+      <c r="L127" s="14" t="s">
         <v>1281</v>
       </c>
-      <c r="M127" s="13"/>
-      <c r="N127" s="13" t="s">
+      <c r="M127" s="14"/>
+      <c r="N127" s="14" t="s">
         <v>899</v>
       </c>
-      <c r="O127" s="12" t="s">
+      <c r="O127" s="13" t="s">
         <v>1282</v>
       </c>
-      <c r="P127" s="12" t="s">
+      <c r="P127" s="13" t="s">
         <v>1283</v>
       </c>
-      <c r="Q127" s="12">
+      <c r="Q127" s="13">
         <v>322</v>
       </c>
-      <c r="R127" s="16" t="s">
+      <c r="R127" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S127" s="16">
+      <c r="S127" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="15" t="s">
+    <row r="128" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="16" t="s">
         <v>883</v>
       </c>
-      <c r="B128" s="12" t="s">
+      <c r="B128" s="13" t="s">
         <v>884</v>
       </c>
-      <c r="C128" s="12" t="s">
+      <c r="C128" s="13" t="s">
         <v>885</v>
       </c>
-      <c r="D128" s="12"/>
-      <c r="E128" s="12"/>
-      <c r="F128" s="12" t="s">
+      <c r="D128" s="13"/>
+      <c r="E128" s="13"/>
+      <c r="F128" s="13" t="s">
         <v>886</v>
       </c>
-      <c r="G128" s="12" t="s">
+      <c r="G128" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="H128" s="12" t="s">
+      <c r="H128" s="13" t="s">
         <v>887</v>
       </c>
-      <c r="I128" s="12" t="s">
+      <c r="I128" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="J128" s="12" t="s">
+      <c r="J128" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="K128" s="12" t="s">
+      <c r="K128" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="L128" s="13" t="s">
+      <c r="L128" s="14" t="s">
         <v>1284</v>
       </c>
-      <c r="M128" s="13"/>
-      <c r="N128" s="13" t="s">
+      <c r="M128" s="14"/>
+      <c r="N128" s="14" t="s">
         <v>1285</v>
       </c>
-      <c r="O128" s="12" t="s">
+      <c r="O128" s="13" t="s">
         <v>1286</v>
       </c>
-      <c r="P128" s="12">
+      <c r="P128" s="13">
         <v>182</v>
       </c>
-      <c r="Q128" s="12">
+      <c r="Q128" s="13">
         <v>323</v>
       </c>
-      <c r="R128" s="16" t="s">
+      <c r="R128" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S128" s="16">
+      <c r="S128" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:19" s="26" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="18" t="s">
+    <row r="129" spans="1:19" s="27" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="19" t="s">
         <v>1292</v>
       </c>
-      <c r="B129" s="12" t="s">
+      <c r="B129" s="13" t="s">
         <v>884</v>
       </c>
-      <c r="C129" s="12" t="s">
+      <c r="C129" s="13" t="s">
         <v>885</v>
       </c>
-      <c r="D129" s="12"/>
-      <c r="E129" s="12"/>
-      <c r="F129" s="12" t="s">
+      <c r="D129" s="13"/>
+      <c r="E129" s="13"/>
+      <c r="F129" s="13" t="s">
         <v>886</v>
       </c>
-      <c r="G129" s="12" t="s">
+      <c r="G129" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="H129" s="12" t="s">
+      <c r="H129" s="13" t="s">
         <v>1287</v>
       </c>
-      <c r="I129" s="12" t="s">
+      <c r="I129" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="J129" s="12" t="s">
+      <c r="J129" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="K129" s="12" t="s">
+      <c r="K129" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="L129" s="13" t="s">
+      <c r="L129" s="14" t="s">
         <v>1291</v>
       </c>
-      <c r="M129" s="13"/>
-      <c r="N129" s="13" t="s">
+      <c r="M129" s="14"/>
+      <c r="N129" s="14" t="s">
         <v>1288</v>
       </c>
-      <c r="O129" s="12" t="s">
+      <c r="O129" s="13" t="s">
         <v>1289</v>
       </c>
-      <c r="P129" s="12">
+      <c r="P129" s="13">
         <v>182</v>
       </c>
-      <c r="Q129" s="12">
+      <c r="Q129" s="13">
         <v>317</v>
       </c>
-      <c r="R129" s="16" t="s">
+      <c r="R129" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S129" s="16">
+      <c r="S129" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="15" t="s">
+    <row r="130" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="16" t="s">
         <v>889</v>
       </c>
-      <c r="B130" s="12" t="s">
+      <c r="B130" s="13" t="s">
         <v>884</v>
       </c>
-      <c r="C130" s="12" t="s">
+      <c r="C130" s="13" t="s">
         <v>885</v>
       </c>
-      <c r="D130" s="12"/>
-      <c r="E130" s="12"/>
-      <c r="F130" s="12" t="s">
+      <c r="D130" s="13"/>
+      <c r="E130" s="13"/>
+      <c r="F130" s="13" t="s">
         <v>886</v>
       </c>
-      <c r="G130" s="12" t="s">
+      <c r="G130" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="H130" s="16" t="s">
+      <c r="H130" s="17" t="s">
         <v>890</v>
       </c>
-      <c r="I130" s="16" t="s">
+      <c r="I130" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="J130" s="16" t="s">
+      <c r="J130" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="K130" s="16" t="s">
+      <c r="K130" s="17" t="s">
         <v>891</v>
       </c>
-      <c r="L130" s="13" t="s">
+      <c r="L130" s="14" t="s">
         <v>892</v>
       </c>
-      <c r="M130" s="16"/>
-      <c r="N130" s="16" t="s">
+      <c r="M130" s="17"/>
+      <c r="N130" s="17" t="s">
         <v>893</v>
       </c>
-      <c r="O130" s="16" t="s">
+      <c r="O130" s="17" t="s">
         <v>894</v>
       </c>
-      <c r="P130" s="16" t="s">
+      <c r="P130" s="17" t="s">
         <v>895</v>
       </c>
-      <c r="Q130" s="16" t="s">
+      <c r="Q130" s="17" t="s">
         <v>896</v>
       </c>
-      <c r="R130" s="16" t="s">
+      <c r="R130" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S130" s="16">
+      <c r="S130" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="15" t="s">
+    <row r="131" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="16" t="s">
         <v>900</v>
       </c>
-      <c r="B131" s="12" t="s">
+      <c r="B131" s="13" t="s">
         <v>884</v>
       </c>
-      <c r="C131" s="12" t="s">
+      <c r="C131" s="13" t="s">
         <v>885</v>
       </c>
-      <c r="D131" s="12"/>
-      <c r="E131" s="12"/>
-      <c r="F131" s="12" t="s">
+      <c r="D131" s="13"/>
+      <c r="E131" s="13"/>
+      <c r="F131" s="13" t="s">
         <v>886</v>
       </c>
-      <c r="G131" s="12" t="s">
+      <c r="G131" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="H131" s="16" t="s">
+      <c r="H131" s="17" t="s">
         <v>588</v>
       </c>
-      <c r="I131" s="16" t="s">
+      <c r="I131" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="J131" s="16" t="s">
+      <c r="J131" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="K131" s="16" t="s">
+      <c r="K131" s="17" t="s">
         <v>898</v>
       </c>
-      <c r="L131" s="13" t="s">
+      <c r="L131" s="14" t="s">
         <v>901</v>
       </c>
-      <c r="M131" s="17"/>
-      <c r="N131" s="16" t="s">
+      <c r="M131" s="18"/>
+      <c r="N131" s="17" t="s">
         <v>285</v>
       </c>
-      <c r="O131" s="16" t="s">
+      <c r="O131" s="17" t="s">
         <v>459</v>
       </c>
-      <c r="P131" s="16" t="s">
+      <c r="P131" s="17" t="s">
         <v>902</v>
       </c>
-      <c r="Q131" s="16" t="s">
+      <c r="Q131" s="17" t="s">
         <v>903</v>
       </c>
-      <c r="R131" s="16" t="s">
+      <c r="R131" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S131" s="16">
+      <c r="S131" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="15" t="s">
+    <row r="132" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="16" t="s">
         <v>904</v>
       </c>
-      <c r="B132" s="12" t="s">
+      <c r="B132" s="13" t="s">
         <v>905</v>
       </c>
-      <c r="C132" s="12" t="s">
+      <c r="C132" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="D132" s="12"/>
-      <c r="E132" s="12"/>
-      <c r="F132" s="12" t="s">
+      <c r="D132" s="13"/>
+      <c r="E132" s="13"/>
+      <c r="F132" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="G132" s="12" t="s">
+      <c r="G132" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="H132" s="12" t="s">
+      <c r="H132" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="I132" s="12" t="s">
+      <c r="I132" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="J132" s="12" t="s">
+      <c r="J132" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="K132" s="12"/>
-      <c r="L132" s="13" t="s">
+      <c r="K132" s="13"/>
+      <c r="L132" s="14" t="s">
         <v>907</v>
       </c>
-      <c r="M132" s="13"/>
-      <c r="N132" s="13" t="s">
+      <c r="M132" s="14"/>
+      <c r="N132" s="14" t="s">
         <v>908</v>
       </c>
-      <c r="O132" s="12" t="s">
+      <c r="O132" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="P132" s="12" t="s">
+      <c r="P132" s="13" t="s">
         <v>909</v>
       </c>
-      <c r="Q132" s="12" t="s">
+      <c r="Q132" s="13" t="s">
         <v>910</v>
       </c>
-      <c r="R132" s="12" t="s">
+      <c r="R132" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="S132" s="12">
+      <c r="S132" s="13">
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="15" t="s">
+    <row r="133" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="16" t="s">
         <v>911</v>
       </c>
-      <c r="B133" s="16" t="s">
+      <c r="B133" s="17" t="s">
         <v>905</v>
       </c>
-      <c r="C133" s="16" t="s">
+      <c r="C133" s="17" t="s">
         <v>906</v>
       </c>
-      <c r="D133" s="14"/>
-      <c r="E133" s="14"/>
-      <c r="F133" s="12" t="s">
+      <c r="D133" s="15"/>
+      <c r="E133" s="15"/>
+      <c r="F133" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="G133" s="12" t="s">
+      <c r="G133" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="H133" s="16" t="s">
+      <c r="H133" s="17" t="s">
         <v>912</v>
       </c>
-      <c r="I133" s="16" t="s">
+      <c r="I133" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="J133" s="16" t="s">
+      <c r="J133" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="K133" s="17"/>
-      <c r="L133" s="13" t="s">
+      <c r="K133" s="18"/>
+      <c r="L133" s="14" t="s">
         <v>913</v>
       </c>
-      <c r="M133" s="17"/>
-      <c r="N133" s="17"/>
-      <c r="O133" s="16" t="s">
+      <c r="M133" s="18"/>
+      <c r="N133" s="18"/>
+      <c r="O133" s="17" t="s">
         <v>345</v>
       </c>
-      <c r="P133" s="17"/>
-      <c r="Q133" s="17"/>
-      <c r="R133" s="16" t="s">
+      <c r="P133" s="18"/>
+      <c r="Q133" s="18"/>
+      <c r="R133" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="S133" s="16">
+      <c r="S133" s="17">
         <v>3</v>
       </c>
     </row>
-    <row r="134" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="15" t="s">
+    <row r="134" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="16" t="s">
         <v>914</v>
       </c>
-      <c r="B134" s="12" t="s">
+      <c r="B134" s="13" t="s">
         <v>915</v>
       </c>
-      <c r="C134" s="12" t="s">
+      <c r="C134" s="13" t="s">
         <v>916</v>
       </c>
-      <c r="D134" s="12"/>
-      <c r="E134" s="12"/>
-      <c r="F134" s="12" t="s">
+      <c r="D134" s="13"/>
+      <c r="E134" s="13"/>
+      <c r="F134" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="G134" s="12" t="s">
+      <c r="G134" s="13" t="s">
         <v>669</v>
       </c>
-      <c r="H134" s="12" t="s">
+      <c r="H134" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="I134" s="12" t="s">
+      <c r="I134" s="13" t="s">
         <v>917</v>
       </c>
-      <c r="J134" s="12" t="s">
+      <c r="J134" s="13" t="s">
         <v>918</v>
       </c>
-      <c r="K134" s="12" t="s">
+      <c r="K134" s="13" t="s">
         <v>919</v>
       </c>
-      <c r="L134" s="13" t="s">
+      <c r="L134" s="14" t="s">
         <v>920</v>
       </c>
-      <c r="M134" s="13"/>
-      <c r="N134" s="13" t="s">
+      <c r="M134" s="14"/>
+      <c r="N134" s="14" t="s">
         <v>921</v>
       </c>
-      <c r="O134" s="12" t="s">
+      <c r="O134" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="P134" s="12" t="s">
+      <c r="P134" s="13" t="s">
         <v>922</v>
       </c>
-      <c r="Q134" s="12" t="s">
+      <c r="Q134" s="13" t="s">
         <v>923</v>
       </c>
-      <c r="R134" s="12" t="s">
+      <c r="R134" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="S134" s="12">
+      <c r="S134" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="15" t="s">
+    <row r="135" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="16" t="s">
         <v>924</v>
       </c>
-      <c r="B135" s="16" t="s">
+      <c r="B135" s="17" t="s">
         <v>915</v>
       </c>
-      <c r="C135" s="16" t="s">
+      <c r="C135" s="17" t="s">
         <v>916</v>
       </c>
-      <c r="D135" s="14"/>
-      <c r="E135" s="14"/>
-      <c r="F135" s="12" t="s">
+      <c r="D135" s="15"/>
+      <c r="E135" s="15"/>
+      <c r="F135" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="G135" s="12" t="s">
+      <c r="G135" s="13" t="s">
         <v>669</v>
       </c>
-      <c r="H135" s="16" t="s">
+      <c r="H135" s="17" t="s">
         <v>925</v>
       </c>
-      <c r="I135" s="16" t="s">
+      <c r="I135" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="J135" s="16" t="s">
+      <c r="J135" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="K135" s="16" t="s">
+      <c r="K135" s="17" t="s">
         <v>926</v>
       </c>
-      <c r="L135" s="13" t="s">
+      <c r="L135" s="14" t="s">
         <v>927</v>
       </c>
-      <c r="M135" s="17"/>
-      <c r="N135" s="16" t="s">
+      <c r="M135" s="18"/>
+      <c r="N135" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="O135" s="16" t="s">
+      <c r="O135" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="P135" s="16" t="s">
+      <c r="P135" s="17" t="s">
         <v>928</v>
       </c>
-      <c r="Q135" s="16" t="s">
+      <c r="Q135" s="17" t="s">
         <v>929</v>
       </c>
-      <c r="R135" s="16" t="s">
+      <c r="R135" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S135" s="16">
+      <c r="S135" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="15" t="s">
+    <row r="136" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="16" t="s">
         <v>930</v>
       </c>
-      <c r="B136" s="16" t="s">
+      <c r="B136" s="17" t="s">
         <v>915</v>
       </c>
-      <c r="C136" s="16" t="s">
+      <c r="C136" s="17" t="s">
         <v>916</v>
       </c>
-      <c r="D136" s="14"/>
-      <c r="E136" s="14"/>
-      <c r="F136" s="12" t="s">
+      <c r="D136" s="15"/>
+      <c r="E136" s="15"/>
+      <c r="F136" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="G136" s="12" t="s">
+      <c r="G136" s="13" t="s">
         <v>669</v>
       </c>
-      <c r="H136" s="16" t="s">
+      <c r="H136" s="17" t="s">
         <v>931</v>
       </c>
-      <c r="I136" s="16" t="s">
+      <c r="I136" s="17" t="s">
         <v>932</v>
       </c>
-      <c r="J136" s="16" t="s">
+      <c r="J136" s="17" t="s">
         <v>933</v>
       </c>
-      <c r="K136" s="16" t="s">
+      <c r="K136" s="17" t="s">
         <v>934</v>
       </c>
-      <c r="L136" s="13" t="s">
+      <c r="L136" s="14" t="s">
         <v>935</v>
       </c>
-      <c r="M136" s="13"/>
-      <c r="N136" s="16" t="s">
+      <c r="M136" s="14"/>
+      <c r="N136" s="17" t="s">
         <v>936</v>
       </c>
-      <c r="O136" s="16" t="s">
+      <c r="O136" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="P136" s="16" t="s">
+      <c r="P136" s="17" t="s">
         <v>937</v>
       </c>
-      <c r="Q136" s="16" t="s">
+      <c r="Q136" s="17" t="s">
         <v>938</v>
       </c>
-      <c r="R136" s="16" t="s">
+      <c r="R136" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S136" s="16">
+      <c r="S136" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="15" t="s">
+    <row r="137" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="16" t="s">
         <v>939</v>
       </c>
-      <c r="B137" s="16" t="s">
+      <c r="B137" s="17" t="s">
         <v>915</v>
       </c>
-      <c r="C137" s="16" t="s">
+      <c r="C137" s="17" t="s">
         <v>916</v>
       </c>
-      <c r="D137" s="14"/>
-      <c r="E137" s="14"/>
-      <c r="F137" s="12" t="s">
+      <c r="D137" s="15"/>
+      <c r="E137" s="15"/>
+      <c r="F137" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="G137" s="12" t="s">
+      <c r="G137" s="13" t="s">
         <v>669</v>
       </c>
-      <c r="H137" s="16" t="s">
+      <c r="H137" s="17" t="s">
         <v>940</v>
       </c>
-      <c r="I137" s="16" t="s">
+      <c r="I137" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="J137" s="16" t="s">
+      <c r="J137" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="K137" s="16" t="s">
+      <c r="K137" s="17" t="s">
         <v>941</v>
       </c>
-      <c r="L137" s="13" t="s">
+      <c r="L137" s="14" t="s">
         <v>942</v>
       </c>
-      <c r="M137" s="17"/>
-      <c r="N137" s="16" t="s">
+      <c r="M137" s="18"/>
+      <c r="N137" s="17" t="s">
         <v>943</v>
       </c>
-      <c r="O137" s="16" t="s">
+      <c r="O137" s="17" t="s">
         <v>944</v>
       </c>
-      <c r="P137" s="16" t="s">
+      <c r="P137" s="17" t="s">
         <v>945</v>
       </c>
-      <c r="Q137" s="16" t="s">
+      <c r="Q137" s="17" t="s">
         <v>946</v>
       </c>
-      <c r="R137" s="16" t="s">
+      <c r="R137" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S137" s="16">
+      <c r="S137" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="15" t="s">
+    <row r="138" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="16" t="s">
         <v>947</v>
       </c>
-      <c r="B138" s="16" t="s">
+      <c r="B138" s="17" t="s">
         <v>915</v>
       </c>
-      <c r="C138" s="16" t="s">
+      <c r="C138" s="17" t="s">
         <v>916</v>
       </c>
-      <c r="D138" s="14"/>
-      <c r="E138" s="14"/>
-      <c r="F138" s="12" t="s">
+      <c r="D138" s="15"/>
+      <c r="E138" s="15"/>
+      <c r="F138" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="G138" s="12" t="s">
+      <c r="G138" s="13" t="s">
         <v>669</v>
       </c>
-      <c r="H138" s="16" t="s">
+      <c r="H138" s="17" t="s">
         <v>948</v>
       </c>
-      <c r="I138" s="16" t="s">
+      <c r="I138" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="J138" s="16" t="s">
+      <c r="J138" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="K138" s="16" t="s">
+      <c r="K138" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="L138" s="13" t="s">
+      <c r="L138" s="14" t="s">
         <v>949</v>
       </c>
-      <c r="M138" s="17"/>
-      <c r="N138" s="16" t="s">
+      <c r="M138" s="18"/>
+      <c r="N138" s="17" t="s">
         <v>950</v>
       </c>
-      <c r="O138" s="16" t="s">
+      <c r="O138" s="17" t="s">
         <v>951</v>
       </c>
-      <c r="P138" s="16" t="s">
+      <c r="P138" s="17" t="s">
         <v>952</v>
       </c>
-      <c r="Q138" s="16" t="s">
+      <c r="Q138" s="17" t="s">
         <v>953</v>
       </c>
-      <c r="R138" s="16" t="s">
+      <c r="R138" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S138" s="16">
+      <c r="S138" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="15" t="s">
+    <row r="139" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="16" t="s">
         <v>954</v>
       </c>
-      <c r="B139" s="12" t="s">
+      <c r="B139" s="13" t="s">
         <v>915</v>
       </c>
-      <c r="C139" s="12" t="s">
+      <c r="C139" s="13" t="s">
         <v>955</v>
       </c>
-      <c r="D139" s="12"/>
-      <c r="E139" s="12"/>
-      <c r="F139" s="12" t="s">
+      <c r="D139" s="13"/>
+      <c r="E139" s="13"/>
+      <c r="F139" s="13" t="s">
         <v>956</v>
       </c>
-      <c r="G139" s="12" t="s">
+      <c r="G139" s="13" t="s">
         <v>957</v>
       </c>
-      <c r="H139" s="12" t="s">
+      <c r="H139" s="13" t="s">
         <v>457</v>
       </c>
-      <c r="I139" s="12"/>
-      <c r="J139" s="12" t="s">
+      <c r="I139" s="13"/>
+      <c r="J139" s="13" t="s">
         <v>958</v>
       </c>
-      <c r="K139" s="12"/>
-      <c r="L139" s="13" t="s">
+      <c r="K139" s="13"/>
+      <c r="L139" s="14" t="s">
         <v>959</v>
       </c>
-      <c r="M139" s="13"/>
-      <c r="N139" s="13" t="s">
+      <c r="M139" s="14"/>
+      <c r="N139" s="14" t="s">
         <v>960</v>
       </c>
-      <c r="O139" s="12" t="s">
+      <c r="O139" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="P139" s="12" t="s">
+      <c r="P139" s="13" t="s">
         <v>961</v>
       </c>
-      <c r="Q139" s="12" t="s">
+      <c r="Q139" s="13" t="s">
         <v>962</v>
       </c>
-      <c r="R139" s="12" t="s">
+      <c r="R139" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="S139" s="12">
+      <c r="S139" s="13">
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="15" t="s">
+    <row r="140" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="16" t="s">
         <v>963</v>
       </c>
-      <c r="B140" s="16" t="s">
+      <c r="B140" s="17" t="s">
         <v>915</v>
       </c>
-      <c r="C140" s="16" t="s">
+      <c r="C140" s="17" t="s">
         <v>955</v>
       </c>
-      <c r="D140" s="14"/>
-      <c r="E140" s="14"/>
-      <c r="F140" s="12" t="s">
+      <c r="D140" s="15"/>
+      <c r="E140" s="15"/>
+      <c r="F140" s="13" t="s">
         <v>956</v>
       </c>
-      <c r="G140" s="12" t="s">
+      <c r="G140" s="13" t="s">
         <v>957</v>
       </c>
-      <c r="H140" s="16" t="s">
+      <c r="H140" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="I140" s="16" t="s">
+      <c r="I140" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="J140" s="16" t="s">
+      <c r="J140" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="K140" s="17"/>
-      <c r="L140" s="13" t="s">
+      <c r="K140" s="18"/>
+      <c r="L140" s="14" t="s">
         <v>964</v>
       </c>
-      <c r="M140" s="17"/>
-      <c r="N140" s="17"/>
-      <c r="O140" s="16" t="s">
+      <c r="M140" s="18"/>
+      <c r="N140" s="18"/>
+      <c r="O140" s="17" t="s">
         <v>965</v>
       </c>
-      <c r="P140" s="17"/>
-      <c r="Q140" s="17"/>
-      <c r="R140" s="16" t="s">
+      <c r="P140" s="18"/>
+      <c r="Q140" s="18"/>
+      <c r="R140" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S140" s="16">
+      <c r="S140" s="17">
         <v>3</v>
       </c>
     </row>
-    <row r="141" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="15" t="s">
+    <row r="141" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="16" t="s">
         <v>966</v>
       </c>
-      <c r="B141" s="12" t="s">
+      <c r="B141" s="13" t="s">
         <v>967</v>
       </c>
-      <c r="C141" s="12" t="s">
+      <c r="C141" s="13" t="s">
         <v>968</v>
       </c>
-      <c r="D141" s="12" t="s">
+      <c r="D141" s="13" t="s">
         <v>969</v>
       </c>
-      <c r="E141" s="12"/>
-      <c r="F141" s="12" t="s">
+      <c r="E141" s="13"/>
+      <c r="F141" s="13" t="s">
         <v>970</v>
       </c>
-      <c r="G141" s="12" t="s">
+      <c r="G141" s="13" t="s">
         <v>486</v>
       </c>
-      <c r="H141" s="12" t="s">
+      <c r="H141" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="I141" s="12" t="s">
+      <c r="I141" s="13" t="s">
         <v>854</v>
       </c>
-      <c r="J141" s="12" t="s">
+      <c r="J141" s="13" t="s">
         <v>971</v>
       </c>
-      <c r="K141" s="12"/>
-      <c r="L141" s="13" t="s">
+      <c r="K141" s="13"/>
+      <c r="L141" s="14" t="s">
         <v>972</v>
       </c>
-      <c r="M141" s="13"/>
-      <c r="N141" s="13" t="s">
+      <c r="M141" s="14"/>
+      <c r="N141" s="14" t="s">
         <v>973</v>
       </c>
-      <c r="O141" s="12" t="s">
+      <c r="O141" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="P141" s="12" t="s">
+      <c r="P141" s="13" t="s">
         <v>974</v>
       </c>
-      <c r="Q141" s="12" t="s">
+      <c r="Q141" s="13" t="s">
         <v>975</v>
       </c>
-      <c r="R141" s="12" t="s">
+      <c r="R141" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="S141" s="12">
+      <c r="S141" s="13">
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="15" t="s">
+    <row r="142" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="16" t="s">
         <v>976</v>
       </c>
-      <c r="B142" s="16" t="s">
+      <c r="B142" s="17" t="s">
         <v>967</v>
       </c>
-      <c r="C142" s="16" t="s">
+      <c r="C142" s="17" t="s">
         <v>968</v>
       </c>
-      <c r="D142" s="14"/>
-      <c r="E142" s="14"/>
-      <c r="F142" s="12" t="s">
+      <c r="D142" s="15"/>
+      <c r="E142" s="15"/>
+      <c r="F142" s="13" t="s">
         <v>970</v>
       </c>
-      <c r="G142" s="12" t="s">
+      <c r="G142" s="13" t="s">
         <v>486</v>
       </c>
-      <c r="H142" s="16" t="s">
+      <c r="H142" s="17" t="s">
         <v>315</v>
       </c>
-      <c r="I142" s="16" t="s">
+      <c r="I142" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="J142" s="16" t="s">
+      <c r="J142" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="K142" s="17"/>
-      <c r="L142" s="13" t="s">
+      <c r="K142" s="18"/>
+      <c r="L142" s="14" t="s">
         <v>977</v>
       </c>
-      <c r="M142" s="17"/>
-      <c r="N142" s="17"/>
-      <c r="O142" s="16" t="s">
+      <c r="M142" s="18"/>
+      <c r="N142" s="18"/>
+      <c r="O142" s="17" t="s">
         <v>345</v>
       </c>
-      <c r="P142" s="16" t="s">
+      <c r="P142" s="17" t="s">
         <v>978</v>
       </c>
-      <c r="Q142" s="16" t="s">
+      <c r="Q142" s="17" t="s">
         <v>568</v>
       </c>
-      <c r="R142" s="16" t="s">
+      <c r="R142" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S142" s="16">
+      <c r="S142" s="17">
         <v>3</v>
       </c>
     </row>
-    <row r="143" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="15" t="s">
+    <row r="143" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="16" t="s">
         <v>979</v>
       </c>
-      <c r="B143" s="12" t="s">
+      <c r="B143" s="13" t="s">
         <v>980</v>
       </c>
-      <c r="C143" s="12" t="s">
+      <c r="C143" s="13" t="s">
         <v>981</v>
       </c>
-      <c r="D143" s="12" t="s">
+      <c r="D143" s="13" t="s">
         <v>982</v>
       </c>
-      <c r="E143" s="12" t="s">
+      <c r="E143" s="13" t="s">
         <v>982</v>
       </c>
-      <c r="F143" s="12" t="s">
+      <c r="F143" s="13" t="s">
         <v>983</v>
       </c>
-      <c r="G143" s="12" t="s">
+      <c r="G143" s="13" t="s">
         <v>984</v>
       </c>
-      <c r="H143" s="12" t="s">
+      <c r="H143" s="13" t="s">
         <v>985</v>
       </c>
-      <c r="I143" s="12" t="s">
+      <c r="I143" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="J143" s="12" t="s">
+      <c r="J143" s="13" t="s">
         <v>986</v>
       </c>
-      <c r="K143" s="12"/>
-      <c r="L143" s="13" t="s">
+      <c r="K143" s="13"/>
+      <c r="L143" s="14" t="s">
         <v>987</v>
       </c>
-      <c r="M143" s="13"/>
-      <c r="N143" s="13"/>
-      <c r="O143" s="12" t="s">
+      <c r="M143" s="14"/>
+      <c r="N143" s="14"/>
+      <c r="O143" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="P143" s="12"/>
-      <c r="Q143" s="12"/>
-      <c r="R143" s="12" t="s">
+      <c r="P143" s="13"/>
+      <c r="Q143" s="13"/>
+      <c r="R143" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="S143" s="12">
+      <c r="S143" s="13">
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="15" t="s">
+    <row r="144" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="16" t="s">
         <v>988</v>
       </c>
-      <c r="B144" s="16" t="s">
+      <c r="B144" s="17" t="s">
         <v>980</v>
       </c>
-      <c r="C144" s="16" t="s">
+      <c r="C144" s="17" t="s">
         <v>981</v>
       </c>
-      <c r="D144" s="14"/>
-      <c r="E144" s="14"/>
-      <c r="F144" s="12" t="s">
+      <c r="D144" s="15"/>
+      <c r="E144" s="15"/>
+      <c r="F144" s="13" t="s">
         <v>983</v>
       </c>
-      <c r="G144" s="12" t="s">
+      <c r="G144" s="13" t="s">
         <v>984</v>
       </c>
-      <c r="H144" s="16" t="s">
+      <c r="H144" s="17" t="s">
         <v>989</v>
       </c>
-      <c r="I144" s="16" t="s">
+      <c r="I144" s="17" t="s">
         <v>840</v>
       </c>
-      <c r="J144" s="16" t="s">
+      <c r="J144" s="17" t="s">
         <v>990</v>
       </c>
-      <c r="K144" s="17"/>
-      <c r="L144" s="13" t="s">
+      <c r="K144" s="18"/>
+      <c r="L144" s="14" t="s">
         <v>991</v>
       </c>
-      <c r="M144" s="17"/>
-      <c r="N144" s="17"/>
-      <c r="O144" s="16" t="s">
+      <c r="M144" s="18"/>
+      <c r="N144" s="18"/>
+      <c r="O144" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="P144" s="17"/>
-      <c r="Q144" s="17"/>
-      <c r="R144" s="16" t="s">
+      <c r="P144" s="18"/>
+      <c r="Q144" s="18"/>
+      <c r="R144" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S144" s="16">
+      <c r="S144" s="17">
         <v>3</v>
       </c>
     </row>
-    <row r="145" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="15" t="s">
+    <row r="145" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="16" t="s">
         <v>992</v>
       </c>
       <c r="B145" s="7" t="s">
@@ -12047,8 +12051,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="15" t="s">
+    <row r="146" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="16" t="s">
         <v>998</v>
       </c>
       <c r="B146" s="7" t="s">
@@ -12096,8 +12100,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="15" t="s">
+    <row r="147" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="16" t="s">
         <v>1007</v>
       </c>
       <c r="B147" s="7" t="s">
@@ -12145,8 +12149,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="15" t="s">
+    <row r="148" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="16" t="s">
         <v>1011</v>
       </c>
       <c r="B148" s="7" t="s">
@@ -12194,8 +12198,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="15" t="s">
+    <row r="149" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="16" t="s">
         <v>1017</v>
       </c>
       <c r="B149" s="7" t="s">
@@ -12243,8 +12247,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="15" t="s">
+    <row r="150" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="16" t="s">
         <v>1021</v>
       </c>
       <c r="B150" s="7" t="s">
@@ -12294,8 +12298,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="15" t="s">
+    <row r="151" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="16" t="s">
         <v>1029</v>
       </c>
       <c r="B151" s="7" t="s">
@@ -12343,8 +12347,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="15" t="s">
+    <row r="152" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="16" t="s">
         <v>1033</v>
       </c>
       <c r="B152" s="7" t="s">
@@ -12392,8 +12396,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="15" t="s">
+    <row r="153" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="16" t="s">
         <v>1038</v>
       </c>
       <c r="B153" s="7" t="s">
@@ -12441,8 +12445,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="23" t="s">
+    <row r="154" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="12" t="s">
         <v>1040</v>
       </c>
       <c r="B154" s="7" t="s">
@@ -12481,7 +12485,7 @@
         <v>1001</v>
       </c>
       <c r="Q154" s="7" t="s">
-        <v>1002</v>
+        <v>1340</v>
       </c>
       <c r="R154" s="7" t="s">
         <v>190</v>
@@ -12490,8 +12494,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:19" s="26" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="15" t="s">
+    <row r="155" spans="1:19" s="27" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="16" t="s">
         <v>1003</v>
       </c>
       <c r="B155" s="7" t="s">
@@ -12539,124 +12543,124 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="18" t="s">
+    <row r="156" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="19" t="s">
         <v>1314</v>
       </c>
-      <c r="B156" s="12" t="s">
+      <c r="B156" s="13" t="s">
         <v>1041</v>
       </c>
-      <c r="C156" s="12" t="s">
+      <c r="C156" s="13" t="s">
         <v>839</v>
       </c>
-      <c r="D156" s="12" t="s">
+      <c r="D156" s="13" t="s">
         <v>1042</v>
       </c>
-      <c r="E156" s="12" t="s">
+      <c r="E156" s="13" t="s">
         <v>1042</v>
       </c>
-      <c r="F156" s="12" t="s">
+      <c r="F156" s="13" t="s">
         <v>1043</v>
       </c>
-      <c r="G156" s="12" t="s">
+      <c r="G156" s="13" t="s">
         <v>1044</v>
       </c>
-      <c r="H156" s="12" t="s">
+      <c r="H156" s="13" t="s">
         <v>1303</v>
       </c>
-      <c r="I156" s="12" t="s">
+      <c r="I156" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="J156" s="12" t="s">
+      <c r="J156" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="K156" s="12" t="s">
+      <c r="K156" s="13" t="s">
         <v>1304</v>
       </c>
-      <c r="L156" s="13" t="s">
+      <c r="L156" s="14" t="s">
         <v>1305</v>
       </c>
-      <c r="M156" s="13"/>
-      <c r="N156" s="13" t="s">
+      <c r="M156" s="14"/>
+      <c r="N156" s="14" t="s">
         <v>1306</v>
       </c>
-      <c r="O156" s="12" t="s">
+      <c r="O156" s="13" t="s">
         <v>1307</v>
       </c>
-      <c r="P156" s="12">
+      <c r="P156" s="13">
         <v>240</v>
       </c>
-      <c r="Q156" s="12">
+      <c r="Q156" s="13">
         <v>223</v>
       </c>
-      <c r="R156" s="12" t="s">
+      <c r="R156" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="S156" s="12">
+      <c r="S156" s="13">
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="18" t="s">
+    <row r="157" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="19" t="s">
         <v>1315</v>
       </c>
-      <c r="B157" s="12" t="s">
+      <c r="B157" s="13" t="s">
         <v>1041</v>
       </c>
-      <c r="C157" s="12" t="s">
+      <c r="C157" s="13" t="s">
         <v>839</v>
       </c>
-      <c r="D157" s="12" t="s">
+      <c r="D157" s="13" t="s">
         <v>1042</v>
       </c>
-      <c r="E157" s="12" t="s">
+      <c r="E157" s="13" t="s">
         <v>1042</v>
       </c>
-      <c r="F157" s="12" t="s">
+      <c r="F157" s="13" t="s">
         <v>1043</v>
       </c>
-      <c r="G157" s="12" t="s">
+      <c r="G157" s="13" t="s">
         <v>1044</v>
       </c>
-      <c r="H157" s="12" t="s">
+      <c r="H157" s="13" t="s">
         <v>1308</v>
       </c>
-      <c r="I157" s="12" t="s">
+      <c r="I157" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="J157" s="12" t="s">
+      <c r="J157" s="13" t="s">
         <v>1309</v>
       </c>
-      <c r="K157" s="12" t="s">
+      <c r="K157" s="13" t="s">
         <v>1310</v>
       </c>
-      <c r="L157" s="13" t="s">
+      <c r="L157" s="14" t="s">
         <v>1311</v>
       </c>
-      <c r="M157" s="13" t="s">
+      <c r="M157" s="14" t="s">
         <v>1312</v>
       </c>
-      <c r="N157" s="13" t="s">
+      <c r="N157" s="14" t="s">
         <v>1313</v>
       </c>
-      <c r="O157" s="12" t="s">
+      <c r="O157" s="13" t="s">
         <v>423</v>
       </c>
-      <c r="P157" s="12">
+      <c r="P157" s="13">
         <v>190</v>
       </c>
-      <c r="Q157" s="12">
+      <c r="Q157" s="13">
         <v>122</v>
       </c>
-      <c r="R157" s="16" t="s">
+      <c r="R157" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S157" s="16">
+      <c r="S157" s="17">
         <v>3</v>
       </c>
     </row>
-    <row r="158" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="15" t="s">
+    <row r="158" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="16" t="s">
         <v>1045</v>
       </c>
       <c r="B158" s="1" t="s">
@@ -12700,50 +12704,50 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:19" s="29" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="18" t="s">
+    <row r="159" spans="1:19" s="30" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="19" t="s">
         <v>1294</v>
       </c>
-      <c r="B159" s="19" t="s">
+      <c r="B159" s="20" t="s">
         <v>1046</v>
       </c>
-      <c r="C159" s="19" t="s">
+      <c r="C159" s="20" t="s">
         <v>1047</v>
       </c>
-      <c r="D159" s="19"/>
-      <c r="E159" s="19"/>
-      <c r="F159" s="19" t="s">
+      <c r="D159" s="20"/>
+      <c r="E159" s="20"/>
+      <c r="F159" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="G159" s="19" t="s">
+      <c r="G159" s="20" t="s">
         <v>571</v>
       </c>
-      <c r="H159" s="16" t="s">
+      <c r="H159" s="17" t="s">
         <v>1295</v>
       </c>
-      <c r="I159" s="16" t="s">
+      <c r="I159" s="17" t="s">
         <v>1296</v>
       </c>
-      <c r="J159" s="16" t="s">
+      <c r="J159" s="17" t="s">
         <v>1297</v>
       </c>
-      <c r="K159" s="20" t="s">
+      <c r="K159" s="21" t="s">
         <v>1298</v>
       </c>
-      <c r="L159" s="13" t="s">
+      <c r="L159" s="14" t="s">
         <v>1299</v>
       </c>
-      <c r="M159" s="20"/>
-      <c r="N159" s="20" t="s">
+      <c r="M159" s="21"/>
+      <c r="N159" s="21" t="s">
         <v>1300</v>
       </c>
-      <c r="O159" s="16" t="s">
+      <c r="O159" s="17" t="s">
         <v>554</v>
       </c>
-      <c r="P159" s="20" t="s">
+      <c r="P159" s="21" t="s">
         <v>1301</v>
       </c>
-      <c r="Q159" s="20">
+      <c r="Q159" s="21">
         <v>27</v>
       </c>
       <c r="R159" s="1" t="s">
@@ -12753,292 +12757,292 @@
         <v>3</v>
       </c>
     </row>
-    <row r="160" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="15" t="s">
+    <row r="160" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="16" t="s">
         <v>1051</v>
       </c>
-      <c r="B160" s="12" t="s">
+      <c r="B160" s="13" t="s">
         <v>1052</v>
       </c>
-      <c r="C160" s="12" t="s">
+      <c r="C160" s="13" t="s">
         <v>1053</v>
       </c>
-      <c r="D160" s="12"/>
-      <c r="E160" s="12"/>
-      <c r="F160" s="12" t="s">
+      <c r="D160" s="13"/>
+      <c r="E160" s="13"/>
+      <c r="F160" s="13" t="s">
         <v>801</v>
       </c>
-      <c r="G160" s="12" t="s">
+      <c r="G160" s="13" t="s">
         <v>1054</v>
       </c>
-      <c r="H160" s="12" t="s">
+      <c r="H160" s="13" t="s">
         <v>1055</v>
       </c>
-      <c r="I160" s="12" t="s">
+      <c r="I160" s="13" t="s">
         <v>1056</v>
       </c>
-      <c r="J160" s="12" t="s">
+      <c r="J160" s="13" t="s">
         <v>1057</v>
       </c>
-      <c r="K160" s="12"/>
-      <c r="L160" s="13" t="s">
+      <c r="K160" s="13"/>
+      <c r="L160" s="14" t="s">
         <v>1058</v>
       </c>
-      <c r="M160" s="13"/>
-      <c r="N160" s="13"/>
-      <c r="O160" s="12" t="s">
+      <c r="M160" s="14"/>
+      <c r="N160" s="14"/>
+      <c r="O160" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="P160" s="12" t="s">
+      <c r="P160" s="13" t="s">
         <v>1059</v>
       </c>
-      <c r="Q160" s="12" t="s">
+      <c r="Q160" s="13" t="s">
         <v>1060</v>
       </c>
-      <c r="R160" s="12" t="s">
+      <c r="R160" s="13" t="s">
         <v>807</v>
       </c>
-      <c r="S160" s="12">
+      <c r="S160" s="13">
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="15" t="s">
+    <row r="161" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="16" t="s">
         <v>1061</v>
       </c>
-      <c r="B161" s="16" t="s">
+      <c r="B161" s="17" t="s">
         <v>1052</v>
       </c>
-      <c r="C161" s="16" t="s">
+      <c r="C161" s="17" t="s">
         <v>1053</v>
       </c>
-      <c r="D161" s="14"/>
-      <c r="E161" s="14"/>
-      <c r="F161" s="12" t="s">
+      <c r="D161" s="15"/>
+      <c r="E161" s="15"/>
+      <c r="F161" s="13" t="s">
         <v>801</v>
       </c>
-      <c r="G161" s="12" t="s">
+      <c r="G161" s="13" t="s">
         <v>1054</v>
       </c>
-      <c r="H161" s="16" t="s">
+      <c r="H161" s="17" t="s">
         <v>809</v>
       </c>
-      <c r="I161" s="16" t="s">
+      <c r="I161" s="17" t="s">
         <v>1056</v>
       </c>
-      <c r="J161" s="16" t="s">
+      <c r="J161" s="17" t="s">
         <v>1062</v>
       </c>
-      <c r="K161" s="17"/>
-      <c r="L161" s="13" t="s">
+      <c r="K161" s="18"/>
+      <c r="L161" s="14" t="s">
         <v>543</v>
       </c>
-      <c r="M161" s="17"/>
-      <c r="N161" s="17"/>
-      <c r="O161" s="16" t="s">
+      <c r="M161" s="18"/>
+      <c r="N161" s="18"/>
+      <c r="O161" s="17" t="s">
         <v>412</v>
       </c>
-      <c r="P161" s="17"/>
-      <c r="Q161" s="17"/>
-      <c r="R161" s="16" t="s">
+      <c r="P161" s="18"/>
+      <c r="Q161" s="18"/>
+      <c r="R161" s="17" t="s">
         <v>807</v>
       </c>
-      <c r="S161" s="16">
+      <c r="S161" s="17">
         <v>3</v>
       </c>
     </row>
-    <row r="162" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="15" t="s">
+    <row r="162" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="16" t="s">
         <v>1063</v>
       </c>
-      <c r="B162" s="12" t="s">
+      <c r="B162" s="13" t="s">
         <v>1064</v>
       </c>
-      <c r="C162" s="12" t="s">
+      <c r="C162" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="D162" s="12" t="s">
+      <c r="D162" s="13" t="s">
         <v>1065</v>
       </c>
-      <c r="E162" s="12" t="s">
+      <c r="E162" s="13" t="s">
         <v>1065</v>
       </c>
-      <c r="F162" s="12" t="s">
+      <c r="F162" s="13" t="s">
         <v>1066</v>
       </c>
-      <c r="G162" s="12" t="s">
+      <c r="G162" s="13" t="s">
         <v>457</v>
       </c>
-      <c r="H162" s="12" t="s">
+      <c r="H162" s="13" t="s">
         <v>956</v>
       </c>
-      <c r="I162" s="12" t="s">
+      <c r="I162" s="13" t="s">
         <v>840</v>
       </c>
-      <c r="J162" s="12" t="s">
+      <c r="J162" s="13" t="s">
         <v>1067</v>
       </c>
-      <c r="K162" s="12"/>
-      <c r="L162" s="13" t="s">
+      <c r="K162" s="13"/>
+      <c r="L162" s="14" t="s">
         <v>1068</v>
       </c>
-      <c r="M162" s="13"/>
-      <c r="N162" s="13"/>
-      <c r="O162" s="12" t="s">
+      <c r="M162" s="14"/>
+      <c r="N162" s="14"/>
+      <c r="O162" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="P162" s="12"/>
-      <c r="Q162" s="12"/>
-      <c r="R162" s="12" t="s">
+      <c r="P162" s="13"/>
+      <c r="Q162" s="13"/>
+      <c r="R162" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="S162" s="12">
+      <c r="S162" s="13">
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="15" t="s">
+    <row r="163" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="16" t="s">
         <v>1069</v>
       </c>
-      <c r="B163" s="16" t="s">
+      <c r="B163" s="17" t="s">
         <v>1064</v>
       </c>
-      <c r="C163" s="16" t="s">
+      <c r="C163" s="17" t="s">
         <v>394</v>
       </c>
-      <c r="D163" s="12" t="s">
+      <c r="D163" s="13" t="s">
         <v>1065</v>
       </c>
-      <c r="E163" s="12" t="s">
+      <c r="E163" s="13" t="s">
         <v>1065</v>
       </c>
-      <c r="F163" s="12" t="s">
+      <c r="F163" s="13" t="s">
         <v>1066</v>
       </c>
-      <c r="G163" s="12" t="s">
+      <c r="G163" s="13" t="s">
         <v>457</v>
       </c>
-      <c r="H163" s="16" t="s">
+      <c r="H163" s="17" t="s">
         <v>1070</v>
       </c>
-      <c r="I163" s="16" t="s">
+      <c r="I163" s="17" t="s">
         <v>1071</v>
       </c>
-      <c r="J163" s="16" t="s">
+      <c r="J163" s="17" t="s">
         <v>1072</v>
       </c>
-      <c r="K163" s="17"/>
-      <c r="L163" s="13" t="s">
+      <c r="K163" s="18"/>
+      <c r="L163" s="14" t="s">
         <v>846</v>
       </c>
-      <c r="M163" s="17"/>
-      <c r="N163" s="17"/>
-      <c r="O163" s="16" t="s">
+      <c r="M163" s="18"/>
+      <c r="N163" s="18"/>
+      <c r="O163" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="P163" s="17"/>
-      <c r="Q163" s="17"/>
-      <c r="R163" s="16" t="s">
+      <c r="P163" s="18"/>
+      <c r="Q163" s="18"/>
+      <c r="R163" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S163" s="16">
+      <c r="S163" s="17">
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="15" t="s">
+    <row r="164" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="16" t="s">
         <v>1073</v>
       </c>
-      <c r="B164" s="12" t="s">
+      <c r="B164" s="13" t="s">
         <v>1074</v>
       </c>
-      <c r="C164" s="12" t="s">
+      <c r="C164" s="13" t="s">
         <v>1075</v>
       </c>
-      <c r="D164" s="12"/>
-      <c r="E164" s="12"/>
-      <c r="F164" s="12" t="s">
+      <c r="D164" s="13"/>
+      <c r="E164" s="13"/>
+      <c r="F164" s="13" t="s">
         <v>1076</v>
       </c>
-      <c r="G164" s="12" t="s">
+      <c r="G164" s="13" t="s">
         <v>1077</v>
       </c>
-      <c r="H164" s="12" t="s">
+      <c r="H164" s="13" t="s">
         <v>1078</v>
       </c>
-      <c r="I164" s="12" t="s">
+      <c r="I164" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="J164" s="12" t="s">
+      <c r="J164" s="13" t="s">
         <v>1079</v>
       </c>
-      <c r="K164" s="12"/>
-      <c r="L164" s="13" t="s">
+      <c r="K164" s="13"/>
+      <c r="L164" s="14" t="s">
         <v>1080</v>
       </c>
-      <c r="M164" s="13"/>
-      <c r="N164" s="13" t="s">
+      <c r="M164" s="14"/>
+      <c r="N164" s="14" t="s">
         <v>1081</v>
       </c>
-      <c r="O164" s="12" t="s">
+      <c r="O164" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="P164" s="12"/>
-      <c r="Q164" s="12"/>
-      <c r="R164" s="12" t="s">
+      <c r="P164" s="13"/>
+      <c r="Q164" s="13"/>
+      <c r="R164" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="S164" s="12">
+      <c r="S164" s="13">
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="18" t="s">
+    <row r="165" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="19" t="s">
         <v>1302</v>
       </c>
-      <c r="B165" s="16" t="s">
+      <c r="B165" s="17" t="s">
         <v>1074</v>
       </c>
-      <c r="C165" s="16" t="s">
+      <c r="C165" s="17" t="s">
         <v>1075</v>
       </c>
-      <c r="D165" s="14"/>
-      <c r="E165" s="14"/>
-      <c r="F165" s="12" t="s">
+      <c r="D165" s="15"/>
+      <c r="E165" s="15"/>
+      <c r="F165" s="13" t="s">
         <v>1076</v>
       </c>
-      <c r="G165" s="12" t="s">
+      <c r="G165" s="13" t="s">
         <v>1077</v>
       </c>
-      <c r="H165" s="16" t="s">
+      <c r="H165" s="17" t="s">
         <v>1082</v>
       </c>
-      <c r="I165" s="16" t="s">
+      <c r="I165" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="J165" s="16" t="s">
+      <c r="J165" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="K165" s="17"/>
-      <c r="L165" s="13" t="s">
+      <c r="K165" s="18"/>
+      <c r="L165" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="M165" s="17"/>
-      <c r="N165" s="17"/>
-      <c r="O165" s="16" t="s">
+      <c r="M165" s="18"/>
+      <c r="N165" s="18"/>
+      <c r="O165" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="P165" s="17"/>
-      <c r="Q165" s="17"/>
-      <c r="R165" s="16" t="s">
+      <c r="P165" s="18"/>
+      <c r="Q165" s="18"/>
+      <c r="R165" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="S165" s="16">
+      <c r="S165" s="17">
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="15" t="s">
+    <row r="166" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="16" t="s">
         <v>1083</v>
       </c>
       <c r="B166" s="1" t="s">
@@ -13092,8 +13096,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="23" t="s">
+    <row r="167" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="24" t="s">
         <v>1095</v>
       </c>
       <c r="B167" s="1" t="s">
@@ -13147,8 +13151,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="23" t="s">
+    <row r="168" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="24" t="s">
         <v>1101</v>
       </c>
       <c r="B168" s="1" t="s">
@@ -13202,8 +13206,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="15" t="s">
+    <row r="169" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="16" t="s">
         <v>1106</v>
       </c>
       <c r="B169" s="1" t="s">
@@ -13257,8 +13261,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="15" t="s">
+    <row r="170" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="16" t="s">
         <v>1110</v>
       </c>
       <c r="B170" s="1" t="s">
@@ -13312,8 +13316,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="15" t="s">
+    <row r="171" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="16" t="s">
         <v>1114</v>
       </c>
       <c r="B171" s="1" t="s">
@@ -13342,10 +13346,10 @@
       <c r="K171" s="1" t="s">
         <v>1088</v>
       </c>
-      <c r="L171" s="24" t="s">
+      <c r="L171" s="25" t="s">
         <v>1115</v>
       </c>
-      <c r="M171" s="24" t="s">
+      <c r="M171" s="25" t="s">
         <v>1090</v>
       </c>
       <c r="N171" s="1" t="s">
@@ -13367,8 +13371,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="15" t="s">
+    <row r="172" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="16" t="s">
         <v>1119</v>
       </c>
       <c r="B172" s="1" t="s">
@@ -13397,10 +13401,10 @@
       <c r="K172" s="1" t="s">
         <v>1088</v>
       </c>
-      <c r="L172" s="24" t="s">
+      <c r="L172" s="25" t="s">
         <v>1120</v>
       </c>
-      <c r="M172" s="24" t="s">
+      <c r="M172" s="25" t="s">
         <v>1090</v>
       </c>
       <c r="N172" s="1" t="s">
@@ -13422,8 +13426,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="15" t="s">
+    <row r="173" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="16" t="s">
         <v>1124</v>
       </c>
       <c r="B173" s="1" t="s">
@@ -13452,10 +13456,10 @@
       <c r="K173" s="1" t="s">
         <v>1126</v>
       </c>
-      <c r="L173" s="24" t="s">
+      <c r="L173" s="25" t="s">
         <v>1127</v>
       </c>
-      <c r="M173" s="24" t="s">
+      <c r="M173" s="25" t="s">
         <v>1128</v>
       </c>
       <c r="N173" s="1" t="s">
@@ -13477,8 +13481,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="15" t="s">
+    <row r="174" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="16" t="s">
         <v>1131</v>
       </c>
       <c r="B174" s="1" t="s">
@@ -13507,10 +13511,10 @@
       <c r="K174" s="1" t="s">
         <v>1133</v>
       </c>
-      <c r="L174" s="24" t="s">
+      <c r="L174" s="25" t="s">
         <v>1134</v>
       </c>
-      <c r="M174" s="24"/>
+      <c r="M174" s="25"/>
       <c r="N174" s="1" t="s">
         <v>1135</v>
       </c>
@@ -13530,8 +13534,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="15" t="s">
+    <row r="175" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="16" t="s">
         <v>1138</v>
       </c>
       <c r="B175" s="1" t="s">
@@ -13560,10 +13564,10 @@
       <c r="K175" s="1" t="s">
         <v>1139</v>
       </c>
-      <c r="L175" s="24" t="s">
+      <c r="L175" s="25" t="s">
         <v>1140</v>
       </c>
-      <c r="M175" s="24"/>
+      <c r="M175" s="25"/>
       <c r="N175" s="1" t="s">
         <v>1141</v>
       </c>
@@ -13583,8 +13587,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="25" t="s">
+    <row r="176" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="26" t="s">
         <v>1144</v>
       </c>
       <c r="B176" s="1" t="s">
@@ -13636,8 +13640,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="25" t="s">
+    <row r="177" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="26" t="s">
         <v>1152</v>
       </c>
       <c r="B177" s="1" t="s">
@@ -13689,8 +13693,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="25" t="s">
+    <row r="178" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="26" t="s">
         <v>1160</v>
       </c>
       <c r="B178" s="1" t="s">
@@ -13742,8 +13746,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="25" t="s">
+    <row r="179" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="26" t="s">
         <v>1170</v>
       </c>
       <c r="B179" s="1" t="s">
@@ -13795,8 +13799,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="25" t="s">
+    <row r="180" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="26" t="s">
         <v>1176</v>
       </c>
       <c r="B180" s="1" t="s">
@@ -13848,8 +13852,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="25" t="s">
+    <row r="181" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="26" t="s">
         <v>1183</v>
       </c>
       <c r="B181" s="1" t="s">
@@ -13901,8 +13905,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="23" t="s">
+    <row r="182" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="24" t="s">
         <v>1191</v>
       </c>
       <c r="B182" s="1" t="s">
@@ -13954,8 +13958,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="23" t="s">
+    <row r="183" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="24" t="s">
         <v>1199</v>
       </c>
       <c r="B183" s="1" t="s">
@@ -14007,8 +14011,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="25" t="s">
+    <row r="184" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="26" t="s">
         <v>1208</v>
       </c>
       <c r="B184" s="1" t="s">
@@ -14060,8 +14064,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="25" t="s">
+    <row r="185" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="26" t="s">
         <v>1214</v>
       </c>
       <c r="B185" s="1" t="s">
@@ -14113,8 +14117,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="15" t="s">
+    <row r="186" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="16" t="s">
         <v>1222</v>
       </c>
       <c r="B186" s="6" t="s">
@@ -14168,8 +14172,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="15" t="s">
+    <row r="187" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="16" t="s">
         <v>1232</v>
       </c>
       <c r="B187" s="6" t="s">
@@ -14221,8 +14225,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="15" t="s">
+    <row r="188" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="16" t="s">
         <v>1233</v>
       </c>
       <c r="B188" s="6" t="s">
@@ -14274,8 +14278,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="15" t="s">
+    <row r="189" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="16" t="s">
         <v>1237</v>
       </c>
       <c r="B189" s="6" t="s">
@@ -14327,8 +14331,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="15" t="s">
+    <row r="190" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="16" t="s">
         <v>1241</v>
       </c>
       <c r="B190" s="6" t="s">
@@ -14382,8 +14386,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="15" t="s">
+    <row r="191" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="16" t="s">
         <v>1245</v>
       </c>
       <c r="B191" s="6" t="s">
@@ -14435,8 +14439,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="15" t="s">
+    <row r="192" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="16" t="s">
         <v>1250</v>
       </c>
       <c r="B192" s="6" t="s">
@@ -14488,8 +14492,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="15" t="s">
+    <row r="193" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="16" t="s">
         <v>1254</v>
       </c>
       <c r="B193" s="6" t="s">
@@ -14541,8 +14545,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:19" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="15" t="s">
+    <row r="194" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="16" t="s">
         <v>1258</v>
       </c>
       <c r="B194" s="1" t="s">
@@ -14738,55 +14742,55 @@
     <hyperlink ref="A151" r:id="rId142" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
     <hyperlink ref="A152" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
     <hyperlink ref="A153" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="A154" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="A155" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="A158" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="A160" r:id="rId148" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="A161" r:id="rId149" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="A162" r:id="rId150" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="A163" r:id="rId151" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="A164" r:id="rId152" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="A166" r:id="rId153" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="A167" r:id="rId154" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="A168" r:id="rId155" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="A169" r:id="rId156" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="A170" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="A171" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="A172" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="A173" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="A174" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="A175" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="A176" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="A177" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="A178" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="A179" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="A180" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="A181" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="A182" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="A183" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="A184" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="A185" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="A186" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="A187" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="A188" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="A189" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="A190" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="A191" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="A192" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="A193" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="A194" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="A122" r:id="rId182" xr:uid="{5387F726-DCFD-4836-AE7E-7DC737AD9B52}"/>
-    <hyperlink ref="A126" r:id="rId183" xr:uid="{2DD984AB-7E65-440E-990B-3DEB390F5232}"/>
-    <hyperlink ref="A127" r:id="rId184" xr:uid="{C1D5EDB1-0DBC-460B-BFE8-8A64BA531FE9}"/>
-    <hyperlink ref="A129" r:id="rId185" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0b/Paolo_Uccello_%E2%80%94_The_Decisive_Attack_of_Micheletto_Attendolo_at_San_Romano.jpg/1280px-Paolo_Uccello_%E2%80%94_The_Decisive_Attack_of_Micheletto_Attendolo_at_San_Romano.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8568C58D-9F0D-448F-A287-7E73E21239CF}"/>
-    <hyperlink ref="A51" r:id="rId186" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Beato_angelico_e_lorenzo_monaco%2C_pala_di_santa_trinita_%28deposizione_e_santi%29%2C_ante_1432%2C_01.jpg/1920px-Beato_angelico_e_lorenzo_monaco%2C_pala_di_santa_trinita_%28deposizione_e_santi%29%2C_ante_1432%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9A5901B2-A8C7-4333-8C93-3BA24B441446}"/>
-    <hyperlink ref="A159" r:id="rId187" xr:uid="{66FFDBF1-519C-4A74-8049-39696640DDD4}"/>
-    <hyperlink ref="A165" r:id="rId188" xr:uid="{C484BA40-5873-4062-BAC8-9BEE869078E5}"/>
-    <hyperlink ref="A156" r:id="rId189" xr:uid="{F646FB71-58FB-457D-8A7A-0FB460CB78F9}"/>
-    <hyperlink ref="A157" r:id="rId190" xr:uid="{2E363D48-40BE-441E-AC26-10AFA79ECF4B}"/>
-    <hyperlink ref="A102" r:id="rId191" xr:uid="{FA3B3813-9FCD-4BF6-BB3B-DA6B2910415D}"/>
-    <hyperlink ref="A93" r:id="rId192" xr:uid="{F9194648-35D5-46AD-8B7C-6F8007C9A92F}"/>
-    <hyperlink ref="A95" r:id="rId193" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5e/Apocalypse_figur%C3%A9e_des_ducs_de_Savoie_-_Escorial_E_Vit.5_-_Adoration_of_the_lamb2.jpg/960px-Apocalypse_figur%C3%A9e_des_ducs_de_Savoie_-_Escorial_E_Vit.5_-_Adoration_of_the_lamb2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{05264A43-B26E-4B7D-98A2-6DA5DE2DB650}"/>
+    <hyperlink ref="A155" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="A158" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="A160" r:id="rId147" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="A161" r:id="rId148" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="A162" r:id="rId149" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="A163" r:id="rId150" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="A164" r:id="rId151" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="A166" r:id="rId152" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="A167" r:id="rId153" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="A168" r:id="rId154" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="A169" r:id="rId155" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="A170" r:id="rId156" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="A171" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="A172" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="A173" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="A174" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="A175" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="A176" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="A177" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="A178" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="A179" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="A180" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="A181" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="A182" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="A183" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="A184" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="A185" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="A186" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="A187" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="A188" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="A189" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="A190" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="A191" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="A192" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="A193" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="A194" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="A122" r:id="rId181" xr:uid="{5387F726-DCFD-4836-AE7E-7DC737AD9B52}"/>
+    <hyperlink ref="A126" r:id="rId182" xr:uid="{2DD984AB-7E65-440E-990B-3DEB390F5232}"/>
+    <hyperlink ref="A127" r:id="rId183" xr:uid="{C1D5EDB1-0DBC-460B-BFE8-8A64BA531FE9}"/>
+    <hyperlink ref="A129" r:id="rId184" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0b/Paolo_Uccello_%E2%80%94_The_Decisive_Attack_of_Micheletto_Attendolo_at_San_Romano.jpg/1280px-Paolo_Uccello_%E2%80%94_The_Decisive_Attack_of_Micheletto_Attendolo_at_San_Romano.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8568C58D-9F0D-448F-A287-7E73E21239CF}"/>
+    <hyperlink ref="A51" r:id="rId185" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Beato_angelico_e_lorenzo_monaco%2C_pala_di_santa_trinita_%28deposizione_e_santi%29%2C_ante_1432%2C_01.jpg/1920px-Beato_angelico_e_lorenzo_monaco%2C_pala_di_santa_trinita_%28deposizione_e_santi%29%2C_ante_1432%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9A5901B2-A8C7-4333-8C93-3BA24B441446}"/>
+    <hyperlink ref="A159" r:id="rId186" xr:uid="{66FFDBF1-519C-4A74-8049-39696640DDD4}"/>
+    <hyperlink ref="A165" r:id="rId187" xr:uid="{C484BA40-5873-4062-BAC8-9BEE869078E5}"/>
+    <hyperlink ref="A156" r:id="rId188" xr:uid="{F646FB71-58FB-457D-8A7A-0FB460CB78F9}"/>
+    <hyperlink ref="A157" r:id="rId189" xr:uid="{2E363D48-40BE-441E-AC26-10AFA79ECF4B}"/>
+    <hyperlink ref="A102" r:id="rId190" xr:uid="{FA3B3813-9FCD-4BF6-BB3B-DA6B2910415D}"/>
+    <hyperlink ref="A93" r:id="rId191" xr:uid="{F9194648-35D5-46AD-8B7C-6F8007C9A92F}"/>
+    <hyperlink ref="A95" r:id="rId192" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5e/Apocalypse_figur%C3%A9e_des_ducs_de_Savoie_-_Escorial_E_Vit.5_-_Adoration_of_the_lamb2.jpg/960px-Apocalypse_figur%C3%A9e_des_ducs_de_Savoie_-_Escorial_E_Vit.5_-_Adoration_of_the_lamb2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{05264A43-B26E-4B7D-98A2-6DA5DE2DB650}"/>
+    <hyperlink ref="A154" r:id="rId193" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0d/Triptyque_de_la_famille_Braque_-_Rogier_van_der_Weyden_-_Mus%C3%A9e_du_Louvre_Peintures_RF_2063.jpg/1280px-Triptyque_de_la_famille_Braque_-_Rogier_van_der_Weyden_-_Mus%C3%A9e_du_Louvre_Peintures_RF_2063.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C1A2A759-47A8-4BC8-B605-8905A4F124B3}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-15e.xlsx
+++ b/quizzes/peinture-15e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C607AA8-C605-4C02-AA8A-8A487E73EA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BDADDE-BF1D-4A0E-8928-1B4165E44B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2606" uniqueCount="1341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2593" uniqueCount="1339">
   <si>
     <t>Image</t>
   </si>
@@ -3016,9 +3016,6 @@
     <t>262 cm</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/65/Rogier_van_der_Weyden_006.jpg/1280px-Rogier_van_der_Weyden_006.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>c.1452</t>
   </si>
   <si>
@@ -3026,9 +3023,6 @@
   </si>
   <si>
     <t>41 cm</t>
-  </si>
-  <si>
-    <t>34 cm</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2d/Rogier_van_der_Weyden_-_The_Altar_of_Our_Lady_%28Miraflores_Altar%29_-_Google_Art_Project.jpg/1280px-Rogier_van_der_Weyden_-_The_Altar_of_Our_Lady_%28Miraflores_Altar%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
@@ -4204,7 +4198,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4236,19 +4230,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4270,15 +4257,12 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -4582,91 +4566,91 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S194"/>
+  <dimension ref="A1:S193"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59.140625" style="31" customWidth="1"/>
-    <col min="2" max="2" width="12" style="32" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="32" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="5.85546875" style="33" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" style="32" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="32" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" style="32" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="32" customWidth="1"/>
-    <col min="10" max="10" width="32.85546875" style="32" customWidth="1"/>
-    <col min="11" max="11" width="7.85546875" style="32" customWidth="1"/>
-    <col min="12" max="12" width="30.28515625" style="32" customWidth="1"/>
-    <col min="13" max="13" width="5.140625" style="32" customWidth="1"/>
-    <col min="14" max="14" width="18.85546875" style="32" customWidth="1"/>
-    <col min="15" max="15" width="15" style="32" customWidth="1"/>
-    <col min="16" max="16" width="10" style="32" customWidth="1"/>
-    <col min="17" max="17" width="7.42578125" style="32" customWidth="1"/>
-    <col min="18" max="18" width="9.140625" style="32" customWidth="1"/>
-    <col min="19" max="19" width="8.85546875" style="32" customWidth="1"/>
+    <col min="1" max="1" width="59.140625" customWidth="1"/>
+    <col min="2" max="2" width="12" style="27" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" style="27" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" customWidth="1"/>
+    <col min="5" max="5" width="5.85546875" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" style="27" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="27" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" style="27" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="27" customWidth="1"/>
+    <col min="10" max="10" width="32.85546875" style="27" customWidth="1"/>
+    <col min="11" max="11" width="7.85546875" style="27" customWidth="1"/>
+    <col min="12" max="12" width="30.28515625" style="27" customWidth="1"/>
+    <col min="13" max="13" width="5.140625" style="27" customWidth="1"/>
+    <col min="14" max="14" width="18.85546875" style="27" customWidth="1"/>
+    <col min="15" max="15" width="15" style="27" customWidth="1"/>
+    <col min="16" max="16" width="10" style="27" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" style="27" customWidth="1"/>
+    <col min="18" max="18" width="9.140625" style="27" customWidth="1"/>
+    <col min="19" max="19" width="8.85546875" style="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="23" t="s">
+      <c r="J1" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="23" t="s">
+      <c r="K1" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="23" t="s">
+      <c r="L1" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="23" t="s">
+      <c r="M1" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="23" t="s">
+      <c r="N1" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="23" t="s">
+      <c r="O1" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="23" t="s">
+      <c r="P1" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="23" t="s">
+      <c r="Q1" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="23" t="s">
+      <c r="R1" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="23" t="s">
+      <c r="S1" s="20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+    <row r="2" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
         <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -4710,8 +4694,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+    <row r="3" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
         <v>30</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -4763,8 +4747,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+    <row r="4" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
         <v>39</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -4816,8 +4800,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+    <row r="5" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
         <v>50</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -4869,8 +4853,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+    <row r="6" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
         <v>57</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -4922,8 +4906,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+    <row r="7" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
         <v>67</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -4977,8 +4961,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+    <row r="8" spans="1:19" s="24" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
         <v>74</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -5030,8 +5014,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:19" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
+    <row r="9" spans="1:19" s="24" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
         <v>84</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -5083,8 +5067,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+    <row r="10" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
         <v>93</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -5130,8 +5114,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="24" t="s">
+    <row r="11" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
         <v>102</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -5183,8 +5167,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="24" t="s">
+    <row r="12" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
         <v>110</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -5236,8 +5220,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+    <row r="13" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
         <v>116</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -5289,8 +5273,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
+    <row r="14" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="21" t="s">
         <v>120</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -5342,8 +5326,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+    <row r="15" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
         <v>127</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -5397,8 +5381,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
+    <row r="16" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
         <v>132</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -5450,8 +5434,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
+    <row r="17" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="21" t="s">
         <v>141</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -5503,8 +5487,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
+    <row r="18" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
         <v>149</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -5558,8 +5542,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
+    <row r="19" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="21" t="s">
         <v>161</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -5611,8 +5595,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="24" t="s">
+    <row r="20" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="21" t="s">
         <v>167</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -5664,8 +5648,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="24" t="s">
+    <row r="21" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="21" t="s">
         <v>175</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -5717,8 +5701,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
+    <row r="22" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
         <v>179</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -5766,8 +5750,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="24" t="s">
+    <row r="23" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="21" t="s">
         <v>191</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -5819,8 +5803,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+    <row r="24" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
         <v>197</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -5874,8 +5858,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="24" t="s">
+    <row r="25" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="21" t="s">
         <v>211</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -5927,8 +5911,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
+    <row r="26" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
         <v>218</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -5980,8 +5964,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="24" t="s">
+    <row r="27" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="21" t="s">
         <v>226</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -6033,8 +6017,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="16" t="s">
+    <row r="28" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
         <v>231</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -6086,8 +6070,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="24" t="s">
+    <row r="29" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="21" t="s">
         <v>241</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -6139,8 +6123,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
+    <row r="30" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
         <v>245</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -6192,8 +6176,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="24" t="s">
+    <row r="31" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="21" t="s">
         <v>254</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -6245,8 +6229,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
+    <row r="32" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
         <v>263</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -6300,8 +6284,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="24" t="s">
+    <row r="33" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="21" t="s">
         <v>275</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -6355,8 +6339,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+    <row r="34" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
         <v>276</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -6410,8 +6394,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
+    <row r="35" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
         <v>287</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -6465,8 +6449,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
+    <row r="36" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
         <v>293</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -6518,8 +6502,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="24" t="s">
+    <row r="37" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="21" t="s">
         <v>303</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -6573,8 +6557,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="16" t="s">
+    <row r="38" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
         <v>311</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -6628,8 +6612,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="24" t="s">
+    <row r="39" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="21" t="s">
         <v>322</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -6681,8 +6665,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
+    <row r="40" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
         <v>325</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -6728,8 +6712,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="16" t="s">
+    <row r="41" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="14" t="s">
         <v>334</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -6777,8 +6761,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="16" t="s">
+    <row r="42" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="14" t="s">
         <v>339</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -6826,8 +6810,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="16" t="s">
+    <row r="43" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="14" t="s">
         <v>349</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -6875,8 +6859,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="16" t="s">
+    <row r="44" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="14" t="s">
         <v>356</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -6920,8 +6904,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="16" t="s">
+    <row r="45" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="14" t="s">
         <v>363</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -6965,8 +6949,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="16" t="s">
+    <row r="46" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
         <v>368</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -7010,8 +6994,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="16" t="s">
+    <row r="47" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
         <v>375</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -7055,8 +7039,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="16" t="s">
+    <row r="48" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="14" t="s">
         <v>379</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -7106,8 +7090,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="16" t="s">
+    <row r="49" spans="1:19" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="14" t="s">
         <v>388</v>
       </c>
       <c r="B49" s="10" t="s">
@@ -7155,534 +7139,534 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="16" t="s">
+    <row r="50" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="14" t="s">
         <v>392</v>
       </c>
-      <c r="B50" s="13" t="s">
+      <c r="B50" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="C50" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="D50" s="13" t="s">
+      <c r="D50" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="E50" s="13" t="s">
+      <c r="E50" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="F50" s="13" t="s">
+      <c r="F50" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="G50" s="13" t="s">
+      <c r="G50" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="H50" s="13" t="s">
+      <c r="H50" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="I50" s="13" t="s">
+      <c r="I50" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J50" s="13" t="s">
+      <c r="J50" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="K50" s="13" t="s">
+      <c r="K50" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="L50" s="14" t="s">
+      <c r="L50" s="13" t="s">
         <v>401</v>
       </c>
-      <c r="M50" s="14" t="s">
+      <c r="M50" s="13" t="s">
         <v>402</v>
       </c>
-      <c r="N50" s="14" t="s">
+      <c r="N50" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="O50" s="13" t="s">
+      <c r="O50" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="P50" s="13" t="s">
+      <c r="P50" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="Q50" s="13" t="s">
+      <c r="Q50" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="R50" s="13" t="s">
+      <c r="R50" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="S50" s="13">
+      <c r="S50" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="19" t="s">
-        <v>1293</v>
-      </c>
-      <c r="B51" s="17" t="s">
+    <row r="51" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="16" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B51" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="C51" s="17" t="s">
+      <c r="C51" s="15" t="s">
         <v>394</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="E51" s="13" t="s">
+      <c r="E51" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="F51" s="13" t="s">
+      <c r="F51" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="G51" s="13" t="s">
+      <c r="G51" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="H51" s="17" t="s">
+      <c r="H51" s="15" t="s">
         <v>406</v>
       </c>
-      <c r="I51" s="17" t="s">
+      <c r="I51" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="J51" s="17" t="s">
+      <c r="J51" s="15" t="s">
         <v>407</v>
       </c>
-      <c r="K51" s="18" t="s">
+      <c r="K51" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="L51" s="14" t="s">
+      <c r="L51" s="13" t="s">
         <v>409</v>
       </c>
-      <c r="M51" s="18" t="s">
+      <c r="M51" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="N51" s="18" t="s">
+      <c r="N51" s="6" t="s">
         <v>411</v>
       </c>
-      <c r="O51" s="17" t="s">
+      <c r="O51" s="15" t="s">
         <v>412</v>
       </c>
-      <c r="P51" s="17" t="s">
+      <c r="P51" s="15" t="s">
         <v>413</v>
       </c>
-      <c r="Q51" s="17" t="s">
+      <c r="Q51" s="15" t="s">
         <v>414</v>
       </c>
-      <c r="R51" s="17" t="s">
+      <c r="R51" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="S51" s="17">
+      <c r="S51" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="16" t="s">
+    <row r="52" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="14" t="s">
         <v>415</v>
       </c>
-      <c r="B52" s="17" t="s">
+      <c r="B52" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="C52" s="17" t="s">
+      <c r="C52" s="15" t="s">
         <v>394</v>
       </c>
-      <c r="D52" s="17" t="s">
+      <c r="D52" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="E52" s="17" t="s">
+      <c r="E52" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="F52" s="17" t="s">
+      <c r="F52" s="15" t="s">
         <v>396</v>
       </c>
-      <c r="G52" s="17" t="s">
+      <c r="G52" s="15" t="s">
         <v>397</v>
       </c>
-      <c r="H52" s="17" t="s">
+      <c r="H52" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="I52" s="17" t="s">
+      <c r="I52" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="J52" s="17" t="s">
+      <c r="J52" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="K52" s="17" t="s">
+      <c r="K52" s="15" t="s">
         <v>417</v>
       </c>
-      <c r="L52" s="14" t="s">
+      <c r="L52" s="13" t="s">
         <v>418</v>
       </c>
-      <c r="M52" s="15"/>
-      <c r="N52" s="17" t="s">
+      <c r="M52" s="3"/>
+      <c r="N52" s="15" t="s">
         <v>419</v>
       </c>
-      <c r="O52" s="17" t="s">
+      <c r="O52" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="P52" s="17" t="s">
+      <c r="P52" s="15" t="s">
         <v>420</v>
       </c>
-      <c r="Q52" s="17" t="s">
+      <c r="Q52" s="15" t="s">
         <v>420</v>
       </c>
-      <c r="R52" s="17" t="s">
+      <c r="R52" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="S52" s="17">
+      <c r="S52" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="16" t="s">
+    <row r="53" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="14" t="s">
         <v>421</v>
       </c>
-      <c r="B53" s="17" t="s">
+      <c r="B53" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="C53" s="17" t="s">
+      <c r="C53" s="15" t="s">
         <v>394</v>
       </c>
-      <c r="D53" s="17" t="s">
+      <c r="D53" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="E53" s="17" t="s">
+      <c r="E53" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="F53" s="17" t="s">
+      <c r="F53" s="15" t="s">
         <v>396</v>
       </c>
-      <c r="G53" s="17" t="s">
+      <c r="G53" s="15" t="s">
         <v>397</v>
       </c>
-      <c r="H53" s="17" t="s">
+      <c r="H53" s="15" t="s">
         <v>422</v>
       </c>
-      <c r="I53" s="17" t="s">
+      <c r="I53" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="J53" s="17" t="s">
+      <c r="J53" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="K53" s="17" t="s">
+      <c r="K53" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="L53" s="14" t="s">
+      <c r="L53" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="M53" s="15"/>
-      <c r="N53" s="17" t="s">
+      <c r="M53" s="3"/>
+      <c r="N53" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="O53" s="17" t="s">
+      <c r="O53" s="15" t="s">
         <v>423</v>
       </c>
-      <c r="P53" s="17" t="s">
+      <c r="P53" s="15" t="s">
         <v>424</v>
       </c>
-      <c r="Q53" s="17" t="s">
+      <c r="Q53" s="15" t="s">
         <v>425</v>
       </c>
-      <c r="R53" s="17" t="s">
+      <c r="R53" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="S53" s="17">
+      <c r="S53" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="16" t="s">
+    <row r="54" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="14" t="s">
         <v>426</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="B54" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13" t="s">
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="G54" s="13" t="s">
+      <c r="G54" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="H54" s="13" t="s">
+      <c r="H54" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="I54" s="13" t="s">
+      <c r="I54" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J54" s="13" t="s">
+      <c r="J54" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="K54" s="13"/>
-      <c r="L54" s="14" t="s">
+      <c r="K54" s="1"/>
+      <c r="L54" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="M54" s="14"/>
-      <c r="N54" s="14" t="s">
+      <c r="M54" s="13"/>
+      <c r="N54" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="O54" s="13" t="s">
+      <c r="O54" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="P54" s="13" t="s">
+      <c r="P54" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="Q54" s="13" t="s">
+      <c r="Q54" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="R54" s="13" t="s">
+      <c r="R54" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="S54" s="13">
+      <c r="S54" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="16" t="s">
+    <row r="55" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="14" t="s">
         <v>435</v>
       </c>
-      <c r="B55" s="17" t="s">
+      <c r="B55" s="15" t="s">
         <v>427</v>
       </c>
-      <c r="C55" s="17" t="s">
+      <c r="C55" s="15" t="s">
         <v>381</v>
       </c>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="13" t="s">
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="G55" s="13" t="s">
+      <c r="G55" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="H55" s="17" t="s">
+      <c r="H55" s="15" t="s">
         <v>436</v>
       </c>
-      <c r="I55" s="17" t="s">
+      <c r="I55" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="J55" s="17" t="s">
+      <c r="J55" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="K55" s="15"/>
-      <c r="L55" s="14" t="s">
+      <c r="K55" s="3"/>
+      <c r="L55" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="M55" s="15"/>
-      <c r="N55" s="15"/>
-      <c r="O55" s="17" t="s">
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="P55" s="17" t="s">
+      <c r="P55" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="Q55" s="17" t="s">
+      <c r="Q55" s="15" t="s">
         <v>437</v>
       </c>
-      <c r="R55" s="17" t="s">
+      <c r="R55" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="S55" s="17">
+      <c r="S55" s="15">
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="16" t="s">
+    <row r="56" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="14" t="s">
         <v>438</v>
       </c>
-      <c r="B56" s="13" t="s">
+      <c r="B56" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C56" s="13" t="s">
+      <c r="C56" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13" t="s">
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="G56" s="13" t="s">
+      <c r="G56" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="H56" s="13" t="s">
+      <c r="H56" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="I56" s="13" t="s">
+      <c r="I56" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="J56" s="13" t="s">
+      <c r="J56" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="K56" s="13"/>
-      <c r="L56" s="14" t="s">
+      <c r="K56" s="1"/>
+      <c r="L56" s="13" t="s">
         <v>445</v>
       </c>
-      <c r="M56" s="14"/>
-      <c r="N56" s="14" t="s">
+      <c r="M56" s="13"/>
+      <c r="N56" s="13" t="s">
         <v>446</v>
       </c>
-      <c r="O56" s="13" t="s">
+      <c r="O56" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="P56" s="13"/>
-      <c r="Q56" s="13"/>
-      <c r="R56" s="13" t="s">
+      <c r="P56" s="1"/>
+      <c r="Q56" s="1"/>
+      <c r="R56" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="S56" s="13">
+      <c r="S56" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="16" t="s">
+    <row r="57" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="14" t="s">
         <v>447</v>
       </c>
-      <c r="B57" s="17" t="s">
+      <c r="B57" s="15" t="s">
         <v>439</v>
       </c>
-      <c r="C57" s="17" t="s">
+      <c r="C57" s="15" t="s">
         <v>440</v>
       </c>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="13" t="s">
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="G57" s="13" t="s">
+      <c r="G57" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="H57" s="17" t="s">
+      <c r="H57" s="15" t="s">
         <v>448</v>
       </c>
-      <c r="I57" s="17" t="s">
+      <c r="I57" s="15" t="s">
         <v>449</v>
       </c>
-      <c r="J57" s="17" t="s">
+      <c r="J57" s="15" t="s">
         <v>450</v>
       </c>
-      <c r="K57" s="15"/>
-      <c r="L57" s="14" t="s">
+      <c r="K57" s="3"/>
+      <c r="L57" s="13" t="s">
         <v>418</v>
       </c>
-      <c r="M57" s="15"/>
-      <c r="N57" s="15"/>
-      <c r="O57" s="17" t="s">
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="P57" s="17" t="s">
+      <c r="P57" s="15" t="s">
         <v>451</v>
       </c>
-      <c r="Q57" s="17" t="s">
+      <c r="Q57" s="15" t="s">
         <v>452</v>
       </c>
-      <c r="R57" s="17" t="s">
+      <c r="R57" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="S57" s="17">
+      <c r="S57" s="15">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="16" t="s">
+    <row r="58" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="14" t="s">
         <v>453</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="B58" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C58" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13" t="s">
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="G58" s="13" t="s">
+      <c r="G58" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="H58" s="13" t="s">
+      <c r="H58" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="I58" s="13" t="s">
+      <c r="I58" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="J58" s="13" t="s">
+      <c r="J58" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="K58" s="13"/>
-      <c r="L58" s="14" t="s">
+      <c r="K58" s="1"/>
+      <c r="L58" s="13" t="s">
         <v>458</v>
       </c>
-      <c r="M58" s="14"/>
-      <c r="N58" s="14"/>
-      <c r="O58" s="13" t="s">
+      <c r="M58" s="13"/>
+      <c r="N58" s="13"/>
+      <c r="O58" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="P58" s="13" t="s">
+      <c r="P58" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="Q58" s="13" t="s">
+      <c r="Q58" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="R58" s="13" t="s">
+      <c r="R58" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="S58" s="13">
+      <c r="S58" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="16" t="s">
+    <row r="59" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="14" t="s">
         <v>462</v>
       </c>
-      <c r="B59" s="17" t="s">
+      <c r="B59" s="15" t="s">
         <v>454</v>
       </c>
-      <c r="C59" s="17" t="s">
+      <c r="C59" s="15" t="s">
         <v>455</v>
       </c>
-      <c r="D59" s="15"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="13" t="s">
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="G59" s="13" t="s">
+      <c r="G59" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="H59" s="17" t="s">
+      <c r="H59" s="15" t="s">
         <v>463</v>
       </c>
-      <c r="I59" s="17" t="s">
+      <c r="I59" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="J59" s="17" t="s">
+      <c r="J59" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="K59" s="15"/>
-      <c r="L59" s="14" t="s">
+      <c r="K59" s="3"/>
+      <c r="L59" s="13" t="s">
         <v>464</v>
       </c>
-      <c r="M59" s="15"/>
-      <c r="N59" s="15"/>
-      <c r="O59" s="17" t="s">
+      <c r="M59" s="3"/>
+      <c r="N59" s="3"/>
+      <c r="O59" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="P59" s="17" t="s">
+      <c r="P59" s="15" t="s">
         <v>465</v>
       </c>
-      <c r="Q59" s="17" t="s">
+      <c r="Q59" s="15" t="s">
         <v>466</v>
       </c>
-      <c r="R59" s="17" t="s">
+      <c r="R59" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="S59" s="17">
+      <c r="S59" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="16" t="s">
+    <row r="60" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="14" t="s">
         <v>467</v>
       </c>
       <c r="B60" s="1" t="s">
@@ -7732,151 +7716,151 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="16" t="s">
+    <row r="61" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="B61" s="17" t="s">
+      <c r="B61" s="15" t="s">
         <v>454</v>
       </c>
-      <c r="C61" s="17" t="s">
+      <c r="C61" s="15" t="s">
         <v>468</v>
       </c>
-      <c r="D61" s="15"/>
-      <c r="E61" s="15"/>
-      <c r="F61" s="13" t="s">
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="G61" s="13" t="s">
+      <c r="G61" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="H61" s="17" t="s">
+      <c r="H61" s="15" t="s">
         <v>477</v>
       </c>
-      <c r="I61" s="17" t="s">
+      <c r="I61" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="J61" s="17" t="s">
+      <c r="J61" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="K61" s="18"/>
-      <c r="L61" s="14" t="s">
+      <c r="K61" s="6"/>
+      <c r="L61" s="13" t="s">
         <v>478</v>
       </c>
-      <c r="M61" s="18"/>
-      <c r="N61" s="18"/>
-      <c r="O61" s="17" t="s">
+      <c r="M61" s="6"/>
+      <c r="N61" s="6"/>
+      <c r="O61" s="15" t="s">
         <v>479</v>
       </c>
-      <c r="P61" s="17" t="s">
+      <c r="P61" s="15" t="s">
         <v>480</v>
       </c>
-      <c r="Q61" s="17" t="s">
+      <c r="Q61" s="15" t="s">
         <v>481</v>
       </c>
-      <c r="R61" s="17" t="s">
+      <c r="R61" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="S61" s="17">
+      <c r="S61" s="15">
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="16" t="s">
+    <row r="62" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="14" t="s">
         <v>482</v>
       </c>
-      <c r="B62" s="13" t="s">
+      <c r="B62" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="C62" s="13" t="s">
+      <c r="C62" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13" t="s">
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="G62" s="13" t="s">
+      <c r="G62" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="H62" s="13" t="s">
+      <c r="H62" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="I62" s="13" t="s">
+      <c r="I62" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="J62" s="13" t="s">
+      <c r="J62" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="K62" s="13"/>
-      <c r="L62" s="14" t="s">
+      <c r="K62" s="1"/>
+      <c r="L62" s="13" t="s">
         <v>490</v>
       </c>
-      <c r="M62" s="14"/>
-      <c r="N62" s="14"/>
-      <c r="O62" s="13" t="s">
+      <c r="M62" s="13"/>
+      <c r="N62" s="13"/>
+      <c r="O62" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="P62" s="13"/>
-      <c r="Q62" s="13"/>
-      <c r="R62" s="13" t="s">
+      <c r="P62" s="1"/>
+      <c r="Q62" s="1"/>
+      <c r="R62" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="S62" s="13">
+      <c r="S62" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="16" t="s">
+    <row r="63" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="14" t="s">
         <v>491</v>
       </c>
-      <c r="B63" s="17" t="s">
+      <c r="B63" s="15" t="s">
         <v>483</v>
       </c>
-      <c r="C63" s="17" t="s">
+      <c r="C63" s="15" t="s">
         <v>484</v>
       </c>
-      <c r="D63" s="15"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="13" t="s">
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="G63" s="13" t="s">
+      <c r="G63" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="H63" s="17" t="s">
+      <c r="H63" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="I63" s="17" t="s">
+      <c r="I63" s="15" t="s">
         <v>492</v>
       </c>
-      <c r="J63" s="17" t="s">
+      <c r="J63" s="15" t="s">
         <v>493</v>
       </c>
-      <c r="K63" s="18"/>
-      <c r="L63" s="14" t="s">
+      <c r="K63" s="6"/>
+      <c r="L63" s="13" t="s">
         <v>494</v>
       </c>
-      <c r="M63" s="18"/>
-      <c r="N63" s="18"/>
-      <c r="O63" s="17" t="s">
+      <c r="M63" s="6"/>
+      <c r="N63" s="6"/>
+      <c r="O63" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="P63" s="17" t="s">
+      <c r="P63" s="15" t="s">
         <v>495</v>
       </c>
-      <c r="Q63" s="17" t="s">
+      <c r="Q63" s="15" t="s">
         <v>496</v>
       </c>
-      <c r="R63" s="17" t="s">
+      <c r="R63" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="S63" s="17">
+      <c r="S63" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="16" t="s">
+    <row r="64" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="14" t="s">
         <v>497</v>
       </c>
       <c r="B64" s="1" t="s">
@@ -7926,803 +7910,803 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="16" t="s">
+    <row r="65" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="14" t="s">
         <v>507</v>
       </c>
-      <c r="B65" s="17" t="s">
+      <c r="B65" s="15" t="s">
         <v>498</v>
       </c>
-      <c r="C65" s="17" t="s">
+      <c r="C65" s="15" t="s">
         <v>455</v>
       </c>
-      <c r="D65" s="15"/>
-      <c r="E65" s="15"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
       <c r="F65" s="1" t="s">
         <v>135</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="H65" s="17" t="s">
+      <c r="H65" s="15" t="s">
         <v>508</v>
       </c>
-      <c r="I65" s="17" t="s">
+      <c r="I65" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="J65" s="17" t="s">
+      <c r="J65" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="K65" s="17" t="s">
+      <c r="K65" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="L65" s="14" t="s">
+      <c r="L65" s="13" t="s">
         <v>509</v>
       </c>
-      <c r="M65" s="18"/>
-      <c r="N65" s="17" t="s">
+      <c r="M65" s="6"/>
+      <c r="N65" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="O65" s="17" t="s">
+      <c r="O65" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="P65" s="17" t="s">
+      <c r="P65" s="15" t="s">
         <v>510</v>
       </c>
-      <c r="Q65" s="17" t="s">
+      <c r="Q65" s="15" t="s">
         <v>511</v>
       </c>
-      <c r="R65" s="17" t="s">
+      <c r="R65" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="S65" s="17">
+      <c r="S65" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="16" t="s">
+    <row r="66" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="14" t="s">
         <v>512</v>
       </c>
-      <c r="B66" s="17" t="s">
+      <c r="B66" s="15" t="s">
         <v>498</v>
       </c>
-      <c r="C66" s="17" t="s">
+      <c r="C66" s="15" t="s">
         <v>455</v>
       </c>
-      <c r="D66" s="15"/>
-      <c r="E66" s="15"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
       <c r="F66" s="1" t="s">
         <v>135</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="H66" s="17" t="s">
+      <c r="H66" s="15" t="s">
         <v>364</v>
       </c>
-      <c r="I66" s="17" t="s">
+      <c r="I66" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="J66" s="17" t="s">
+      <c r="J66" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="K66" s="17" t="s">
+      <c r="K66" s="15" t="s">
         <v>513</v>
       </c>
-      <c r="L66" s="14" t="s">
+      <c r="L66" s="13" t="s">
         <v>514</v>
       </c>
-      <c r="M66" s="18"/>
-      <c r="N66" s="17" t="s">
+      <c r="M66" s="6"/>
+      <c r="N66" s="15" t="s">
         <v>515</v>
       </c>
-      <c r="O66" s="17" t="s">
+      <c r="O66" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="P66" s="17" t="s">
+      <c r="P66" s="15" t="s">
         <v>516</v>
       </c>
-      <c r="Q66" s="17" t="s">
+      <c r="Q66" s="15" t="s">
         <v>517</v>
       </c>
-      <c r="R66" s="17" t="s">
+      <c r="R66" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="S66" s="17">
+      <c r="S66" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="16" t="s">
+    <row r="67" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="14" t="s">
         <v>518</v>
       </c>
-      <c r="B67" s="17" t="s">
+      <c r="B67" s="15" t="s">
         <v>498</v>
       </c>
-      <c r="C67" s="17" t="s">
+      <c r="C67" s="15" t="s">
         <v>455</v>
       </c>
-      <c r="D67" s="15"/>
-      <c r="E67" s="15"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
       <c r="F67" s="1" t="s">
         <v>135</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="H67" s="17" t="s">
+      <c r="H67" s="15" t="s">
         <v>519</v>
       </c>
-      <c r="I67" s="17" t="s">
+      <c r="I67" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="J67" s="17" t="s">
+      <c r="J67" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="K67" s="17" t="s">
+      <c r="K67" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="L67" s="14" t="s">
+      <c r="L67" s="13" t="s">
         <v>520</v>
       </c>
-      <c r="M67" s="18"/>
-      <c r="N67" s="17" t="s">
+      <c r="M67" s="6"/>
+      <c r="N67" s="15" t="s">
         <v>521</v>
       </c>
-      <c r="O67" s="17" t="s">
+      <c r="O67" s="15" t="s">
         <v>522</v>
       </c>
-      <c r="P67" s="17" t="s">
+      <c r="P67" s="15" t="s">
         <v>523</v>
       </c>
-      <c r="Q67" s="17" t="s">
+      <c r="Q67" s="15" t="s">
         <v>390</v>
       </c>
-      <c r="R67" s="17" t="s">
+      <c r="R67" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="S67" s="17">
+      <c r="S67" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="16" t="s">
+    <row r="68" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B68" s="17" t="s">
+      <c r="B68" s="15" t="s">
         <v>498</v>
       </c>
-      <c r="C68" s="17" t="s">
+      <c r="C68" s="15" t="s">
         <v>455</v>
       </c>
-      <c r="D68" s="15"/>
-      <c r="E68" s="15"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
       <c r="F68" s="1" t="s">
         <v>135</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="H68" s="17" t="s">
+      <c r="H68" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="I68" s="17" t="s">
+      <c r="I68" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="J68" s="17" t="s">
+      <c r="J68" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="K68" s="17" t="s">
+      <c r="K68" s="15" t="s">
         <v>525</v>
       </c>
-      <c r="L68" s="14" t="s">
+      <c r="L68" s="13" t="s">
         <v>526</v>
       </c>
-      <c r="M68" s="18"/>
-      <c r="N68" s="17" t="s">
+      <c r="M68" s="6"/>
+      <c r="N68" s="15" t="s">
         <v>527</v>
       </c>
-      <c r="O68" s="17" t="s">
+      <c r="O68" s="15" t="s">
         <v>522</v>
       </c>
-      <c r="P68" s="17" t="s">
+      <c r="P68" s="15" t="s">
         <v>528</v>
       </c>
-      <c r="Q68" s="17" t="s">
+      <c r="Q68" s="15" t="s">
         <v>529</v>
       </c>
-      <c r="R68" s="17" t="s">
+      <c r="R68" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="S68" s="17">
+      <c r="S68" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="16" t="s">
+    <row r="69" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="14" t="s">
         <v>530</v>
       </c>
-      <c r="B69" s="17" t="s">
+      <c r="B69" s="15" t="s">
         <v>498</v>
       </c>
-      <c r="C69" s="17" t="s">
+      <c r="C69" s="15" t="s">
         <v>455</v>
       </c>
-      <c r="D69" s="15"/>
-      <c r="E69" s="15"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
       <c r="F69" s="1" t="s">
         <v>135</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="H69" s="17" t="s">
+      <c r="H69" s="15" t="s">
         <v>531</v>
       </c>
-      <c r="I69" s="17" t="s">
+      <c r="I69" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="J69" s="17" t="s">
+      <c r="J69" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="K69" s="17" t="s">
+      <c r="K69" s="15" t="s">
         <v>532</v>
       </c>
-      <c r="L69" s="14" t="s">
+      <c r="L69" s="13" t="s">
         <v>533</v>
       </c>
-      <c r="M69" s="18"/>
-      <c r="N69" s="17" t="s">
+      <c r="M69" s="6"/>
+      <c r="N69" s="15" t="s">
         <v>534</v>
       </c>
-      <c r="O69" s="17" t="s">
+      <c r="O69" s="15" t="s">
         <v>522</v>
       </c>
-      <c r="P69" s="17" t="s">
+      <c r="P69" s="15" t="s">
         <v>535</v>
       </c>
-      <c r="Q69" s="17" t="s">
+      <c r="Q69" s="15" t="s">
         <v>377</v>
       </c>
-      <c r="R69" s="17" t="s">
+      <c r="R69" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="S69" s="17">
+      <c r="S69" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="16" t="s">
+    <row r="70" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="14" t="s">
         <v>536</v>
       </c>
-      <c r="B70" s="13" t="s">
+      <c r="B70" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="C70" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13" t="s">
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G70" s="13" t="s">
+      <c r="G70" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="H70" s="13" t="s">
+      <c r="H70" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="I70" s="13" t="s">
+      <c r="I70" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="J70" s="13" t="s">
+      <c r="J70" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="K70" s="13" t="s">
+      <c r="K70" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="L70" s="14" t="s">
+      <c r="L70" s="13" t="s">
         <v>543</v>
       </c>
-      <c r="M70" s="14"/>
-      <c r="N70" s="14" t="s">
+      <c r="M70" s="13"/>
+      <c r="N70" s="13" t="s">
         <v>544</v>
       </c>
-      <c r="O70" s="13" t="s">
+      <c r="O70" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="P70" s="13" t="s">
+      <c r="P70" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="Q70" s="13" t="s">
+      <c r="Q70" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="R70" s="13" t="s">
+      <c r="R70" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="S70" s="13">
+      <c r="S70" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="16" t="s">
+    <row r="71" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="14" t="s">
         <v>548</v>
       </c>
-      <c r="B71" s="17" t="s">
+      <c r="B71" s="15" t="s">
         <v>537</v>
       </c>
-      <c r="C71" s="17" t="s">
+      <c r="C71" s="15" t="s">
         <v>538</v>
       </c>
-      <c r="D71" s="15"/>
-      <c r="E71" s="15"/>
-      <c r="F71" s="13" t="s">
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G71" s="13" t="s">
+      <c r="G71" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="H71" s="17" t="s">
+      <c r="H71" s="15" t="s">
         <v>549</v>
       </c>
-      <c r="I71" s="17" t="s">
+      <c r="I71" s="15" t="s">
         <v>492</v>
       </c>
-      <c r="J71" s="17" t="s">
+      <c r="J71" s="15" t="s">
         <v>550</v>
       </c>
-      <c r="K71" s="17" t="s">
+      <c r="K71" s="15" t="s">
         <v>551</v>
       </c>
-      <c r="L71" s="14" t="s">
+      <c r="L71" s="13" t="s">
         <v>552</v>
       </c>
-      <c r="M71" s="15"/>
-      <c r="N71" s="17" t="s">
+      <c r="M71" s="3"/>
+      <c r="N71" s="15" t="s">
         <v>553</v>
       </c>
-      <c r="O71" s="17" t="s">
+      <c r="O71" s="15" t="s">
         <v>554</v>
       </c>
-      <c r="P71" s="17" t="s">
+      <c r="P71" s="15" t="s">
         <v>555</v>
       </c>
-      <c r="Q71" s="17" t="s">
+      <c r="Q71" s="15" t="s">
         <v>556</v>
       </c>
-      <c r="R71" s="17" t="s">
+      <c r="R71" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="S71" s="17">
+      <c r="S71" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="16" t="s">
+    <row r="72" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="14" t="s">
         <v>557</v>
       </c>
-      <c r="B72" s="17" t="s">
+      <c r="B72" s="15" t="s">
         <v>537</v>
       </c>
-      <c r="C72" s="17" t="s">
+      <c r="C72" s="15" t="s">
         <v>538</v>
       </c>
-      <c r="D72" s="15"/>
-      <c r="E72" s="15"/>
-      <c r="F72" s="13" t="s">
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G72" s="13" t="s">
+      <c r="G72" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="H72" s="17" t="s">
+      <c r="H72" s="15" t="s">
         <v>457</v>
       </c>
-      <c r="I72" s="17" t="s">
+      <c r="I72" s="15" t="s">
         <v>558</v>
       </c>
-      <c r="J72" s="17" t="s">
+      <c r="J72" s="15" t="s">
         <v>559</v>
       </c>
-      <c r="K72" s="17" t="s">
+      <c r="K72" s="15" t="s">
         <v>560</v>
       </c>
-      <c r="L72" s="14" t="s">
+      <c r="L72" s="13" t="s">
         <v>561</v>
       </c>
-      <c r="M72" s="15"/>
-      <c r="N72" s="17" t="s">
+      <c r="M72" s="3"/>
+      <c r="N72" s="15" t="s">
         <v>562</v>
       </c>
-      <c r="O72" s="17" t="s">
+      <c r="O72" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="P72" s="17" t="s">
+      <c r="P72" s="15" t="s">
         <v>510</v>
       </c>
-      <c r="Q72" s="17" t="s">
+      <c r="Q72" s="15" t="s">
         <v>563</v>
       </c>
-      <c r="R72" s="17" t="s">
+      <c r="R72" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="S72" s="17">
+      <c r="S72" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="16" t="s">
+    <row r="73" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="14" t="s">
         <v>564</v>
       </c>
-      <c r="B73" s="17" t="s">
+      <c r="B73" s="15" t="s">
         <v>537</v>
       </c>
-      <c r="C73" s="17" t="s">
+      <c r="C73" s="15" t="s">
         <v>538</v>
       </c>
-      <c r="D73" s="15"/>
-      <c r="E73" s="15"/>
-      <c r="F73" s="13" t="s">
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G73" s="13" t="s">
+      <c r="G73" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="H73" s="17" t="s">
+      <c r="H73" s="15" t="s">
         <v>565</v>
       </c>
-      <c r="I73" s="17" t="s">
+      <c r="I73" s="15" t="s">
         <v>492</v>
       </c>
-      <c r="J73" s="17" t="s">
+      <c r="J73" s="15" t="s">
         <v>550</v>
       </c>
-      <c r="K73" s="17" t="s">
+      <c r="K73" s="15" t="s">
         <v>551</v>
       </c>
-      <c r="L73" s="14" t="s">
+      <c r="L73" s="13" t="s">
         <v>566</v>
       </c>
-      <c r="M73" s="15"/>
-      <c r="N73" s="17" t="s">
+      <c r="M73" s="3"/>
+      <c r="N73" s="15" t="s">
         <v>567</v>
       </c>
-      <c r="O73" s="17" t="s">
+      <c r="O73" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="P73" s="17" t="s">
+      <c r="P73" s="15" t="s">
         <v>568</v>
       </c>
-      <c r="Q73" s="17" t="s">
+      <c r="Q73" s="15" t="s">
         <v>569</v>
       </c>
-      <c r="R73" s="17" t="s">
+      <c r="R73" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="S73" s="17">
+      <c r="S73" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="16" t="s">
+    <row r="74" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="14" t="s">
         <v>570</v>
       </c>
-      <c r="B74" s="17" t="s">
+      <c r="B74" s="15" t="s">
         <v>537</v>
       </c>
-      <c r="C74" s="17" t="s">
+      <c r="C74" s="15" t="s">
         <v>538</v>
       </c>
-      <c r="D74" s="15"/>
-      <c r="E74" s="15"/>
-      <c r="F74" s="13" t="s">
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G74" s="13" t="s">
+      <c r="G74" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="H74" s="17" t="s">
+      <c r="H74" s="15" t="s">
         <v>571</v>
       </c>
-      <c r="I74" s="17" t="s">
+      <c r="I74" s="15" t="s">
         <v>492</v>
       </c>
-      <c r="J74" s="17" t="s">
+      <c r="J74" s="15" t="s">
         <v>550</v>
       </c>
-      <c r="K74" s="17" t="s">
+      <c r="K74" s="15" t="s">
         <v>551</v>
       </c>
-      <c r="L74" s="14" t="s">
+      <c r="L74" s="13" t="s">
         <v>572</v>
       </c>
-      <c r="M74" s="15"/>
-      <c r="N74" s="17" t="s">
+      <c r="M74" s="3"/>
+      <c r="N74" s="15" t="s">
         <v>573</v>
       </c>
-      <c r="O74" s="17" t="s">
+      <c r="O74" s="15" t="s">
         <v>574</v>
       </c>
-      <c r="P74" s="17" t="s">
+      <c r="P74" s="15" t="s">
         <v>575</v>
       </c>
-      <c r="Q74" s="17" t="s">
+      <c r="Q74" s="15" t="s">
         <v>576</v>
       </c>
-      <c r="R74" s="17" t="s">
+      <c r="R74" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="S74" s="17">
+      <c r="S74" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="16" t="s">
+    <row r="75" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="14" t="s">
         <v>577</v>
       </c>
-      <c r="B75" s="13" t="s">
+      <c r="B75" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="C75" s="13" t="s">
+      <c r="C75" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="13" t="s">
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="G75" s="13" t="s">
+      <c r="G75" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="H75" s="13" t="s">
+      <c r="H75" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="I75" s="13" t="s">
+      <c r="I75" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J75" s="13" t="s">
+      <c r="J75" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="K75" s="13" t="s">
+      <c r="K75" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="L75" s="14" t="s">
+      <c r="L75" s="13" t="s">
         <v>583</v>
       </c>
-      <c r="M75" s="14"/>
-      <c r="N75" s="14" t="s">
+      <c r="M75" s="13"/>
+      <c r="N75" s="13" t="s">
         <v>584</v>
       </c>
-      <c r="O75" s="13" t="s">
+      <c r="O75" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="P75" s="13" t="s">
+      <c r="P75" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="Q75" s="13" t="s">
+      <c r="Q75" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="R75" s="13" t="s">
+      <c r="R75" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="S75" s="13">
+      <c r="S75" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="16" t="s">
+    <row r="76" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="14" t="s">
         <v>587</v>
       </c>
-      <c r="B76" s="17" t="s">
+      <c r="B76" s="15" t="s">
         <v>578</v>
       </c>
-      <c r="C76" s="17" t="s">
+      <c r="C76" s="15" t="s">
         <v>579</v>
       </c>
-      <c r="D76" s="15"/>
-      <c r="E76" s="15"/>
-      <c r="F76" s="13" t="s">
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="G76" s="13" t="s">
+      <c r="G76" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="H76" s="17" t="s">
+      <c r="H76" s="15" t="s">
         <v>588</v>
       </c>
-      <c r="I76" s="17" t="s">
+      <c r="I76" s="15" t="s">
         <v>330</v>
       </c>
-      <c r="J76" s="17" t="s">
+      <c r="J76" s="15" t="s">
         <v>331</v>
       </c>
-      <c r="K76" s="17" t="s">
+      <c r="K76" s="15" t="s">
         <v>560</v>
       </c>
-      <c r="L76" s="14" t="s">
+      <c r="L76" s="13" t="s">
         <v>589</v>
       </c>
-      <c r="M76" s="15"/>
-      <c r="N76" s="17" t="s">
+      <c r="M76" s="3"/>
+      <c r="N76" s="15" t="s">
         <v>590</v>
       </c>
-      <c r="O76" s="17" t="s">
+      <c r="O76" s="15" t="s">
         <v>554</v>
       </c>
-      <c r="P76" s="17" t="s">
+      <c r="P76" s="15" t="s">
         <v>591</v>
       </c>
-      <c r="Q76" s="17" t="s">
+      <c r="Q76" s="15" t="s">
         <v>592</v>
       </c>
-      <c r="R76" s="17" t="s">
+      <c r="R76" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="S76" s="17">
+      <c r="S76" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="16" t="s">
+    <row r="77" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="14" t="s">
         <v>593</v>
       </c>
-      <c r="B77" s="17" t="s">
+      <c r="B77" s="15" t="s">
         <v>578</v>
       </c>
-      <c r="C77" s="17" t="s">
+      <c r="C77" s="15" t="s">
         <v>579</v>
       </c>
-      <c r="D77" s="15"/>
-      <c r="E77" s="15"/>
-      <c r="F77" s="13" t="s">
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="G77" s="13" t="s">
+      <c r="G77" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="H77" s="17" t="s">
+      <c r="H77" s="15" t="s">
         <v>594</v>
       </c>
-      <c r="I77" s="17" t="s">
+      <c r="I77" s="15" t="s">
         <v>595</v>
       </c>
-      <c r="J77" s="17" t="s">
+      <c r="J77" s="15" t="s">
         <v>596</v>
       </c>
-      <c r="K77" s="17" t="s">
+      <c r="K77" s="15" t="s">
         <v>597</v>
       </c>
-      <c r="L77" s="14" t="s">
+      <c r="L77" s="13" t="s">
         <v>598</v>
       </c>
-      <c r="M77" s="15"/>
-      <c r="N77" s="17" t="s">
+      <c r="M77" s="3"/>
+      <c r="N77" s="15" t="s">
         <v>599</v>
       </c>
-      <c r="O77" s="17" t="s">
+      <c r="O77" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="P77" s="17" t="s">
+      <c r="P77" s="15" t="s">
         <v>495</v>
       </c>
-      <c r="Q77" s="17" t="s">
+      <c r="Q77" s="15" t="s">
         <v>505</v>
       </c>
-      <c r="R77" s="17" t="s">
+      <c r="R77" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="S77" s="17">
+      <c r="S77" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="16" t="s">
+    <row r="78" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="14" t="s">
         <v>600</v>
       </c>
-      <c r="B78" s="17" t="s">
+      <c r="B78" s="15" t="s">
         <v>578</v>
       </c>
-      <c r="C78" s="17" t="s">
+      <c r="C78" s="15" t="s">
         <v>579</v>
       </c>
-      <c r="D78" s="15"/>
-      <c r="E78" s="15"/>
-      <c r="F78" s="13" t="s">
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="G78" s="13" t="s">
+      <c r="G78" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="H78" s="17" t="s">
+      <c r="H78" s="15" t="s">
         <v>500</v>
       </c>
-      <c r="I78" s="17" t="s">
+      <c r="I78" s="15" t="s">
         <v>492</v>
       </c>
-      <c r="J78" s="17" t="s">
+      <c r="J78" s="15" t="s">
         <v>493</v>
       </c>
-      <c r="K78" s="17" t="s">
+      <c r="K78" s="15" t="s">
         <v>601</v>
       </c>
-      <c r="L78" s="14" t="s">
+      <c r="L78" s="13" t="s">
         <v>602</v>
       </c>
-      <c r="M78" s="15"/>
-      <c r="N78" s="17" t="s">
+      <c r="M78" s="3"/>
+      <c r="N78" s="15" t="s">
         <v>603</v>
       </c>
-      <c r="O78" s="17" t="s">
+      <c r="O78" s="15" t="s">
         <v>554</v>
       </c>
-      <c r="P78" s="17" t="s">
+      <c r="P78" s="15" t="s">
         <v>604</v>
       </c>
-      <c r="Q78" s="17" t="s">
+      <c r="Q78" s="15" t="s">
         <v>605</v>
       </c>
-      <c r="R78" s="17" t="s">
+      <c r="R78" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="S78" s="17">
+      <c r="S78" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="16" t="s">
+    <row r="79" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="14" t="s">
         <v>606</v>
       </c>
-      <c r="B79" s="17" t="s">
+      <c r="B79" s="15" t="s">
         <v>578</v>
       </c>
-      <c r="C79" s="17" t="s">
+      <c r="C79" s="15" t="s">
         <v>579</v>
       </c>
-      <c r="D79" s="15"/>
-      <c r="E79" s="15"/>
-      <c r="F79" s="13" t="s">
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="G79" s="13" t="s">
+      <c r="G79" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="H79" s="17" t="s">
+      <c r="H79" s="15" t="s">
         <v>500</v>
       </c>
-      <c r="I79" s="17" t="s">
+      <c r="I79" s="15" t="s">
         <v>330</v>
       </c>
-      <c r="J79" s="17" t="s">
+      <c r="J79" s="15" t="s">
         <v>331</v>
       </c>
-      <c r="K79" s="17" t="s">
+      <c r="K79" s="15" t="s">
         <v>560</v>
       </c>
-      <c r="L79" s="14" t="s">
+      <c r="L79" s="13" t="s">
         <v>607</v>
       </c>
-      <c r="M79" s="15"/>
-      <c r="N79" s="17" t="s">
+      <c r="M79" s="3"/>
+      <c r="N79" s="15" t="s">
         <v>608</v>
       </c>
-      <c r="O79" s="17" t="s">
+      <c r="O79" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="P79" s="17" t="s">
+      <c r="P79" s="15" t="s">
         <v>609</v>
       </c>
-      <c r="Q79" s="17" t="s">
+      <c r="Q79" s="15" t="s">
         <v>610</v>
       </c>
-      <c r="R79" s="17" t="s">
+      <c r="R79" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="S79" s="17">
+      <c r="S79" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="16" t="s">
+    <row r="80" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="14" t="s">
         <v>611</v>
       </c>
       <c r="B80" s="1" t="s">
@@ -8770,8 +8754,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="16" t="s">
+    <row r="81" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="14" t="s">
         <v>620</v>
       </c>
       <c r="B81" s="1" t="s">
@@ -8823,8 +8807,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="16" t="s">
+    <row r="82" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="14" t="s">
         <v>627</v>
       </c>
       <c r="B82" s="1" t="s">
@@ -8876,8 +8860,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="16" t="s">
+    <row r="83" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="14" t="s">
         <v>634</v>
       </c>
       <c r="B83" s="1" t="s">
@@ -8929,8 +8913,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="16" t="s">
+    <row r="84" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="14" t="s">
         <v>639</v>
       </c>
       <c r="B84" s="1" t="s">
@@ -8982,8 +8966,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="16" t="s">
+    <row r="85" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="14" t="s">
         <v>643</v>
       </c>
       <c r="B85" s="1" t="s">
@@ -9035,8 +9019,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="16" t="s">
+    <row r="86" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="14" t="s">
         <v>651</v>
       </c>
       <c r="B86" s="1" t="s">
@@ -9088,8 +9072,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="16" t="s">
+    <row r="87" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="14" t="s">
         <v>654</v>
       </c>
       <c r="B87" s="1" t="s">
@@ -9141,8 +9125,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="24" t="s">
+    <row r="88" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="21" t="s">
         <v>657</v>
       </c>
       <c r="B88" s="1" t="s">
@@ -9194,8 +9178,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="16" t="s">
+    <row r="89" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="14" t="s">
         <v>662</v>
       </c>
       <c r="B89" s="1" t="s">
@@ -9247,98 +9231,98 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="16" t="s">
+    <row r="90" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="14" t="s">
         <v>665</v>
       </c>
-      <c r="B90" s="13" t="s">
+      <c r="B90" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="C90" s="13" t="s">
+      <c r="C90" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="D90" s="13"/>
-      <c r="E90" s="13"/>
-      <c r="F90" s="13" t="s">
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="G90" s="13" t="s">
+      <c r="G90" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="H90" s="13" t="s">
+      <c r="H90" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="I90" s="13" t="s">
+      <c r="I90" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="J90" s="13" t="s">
+      <c r="J90" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="K90" s="13"/>
-      <c r="L90" s="14" t="s">
+      <c r="K90" s="1"/>
+      <c r="L90" s="13" t="s">
         <v>672</v>
       </c>
-      <c r="M90" s="14"/>
-      <c r="N90" s="14"/>
-      <c r="O90" s="13" t="s">
+      <c r="M90" s="13"/>
+      <c r="N90" s="13"/>
+      <c r="O90" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="P90" s="13"/>
-      <c r="Q90" s="13"/>
-      <c r="R90" s="13" t="s">
+      <c r="P90" s="1"/>
+      <c r="Q90" s="1"/>
+      <c r="R90" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="S90" s="13">
+      <c r="S90" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="16" t="s">
+    <row r="91" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="14" t="s">
         <v>673</v>
       </c>
-      <c r="B91" s="17" t="s">
+      <c r="B91" s="15" t="s">
         <v>666</v>
       </c>
-      <c r="C91" s="17" t="s">
+      <c r="C91" s="15" t="s">
         <v>667</v>
       </c>
-      <c r="D91" s="15"/>
-      <c r="E91" s="15"/>
-      <c r="F91" s="13" t="s">
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="G91" s="13" t="s">
+      <c r="G91" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="H91" s="17" t="s">
+      <c r="H91" s="15" t="s">
         <v>674</v>
       </c>
-      <c r="I91" s="17" t="s">
+      <c r="I91" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="J91" s="17" t="s">
+      <c r="J91" s="15" t="s">
         <v>675</v>
       </c>
-      <c r="K91" s="15"/>
-      <c r="L91" s="14" t="s">
+      <c r="K91" s="3"/>
+      <c r="L91" s="13" t="s">
         <v>676</v>
       </c>
-      <c r="M91" s="15"/>
-      <c r="N91" s="15"/>
-      <c r="O91" s="17" t="s">
+      <c r="M91" s="3"/>
+      <c r="N91" s="3"/>
+      <c r="O91" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="P91" s="15"/>
-      <c r="Q91" s="15"/>
-      <c r="R91" s="17" t="s">
+      <c r="P91" s="3"/>
+      <c r="Q91" s="3"/>
+      <c r="R91" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="S91" s="17">
+      <c r="S91" s="15">
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="16" t="s">
+    <row r="92" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="14" t="s">
         <v>677</v>
       </c>
       <c r="B92" s="1" t="s">
@@ -9382,9 +9366,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="19" t="s">
-        <v>1329</v>
+    <row r="93" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="16" t="s">
+        <v>1327</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>678</v>
@@ -9401,23 +9385,23 @@
         <v>681</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>501</v>
       </c>
       <c r="J93" s="1" t="s">
+        <v>1322</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="L93" s="2" t="s">
         <v>1324</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>1325</v>
-      </c>
-      <c r="L93" s="2" t="s">
-        <v>1326</v>
       </c>
       <c r="M93" s="2"/>
       <c r="N93" s="2" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="O93" s="1" t="s">
         <v>38</v>
@@ -9435,8 +9419,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="16" t="s">
+    <row r="94" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="14" t="s">
         <v>687</v>
       </c>
       <c r="B94" s="1" t="s">
@@ -9464,17 +9448,17 @@
       </c>
       <c r="K94" s="1"/>
       <c r="L94" s="2" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="M94" s="2"/>
       <c r="N94" s="2" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="O94" s="1" t="s">
         <v>686</v>
       </c>
       <c r="P94" s="1" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="Q94" s="1">
         <v>21</v>
@@ -9486,9 +9470,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="19" t="s">
-        <v>1338</v>
+    <row r="95" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="16" t="s">
+        <v>1336</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>678</v>
@@ -9505,30 +9489,30 @@
         <v>689</v>
       </c>
       <c r="H95" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="J95" s="1" t="s">
         <v>1332</v>
       </c>
-      <c r="I95" s="1" t="s">
+      <c r="K95" s="1" t="s">
         <v>1333</v>
       </c>
-      <c r="J95" s="1" t="s">
-        <v>1334</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>1335</v>
-      </c>
       <c r="L95" s="2" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="M95" s="2"/>
       <c r="N95" s="2"/>
       <c r="O95" s="1" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="Q95" s="1" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="R95" s="1" t="s">
         <v>348</v>
@@ -9537,8 +9521,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="16" t="s">
+    <row r="96" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="14" t="s">
         <v>693</v>
       </c>
       <c r="B96" s="1" t="s">
@@ -9586,8 +9570,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="24" t="s">
+    <row r="97" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="21" t="s">
         <v>703</v>
       </c>
       <c r="B97" s="1" t="s">
@@ -9635,8 +9619,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="24" t="s">
+    <row r="98" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="21" t="s">
         <v>707</v>
       </c>
       <c r="B98" s="1" t="s">
@@ -9686,8 +9670,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="24" t="s">
+    <row r="99" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="21" t="s">
         <v>712</v>
       </c>
       <c r="B99" s="1" t="s">
@@ -9737,8 +9721,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="24" t="s">
+    <row r="100" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="21" t="s">
         <v>717</v>
       </c>
       <c r="B100" s="1" t="s">
@@ -9788,104 +9772,104 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="16" t="s">
+    <row r="101" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="14" t="s">
         <v>723</v>
       </c>
-      <c r="B101" s="13" t="s">
+      <c r="B101" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="C101" s="13" t="s">
+      <c r="C101" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="D101" s="13"/>
-      <c r="E101" s="13"/>
-      <c r="F101" s="13" t="s">
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="G101" s="13" t="s">
+      <c r="G101" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H101" s="13" t="s">
+      <c r="H101" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="I101" s="13" t="s">
+      <c r="I101" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="J101" s="13" t="s">
+      <c r="J101" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="K101" s="13"/>
-      <c r="L101" s="14" t="s">
+      <c r="K101" s="1"/>
+      <c r="L101" s="13" t="s">
         <v>729</v>
       </c>
-      <c r="M101" s="14"/>
-      <c r="N101" s="14"/>
-      <c r="O101" s="13"/>
-      <c r="P101" s="13"/>
-      <c r="Q101" s="13"/>
-      <c r="R101" s="13" t="s">
+      <c r="M101" s="13"/>
+      <c r="N101" s="13"/>
+      <c r="O101" s="1"/>
+      <c r="P101" s="1"/>
+      <c r="Q101" s="1"/>
+      <c r="R101" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="S101" s="13">
+      <c r="S101" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="19" t="s">
-        <v>1322</v>
-      </c>
-      <c r="B102" s="13" t="s">
+    <row r="102" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="16" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="C102" s="13" t="s">
+      <c r="C102" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="D102" s="13"/>
-      <c r="E102" s="13"/>
-      <c r="F102" s="13" t="s">
+      <c r="D102" s="1"/>
+      <c r="E102" s="1"/>
+      <c r="F102" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="G102" s="13" t="s">
+      <c r="G102" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H102" s="13" t="s">
+      <c r="H102" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="K102" s="1" t="s">
         <v>1316</v>
-      </c>
-      <c r="I102" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="J102" s="13" t="s">
-        <v>1317</v>
-      </c>
-      <c r="K102" s="13" t="s">
-        <v>1318</v>
       </c>
       <c r="L102" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="M102" s="14"/>
-      <c r="N102" s="14" t="s">
+      <c r="M102" s="13"/>
+      <c r="N102" s="13" t="s">
+        <v>1317</v>
+      </c>
+      <c r="O102" s="1" t="s">
+        <v>1318</v>
+      </c>
+      <c r="P102" s="1" t="s">
         <v>1319</v>
       </c>
-      <c r="O102" s="13" t="s">
-        <v>1320</v>
-      </c>
-      <c r="P102" s="13" t="s">
-        <v>1321</v>
-      </c>
-      <c r="Q102" s="13">
+      <c r="Q102" s="1">
         <v>18</v>
       </c>
-      <c r="R102" s="13" t="s">
+      <c r="R102" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="S102" s="13">
+      <c r="S102" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="16" t="s">
+    <row r="103" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="14" t="s">
         <v>730</v>
       </c>
       <c r="B103" s="1" t="s">
@@ -9937,8 +9921,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="16" t="s">
+    <row r="104" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="14" t="s">
         <v>740</v>
       </c>
       <c r="B104" s="1" t="s">
@@ -9986,8 +9970,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="16" t="s">
+    <row r="105" spans="1:19" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="14" t="s">
         <v>745</v>
       </c>
       <c r="B105" s="1" t="s">
@@ -10039,8 +10023,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="16" t="s">
+    <row r="106" spans="1:19" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="14" t="s">
         <v>751</v>
       </c>
       <c r="B106" s="1" t="s">
@@ -10092,8 +10076,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="16" t="s">
+    <row r="107" spans="1:19" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="14" t="s">
         <v>757</v>
       </c>
       <c r="B107" s="1" t="s">
@@ -10145,8 +10129,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="16" t="s">
+    <row r="108" spans="1:19" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="14" t="s">
         <v>767</v>
       </c>
       <c r="B108" s="1" t="s">
@@ -10198,8 +10182,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="16" t="s">
+    <row r="109" spans="1:19" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="14" t="s">
         <v>770</v>
       </c>
       <c r="B109" s="1" t="s">
@@ -10251,8 +10235,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="16" t="s">
+    <row r="110" spans="1:19" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="14" t="s">
         <v>778</v>
       </c>
       <c r="B110" s="1" t="s">
@@ -10304,8 +10288,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="16" t="s">
+    <row r="111" spans="1:19" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="14" t="s">
         <v>784</v>
       </c>
       <c r="B111" s="1" t="s">
@@ -10357,8 +10341,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="16" t="s">
+    <row r="112" spans="1:19" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="14" t="s">
         <v>791</v>
       </c>
       <c r="B112" s="1" t="s">
@@ -10410,8 +10394,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="16" t="s">
+    <row r="113" spans="1:19" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="14" t="s">
         <v>798</v>
       </c>
       <c r="B113" s="7" t="s">
@@ -10459,8 +10443,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="16" t="s">
+    <row r="114" spans="1:19" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="14" t="s">
         <v>808</v>
       </c>
       <c r="B114" s="10" t="s">
@@ -10504,8 +10488,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="16" t="s">
+    <row r="115" spans="1:19" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="14" t="s">
         <v>811</v>
       </c>
       <c r="B115" s="7" t="s">
@@ -10549,8 +10533,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="16" t="s">
+    <row r="116" spans="1:19" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="14" t="s">
         <v>819</v>
       </c>
       <c r="B116" s="10" t="s">
@@ -10598,8 +10582,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="16" t="s">
+    <row r="117" spans="1:19" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="14" t="s">
         <v>823</v>
       </c>
       <c r="B117" s="7" t="s">
@@ -10651,8 +10635,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="16" t="s">
+    <row r="118" spans="1:19" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="14" t="s">
         <v>833</v>
       </c>
       <c r="B118" s="10" t="s">
@@ -10680,10 +10664,10 @@
         <v>25</v>
       </c>
       <c r="J118" s="10" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="K118" s="11" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="L118" s="2" t="s">
         <v>834</v>
@@ -10706,8 +10690,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="16" t="s">
+    <row r="119" spans="1:19" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="14" t="s">
         <v>837</v>
       </c>
       <c r="B119" s="7" t="s">
@@ -10753,8 +10737,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:19" s="28" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="16" t="s">
+    <row r="120" spans="1:19" s="25" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="14" t="s">
         <v>844</v>
       </c>
       <c r="B120" s="10" t="s">
@@ -10802,8 +10786,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="16" t="s">
+    <row r="121" spans="1:19" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="14" t="s">
         <v>849</v>
       </c>
       <c r="B121" s="7" t="s">
@@ -10853,9 +10837,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="122" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="19" t="s">
-        <v>1266</v>
+    <row r="122" spans="1:19" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="16" t="s">
+        <v>1264</v>
       </c>
       <c r="B122" s="10" t="s">
         <v>850</v>
@@ -10872,32 +10856,32 @@
         <v>315</v>
       </c>
       <c r="H122" s="10" t="s">
+        <v>1266</v>
+      </c>
+      <c r="I122" s="10" t="s">
+        <v>1267</v>
+      </c>
+      <c r="J122" s="10" t="s">
         <v>1268</v>
       </c>
-      <c r="I122" s="10" t="s">
+      <c r="K122" s="11" t="s">
         <v>1269</v>
       </c>
-      <c r="J122" s="10" t="s">
+      <c r="L122" s="2" t="s">
         <v>1270</v>
-      </c>
-      <c r="K122" s="11" t="s">
-        <v>1271</v>
-      </c>
-      <c r="L122" s="2" t="s">
-        <v>1272</v>
       </c>
       <c r="M122" s="11"/>
       <c r="N122" s="11" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="O122" s="10" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="P122" s="10">
         <v>800</v>
       </c>
       <c r="Q122" s="10" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="R122" s="10" t="s">
         <v>29</v>
@@ -10906,8 +10890,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="16" t="s">
+    <row r="123" spans="1:19" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="14" t="s">
         <v>863</v>
       </c>
       <c r="B123" s="7" t="s">
@@ -10951,8 +10935,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:19" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="16" t="s">
+    <row r="124" spans="1:19" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="14" t="s">
         <v>872</v>
       </c>
       <c r="B124" s="10" t="s">
@@ -10996,8 +10980,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="16" t="s">
+    <row r="125" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="14" t="s">
         <v>875</v>
       </c>
       <c r="B125" s="1" t="s">
@@ -11037,9 +11021,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="19" t="s">
-        <v>1280</v>
+    <row r="126" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="16" t="s">
+        <v>1278</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>876</v>
@@ -11052,7 +11036,7 @@
       <c r="F126" s="1"/>
       <c r="G126" s="1"/>
       <c r="H126" s="1" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>878</v>
@@ -11061,17 +11045,17 @@
         <v>879</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="L126" s="2" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="M126" s="2"/>
       <c r="N126" s="2" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="O126" s="1" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="P126" s="1">
         <v>211</v>
@@ -11079,931 +11063,931 @@
       <c r="Q126" s="1">
         <v>91</v>
       </c>
-      <c r="R126" s="17" t="s">
+      <c r="R126" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="S126" s="17">
+      <c r="S126" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="19" t="s">
+    <row r="127" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="16" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="D127" s="1"/>
+      <c r="E127" s="1"/>
+      <c r="F127" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="L127" s="13" t="s">
+        <v>1279</v>
+      </c>
+      <c r="M127" s="13"/>
+      <c r="N127" s="13" t="s">
+        <v>899</v>
+      </c>
+      <c r="O127" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="P127" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="Q127" s="1">
+        <v>322</v>
+      </c>
+      <c r="R127" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="S127" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="14" t="s">
+        <v>883</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="D128" s="1"/>
+      <c r="E128" s="1"/>
+      <c r="F128" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K128" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="L128" s="13" t="s">
+        <v>1282</v>
+      </c>
+      <c r="M128" s="13"/>
+      <c r="N128" s="13" t="s">
+        <v>1283</v>
+      </c>
+      <c r="O128" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="P128" s="1">
+        <v>182</v>
+      </c>
+      <c r="Q128" s="1">
+        <v>323</v>
+      </c>
+      <c r="R128" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="S128" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19" s="24" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="16" t="s">
         <v>1290</v>
       </c>
-      <c r="B127" s="13" t="s">
+      <c r="B129" s="1" t="s">
         <v>884</v>
       </c>
-      <c r="C127" s="13" t="s">
+      <c r="C129" s="1" t="s">
         <v>885</v>
       </c>
-      <c r="D127" s="13"/>
-      <c r="E127" s="13"/>
-      <c r="F127" s="13" t="s">
+      <c r="D129" s="1"/>
+      <c r="E129" s="1"/>
+      <c r="F129" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="G127" s="13" t="s">
+      <c r="G129" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="H127" s="13" t="s">
-        <v>897</v>
-      </c>
-      <c r="I127" s="13" t="s">
+      <c r="H129" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J129" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K129" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L129" s="13" t="s">
+        <v>1289</v>
+      </c>
+      <c r="M129" s="13"/>
+      <c r="N129" s="13" t="s">
+        <v>1286</v>
+      </c>
+      <c r="O129" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="P129" s="1">
+        <v>182</v>
+      </c>
+      <c r="Q129" s="1">
+        <v>317</v>
+      </c>
+      <c r="R129" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="S129" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="14" t="s">
+        <v>889</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="D130" s="1"/>
+      <c r="E130" s="1"/>
+      <c r="F130" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H130" s="15" t="s">
+        <v>890</v>
+      </c>
+      <c r="I130" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="J130" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="K130" s="15" t="s">
+        <v>891</v>
+      </c>
+      <c r="L130" s="13" t="s">
+        <v>892</v>
+      </c>
+      <c r="M130" s="15"/>
+      <c r="N130" s="15" t="s">
+        <v>893</v>
+      </c>
+      <c r="O130" s="15" t="s">
+        <v>894</v>
+      </c>
+      <c r="P130" s="15" t="s">
+        <v>895</v>
+      </c>
+      <c r="Q130" s="15" t="s">
+        <v>896</v>
+      </c>
+      <c r="R130" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="S130" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="14" t="s">
+        <v>900</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="D131" s="1"/>
+      <c r="E131" s="1"/>
+      <c r="F131" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H131" s="15" t="s">
+        <v>588</v>
+      </c>
+      <c r="I131" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="J127" s="13" t="s">
+      <c r="J131" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="K127" s="13" t="s">
+      <c r="K131" s="15" t="s">
         <v>898</v>
       </c>
-      <c r="L127" s="14" t="s">
-        <v>1281</v>
-      </c>
-      <c r="M127" s="14"/>
-      <c r="N127" s="14" t="s">
-        <v>899</v>
-      </c>
-      <c r="O127" s="13" t="s">
-        <v>1282</v>
-      </c>
-      <c r="P127" s="13" t="s">
-        <v>1283</v>
-      </c>
-      <c r="Q127" s="13">
-        <v>322</v>
-      </c>
-      <c r="R127" s="17" t="s">
+      <c r="L131" s="13" t="s">
+        <v>901</v>
+      </c>
+      <c r="M131" s="6"/>
+      <c r="N131" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="O131" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="P131" s="15" t="s">
+        <v>902</v>
+      </c>
+      <c r="Q131" s="15" t="s">
+        <v>903</v>
+      </c>
+      <c r="R131" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="S127" s="17">
+      <c r="S131" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="16" t="s">
-        <v>883</v>
-      </c>
-      <c r="B128" s="13" t="s">
-        <v>884</v>
-      </c>
-      <c r="C128" s="13" t="s">
-        <v>885</v>
-      </c>
-      <c r="D128" s="13"/>
-      <c r="E128" s="13"/>
-      <c r="F128" s="13" t="s">
-        <v>886</v>
-      </c>
-      <c r="G128" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="H128" s="13" t="s">
-        <v>887</v>
-      </c>
-      <c r="I128" s="13" t="s">
+    <row r="132" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="14" t="s">
+        <v>904</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="D132" s="1"/>
+      <c r="E132" s="1"/>
+      <c r="F132" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="J132" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="K132" s="1"/>
+      <c r="L132" s="13" t="s">
+        <v>907</v>
+      </c>
+      <c r="M132" s="13"/>
+      <c r="N132" s="13" t="s">
+        <v>908</v>
+      </c>
+      <c r="O132" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="P132" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="Q132" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="R132" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="S132" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="14" t="s">
+        <v>911</v>
+      </c>
+      <c r="B133" s="15" t="s">
+        <v>905</v>
+      </c>
+      <c r="C133" s="15" t="s">
+        <v>906</v>
+      </c>
+      <c r="D133" s="3"/>
+      <c r="E133" s="3"/>
+      <c r="F133" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H133" s="15" t="s">
+        <v>912</v>
+      </c>
+      <c r="I133" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J133" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="K133" s="6"/>
+      <c r="L133" s="13" t="s">
+        <v>913</v>
+      </c>
+      <c r="M133" s="6"/>
+      <c r="N133" s="6"/>
+      <c r="O133" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="P133" s="6"/>
+      <c r="Q133" s="6"/>
+      <c r="R133" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="S133" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="14" t="s">
+        <v>914</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="D134" s="1"/>
+      <c r="E134" s="1"/>
+      <c r="F134" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="J134" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="K134" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="L134" s="13" t="s">
+        <v>920</v>
+      </c>
+      <c r="M134" s="13"/>
+      <c r="N134" s="13" t="s">
+        <v>921</v>
+      </c>
+      <c r="O134" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="P134" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="Q134" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="R134" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S134" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="14" t="s">
+        <v>924</v>
+      </c>
+      <c r="B135" s="15" t="s">
+        <v>915</v>
+      </c>
+      <c r="C135" s="15" t="s">
+        <v>916</v>
+      </c>
+      <c r="D135" s="3"/>
+      <c r="E135" s="3"/>
+      <c r="F135" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="H135" s="15" t="s">
+        <v>925</v>
+      </c>
+      <c r="I135" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="J135" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="K135" s="15" t="s">
+        <v>926</v>
+      </c>
+      <c r="L135" s="13" t="s">
+        <v>927</v>
+      </c>
+      <c r="M135" s="6"/>
+      <c r="N135" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="O135" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="P135" s="15" t="s">
+        <v>928</v>
+      </c>
+      <c r="Q135" s="15" t="s">
+        <v>929</v>
+      </c>
+      <c r="R135" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="S135" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="14" t="s">
+        <v>930</v>
+      </c>
+      <c r="B136" s="15" t="s">
+        <v>915</v>
+      </c>
+      <c r="C136" s="15" t="s">
+        <v>916</v>
+      </c>
+      <c r="D136" s="3"/>
+      <c r="E136" s="3"/>
+      <c r="F136" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="H136" s="15" t="s">
+        <v>931</v>
+      </c>
+      <c r="I136" s="15" t="s">
+        <v>932</v>
+      </c>
+      <c r="J136" s="15" t="s">
+        <v>933</v>
+      </c>
+      <c r="K136" s="15" t="s">
+        <v>934</v>
+      </c>
+      <c r="L136" s="13" t="s">
+        <v>935</v>
+      </c>
+      <c r="M136" s="13"/>
+      <c r="N136" s="15" t="s">
+        <v>936</v>
+      </c>
+      <c r="O136" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="P136" s="15" t="s">
+        <v>937</v>
+      </c>
+      <c r="Q136" s="15" t="s">
+        <v>938</v>
+      </c>
+      <c r="R136" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="S136" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="14" t="s">
+        <v>939</v>
+      </c>
+      <c r="B137" s="15" t="s">
+        <v>915</v>
+      </c>
+      <c r="C137" s="15" t="s">
+        <v>916</v>
+      </c>
+      <c r="D137" s="3"/>
+      <c r="E137" s="3"/>
+      <c r="F137" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="H137" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="I137" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="J128" s="13" t="s">
+      <c r="J137" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="K128" s="13" t="s">
-        <v>888</v>
-      </c>
-      <c r="L128" s="14" t="s">
-        <v>1284</v>
-      </c>
-      <c r="M128" s="14"/>
-      <c r="N128" s="14" t="s">
-        <v>1285</v>
-      </c>
-      <c r="O128" s="13" t="s">
-        <v>1286</v>
-      </c>
-      <c r="P128" s="13">
-        <v>182</v>
-      </c>
-      <c r="Q128" s="13">
-        <v>323</v>
-      </c>
-      <c r="R128" s="17" t="s">
+      <c r="K137" s="15" t="s">
+        <v>941</v>
+      </c>
+      <c r="L137" s="13" t="s">
+        <v>942</v>
+      </c>
+      <c r="M137" s="6"/>
+      <c r="N137" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="O137" s="15" t="s">
+        <v>944</v>
+      </c>
+      <c r="P137" s="15" t="s">
+        <v>945</v>
+      </c>
+      <c r="Q137" s="15" t="s">
+        <v>946</v>
+      </c>
+      <c r="R137" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="S128" s="17">
+      <c r="S137" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:19" s="27" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="19" t="s">
-        <v>1292</v>
-      </c>
-      <c r="B129" s="13" t="s">
-        <v>884</v>
-      </c>
-      <c r="C129" s="13" t="s">
-        <v>885</v>
-      </c>
-      <c r="D129" s="13"/>
-      <c r="E129" s="13"/>
-      <c r="F129" s="13" t="s">
-        <v>886</v>
-      </c>
-      <c r="G129" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="H129" s="13" t="s">
-        <v>1287</v>
-      </c>
-      <c r="I129" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J129" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K129" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="L129" s="14" t="s">
-        <v>1291</v>
-      </c>
-      <c r="M129" s="14"/>
-      <c r="N129" s="14" t="s">
-        <v>1288</v>
-      </c>
-      <c r="O129" s="13" t="s">
-        <v>1289</v>
-      </c>
-      <c r="P129" s="13">
-        <v>182</v>
-      </c>
-      <c r="Q129" s="13">
-        <v>317</v>
-      </c>
-      <c r="R129" s="17" t="s">
+    <row r="138" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="14" t="s">
+        <v>947</v>
+      </c>
+      <c r="B138" s="15" t="s">
+        <v>915</v>
+      </c>
+      <c r="C138" s="15" t="s">
+        <v>916</v>
+      </c>
+      <c r="D138" s="3"/>
+      <c r="E138" s="3"/>
+      <c r="F138" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="H138" s="15" t="s">
+        <v>948</v>
+      </c>
+      <c r="I138" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="J138" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="K138" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="L138" s="13" t="s">
+        <v>949</v>
+      </c>
+      <c r="M138" s="6"/>
+      <c r="N138" s="15" t="s">
+        <v>950</v>
+      </c>
+      <c r="O138" s="15" t="s">
+        <v>951</v>
+      </c>
+      <c r="P138" s="15" t="s">
+        <v>952</v>
+      </c>
+      <c r="Q138" s="15" t="s">
+        <v>953</v>
+      </c>
+      <c r="R138" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="S129" s="17">
+      <c r="S138" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="16" t="s">
-        <v>889</v>
-      </c>
-      <c r="B130" s="13" t="s">
-        <v>884</v>
-      </c>
-      <c r="C130" s="13" t="s">
-        <v>885</v>
-      </c>
-      <c r="D130" s="13"/>
-      <c r="E130" s="13"/>
-      <c r="F130" s="13" t="s">
-        <v>886</v>
-      </c>
-      <c r="G130" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="H130" s="17" t="s">
-        <v>890</v>
-      </c>
-      <c r="I130" s="17" t="s">
+    <row r="139" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="14" t="s">
+        <v>954</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="D139" s="1"/>
+      <c r="E139" s="1"/>
+      <c r="F139" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="I139" s="1"/>
+      <c r="J139" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="K139" s="1"/>
+      <c r="L139" s="13" t="s">
+        <v>959</v>
+      </c>
+      <c r="M139" s="13"/>
+      <c r="N139" s="13" t="s">
+        <v>960</v>
+      </c>
+      <c r="O139" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P139" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="Q139" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="R139" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S139" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="14" t="s">
+        <v>963</v>
+      </c>
+      <c r="B140" s="15" t="s">
+        <v>915</v>
+      </c>
+      <c r="C140" s="15" t="s">
+        <v>955</v>
+      </c>
+      <c r="D140" s="3"/>
+      <c r="E140" s="3"/>
+      <c r="F140" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="H140" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="I140" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="J140" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="K140" s="6"/>
+      <c r="L140" s="13" t="s">
+        <v>964</v>
+      </c>
+      <c r="M140" s="6"/>
+      <c r="N140" s="6"/>
+      <c r="O140" s="15" t="s">
+        <v>965</v>
+      </c>
+      <c r="P140" s="6"/>
+      <c r="Q140" s="6"/>
+      <c r="R140" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="S140" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="141" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="14" t="s">
+        <v>966</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="E141" s="1"/>
+      <c r="F141" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H141" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="J141" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="K141" s="1"/>
+      <c r="L141" s="13" t="s">
+        <v>972</v>
+      </c>
+      <c r="M141" s="13"/>
+      <c r="N141" s="13" t="s">
+        <v>973</v>
+      </c>
+      <c r="O141" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="P141" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="Q141" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="R141" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S141" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="14" t="s">
+        <v>976</v>
+      </c>
+      <c r="B142" s="15" t="s">
+        <v>967</v>
+      </c>
+      <c r="C142" s="15" t="s">
+        <v>968</v>
+      </c>
+      <c r="D142" s="3"/>
+      <c r="E142" s="3"/>
+      <c r="F142" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H142" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="I142" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="J130" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="K130" s="17" t="s">
-        <v>891</v>
-      </c>
-      <c r="L130" s="14" t="s">
-        <v>892</v>
-      </c>
-      <c r="M130" s="17"/>
-      <c r="N130" s="17" t="s">
-        <v>893</v>
-      </c>
-      <c r="O130" s="17" t="s">
-        <v>894</v>
-      </c>
-      <c r="P130" s="17" t="s">
-        <v>895</v>
-      </c>
-      <c r="Q130" s="17" t="s">
-        <v>896</v>
-      </c>
-      <c r="R130" s="17" t="s">
+      <c r="J142" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="K142" s="6"/>
+      <c r="L142" s="13" t="s">
+        <v>977</v>
+      </c>
+      <c r="M142" s="6"/>
+      <c r="N142" s="6"/>
+      <c r="O142" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="P142" s="15" t="s">
+        <v>978</v>
+      </c>
+      <c r="Q142" s="15" t="s">
+        <v>568</v>
+      </c>
+      <c r="R142" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="S130" s="17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="131" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="16" t="s">
-        <v>900</v>
-      </c>
-      <c r="B131" s="13" t="s">
-        <v>884</v>
-      </c>
-      <c r="C131" s="13" t="s">
-        <v>885</v>
-      </c>
-      <c r="D131" s="13"/>
-      <c r="E131" s="13"/>
-      <c r="F131" s="13" t="s">
-        <v>886</v>
-      </c>
-      <c r="G131" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="H131" s="17" t="s">
-        <v>588</v>
-      </c>
-      <c r="I131" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="J131" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="K131" s="17" t="s">
-        <v>898</v>
-      </c>
-      <c r="L131" s="14" t="s">
-        <v>901</v>
-      </c>
-      <c r="M131" s="18"/>
-      <c r="N131" s="17" t="s">
-        <v>285</v>
-      </c>
-      <c r="O131" s="17" t="s">
-        <v>459</v>
-      </c>
-      <c r="P131" s="17" t="s">
-        <v>902</v>
-      </c>
-      <c r="Q131" s="17" t="s">
-        <v>903</v>
-      </c>
-      <c r="R131" s="17" t="s">
+      <c r="S142" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="143" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="14" t="s">
+        <v>979</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="H143" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="J143" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="K143" s="1"/>
+      <c r="L143" s="13" t="s">
+        <v>987</v>
+      </c>
+      <c r="M143" s="13"/>
+      <c r="N143" s="13"/>
+      <c r="O143" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="P143" s="1"/>
+      <c r="Q143" s="1"/>
+      <c r="R143" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="S131" s="17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="132" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="16" t="s">
-        <v>904</v>
-      </c>
-      <c r="B132" s="13" t="s">
-        <v>905</v>
-      </c>
-      <c r="C132" s="13" t="s">
-        <v>906</v>
-      </c>
-      <c r="D132" s="13"/>
-      <c r="E132" s="13"/>
-      <c r="F132" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="G132" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="H132" s="13" t="s">
-        <v>364</v>
-      </c>
-      <c r="I132" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="J132" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="K132" s="13"/>
-      <c r="L132" s="14" t="s">
-        <v>907</v>
-      </c>
-      <c r="M132" s="14"/>
-      <c r="N132" s="14" t="s">
-        <v>908</v>
-      </c>
-      <c r="O132" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="P132" s="13" t="s">
-        <v>909</v>
-      </c>
-      <c r="Q132" s="13" t="s">
-        <v>910</v>
-      </c>
-      <c r="R132" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="S132" s="13">
+      <c r="S143" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="16" t="s">
-        <v>911</v>
-      </c>
-      <c r="B133" s="17" t="s">
-        <v>905</v>
-      </c>
-      <c r="C133" s="17" t="s">
-        <v>906</v>
-      </c>
-      <c r="D133" s="15"/>
-      <c r="E133" s="15"/>
-      <c r="F133" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="G133" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="H133" s="17" t="s">
-        <v>912</v>
-      </c>
-      <c r="I133" s="17" t="s">
-        <v>256</v>
-      </c>
-      <c r="J133" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="K133" s="18"/>
-      <c r="L133" s="14" t="s">
-        <v>913</v>
-      </c>
-      <c r="M133" s="18"/>
-      <c r="N133" s="18"/>
-      <c r="O133" s="17" t="s">
-        <v>345</v>
-      </c>
-      <c r="P133" s="18"/>
-      <c r="Q133" s="18"/>
-      <c r="R133" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="S133" s="17">
+    <row r="144" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="14" t="s">
+        <v>988</v>
+      </c>
+      <c r="B144" s="15" t="s">
+        <v>980</v>
+      </c>
+      <c r="C144" s="15" t="s">
+        <v>981</v>
+      </c>
+      <c r="D144" s="3"/>
+      <c r="E144" s="3"/>
+      <c r="F144" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="H144" s="15" t="s">
+        <v>989</v>
+      </c>
+      <c r="I144" s="15" t="s">
+        <v>840</v>
+      </c>
+      <c r="J144" s="15" t="s">
+        <v>990</v>
+      </c>
+      <c r="K144" s="6"/>
+      <c r="L144" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="M144" s="6"/>
+      <c r="N144" s="6"/>
+      <c r="O144" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="P144" s="6"/>
+      <c r="Q144" s="6"/>
+      <c r="R144" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="S144" s="15">
         <v>3</v>
       </c>
     </row>
-    <row r="134" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="16" t="s">
-        <v>914</v>
-      </c>
-      <c r="B134" s="13" t="s">
-        <v>915</v>
-      </c>
-      <c r="C134" s="13" t="s">
-        <v>916</v>
-      </c>
-      <c r="D134" s="13"/>
-      <c r="E134" s="13"/>
-      <c r="F134" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="G134" s="13" t="s">
-        <v>669</v>
-      </c>
-      <c r="H134" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="I134" s="13" t="s">
-        <v>917</v>
-      </c>
-      <c r="J134" s="13" t="s">
-        <v>918</v>
-      </c>
-      <c r="K134" s="13" t="s">
-        <v>919</v>
-      </c>
-      <c r="L134" s="14" t="s">
-        <v>920</v>
-      </c>
-      <c r="M134" s="14"/>
-      <c r="N134" s="14" t="s">
-        <v>921</v>
-      </c>
-      <c r="O134" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="P134" s="13" t="s">
-        <v>922</v>
-      </c>
-      <c r="Q134" s="13" t="s">
-        <v>923</v>
-      </c>
-      <c r="R134" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="S134" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="135" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="16" t="s">
-        <v>924</v>
-      </c>
-      <c r="B135" s="17" t="s">
-        <v>915</v>
-      </c>
-      <c r="C135" s="17" t="s">
-        <v>916</v>
-      </c>
-      <c r="D135" s="15"/>
-      <c r="E135" s="15"/>
-      <c r="F135" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="G135" s="13" t="s">
-        <v>669</v>
-      </c>
-      <c r="H135" s="17" t="s">
-        <v>925</v>
-      </c>
-      <c r="I135" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="J135" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="K135" s="17" t="s">
-        <v>926</v>
-      </c>
-      <c r="L135" s="14" t="s">
-        <v>927</v>
-      </c>
-      <c r="M135" s="18"/>
-      <c r="N135" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="O135" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="P135" s="17" t="s">
-        <v>928</v>
-      </c>
-      <c r="Q135" s="17" t="s">
-        <v>929</v>
-      </c>
-      <c r="R135" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="S135" s="17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="136" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="16" t="s">
-        <v>930</v>
-      </c>
-      <c r="B136" s="17" t="s">
-        <v>915</v>
-      </c>
-      <c r="C136" s="17" t="s">
-        <v>916</v>
-      </c>
-      <c r="D136" s="15"/>
-      <c r="E136" s="15"/>
-      <c r="F136" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="G136" s="13" t="s">
-        <v>669</v>
-      </c>
-      <c r="H136" s="17" t="s">
-        <v>931</v>
-      </c>
-      <c r="I136" s="17" t="s">
-        <v>932</v>
-      </c>
-      <c r="J136" s="17" t="s">
-        <v>933</v>
-      </c>
-      <c r="K136" s="17" t="s">
-        <v>934</v>
-      </c>
-      <c r="L136" s="14" t="s">
-        <v>935</v>
-      </c>
-      <c r="M136" s="14"/>
-      <c r="N136" s="17" t="s">
-        <v>936</v>
-      </c>
-      <c r="O136" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="P136" s="17" t="s">
-        <v>937</v>
-      </c>
-      <c r="Q136" s="17" t="s">
-        <v>938</v>
-      </c>
-      <c r="R136" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="S136" s="17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="137" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="16" t="s">
-        <v>939</v>
-      </c>
-      <c r="B137" s="17" t="s">
-        <v>915</v>
-      </c>
-      <c r="C137" s="17" t="s">
-        <v>916</v>
-      </c>
-      <c r="D137" s="15"/>
-      <c r="E137" s="15"/>
-      <c r="F137" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="G137" s="13" t="s">
-        <v>669</v>
-      </c>
-      <c r="H137" s="17" t="s">
-        <v>940</v>
-      </c>
-      <c r="I137" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="J137" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="K137" s="17" t="s">
-        <v>941</v>
-      </c>
-      <c r="L137" s="14" t="s">
-        <v>942</v>
-      </c>
-      <c r="M137" s="18"/>
-      <c r="N137" s="17" t="s">
-        <v>943</v>
-      </c>
-      <c r="O137" s="17" t="s">
-        <v>944</v>
-      </c>
-      <c r="P137" s="17" t="s">
-        <v>945</v>
-      </c>
-      <c r="Q137" s="17" t="s">
-        <v>946</v>
-      </c>
-      <c r="R137" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="S137" s="17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="16" t="s">
-        <v>947</v>
-      </c>
-      <c r="B138" s="17" t="s">
-        <v>915</v>
-      </c>
-      <c r="C138" s="17" t="s">
-        <v>916</v>
-      </c>
-      <c r="D138" s="15"/>
-      <c r="E138" s="15"/>
-      <c r="F138" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="G138" s="13" t="s">
-        <v>669</v>
-      </c>
-      <c r="H138" s="17" t="s">
-        <v>948</v>
-      </c>
-      <c r="I138" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="J138" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="K138" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="L138" s="14" t="s">
-        <v>949</v>
-      </c>
-      <c r="M138" s="18"/>
-      <c r="N138" s="17" t="s">
-        <v>950</v>
-      </c>
-      <c r="O138" s="17" t="s">
-        <v>951</v>
-      </c>
-      <c r="P138" s="17" t="s">
-        <v>952</v>
-      </c>
-      <c r="Q138" s="17" t="s">
-        <v>953</v>
-      </c>
-      <c r="R138" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="S138" s="17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="139" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="16" t="s">
-        <v>954</v>
-      </c>
-      <c r="B139" s="13" t="s">
-        <v>915</v>
-      </c>
-      <c r="C139" s="13" t="s">
-        <v>955</v>
-      </c>
-      <c r="D139" s="13"/>
-      <c r="E139" s="13"/>
-      <c r="F139" s="13" t="s">
-        <v>956</v>
-      </c>
-      <c r="G139" s="13" t="s">
-        <v>957</v>
-      </c>
-      <c r="H139" s="13" t="s">
-        <v>457</v>
-      </c>
-      <c r="I139" s="13"/>
-      <c r="J139" s="13" t="s">
-        <v>958</v>
-      </c>
-      <c r="K139" s="13"/>
-      <c r="L139" s="14" t="s">
-        <v>959</v>
-      </c>
-      <c r="M139" s="14"/>
-      <c r="N139" s="14" t="s">
-        <v>960</v>
-      </c>
-      <c r="O139" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="P139" s="13" t="s">
-        <v>961</v>
-      </c>
-      <c r="Q139" s="13" t="s">
-        <v>962</v>
-      </c>
-      <c r="R139" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="S139" s="13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="140" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="16" t="s">
-        <v>963</v>
-      </c>
-      <c r="B140" s="17" t="s">
-        <v>915</v>
-      </c>
-      <c r="C140" s="17" t="s">
-        <v>955</v>
-      </c>
-      <c r="D140" s="15"/>
-      <c r="E140" s="15"/>
-      <c r="F140" s="13" t="s">
-        <v>956</v>
-      </c>
-      <c r="G140" s="13" t="s">
-        <v>957</v>
-      </c>
-      <c r="H140" s="17" t="s">
-        <v>248</v>
-      </c>
-      <c r="I140" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="J140" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="K140" s="18"/>
-      <c r="L140" s="14" t="s">
-        <v>964</v>
-      </c>
-      <c r="M140" s="18"/>
-      <c r="N140" s="18"/>
-      <c r="O140" s="17" t="s">
-        <v>965</v>
-      </c>
-      <c r="P140" s="18"/>
-      <c r="Q140" s="18"/>
-      <c r="R140" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="S140" s="17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="141" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="16" t="s">
-        <v>966</v>
-      </c>
-      <c r="B141" s="13" t="s">
-        <v>967</v>
-      </c>
-      <c r="C141" s="13" t="s">
-        <v>968</v>
-      </c>
-      <c r="D141" s="13" t="s">
-        <v>969</v>
-      </c>
-      <c r="E141" s="13"/>
-      <c r="F141" s="13" t="s">
-        <v>970</v>
-      </c>
-      <c r="G141" s="13" t="s">
-        <v>486</v>
-      </c>
-      <c r="H141" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="I141" s="13" t="s">
-        <v>854</v>
-      </c>
-      <c r="J141" s="13" t="s">
-        <v>971</v>
-      </c>
-      <c r="K141" s="13"/>
-      <c r="L141" s="14" t="s">
-        <v>972</v>
-      </c>
-      <c r="M141" s="14"/>
-      <c r="N141" s="14" t="s">
-        <v>973</v>
-      </c>
-      <c r="O141" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="P141" s="13" t="s">
-        <v>974</v>
-      </c>
-      <c r="Q141" s="13" t="s">
-        <v>975</v>
-      </c>
-      <c r="R141" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="S141" s="13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="142" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="16" t="s">
-        <v>976</v>
-      </c>
-      <c r="B142" s="17" t="s">
-        <v>967</v>
-      </c>
-      <c r="C142" s="17" t="s">
-        <v>968</v>
-      </c>
-      <c r="D142" s="15"/>
-      <c r="E142" s="15"/>
-      <c r="F142" s="13" t="s">
-        <v>970</v>
-      </c>
-      <c r="G142" s="13" t="s">
-        <v>486</v>
-      </c>
-      <c r="H142" s="17" t="s">
-        <v>315</v>
-      </c>
-      <c r="I142" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="J142" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="K142" s="18"/>
-      <c r="L142" s="14" t="s">
-        <v>977</v>
-      </c>
-      <c r="M142" s="18"/>
-      <c r="N142" s="18"/>
-      <c r="O142" s="17" t="s">
-        <v>345</v>
-      </c>
-      <c r="P142" s="17" t="s">
-        <v>978</v>
-      </c>
-      <c r="Q142" s="17" t="s">
-        <v>568</v>
-      </c>
-      <c r="R142" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="S142" s="17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="143" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="16" t="s">
-        <v>979</v>
-      </c>
-      <c r="B143" s="13" t="s">
-        <v>980</v>
-      </c>
-      <c r="C143" s="13" t="s">
-        <v>981</v>
-      </c>
-      <c r="D143" s="13" t="s">
-        <v>982</v>
-      </c>
-      <c r="E143" s="13" t="s">
-        <v>982</v>
-      </c>
-      <c r="F143" s="13" t="s">
-        <v>983</v>
-      </c>
-      <c r="G143" s="13" t="s">
-        <v>984</v>
-      </c>
-      <c r="H143" s="13" t="s">
-        <v>985</v>
-      </c>
-      <c r="I143" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="J143" s="13" t="s">
-        <v>986</v>
-      </c>
-      <c r="K143" s="13"/>
-      <c r="L143" s="14" t="s">
-        <v>987</v>
-      </c>
-      <c r="M143" s="14"/>
-      <c r="N143" s="14"/>
-      <c r="O143" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="P143" s="13"/>
-      <c r="Q143" s="13"/>
-      <c r="R143" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="S143" s="13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="144" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="16" t="s">
-        <v>988</v>
-      </c>
-      <c r="B144" s="17" t="s">
-        <v>980</v>
-      </c>
-      <c r="C144" s="17" t="s">
-        <v>981</v>
-      </c>
-      <c r="D144" s="15"/>
-      <c r="E144" s="15"/>
-      <c r="F144" s="13" t="s">
-        <v>983</v>
-      </c>
-      <c r="G144" s="13" t="s">
-        <v>984</v>
-      </c>
-      <c r="H144" s="17" t="s">
-        <v>989</v>
-      </c>
-      <c r="I144" s="17" t="s">
-        <v>840</v>
-      </c>
-      <c r="J144" s="17" t="s">
-        <v>990</v>
-      </c>
-      <c r="K144" s="18"/>
-      <c r="L144" s="14" t="s">
-        <v>991</v>
-      </c>
-      <c r="M144" s="18"/>
-      <c r="N144" s="18"/>
-      <c r="O144" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="P144" s="18"/>
-      <c r="Q144" s="18"/>
-      <c r="R144" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="S144" s="17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="145" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="16" t="s">
+    <row r="145" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="14" t="s">
         <v>992</v>
       </c>
       <c r="B145" s="7" t="s">
@@ -12051,9 +12035,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="16" t="s">
-        <v>998</v>
+    <row r="146" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="14" t="s">
+        <v>1005</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>993</v>
@@ -12070,17 +12054,17 @@
         <v>996</v>
       </c>
       <c r="H146" s="7" t="s">
-        <v>999</v>
+        <v>1006</v>
       </c>
       <c r="I146" s="7" t="s">
-        <v>32</v>
+        <v>698</v>
       </c>
       <c r="J146" s="7" t="s">
-        <v>33</v>
+        <v>699</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="8" t="s">
-        <v>1000</v>
+        <v>1007</v>
       </c>
       <c r="M146" s="7"/>
       <c r="N146" s="7"/>
@@ -12088,10 +12072,10 @@
         <v>345</v>
       </c>
       <c r="P146" s="7" t="s">
-        <v>1001</v>
+        <v>377</v>
       </c>
       <c r="Q146" s="7" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="R146" s="7" t="s">
         <v>190</v>
@@ -12100,9 +12084,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="16" t="s">
-        <v>1007</v>
+    <row r="147" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="14" t="s">
+        <v>1009</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>993</v>
@@ -12119,28 +12103,28 @@
         <v>996</v>
       </c>
       <c r="H147" s="7" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>698</v>
+        <v>1011</v>
       </c>
       <c r="J147" s="7" t="s">
-        <v>699</v>
+        <v>1012</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="8" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="M147" s="7"/>
       <c r="N147" s="7"/>
       <c r="O147" s="7" t="s">
-        <v>345</v>
+        <v>187</v>
       </c>
       <c r="P147" s="7" t="s">
-        <v>377</v>
+        <v>451</v>
       </c>
       <c r="Q147" s="7" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="R147" s="7" t="s">
         <v>190</v>
@@ -12149,9 +12133,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="16" t="s">
-        <v>1011</v>
+    <row r="148" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="14" t="s">
+        <v>1015</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>993</v>
@@ -12168,28 +12152,28 @@
         <v>996</v>
       </c>
       <c r="H148" s="7" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="I148" s="7" t="s">
-        <v>1013</v>
+        <v>330</v>
       </c>
       <c r="J148" s="7" t="s">
-        <v>1014</v>
+        <v>331</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="8" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="M148" s="7"/>
       <c r="N148" s="7"/>
       <c r="O148" s="7" t="s">
-        <v>187</v>
+        <v>345</v>
       </c>
       <c r="P148" s="7" t="s">
-        <v>451</v>
+        <v>576</v>
       </c>
       <c r="Q148" s="7" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="R148" s="7" t="s">
         <v>190</v>
@@ -12198,9 +12182,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="16" t="s">
-        <v>1017</v>
+    <row r="149" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="14" t="s">
+        <v>1019</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>993</v>
@@ -12217,28 +12201,30 @@
         <v>996</v>
       </c>
       <c r="H149" s="7" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>330</v>
+        <v>1021</v>
       </c>
       <c r="J149" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="K149" s="7"/>
+        <v>1022</v>
+      </c>
+      <c r="K149" s="7" t="s">
+        <v>1023</v>
+      </c>
       <c r="L149" s="8" t="s">
-        <v>1019</v>
+        <v>1024</v>
       </c>
       <c r="M149" s="7"/>
       <c r="N149" s="7"/>
       <c r="O149" s="7" t="s">
-        <v>345</v>
+        <v>1025</v>
       </c>
       <c r="P149" s="7" t="s">
-        <v>576</v>
+        <v>355</v>
       </c>
       <c r="Q149" s="7" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="R149" s="7" t="s">
         <v>190</v>
@@ -12247,9 +12233,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="16" t="s">
-        <v>1021</v>
+    <row r="150" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="14" t="s">
+        <v>1027</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>993</v>
@@ -12266,30 +12252,28 @@
         <v>996</v>
       </c>
       <c r="H150" s="7" t="s">
-        <v>1022</v>
+        <v>485</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>1023</v>
+        <v>645</v>
       </c>
       <c r="J150" s="7" t="s">
-        <v>1024</v>
-      </c>
-      <c r="K150" s="7" t="s">
-        <v>1025</v>
-      </c>
+        <v>646</v>
+      </c>
+      <c r="K150" s="7"/>
       <c r="L150" s="8" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="M150" s="7"/>
       <c r="N150" s="7"/>
       <c r="O150" s="7" t="s">
-        <v>1027</v>
+        <v>345</v>
       </c>
       <c r="P150" s="7" t="s">
-        <v>355</v>
+        <v>1029</v>
       </c>
       <c r="Q150" s="7" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="R150" s="7" t="s">
         <v>190</v>
@@ -12298,9 +12282,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="16" t="s">
-        <v>1029</v>
+    <row r="151" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="14" t="s">
+        <v>1031</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>993</v>
@@ -12317,17 +12301,17 @@
         <v>996</v>
       </c>
       <c r="H151" s="7" t="s">
-        <v>485</v>
+        <v>1032</v>
       </c>
       <c r="I151" s="7" t="s">
-        <v>645</v>
+        <v>25</v>
       </c>
       <c r="J151" s="7" t="s">
-        <v>646</v>
+        <v>79</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="8" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="M151" s="7"/>
       <c r="N151" s="7"/>
@@ -12335,10 +12319,10 @@
         <v>345</v>
       </c>
       <c r="P151" s="7" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="Q151" s="7" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="R151" s="7" t="s">
         <v>190</v>
@@ -12347,9 +12331,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="16" t="s">
-        <v>1033</v>
+    <row r="152" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="14" t="s">
+        <v>1036</v>
       </c>
       <c r="B152" s="7" t="s">
         <v>993</v>
@@ -12366,17 +12350,17 @@
         <v>996</v>
       </c>
       <c r="H152" s="7" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="I152" s="7" t="s">
-        <v>25</v>
+        <v>304</v>
       </c>
       <c r="J152" s="7" t="s">
-        <v>79</v>
+        <v>305</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="8" t="s">
-        <v>1035</v>
+        <v>376</v>
       </c>
       <c r="M152" s="7"/>
       <c r="N152" s="7"/>
@@ -12384,10 +12368,10 @@
         <v>345</v>
       </c>
       <c r="P152" s="7" t="s">
-        <v>1036</v>
+        <v>750</v>
       </c>
       <c r="Q152" s="7" t="s">
-        <v>1037</v>
+        <v>568</v>
       </c>
       <c r="R152" s="7" t="s">
         <v>190</v>
@@ -12396,8 +12380,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="16" t="s">
+    <row r="153" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="12" t="s">
         <v>1038</v>
       </c>
       <c r="B153" s="7" t="s">
@@ -12415,17 +12399,17 @@
         <v>996</v>
       </c>
       <c r="H153" s="7" t="s">
-        <v>1039</v>
+        <v>998</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>304</v>
+        <v>32</v>
       </c>
       <c r="J153" s="7" t="s">
-        <v>305</v>
+        <v>33</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="8" t="s">
-        <v>376</v>
+        <v>999</v>
       </c>
       <c r="M153" s="7"/>
       <c r="N153" s="7"/>
@@ -12433,10 +12417,10 @@
         <v>345</v>
       </c>
       <c r="P153" s="7" t="s">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="Q153" s="7" t="s">
-        <v>568</v>
+        <v>1338</v>
       </c>
       <c r="R153" s="7" t="s">
         <v>190</v>
@@ -12445,9 +12429,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="12" t="s">
-        <v>1040</v>
+    <row r="154" spans="1:19" s="24" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="14" t="s">
+        <v>1001</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>993</v>
@@ -12464,17 +12448,17 @@
         <v>996</v>
       </c>
       <c r="H154" s="7" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>32</v>
+        <v>330</v>
       </c>
       <c r="J154" s="7" t="s">
-        <v>33</v>
+        <v>331</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="8" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="M154" s="7"/>
       <c r="N154" s="7"/>
@@ -12482,10 +12466,10 @@
         <v>345</v>
       </c>
       <c r="P154" s="7" t="s">
-        <v>1001</v>
+        <v>765</v>
       </c>
       <c r="Q154" s="7" t="s">
-        <v>1340</v>
+        <v>1004</v>
       </c>
       <c r="R154" s="7" t="s">
         <v>190</v>
@@ -12494,209 +12478,213 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:19" s="27" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="16" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B155" s="7" t="s">
-        <v>993</v>
-      </c>
-      <c r="C155" s="7" t="s">
-        <v>994</v>
-      </c>
-      <c r="D155" s="7"/>
-      <c r="E155" s="7"/>
-      <c r="F155" s="7" t="s">
-        <v>995</v>
-      </c>
-      <c r="G155" s="7" t="s">
-        <v>996</v>
-      </c>
-      <c r="H155" s="7" t="s">
-        <v>1004</v>
-      </c>
-      <c r="I155" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H155" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J155" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K155" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="L155" s="13" t="s">
+        <v>1303</v>
+      </c>
+      <c r="M155" s="13"/>
+      <c r="N155" s="13" t="s">
+        <v>1304</v>
+      </c>
+      <c r="O155" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="P155" s="1">
+        <v>240</v>
+      </c>
+      <c r="Q155" s="1">
+        <v>223</v>
+      </c>
+      <c r="R155" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S155" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="16" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H156" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J156" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="K156" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="L156" s="13" t="s">
+        <v>1309</v>
+      </c>
+      <c r="M156" s="13" t="s">
+        <v>1310</v>
+      </c>
+      <c r="N156" s="13" t="s">
+        <v>1311</v>
+      </c>
+      <c r="O156" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="P156" s="1">
+        <v>190</v>
+      </c>
+      <c r="Q156" s="1">
+        <v>122</v>
+      </c>
+      <c r="R156" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="S156" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="14" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D157" s="1"/>
+      <c r="E157" s="1"/>
+      <c r="F157" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="H157" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="I157" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="J155" s="7" t="s">
+      <c r="J157" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="K155" s="7"/>
-      <c r="L155" s="8" t="s">
-        <v>1005</v>
-      </c>
-      <c r="M155" s="7"/>
-      <c r="N155" s="7"/>
-      <c r="O155" s="7" t="s">
+      <c r="K157" s="1"/>
+      <c r="L157" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="M157" s="2"/>
+      <c r="N157" s="2"/>
+      <c r="O157" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="P155" s="7" t="s">
-        <v>765</v>
-      </c>
-      <c r="Q155" s="7" t="s">
-        <v>1006</v>
-      </c>
-      <c r="R155" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="S155" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="19" t="s">
-        <v>1314</v>
-      </c>
-      <c r="B156" s="13" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C156" s="13" t="s">
-        <v>839</v>
-      </c>
-      <c r="D156" s="13" t="s">
-        <v>1042</v>
-      </c>
-      <c r="E156" s="13" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F156" s="13" t="s">
-        <v>1043</v>
-      </c>
-      <c r="G156" s="13" t="s">
+      <c r="P157" s="1"/>
+      <c r="Q157" s="1"/>
+      <c r="R157" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="S157" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="158" spans="1:19" s="26" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="16" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B158" s="17" t="s">
         <v>1044</v>
       </c>
-      <c r="H156" s="13" t="s">
-        <v>1303</v>
-      </c>
-      <c r="I156" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="J156" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="K156" s="13" t="s">
-        <v>1304</v>
-      </c>
-      <c r="L156" s="14" t="s">
-        <v>1305</v>
-      </c>
-      <c r="M156" s="14"/>
-      <c r="N156" s="14" t="s">
-        <v>1306</v>
-      </c>
-      <c r="O156" s="13" t="s">
-        <v>1307</v>
-      </c>
-      <c r="P156" s="13">
-        <v>240</v>
-      </c>
-      <c r="Q156" s="13">
-        <v>223</v>
-      </c>
-      <c r="R156" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="S156" s="13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="157" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="19" t="s">
-        <v>1315</v>
-      </c>
-      <c r="B157" s="13" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C157" s="13" t="s">
-        <v>839</v>
-      </c>
-      <c r="D157" s="13" t="s">
-        <v>1042</v>
-      </c>
-      <c r="E157" s="13" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F157" s="13" t="s">
-        <v>1043</v>
-      </c>
-      <c r="G157" s="13" t="s">
-        <v>1044</v>
-      </c>
-      <c r="H157" s="13" t="s">
-        <v>1308</v>
-      </c>
-      <c r="I157" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="J157" s="13" t="s">
-        <v>1309</v>
-      </c>
-      <c r="K157" s="13" t="s">
-        <v>1310</v>
-      </c>
-      <c r="L157" s="14" t="s">
-        <v>1311</v>
-      </c>
-      <c r="M157" s="14" t="s">
-        <v>1312</v>
-      </c>
-      <c r="N157" s="14" t="s">
-        <v>1313</v>
-      </c>
-      <c r="O157" s="13" t="s">
-        <v>423</v>
-      </c>
-      <c r="P157" s="13">
-        <v>190</v>
-      </c>
-      <c r="Q157" s="13">
-        <v>122</v>
-      </c>
-      <c r="R157" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="S157" s="17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="158" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="16" t="s">
+      <c r="C158" s="17" t="s">
         <v>1045</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>1047</v>
-      </c>
-      <c r="D158" s="1"/>
-      <c r="E158" s="1"/>
-      <c r="F158" s="1" t="s">
+      <c r="D158" s="17"/>
+      <c r="E158" s="17"/>
+      <c r="F158" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="G158" s="1" t="s">
+      <c r="G158" s="17" t="s">
         <v>571</v>
       </c>
-      <c r="H158" s="1" t="s">
-        <v>1048</v>
-      </c>
-      <c r="I158" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="J158" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="K158" s="1"/>
-      <c r="L158" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="M158" s="2"/>
-      <c r="N158" s="2"/>
-      <c r="O158" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="P158" s="1"/>
-      <c r="Q158" s="1"/>
+      <c r="H158" s="15" t="s">
+        <v>1293</v>
+      </c>
+      <c r="I158" s="15" t="s">
+        <v>1294</v>
+      </c>
+      <c r="J158" s="15" t="s">
+        <v>1295</v>
+      </c>
+      <c r="K158" s="18" t="s">
+        <v>1296</v>
+      </c>
+      <c r="L158" s="13" t="s">
+        <v>1297</v>
+      </c>
+      <c r="M158" s="18"/>
+      <c r="N158" s="18" t="s">
+        <v>1298</v>
+      </c>
+      <c r="O158" s="15" t="s">
+        <v>554</v>
+      </c>
+      <c r="P158" s="18" t="s">
+        <v>1299</v>
+      </c>
+      <c r="Q158" s="18">
+        <v>27</v>
+      </c>
       <c r="R158" s="1" t="s">
         <v>348</v>
       </c>
@@ -12704,363 +12692,365 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:19" s="30" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="19" t="s">
-        <v>1294</v>
-      </c>
-      <c r="B159" s="20" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C159" s="20" t="s">
-        <v>1047</v>
-      </c>
-      <c r="D159" s="20"/>
-      <c r="E159" s="20"/>
-      <c r="F159" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="G159" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="H159" s="17" t="s">
-        <v>1295</v>
-      </c>
-      <c r="I159" s="17" t="s">
-        <v>1296</v>
-      </c>
-      <c r="J159" s="17" t="s">
-        <v>1297</v>
-      </c>
-      <c r="K159" s="21" t="s">
-        <v>1298</v>
-      </c>
-      <c r="L159" s="14" t="s">
-        <v>1299</v>
-      </c>
-      <c r="M159" s="21"/>
-      <c r="N159" s="21" t="s">
-        <v>1300</v>
-      </c>
-      <c r="O159" s="17" t="s">
-        <v>554</v>
-      </c>
-      <c r="P159" s="21" t="s">
-        <v>1301</v>
-      </c>
-      <c r="Q159" s="21">
-        <v>27</v>
+    <row r="159" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="14" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D159" s="1"/>
+      <c r="E159" s="1"/>
+      <c r="F159" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="H159" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J159" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="K159" s="1"/>
+      <c r="L159" s="13" t="s">
+        <v>1056</v>
+      </c>
+      <c r="M159" s="13"/>
+      <c r="N159" s="13"/>
+      <c r="O159" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P159" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="Q159" s="1" t="s">
+        <v>1058</v>
       </c>
       <c r="R159" s="1" t="s">
-        <v>348</v>
+        <v>807</v>
       </c>
       <c r="S159" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="160" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="16" t="s">
+    <row r="160" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="14" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B160" s="15" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C160" s="15" t="s">
         <v>1051</v>
       </c>
-      <c r="B160" s="13" t="s">
+      <c r="D160" s="3"/>
+      <c r="E160" s="3"/>
+      <c r="F160" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="G160" s="1" t="s">
         <v>1052</v>
       </c>
-      <c r="C160" s="13" t="s">
-        <v>1053</v>
-      </c>
-      <c r="D160" s="13"/>
-      <c r="E160" s="13"/>
-      <c r="F160" s="13" t="s">
-        <v>801</v>
-      </c>
-      <c r="G160" s="13" t="s">
+      <c r="H160" s="15" t="s">
+        <v>809</v>
+      </c>
+      <c r="I160" s="15" t="s">
         <v>1054</v>
       </c>
-      <c r="H160" s="13" t="s">
-        <v>1055</v>
-      </c>
-      <c r="I160" s="13" t="s">
-        <v>1056</v>
-      </c>
-      <c r="J160" s="13" t="s">
-        <v>1057</v>
-      </c>
-      <c r="K160" s="13"/>
-      <c r="L160" s="14" t="s">
-        <v>1058</v>
-      </c>
-      <c r="M160" s="14"/>
-      <c r="N160" s="14"/>
-      <c r="O160" s="13" t="s">
+      <c r="J160" s="15" t="s">
+        <v>1060</v>
+      </c>
+      <c r="K160" s="6"/>
+      <c r="L160" s="13" t="s">
+        <v>543</v>
+      </c>
+      <c r="M160" s="6"/>
+      <c r="N160" s="6"/>
+      <c r="O160" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="P160" s="6"/>
+      <c r="Q160" s="6"/>
+      <c r="R160" s="15" t="s">
+        <v>807</v>
+      </c>
+      <c r="S160" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="14" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="H161" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="I161" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="J161" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="K161" s="1"/>
+      <c r="L161" s="13" t="s">
+        <v>1066</v>
+      </c>
+      <c r="M161" s="13"/>
+      <c r="N161" s="13"/>
+      <c r="O161" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="P160" s="13" t="s">
-        <v>1059</v>
-      </c>
-      <c r="Q160" s="13" t="s">
-        <v>1060</v>
-      </c>
-      <c r="R160" s="13" t="s">
-        <v>807</v>
-      </c>
-      <c r="S160" s="13">
+      <c r="P161" s="1"/>
+      <c r="Q161" s="1"/>
+      <c r="R161" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S161" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="16" t="s">
-        <v>1061</v>
-      </c>
-      <c r="B161" s="17" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C161" s="17" t="s">
-        <v>1053</v>
-      </c>
-      <c r="D161" s="15"/>
-      <c r="E161" s="15"/>
-      <c r="F161" s="13" t="s">
-        <v>801</v>
-      </c>
-      <c r="G161" s="13" t="s">
-        <v>1054</v>
-      </c>
-      <c r="H161" s="17" t="s">
-        <v>809</v>
-      </c>
-      <c r="I161" s="17" t="s">
-        <v>1056</v>
-      </c>
-      <c r="J161" s="17" t="s">
+    <row r="162" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="14" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B162" s="15" t="s">
         <v>1062</v>
       </c>
-      <c r="K161" s="18"/>
-      <c r="L161" s="14" t="s">
-        <v>543</v>
-      </c>
-      <c r="M161" s="18"/>
-      <c r="N161" s="18"/>
-      <c r="O161" s="17" t="s">
-        <v>412</v>
-      </c>
-      <c r="P161" s="18"/>
-      <c r="Q161" s="18"/>
-      <c r="R161" s="17" t="s">
-        <v>807</v>
-      </c>
-      <c r="S161" s="17">
+      <c r="C162" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="H162" s="15" t="s">
+        <v>1068</v>
+      </c>
+      <c r="I162" s="15" t="s">
+        <v>1069</v>
+      </c>
+      <c r="J162" s="15" t="s">
+        <v>1070</v>
+      </c>
+      <c r="K162" s="6"/>
+      <c r="L162" s="13" t="s">
+        <v>846</v>
+      </c>
+      <c r="M162" s="6"/>
+      <c r="N162" s="6"/>
+      <c r="O162" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="P162" s="6"/>
+      <c r="Q162" s="6"/>
+      <c r="R162" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="S162" s="15">
         <v>3</v>
       </c>
     </row>
-    <row r="162" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="16" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B162" s="13" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C162" s="13" t="s">
-        <v>394</v>
-      </c>
-      <c r="D162" s="13" t="s">
-        <v>1065</v>
-      </c>
-      <c r="E162" s="13" t="s">
-        <v>1065</v>
-      </c>
-      <c r="F162" s="13" t="s">
-        <v>1066</v>
-      </c>
-      <c r="G162" s="13" t="s">
-        <v>457</v>
-      </c>
-      <c r="H162" s="13" t="s">
-        <v>956</v>
-      </c>
-      <c r="I162" s="13" t="s">
-        <v>840</v>
-      </c>
-      <c r="J162" s="13" t="s">
-        <v>1067</v>
-      </c>
-      <c r="K162" s="13"/>
-      <c r="L162" s="14" t="s">
-        <v>1068</v>
-      </c>
-      <c r="M162" s="14"/>
-      <c r="N162" s="14"/>
-      <c r="O162" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="P162" s="13"/>
-      <c r="Q162" s="13"/>
-      <c r="R162" s="13" t="s">
+    <row r="163" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="14" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D163" s="1"/>
+      <c r="E163" s="1"/>
+      <c r="F163" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H163" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J163" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="K163" s="1"/>
+      <c r="L163" s="13" t="s">
+        <v>1078</v>
+      </c>
+      <c r="M163" s="13"/>
+      <c r="N163" s="13" t="s">
+        <v>1079</v>
+      </c>
+      <c r="O163" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="P163" s="1"/>
+      <c r="Q163" s="1"/>
+      <c r="R163" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="S162" s="13">
+      <c r="S163" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="16" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B163" s="17" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C163" s="17" t="s">
-        <v>394</v>
-      </c>
-      <c r="D163" s="13" t="s">
-        <v>1065</v>
-      </c>
-      <c r="E163" s="13" t="s">
-        <v>1065</v>
-      </c>
-      <c r="F163" s="13" t="s">
-        <v>1066</v>
-      </c>
-      <c r="G163" s="13" t="s">
-        <v>457</v>
-      </c>
-      <c r="H163" s="17" t="s">
-        <v>1070</v>
-      </c>
-      <c r="I163" s="17" t="s">
-        <v>1071</v>
-      </c>
-      <c r="J163" s="17" t="s">
+    <row r="164" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="16" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B164" s="15" t="s">
         <v>1072</v>
       </c>
-      <c r="K163" s="18"/>
-      <c r="L163" s="14" t="s">
-        <v>846</v>
-      </c>
-      <c r="M163" s="18"/>
-      <c r="N163" s="18"/>
-      <c r="O163" s="17" t="s">
+      <c r="C164" s="15" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D164" s="3"/>
+      <c r="E164" s="3"/>
+      <c r="F164" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H164" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="I164" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="J164" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="K164" s="6"/>
+      <c r="L164" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="M164" s="6"/>
+      <c r="N164" s="6"/>
+      <c r="O164" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="P163" s="18"/>
-      <c r="Q163" s="18"/>
-      <c r="R163" s="17" t="s">
+      <c r="P164" s="6"/>
+      <c r="Q164" s="6"/>
+      <c r="R164" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="S163" s="17">
+      <c r="S164" s="15">
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="16" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B164" s="13" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C164" s="13" t="s">
-        <v>1075</v>
-      </c>
-      <c r="D164" s="13"/>
-      <c r="E164" s="13"/>
-      <c r="F164" s="13" t="s">
-        <v>1076</v>
-      </c>
-      <c r="G164" s="13" t="s">
-        <v>1077</v>
-      </c>
-      <c r="H164" s="13" t="s">
-        <v>1078</v>
-      </c>
-      <c r="I164" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="J164" s="13" t="s">
-        <v>1079</v>
-      </c>
-      <c r="K164" s="13"/>
-      <c r="L164" s="14" t="s">
-        <v>1080</v>
-      </c>
-      <c r="M164" s="14"/>
-      <c r="N164" s="14" t="s">
+    <row r="165" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="14" t="s">
         <v>1081</v>
       </c>
-      <c r="O164" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="P164" s="13"/>
-      <c r="Q164" s="13"/>
-      <c r="R164" s="13" t="s">
+      <c r="B165" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D165" s="1"/>
+      <c r="E165" s="1"/>
+      <c r="F165" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H165" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="I165" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J165" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K165" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="L165" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="M165" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="N165" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="O165" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="P165" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="Q165" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="R165" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="S164" s="13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="165" spans="1:19" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="19" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B165" s="17" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C165" s="17" t="s">
-        <v>1075</v>
-      </c>
-      <c r="D165" s="15"/>
-      <c r="E165" s="15"/>
-      <c r="F165" s="13" t="s">
-        <v>1076</v>
-      </c>
-      <c r="G165" s="13" t="s">
-        <v>1077</v>
-      </c>
-      <c r="H165" s="17" t="s">
+      <c r="S165" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="21" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>1082</v>
       </c>
-      <c r="I165" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="J165" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="K165" s="18"/>
-      <c r="L165" s="14" t="s">
-        <v>332</v>
-      </c>
-      <c r="M165" s="18"/>
-      <c r="N165" s="18"/>
-      <c r="O165" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="P165" s="18"/>
-      <c r="Q165" s="18"/>
-      <c r="R165" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="S165" s="17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="166" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="16" t="s">
+      <c r="C166" s="1" t="s">
         <v>1083</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>1084</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>1085</v>
       </c>
       <c r="D166" s="1"/>
       <c r="E166" s="1"/>
       <c r="F166" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>279</v>
+        <v>1094</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>44</v>
@@ -13069,25 +13059,25 @@
         <v>45</v>
       </c>
       <c r="K166" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="L166" s="5" t="s">
+        <v>1095</v>
+      </c>
+      <c r="M166" s="5" t="s">
         <v>1088</v>
       </c>
-      <c r="L166" s="2" t="s">
-        <v>1089</v>
-      </c>
-      <c r="M166" s="2" t="s">
-        <v>1090</v>
-      </c>
-      <c r="N166" s="2" t="s">
-        <v>1091</v>
+      <c r="N166" s="1" t="s">
+        <v>1096</v>
       </c>
       <c r="O166" s="1" t="s">
-        <v>1092</v>
+        <v>459</v>
       </c>
       <c r="P166" s="1" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="Q166" s="1" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="R166" s="1" t="s">
         <v>29</v>
@@ -13096,26 +13086,26 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="24" t="s">
-        <v>1095</v>
+    <row r="167" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="21" t="s">
+        <v>1099</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="D167" s="1"/>
       <c r="E167" s="1"/>
       <c r="F167" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>1096</v>
+        <v>669</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>44</v>
@@ -13124,25 +13114,25 @@
         <v>45</v>
       </c>
       <c r="K167" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="L167" s="5" t="s">
+        <v>1100</v>
+      </c>
+      <c r="M167" s="5" t="s">
         <v>1088</v>
       </c>
-      <c r="L167" s="5" t="s">
-        <v>1097</v>
-      </c>
-      <c r="M167" s="5" t="s">
-        <v>1090</v>
-      </c>
       <c r="N167" s="1" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="O167" s="1" t="s">
         <v>459</v>
       </c>
       <c r="P167" s="1" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="Q167" s="1" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="R167" s="1" t="s">
         <v>29</v>
@@ -13151,26 +13141,26 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="24" t="s">
-        <v>1101</v>
+    <row r="168" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="14" t="s">
+        <v>1104</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="D168" s="1"/>
       <c r="E168" s="1"/>
       <c r="F168" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>669</v>
+        <v>1105</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>44</v>
@@ -13179,25 +13169,25 @@
         <v>45</v>
       </c>
       <c r="K168" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="L168" s="5" t="s">
+        <v>1106</v>
+      </c>
+      <c r="M168" s="5" t="s">
         <v>1088</v>
       </c>
-      <c r="L168" s="5" t="s">
-        <v>1102</v>
-      </c>
-      <c r="M168" s="5" t="s">
-        <v>1090</v>
-      </c>
       <c r="N168" s="1" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="O168" s="1" t="s">
         <v>459</v>
       </c>
       <c r="P168" s="1" t="s">
-        <v>1104</v>
+        <v>480</v>
       </c>
       <c r="Q168" s="1" t="s">
-        <v>1105</v>
+        <v>585</v>
       </c>
       <c r="R168" s="1" t="s">
         <v>29</v>
@@ -13206,26 +13196,26 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="16" t="s">
-        <v>1106</v>
+    <row r="169" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="14" t="s">
+        <v>1108</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="D169" s="1"/>
       <c r="E169" s="1"/>
       <c r="F169" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>1107</v>
+        <v>689</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>44</v>
@@ -13234,16 +13224,16 @@
         <v>45</v>
       </c>
       <c r="K169" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="L169" s="5" t="s">
+        <v>1109</v>
+      </c>
+      <c r="M169" s="5" t="s">
         <v>1088</v>
       </c>
-      <c r="L169" s="5" t="s">
-        <v>1108</v>
-      </c>
-      <c r="M169" s="5" t="s">
-        <v>1090</v>
-      </c>
       <c r="N169" s="1" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="O169" s="1" t="s">
         <v>459</v>
@@ -13252,7 +13242,7 @@
         <v>480</v>
       </c>
       <c r="Q169" s="1" t="s">
-        <v>585</v>
+        <v>1111</v>
       </c>
       <c r="R169" s="1" t="s">
         <v>29</v>
@@ -13261,26 +13251,26 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="16" t="s">
-        <v>1110</v>
+    <row r="170" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="14" t="s">
+        <v>1112</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="D170" s="1"/>
       <c r="E170" s="1"/>
       <c r="F170" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>689</v>
+        <v>1105</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>44</v>
@@ -13289,25 +13279,25 @@
         <v>45</v>
       </c>
       <c r="K170" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="L170" s="22" t="s">
+        <v>1113</v>
+      </c>
+      <c r="M170" s="22" t="s">
         <v>1088</v>
       </c>
-      <c r="L170" s="5" t="s">
-        <v>1111</v>
-      </c>
-      <c r="M170" s="5" t="s">
-        <v>1090</v>
-      </c>
       <c r="N170" s="1" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="O170" s="1" t="s">
         <v>459</v>
       </c>
       <c r="P170" s="1" t="s">
-        <v>480</v>
+        <v>1115</v>
       </c>
       <c r="Q170" s="1" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="R170" s="1" t="s">
         <v>29</v>
@@ -13316,26 +13306,26 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="16" t="s">
-        <v>1114</v>
+    <row r="171" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="14" t="s">
+        <v>1117</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="D171" s="1"/>
       <c r="E171" s="1"/>
       <c r="F171" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>1107</v>
+        <v>689</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>44</v>
@@ -13344,25 +13334,25 @@
         <v>45</v>
       </c>
       <c r="K171" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="L171" s="22" t="s">
+        <v>1118</v>
+      </c>
+      <c r="M171" s="22" t="s">
         <v>1088</v>
       </c>
-      <c r="L171" s="25" t="s">
-        <v>1115</v>
-      </c>
-      <c r="M171" s="25" t="s">
-        <v>1090</v>
-      </c>
       <c r="N171" s="1" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="O171" s="1" t="s">
         <v>459</v>
       </c>
       <c r="P171" s="1" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="Q171" s="1" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="R171" s="1" t="s">
         <v>29</v>
@@ -13371,26 +13361,26 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="16" t="s">
-        <v>1119</v>
+    <row r="172" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="14" t="s">
+        <v>1122</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="D172" s="1"/>
       <c r="E172" s="1"/>
       <c r="F172" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>689</v>
+        <v>1123</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>44</v>
@@ -13399,25 +13389,25 @@
         <v>45</v>
       </c>
       <c r="K172" s="1" t="s">
-        <v>1088</v>
-      </c>
-      <c r="L172" s="25" t="s">
-        <v>1120</v>
-      </c>
-      <c r="M172" s="25" t="s">
-        <v>1090</v>
+        <v>1124</v>
+      </c>
+      <c r="L172" s="22" t="s">
+        <v>1125</v>
+      </c>
+      <c r="M172" s="22" t="s">
+        <v>1126</v>
       </c>
       <c r="N172" s="1" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="O172" s="1" t="s">
-        <v>459</v>
+        <v>286</v>
       </c>
       <c r="P172" s="1" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
       <c r="Q172" s="1" t="s">
-        <v>1123</v>
+        <v>738</v>
       </c>
       <c r="R172" s="1" t="s">
         <v>29</v>
@@ -13426,53 +13416,51 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="16" t="s">
-        <v>1124</v>
+    <row r="173" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="14" t="s">
+        <v>1129</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="D173" s="1"/>
       <c r="E173" s="1"/>
       <c r="F173" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>1125</v>
+        <v>771</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>44</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>45</v>
+        <v>1130</v>
       </c>
       <c r="K173" s="1" t="s">
-        <v>1126</v>
-      </c>
-      <c r="L173" s="25" t="s">
-        <v>1127</v>
-      </c>
-      <c r="M173" s="25" t="s">
-        <v>1128</v>
-      </c>
+        <v>1131</v>
+      </c>
+      <c r="L173" s="22" t="s">
+        <v>1132</v>
+      </c>
+      <c r="M173" s="22"/>
       <c r="N173" s="1" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="O173" s="1" t="s">
-        <v>286</v>
+        <v>345</v>
       </c>
       <c r="P173" s="1" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="Q173" s="1" t="s">
-        <v>738</v>
+        <v>1135</v>
       </c>
       <c r="R173" s="1" t="s">
         <v>29</v>
@@ -13481,51 +13469,51 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="16" t="s">
-        <v>1131</v>
+    <row r="174" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="14" t="s">
+        <v>1136</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="D174" s="1"/>
       <c r="E174" s="1"/>
       <c r="F174" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="H174" s="1" t="s">
         <v>771</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>44</v>
+        <v>683</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>1132</v>
+        <v>1048</v>
       </c>
       <c r="K174" s="1" t="s">
-        <v>1133</v>
-      </c>
-      <c r="L174" s="25" t="s">
-        <v>1134</v>
-      </c>
-      <c r="M174" s="25"/>
+        <v>1137</v>
+      </c>
+      <c r="L174" s="22" t="s">
+        <v>1138</v>
+      </c>
+      <c r="M174" s="22"/>
       <c r="N174" s="1" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="O174" s="1" t="s">
         <v>345</v>
       </c>
       <c r="P174" s="1" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="Q174" s="1" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="R174" s="1" t="s">
         <v>29</v>
@@ -13534,51 +13522,51 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="16" t="s">
-        <v>1138</v>
+    <row r="175" spans="1:19" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="23" t="s">
+        <v>1142</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>1085</v>
-      </c>
-      <c r="D175" s="1"/>
-      <c r="E175" s="1"/>
-      <c r="F175" s="1" t="s">
-        <v>1086</v>
-      </c>
-      <c r="G175" s="1" t="s">
-        <v>1087</v>
-      </c>
-      <c r="H175" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="I175" s="1" t="s">
-        <v>683</v>
-      </c>
-      <c r="J175" s="1" t="s">
-        <v>1050</v>
-      </c>
-      <c r="K175" s="1" t="s">
-        <v>1139</v>
-      </c>
-      <c r="L175" s="25" t="s">
-        <v>1140</v>
-      </c>
-      <c r="M175" s="25"/>
-      <c r="N175" s="1" t="s">
-        <v>1141</v>
-      </c>
-      <c r="O175" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="P175" s="1" t="s">
-        <v>1142</v>
-      </c>
-      <c r="Q175" s="1" t="s">
-        <v>1143</v>
+        <v>1144</v>
+      </c>
+      <c r="D175" s="6"/>
+      <c r="E175" s="6"/>
+      <c r="F175" s="6">
+        <v>1452</v>
+      </c>
+      <c r="G175" s="6">
+        <v>1517</v>
+      </c>
+      <c r="H175" s="6" t="s">
+        <v>1145</v>
+      </c>
+      <c r="I175" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J175" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="K175" s="6" t="s">
+        <v>1146</v>
+      </c>
+      <c r="L175" s="6" t="s">
+        <v>648</v>
+      </c>
+      <c r="M175" s="6"/>
+      <c r="N175" s="6" t="s">
+        <v>1147</v>
+      </c>
+      <c r="O175" s="6" t="s">
+        <v>951</v>
+      </c>
+      <c r="P175" s="6" t="s">
+        <v>1148</v>
+      </c>
+      <c r="Q175" s="6" t="s">
+        <v>1149</v>
       </c>
       <c r="R175" s="1" t="s">
         <v>29</v>
@@ -13587,15 +13575,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="26" t="s">
+    <row r="176" spans="1:19" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="23" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C176" s="1" t="s">
         <v>1144</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>1145</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>1146</v>
       </c>
       <c r="D176" s="6"/>
       <c r="E176" s="6"/>
@@ -13606,32 +13594,32 @@
         <v>1517</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="I176" s="6" t="s">
-        <v>25</v>
+        <v>645</v>
       </c>
       <c r="J176" s="6" t="s">
-        <v>154</v>
+        <v>646</v>
       </c>
       <c r="K176" s="6" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="L176" s="6" t="s">
-        <v>648</v>
+        <v>1153</v>
       </c>
       <c r="M176" s="6"/>
       <c r="N176" s="6" t="s">
-        <v>1149</v>
+        <v>1154</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>951</v>
+        <v>1155</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>1150</v>
+        <v>1156</v>
       </c>
       <c r="Q176" s="6" t="s">
-        <v>1151</v>
+        <v>1157</v>
       </c>
       <c r="R176" s="1" t="s">
         <v>29</v>
@@ -13640,17 +13628,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="26" t="s">
-        <v>1152</v>
+    <row r="177" spans="1:19" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="23" t="s">
+        <v>1158</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>1146</v>
-      </c>
-      <c r="D177" s="6"/>
+        <v>1144</v>
+      </c>
+      <c r="D177" s="3"/>
       <c r="E177" s="6"/>
       <c r="F177" s="6">
         <v>1452</v>
@@ -13659,32 +13647,32 @@
         <v>1517</v>
       </c>
       <c r="H177" s="6" t="s">
-        <v>1153</v>
+        <v>1159</v>
       </c>
       <c r="I177" s="6" t="s">
-        <v>645</v>
+        <v>1160</v>
       </c>
       <c r="J177" s="6" t="s">
-        <v>646</v>
+        <v>1161</v>
       </c>
       <c r="K177" s="6" t="s">
-        <v>1154</v>
+        <v>1162</v>
       </c>
       <c r="L177" s="6" t="s">
-        <v>1155</v>
+        <v>1163</v>
       </c>
       <c r="M177" s="6"/>
       <c r="N177" s="6" t="s">
-        <v>1156</v>
+        <v>1164</v>
       </c>
       <c r="O177" s="6" t="s">
-        <v>1157</v>
+        <v>1165</v>
       </c>
       <c r="P177" s="6" t="s">
-        <v>1158</v>
+        <v>1166</v>
       </c>
       <c r="Q177" s="6" t="s">
-        <v>1159</v>
+        <v>1167</v>
       </c>
       <c r="R177" s="1" t="s">
         <v>29</v>
@@ -13693,17 +13681,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="26" t="s">
-        <v>1160</v>
+    <row r="178" spans="1:19" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="23" t="s">
+        <v>1168</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>1146</v>
-      </c>
-      <c r="D178" s="3"/>
+        <v>1144</v>
+      </c>
+      <c r="D178" s="6"/>
       <c r="E178" s="6"/>
       <c r="F178" s="6">
         <v>1452</v>
@@ -13712,32 +13700,32 @@
         <v>1517</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>1161</v>
+        <v>1169</v>
       </c>
       <c r="I178" s="6" t="s">
-        <v>1162</v>
+        <v>25</v>
       </c>
       <c r="J178" s="6" t="s">
-        <v>1163</v>
+        <v>154</v>
       </c>
       <c r="K178" s="6" t="s">
-        <v>1164</v>
+        <v>1146</v>
       </c>
       <c r="L178" s="6" t="s">
-        <v>1165</v>
+        <v>1170</v>
       </c>
       <c r="M178" s="6"/>
       <c r="N178" s="6" t="s">
-        <v>1166</v>
+        <v>1171</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>1167</v>
+        <v>345</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="Q178" s="6" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="R178" s="1" t="s">
         <v>29</v>
@@ -13746,15 +13734,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="26" t="s">
-        <v>1170</v>
+    <row r="179" spans="1:19" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="23" t="s">
+        <v>1174</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="D179" s="6"/>
       <c r="E179" s="6"/>
@@ -13765,32 +13753,32 @@
         <v>1517</v>
       </c>
       <c r="H179" s="6" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="I179" s="6" t="s">
-        <v>25</v>
+        <v>861</v>
       </c>
       <c r="J179" s="6" t="s">
-        <v>154</v>
+        <v>270</v>
       </c>
       <c r="K179" s="6" t="s">
-        <v>1148</v>
+        <v>862</v>
       </c>
       <c r="L179" s="6" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="M179" s="6"/>
       <c r="N179" s="6" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="O179" s="6" t="s">
-        <v>345</v>
+        <v>1178</v>
       </c>
       <c r="P179" s="6" t="s">
-        <v>1174</v>
+        <v>1179</v>
       </c>
       <c r="Q179" s="6" t="s">
-        <v>1175</v>
+        <v>1180</v>
       </c>
       <c r="R179" s="1" t="s">
         <v>29</v>
@@ -13799,15 +13787,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="26" t="s">
-        <v>1176</v>
+    <row r="180" spans="1:19" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="23" t="s">
+        <v>1181</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="D180" s="6"/>
       <c r="E180" s="6"/>
@@ -13818,32 +13806,32 @@
         <v>1517</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>1177</v>
+        <v>1182</v>
       </c>
       <c r="I180" s="6" t="s">
-        <v>861</v>
+        <v>32</v>
       </c>
       <c r="J180" s="6" t="s">
-        <v>270</v>
+        <v>33</v>
       </c>
       <c r="K180" s="6" t="s">
-        <v>862</v>
+        <v>1183</v>
       </c>
       <c r="L180" s="6" t="s">
-        <v>1178</v>
+        <v>1184</v>
       </c>
       <c r="M180" s="6"/>
       <c r="N180" s="6" t="s">
-        <v>1179</v>
+        <v>1185</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>1180</v>
+        <v>1186</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>1181</v>
+        <v>1187</v>
       </c>
       <c r="Q180" s="6" t="s">
-        <v>1182</v>
+        <v>1188</v>
       </c>
       <c r="R180" s="1" t="s">
         <v>29</v>
@@ -13852,15 +13840,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="26" t="s">
-        <v>1183</v>
+    <row r="181" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="21" t="s">
+        <v>1189</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="D181" s="6"/>
       <c r="E181" s="6"/>
@@ -13871,32 +13859,32 @@
         <v>1517</v>
       </c>
       <c r="H181" s="6" t="s">
-        <v>1184</v>
+        <v>1190</v>
       </c>
       <c r="I181" s="6" t="s">
-        <v>32</v>
+        <v>122</v>
       </c>
       <c r="J181" s="6" t="s">
-        <v>33</v>
+        <v>1191</v>
       </c>
       <c r="K181" s="6" t="s">
-        <v>1185</v>
+        <v>1192</v>
       </c>
       <c r="L181" s="6" t="s">
-        <v>1186</v>
+        <v>1193</v>
       </c>
       <c r="M181" s="6"/>
       <c r="N181" s="6" t="s">
-        <v>1187</v>
+        <v>1194</v>
       </c>
       <c r="O181" s="6" t="s">
-        <v>1188</v>
+        <v>1195</v>
       </c>
       <c r="P181" s="6" t="s">
-        <v>1189</v>
-      </c>
-      <c r="Q181" s="6" t="s">
-        <v>1190</v>
+        <v>1196</v>
+      </c>
+      <c r="Q181" s="6">
+        <v>32</v>
       </c>
       <c r="R181" s="1" t="s">
         <v>29</v>
@@ -13905,15 +13893,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="24" t="s">
-        <v>1191</v>
+    <row r="182" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="21" t="s">
+        <v>1197</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="D182" s="6"/>
       <c r="E182" s="6"/>
@@ -13924,32 +13912,32 @@
         <v>1517</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>1192</v>
+        <v>1198</v>
       </c>
       <c r="I182" s="6" t="s">
-        <v>122</v>
+        <v>1199</v>
       </c>
       <c r="J182" s="6" t="s">
-        <v>1193</v>
+        <v>1200</v>
       </c>
       <c r="K182" s="6" t="s">
-        <v>1194</v>
+        <v>36</v>
       </c>
       <c r="L182" s="6" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="M182" s="6"/>
       <c r="N182" s="6" t="s">
-        <v>1196</v>
+        <v>1202</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>1198</v>
-      </c>
-      <c r="Q182" s="6">
-        <v>32</v>
+        <v>1204</v>
+      </c>
+      <c r="Q182" s="6" t="s">
+        <v>1205</v>
       </c>
       <c r="R182" s="1" t="s">
         <v>29</v>
@@ -13958,15 +13946,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="24" t="s">
-        <v>1199</v>
+    <row r="183" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="23" t="s">
+        <v>1206</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="D183" s="6"/>
       <c r="E183" s="6"/>
@@ -13977,32 +13965,32 @@
         <v>1517</v>
       </c>
       <c r="H183" s="6" t="s">
-        <v>1200</v>
+        <v>1207</v>
       </c>
       <c r="I183" s="6" t="s">
-        <v>1201</v>
+        <v>32</v>
       </c>
       <c r="J183" s="6" t="s">
-        <v>1202</v>
+        <v>33</v>
       </c>
       <c r="K183" s="6" t="s">
-        <v>36</v>
+        <v>1208</v>
       </c>
       <c r="L183" s="6" t="s">
-        <v>1203</v>
+        <v>1209</v>
       </c>
       <c r="M183" s="6"/>
       <c r="N183" s="6" t="s">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="O183" s="6" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="P183" s="6" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
       <c r="Q183" s="6" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="R183" s="1" t="s">
         <v>29</v>
@@ -14011,15 +13999,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="26" t="s">
-        <v>1208</v>
+    <row r="184" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="23" t="s">
+        <v>1212</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="D184" s="6"/>
       <c r="E184" s="6"/>
@@ -14030,32 +14018,32 @@
         <v>1517</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="I184" s="6" t="s">
-        <v>32</v>
+        <v>122</v>
       </c>
       <c r="J184" s="6" t="s">
-        <v>33</v>
+        <v>1214</v>
       </c>
       <c r="K184" s="6" t="s">
-        <v>1210</v>
+        <v>1215</v>
       </c>
       <c r="L184" s="6" t="s">
-        <v>1211</v>
+        <v>64</v>
       </c>
       <c r="M184" s="6"/>
       <c r="N184" s="6" t="s">
-        <v>1211</v>
+        <v>1216</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>1205</v>
+        <v>1217</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>1212</v>
+        <v>1218</v>
       </c>
       <c r="Q184" s="6" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="R184" s="1" t="s">
         <v>29</v>
@@ -14064,51 +14052,53 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="26" t="s">
-        <v>1214</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>1145</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>1146</v>
-      </c>
-      <c r="D185" s="6"/>
-      <c r="E185" s="6"/>
-      <c r="F185" s="6">
-        <v>1452</v>
-      </c>
-      <c r="G185" s="6">
-        <v>1517</v>
+    <row r="185" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="14" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D185" s="3"/>
+      <c r="E185" s="3"/>
+      <c r="F185" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>1224</v>
       </c>
       <c r="H185" s="6" t="s">
-        <v>1215</v>
+        <v>1225</v>
       </c>
       <c r="I185" s="6" t="s">
-        <v>122</v>
+        <v>25</v>
       </c>
       <c r="J185" s="6" t="s">
-        <v>1216</v>
+        <v>79</v>
       </c>
       <c r="K185" s="6" t="s">
-        <v>1217</v>
+        <v>1226</v>
       </c>
       <c r="L185" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="M185" s="6"/>
+        <v>1227</v>
+      </c>
+      <c r="M185" s="6" t="s">
+        <v>1228</v>
+      </c>
       <c r="N185" s="6" t="s">
-        <v>1218</v>
+        <v>1229</v>
       </c>
       <c r="O185" s="6" t="s">
-        <v>1219</v>
-      </c>
-      <c r="P185" s="6" t="s">
-        <v>1220</v>
-      </c>
-      <c r="Q185" s="6" t="s">
-        <v>1221</v>
+        <v>109</v>
+      </c>
+      <c r="P185" s="6">
+        <v>167</v>
+      </c>
+      <c r="Q185" s="6">
+        <v>87</v>
       </c>
       <c r="R185" s="1" t="s">
         <v>29</v>
@@ -14117,26 +14107,26 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="16" t="s">
+    <row r="186" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="14" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C186" s="6" t="s">
         <v>1222</v>
-      </c>
-      <c r="B186" s="6" t="s">
-        <v>1223</v>
-      </c>
-      <c r="C186" s="6" t="s">
-        <v>1224</v>
       </c>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
       <c r="F186" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>1227</v>
+        <v>296</v>
       </c>
       <c r="I186" s="6" t="s">
         <v>25</v>
@@ -14145,25 +14135,23 @@
         <v>79</v>
       </c>
       <c r="K186" s="6" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="L186" s="6" t="s">
-        <v>1229</v>
-      </c>
-      <c r="M186" s="6" t="s">
-        <v>1230</v>
-      </c>
+        <v>1170</v>
+      </c>
+      <c r="M186" s="6"/>
       <c r="N186" s="6" t="s">
-        <v>1231</v>
+        <v>1171</v>
       </c>
       <c r="O186" s="6" t="s">
         <v>109</v>
       </c>
       <c r="P186" s="6">
-        <v>167</v>
+        <v>111</v>
       </c>
       <c r="Q186" s="6">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="R186" s="1" t="s">
         <v>29</v>
@@ -14172,26 +14160,26 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="16" t="s">
-        <v>1232</v>
+    <row r="187" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="14" t="s">
+        <v>1231</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
       <c r="F187" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="H187" s="6" t="s">
-        <v>296</v>
+        <v>1232</v>
       </c>
       <c r="I187" s="6" t="s">
         <v>25</v>
@@ -14200,23 +14188,23 @@
         <v>79</v>
       </c>
       <c r="K187" s="6" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="L187" s="6" t="s">
-        <v>1172</v>
+        <v>1233</v>
       </c>
       <c r="M187" s="6"/>
       <c r="N187" s="6" t="s">
-        <v>1173</v>
+        <v>1234</v>
       </c>
       <c r="O187" s="6" t="s">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="P187" s="6">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="Q187" s="6">
-        <v>134</v>
+        <v>314</v>
       </c>
       <c r="R187" s="1" t="s">
         <v>29</v>
@@ -14225,26 +14213,26 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="16" t="s">
-        <v>1233</v>
+    <row r="188" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="14" t="s">
+        <v>1235</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
       <c r="F188" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>1234</v>
+        <v>268</v>
       </c>
       <c r="I188" s="6" t="s">
         <v>25</v>
@@ -14253,23 +14241,23 @@
         <v>79</v>
       </c>
       <c r="K188" s="6" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="L188" s="6" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="M188" s="6"/>
       <c r="N188" s="6" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>159</v>
+        <v>1238</v>
       </c>
       <c r="P188" s="6">
-        <v>203</v>
+        <v>118</v>
       </c>
       <c r="Q188" s="6">
-        <v>314</v>
+        <v>118</v>
       </c>
       <c r="R188" s="1" t="s">
         <v>29</v>
@@ -14278,51 +14266,53 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="16" t="s">
-        <v>1237</v>
+    <row r="189" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="14" t="s">
+        <v>1239</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
       <c r="F189" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="H189" s="6" t="s">
         <v>268</v>
       </c>
       <c r="I189" s="6" t="s">
-        <v>25</v>
+        <v>269</v>
       </c>
       <c r="J189" s="6" t="s">
-        <v>79</v>
+        <v>270</v>
       </c>
       <c r="K189" s="6" t="s">
-        <v>1228</v>
+        <v>971</v>
       </c>
       <c r="L189" s="6" t="s">
-        <v>1238</v>
-      </c>
-      <c r="M189" s="6"/>
+        <v>1240</v>
+      </c>
+      <c r="M189" s="6" t="s">
+        <v>1241</v>
+      </c>
       <c r="N189" s="6" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="O189" s="6" t="s">
-        <v>1240</v>
+        <v>66</v>
       </c>
       <c r="P189" s="6">
-        <v>118</v>
+        <v>348</v>
       </c>
       <c r="Q189" s="6">
-        <v>118</v>
+        <v>558</v>
       </c>
       <c r="R189" s="1" t="s">
         <v>29</v>
@@ -14331,53 +14321,51 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="16" t="s">
-        <v>1241</v>
+    <row r="190" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="14" t="s">
+        <v>1243</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
       <c r="F190" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>268</v>
+        <v>1244</v>
       </c>
       <c r="I190" s="6" t="s">
-        <v>269</v>
+        <v>86</v>
       </c>
       <c r="J190" s="6" t="s">
-        <v>270</v>
+        <v>87</v>
       </c>
       <c r="K190" s="6" t="s">
-        <v>971</v>
+        <v>112</v>
       </c>
       <c r="L190" s="6" t="s">
-        <v>1242</v>
-      </c>
-      <c r="M190" s="6" t="s">
-        <v>1243</v>
-      </c>
+        <v>1245</v>
+      </c>
+      <c r="M190" s="6"/>
       <c r="N190" s="6" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>66</v>
+        <v>1247</v>
       </c>
       <c r="P190" s="6">
-        <v>348</v>
+        <v>69</v>
       </c>
       <c r="Q190" s="6">
-        <v>558</v>
+        <v>173</v>
       </c>
       <c r="R190" s="1" t="s">
         <v>29</v>
@@ -14386,51 +14374,51 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="16" t="s">
-        <v>1245</v>
+    <row r="191" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="14" t="s">
+        <v>1248</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
       <c r="F191" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="G191" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H191" s="6" t="s">
+        <v>1249</v>
+      </c>
+      <c r="I191" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J191" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="K191" s="6" t="s">
         <v>1226</v>
       </c>
-      <c r="H191" s="6" t="s">
-        <v>1246</v>
-      </c>
-      <c r="I191" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="J191" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="K191" s="6" t="s">
-        <v>112</v>
-      </c>
       <c r="L191" s="6" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="M191" s="6"/>
       <c r="N191" s="6" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="O191" s="6" t="s">
-        <v>1249</v>
+        <v>109</v>
       </c>
       <c r="P191" s="6">
-        <v>69</v>
+        <v>150</v>
       </c>
       <c r="Q191" s="6">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="R191" s="1" t="s">
         <v>29</v>
@@ -14439,26 +14427,26 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="16" t="s">
-        <v>1250</v>
+    <row r="192" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="14" t="s">
+        <v>1252</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
       <c r="F192" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="I192" s="6" t="s">
         <v>25</v>
@@ -14467,23 +14455,23 @@
         <v>79</v>
       </c>
       <c r="K192" s="6" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="L192" s="6" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="M192" s="6"/>
       <c r="N192" s="6" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="O192" s="6" t="s">
         <v>109</v>
       </c>
       <c r="P192" s="6">
-        <v>150</v>
+        <v>62</v>
       </c>
       <c r="Q192" s="6">
-        <v>156</v>
+        <v>91</v>
       </c>
       <c r="R192" s="1" t="s">
         <v>29</v>
@@ -14492,107 +14480,54 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="16" t="s">
-        <v>1254</v>
-      </c>
-      <c r="B193" s="6" t="s">
+    <row r="193" spans="1:19" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="14" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D193" s="1"/>
+      <c r="E193" s="1"/>
+      <c r="F193" s="1" t="s">
         <v>1223</v>
       </c>
-      <c r="C193" s="6" t="s">
+      <c r="G193" s="1" t="s">
         <v>1224</v>
       </c>
-      <c r="D193" s="3"/>
-      <c r="E193" s="3"/>
-      <c r="F193" s="1" t="s">
-        <v>1225</v>
-      </c>
-      <c r="G193" s="1" t="s">
-        <v>1226</v>
-      </c>
-      <c r="H193" s="6" t="s">
-        <v>1255</v>
-      </c>
-      <c r="I193" s="6" t="s">
+      <c r="H193" s="1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="I193" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J193" s="6" t="s">
+      <c r="J193" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="K193" s="6" t="s">
-        <v>1228</v>
-      </c>
-      <c r="L193" s="6" t="s">
-        <v>1256</v>
-      </c>
-      <c r="M193" s="6"/>
-      <c r="N193" s="6" t="s">
-        <v>1257</v>
-      </c>
-      <c r="O193" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P193" s="6">
-        <v>62</v>
-      </c>
-      <c r="Q193" s="6">
-        <v>91</v>
+      <c r="K193" s="1"/>
+      <c r="L193" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="M193" s="2"/>
+      <c r="N193" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="O193" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="P193" s="1" t="s">
+        <v>1260</v>
+      </c>
+      <c r="Q193" s="1" t="s">
+        <v>1261</v>
       </c>
       <c r="R193" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S193" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194" spans="1:19" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="16" t="s">
-        <v>1258</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>1223</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>1224</v>
-      </c>
-      <c r="D194" s="1"/>
-      <c r="E194" s="1"/>
-      <c r="F194" s="1" t="s">
-        <v>1225</v>
-      </c>
-      <c r="G194" s="1" t="s">
-        <v>1226</v>
-      </c>
-      <c r="H194" s="1" t="s">
-        <v>1259</v>
-      </c>
-      <c r="I194" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J194" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K194" s="1"/>
-      <c r="L194" s="2" t="s">
-        <v>1260</v>
-      </c>
-      <c r="M194" s="2"/>
-      <c r="N194" s="2" t="s">
-        <v>1261</v>
-      </c>
-      <c r="O194" s="1" t="s">
-        <v>1092</v>
-      </c>
-      <c r="P194" s="1" t="s">
-        <v>1262</v>
-      </c>
-      <c r="Q194" s="1" t="s">
-        <v>1263</v>
-      </c>
-      <c r="R194" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S194" s="1">
         <v>1</v>
       </c>
     </row>
@@ -14734,63 +14669,62 @@
     <hyperlink ref="A143" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
     <hyperlink ref="A144" r:id="rId135" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
     <hyperlink ref="A145" r:id="rId136" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="A146" r:id="rId137" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="A147" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="A148" r:id="rId139" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="A149" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="A150" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="A151" r:id="rId142" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="A152" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="A153" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="A155" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="A158" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="A160" r:id="rId147" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="A161" r:id="rId148" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="A162" r:id="rId149" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="A163" r:id="rId150" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="A164" r:id="rId151" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="A166" r:id="rId152" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="A167" r:id="rId153" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="A168" r:id="rId154" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="A169" r:id="rId155" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="A170" r:id="rId156" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="A171" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="A172" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="A173" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="A174" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="A175" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="A176" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="A177" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="A178" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="A179" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="A180" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="A181" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="A182" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="A183" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="A184" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="A185" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="A186" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="A187" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="A188" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="A189" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="A190" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="A191" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="A192" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="A193" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="A194" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="A122" r:id="rId181" xr:uid="{5387F726-DCFD-4836-AE7E-7DC737AD9B52}"/>
-    <hyperlink ref="A126" r:id="rId182" xr:uid="{2DD984AB-7E65-440E-990B-3DEB390F5232}"/>
-    <hyperlink ref="A127" r:id="rId183" xr:uid="{C1D5EDB1-0DBC-460B-BFE8-8A64BA531FE9}"/>
-    <hyperlink ref="A129" r:id="rId184" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0b/Paolo_Uccello_%E2%80%94_The_Decisive_Attack_of_Micheletto_Attendolo_at_San_Romano.jpg/1280px-Paolo_Uccello_%E2%80%94_The_Decisive_Attack_of_Micheletto_Attendolo_at_San_Romano.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8568C58D-9F0D-448F-A287-7E73E21239CF}"/>
-    <hyperlink ref="A51" r:id="rId185" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Beato_angelico_e_lorenzo_monaco%2C_pala_di_santa_trinita_%28deposizione_e_santi%29%2C_ante_1432%2C_01.jpg/1920px-Beato_angelico_e_lorenzo_monaco%2C_pala_di_santa_trinita_%28deposizione_e_santi%29%2C_ante_1432%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9A5901B2-A8C7-4333-8C93-3BA24B441446}"/>
-    <hyperlink ref="A159" r:id="rId186" xr:uid="{66FFDBF1-519C-4A74-8049-39696640DDD4}"/>
-    <hyperlink ref="A165" r:id="rId187" xr:uid="{C484BA40-5873-4062-BAC8-9BEE869078E5}"/>
-    <hyperlink ref="A156" r:id="rId188" xr:uid="{F646FB71-58FB-457D-8A7A-0FB460CB78F9}"/>
-    <hyperlink ref="A157" r:id="rId189" xr:uid="{2E363D48-40BE-441E-AC26-10AFA79ECF4B}"/>
-    <hyperlink ref="A102" r:id="rId190" xr:uid="{FA3B3813-9FCD-4BF6-BB3B-DA6B2910415D}"/>
-    <hyperlink ref="A93" r:id="rId191" xr:uid="{F9194648-35D5-46AD-8B7C-6F8007C9A92F}"/>
-    <hyperlink ref="A95" r:id="rId192" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5e/Apocalypse_figur%C3%A9e_des_ducs_de_Savoie_-_Escorial_E_Vit.5_-_Adoration_of_the_lamb2.jpg/960px-Apocalypse_figur%C3%A9e_des_ducs_de_Savoie_-_Escorial_E_Vit.5_-_Adoration_of_the_lamb2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{05264A43-B26E-4B7D-98A2-6DA5DE2DB650}"/>
-    <hyperlink ref="A154" r:id="rId193" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0d/Triptyque_de_la_famille_Braque_-_Rogier_van_der_Weyden_-_Mus%C3%A9e_du_Louvre_Peintures_RF_2063.jpg/1280px-Triptyque_de_la_famille_Braque_-_Rogier_van_der_Weyden_-_Mus%C3%A9e_du_Louvre_Peintures_RF_2063.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C1A2A759-47A8-4BC8-B605-8905A4F124B3}"/>
+    <hyperlink ref="A146" r:id="rId137" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="A147" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="A148" r:id="rId139" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="A149" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="A150" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="A151" r:id="rId142" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="A152" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="A154" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="A157" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="A159" r:id="rId146" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="A160" r:id="rId147" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="A161" r:id="rId148" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="A162" r:id="rId149" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="A163" r:id="rId150" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="A165" r:id="rId151" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="A166" r:id="rId152" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="A167" r:id="rId153" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="A168" r:id="rId154" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="A169" r:id="rId155" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="A170" r:id="rId156" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="A171" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="A172" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="A173" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="A174" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="A175" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="A176" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="A177" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="A178" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="A179" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="A180" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="A181" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="A182" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="A183" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="A184" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="A185" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="A186" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="A187" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="A188" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="A189" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="A190" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="A191" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="A192" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="A193" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="A122" r:id="rId180" xr:uid="{5387F726-DCFD-4836-AE7E-7DC737AD9B52}"/>
+    <hyperlink ref="A126" r:id="rId181" xr:uid="{2DD984AB-7E65-440E-990B-3DEB390F5232}"/>
+    <hyperlink ref="A127" r:id="rId182" xr:uid="{C1D5EDB1-0DBC-460B-BFE8-8A64BA531FE9}"/>
+    <hyperlink ref="A129" r:id="rId183" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0b/Paolo_Uccello_%E2%80%94_The_Decisive_Attack_of_Micheletto_Attendolo_at_San_Romano.jpg/1280px-Paolo_Uccello_%E2%80%94_The_Decisive_Attack_of_Micheletto_Attendolo_at_San_Romano.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8568C58D-9F0D-448F-A287-7E73E21239CF}"/>
+    <hyperlink ref="A51" r:id="rId184" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Beato_angelico_e_lorenzo_monaco%2C_pala_di_santa_trinita_%28deposizione_e_santi%29%2C_ante_1432%2C_01.jpg/1920px-Beato_angelico_e_lorenzo_monaco%2C_pala_di_santa_trinita_%28deposizione_e_santi%29%2C_ante_1432%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9A5901B2-A8C7-4333-8C93-3BA24B441446}"/>
+    <hyperlink ref="A158" r:id="rId185" xr:uid="{66FFDBF1-519C-4A74-8049-39696640DDD4}"/>
+    <hyperlink ref="A164" r:id="rId186" xr:uid="{C484BA40-5873-4062-BAC8-9BEE869078E5}"/>
+    <hyperlink ref="A155" r:id="rId187" xr:uid="{F646FB71-58FB-457D-8A7A-0FB460CB78F9}"/>
+    <hyperlink ref="A156" r:id="rId188" xr:uid="{2E363D48-40BE-441E-AC26-10AFA79ECF4B}"/>
+    <hyperlink ref="A102" r:id="rId189" xr:uid="{FA3B3813-9FCD-4BF6-BB3B-DA6B2910415D}"/>
+    <hyperlink ref="A93" r:id="rId190" xr:uid="{F9194648-35D5-46AD-8B7C-6F8007C9A92F}"/>
+    <hyperlink ref="A95" r:id="rId191" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5e/Apocalypse_figur%C3%A9e_des_ducs_de_Savoie_-_Escorial_E_Vit.5_-_Adoration_of_the_lamb2.jpg/960px-Apocalypse_figur%C3%A9e_des_ducs_de_Savoie_-_Escorial_E_Vit.5_-_Adoration_of_the_lamb2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{05264A43-B26E-4B7D-98A2-6DA5DE2DB650}"/>
+    <hyperlink ref="A153" r:id="rId192" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0d/Triptyque_de_la_famille_Braque_-_Rogier_van_der_Weyden_-_Mus%C3%A9e_du_Louvre_Peintures_RF_2063.jpg/1280px-Triptyque_de_la_famille_Braque_-_Rogier_van_der_Weyden_-_Mus%C3%A9e_du_Louvre_Peintures_RF_2063.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C1A2A759-47A8-4BC8-B605-8905A4F124B3}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-15e.xlsx
+++ b/quizzes/peinture-15e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1061CFE6-C86A-49CB-BF9B-3E53AB45F2DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7BFB29-92D5-485A-B008-910B80677C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -4511,7 +4511,7 @@
     <col min="10" max="10" width="20" customWidth="1"/>
     <col min="11" max="11" width="11.42578125" customWidth="1"/>
     <col min="12" max="12" width="12.7109375" customWidth="1"/>
-    <col min="13" max="13" width="25.140625" customWidth="1"/>
+    <col min="13" max="13" width="32.7109375" customWidth="1"/>
     <col min="14" max="14" width="16.28515625" customWidth="1"/>
     <col min="15" max="15" width="11.7109375" customWidth="1"/>
     <col min="16" max="16" width="17.140625" customWidth="1"/>

--- a/quizzes/peinture-15e.xlsx
+++ b/quizzes/peinture-15e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7BFB29-92D5-485A-B008-910B80677C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1760D9-6A5E-498C-98A0-3D8AEDDB9A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2918" uniqueCount="1379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2879" uniqueCount="1379">
   <si>
     <t>Prénom</t>
   </si>
@@ -4496,7 +4496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X224"/>
+  <dimension ref="A1:X221"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -8493,28 +8493,31 @@
         <v>316</v>
       </c>
       <c r="H85" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="I85" t="s">
-        <v>624</v>
+        <v>29</v>
       </c>
       <c r="J85" t="s">
-        <v>625</v>
+        <v>127</v>
       </c>
       <c r="M85" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="N85" t="s">
-        <v>627</v>
+        <v>632</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>633</v>
       </c>
       <c r="S85" t="s">
-        <v>217</v>
+        <v>634</v>
       </c>
       <c r="T85" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="U85" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="W85" t="s">
         <v>36</v>
@@ -8537,31 +8540,28 @@
         <v>316</v>
       </c>
       <c r="H86" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="I86" t="s">
-        <v>29</v>
+        <v>615</v>
       </c>
       <c r="J86" t="s">
-        <v>127</v>
+        <v>616</v>
       </c>
       <c r="M86" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="N86" t="s">
-        <v>632</v>
-      </c>
-      <c r="Q86" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="S86" t="s">
-        <v>634</v>
+        <v>109</v>
       </c>
       <c r="T86" t="s">
-        <v>635</v>
+        <v>186</v>
       </c>
       <c r="U86" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="W86" t="s">
         <v>36</v>
@@ -8587,25 +8587,25 @@
         <v>637</v>
       </c>
       <c r="I87" t="s">
-        <v>615</v>
+        <v>69</v>
       </c>
       <c r="J87" t="s">
-        <v>616</v>
+        <v>70</v>
       </c>
       <c r="M87" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="N87" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="S87" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="T87" t="s">
-        <v>186</v>
+        <v>643</v>
       </c>
       <c r="U87" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="W87" t="s">
         <v>36</v>
@@ -8628,28 +8628,31 @@
         <v>316</v>
       </c>
       <c r="H88" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="I88" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="J88" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="M88" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="N88" t="s">
-        <v>642</v>
+        <v>647</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>648</v>
       </c>
       <c r="S88" t="s">
-        <v>81</v>
+        <v>486</v>
       </c>
       <c r="T88" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="U88" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="W88" t="s">
         <v>36</v>
@@ -8660,46 +8663,46 @@
     </row>
     <row r="89" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>599</v>
+        <v>651</v>
       </c>
       <c r="B89" t="s">
-        <v>600</v>
+        <v>652</v>
+      </c>
+      <c r="D89" t="s">
+        <v>653</v>
+      </c>
+      <c r="E89" t="s">
+        <v>653</v>
       </c>
       <c r="F89" t="s">
-        <v>266</v>
+        <v>654</v>
       </c>
       <c r="G89" t="s">
-        <v>316</v>
+        <v>655</v>
       </c>
       <c r="H89" t="s">
-        <v>637</v>
+        <v>656</v>
       </c>
       <c r="I89" t="s">
-        <v>104</v>
+        <v>211</v>
       </c>
       <c r="J89" t="s">
-        <v>105</v>
+        <v>657</v>
       </c>
       <c r="M89" t="s">
-        <v>638</v>
+        <v>658</v>
       </c>
       <c r="N89" t="s">
-        <v>639</v>
+        <v>659</v>
       </c>
       <c r="S89" t="s">
-        <v>109</v>
-      </c>
-      <c r="T89" t="s">
-        <v>186</v>
-      </c>
-      <c r="U89" t="s">
-        <v>640</v>
+        <v>217</v>
       </c>
       <c r="W89" t="s">
         <v>36</v>
       </c>
       <c r="X89">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8707,43 +8710,43 @@
         <v>599</v>
       </c>
       <c r="B90" t="s">
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="F90" t="s">
-        <v>266</v>
+        <v>661</v>
       </c>
       <c r="G90" t="s">
-        <v>316</v>
+        <v>662</v>
       </c>
       <c r="H90" t="s">
-        <v>637</v>
-      </c>
-      <c r="I90" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J90" t="s">
-        <v>70</v>
+        <v>663</v>
       </c>
       <c r="M90" t="s">
-        <v>641</v>
+        <v>664</v>
       </c>
       <c r="N90" t="s">
-        <v>642</v>
+        <v>665</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>666</v>
       </c>
       <c r="S90" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="T90" t="s">
-        <v>643</v>
+        <v>667</v>
       </c>
       <c r="U90" t="s">
-        <v>644</v>
+        <v>668</v>
       </c>
       <c r="W90" t="s">
         <v>36</v>
       </c>
       <c r="X90">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8751,84 +8754,81 @@
         <v>599</v>
       </c>
       <c r="B91" t="s">
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="F91" t="s">
-        <v>266</v>
+        <v>661</v>
       </c>
       <c r="G91" t="s">
-        <v>316</v>
+        <v>662</v>
       </c>
       <c r="H91" t="s">
-        <v>645</v>
+        <v>377</v>
       </c>
       <c r="I91" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="J91" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="M91" t="s">
-        <v>646</v>
+        <v>669</v>
       </c>
       <c r="N91" t="s">
-        <v>647</v>
-      </c>
-      <c r="Q91" t="s">
-        <v>648</v>
+        <v>670</v>
       </c>
       <c r="S91" t="s">
-        <v>486</v>
+        <v>671</v>
       </c>
       <c r="T91" t="s">
-        <v>649</v>
+        <v>672</v>
       </c>
       <c r="U91" t="s">
-        <v>650</v>
+        <v>673</v>
       </c>
       <c r="W91" t="s">
         <v>36</v>
       </c>
       <c r="X91">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>651</v>
+        <v>674</v>
       </c>
       <c r="B92" t="s">
-        <v>652</v>
-      </c>
-      <c r="D92" t="s">
-        <v>653</v>
-      </c>
-      <c r="E92" t="s">
-        <v>653</v>
+        <v>675</v>
       </c>
       <c r="F92" t="s">
-        <v>654</v>
+        <v>94</v>
       </c>
       <c r="G92" t="s">
-        <v>655</v>
+        <v>339</v>
       </c>
       <c r="H92" t="s">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="I92" t="s">
-        <v>211</v>
+        <v>69</v>
       </c>
       <c r="J92" t="s">
-        <v>657</v>
+        <v>70</v>
       </c>
       <c r="M92" t="s">
-        <v>658</v>
+        <v>677</v>
       </c>
       <c r="N92" t="s">
-        <v>659</v>
+        <v>678</v>
       </c>
       <c r="S92" t="s">
-        <v>217</v>
+        <v>33</v>
+      </c>
+      <c r="T92" t="s">
+        <v>679</v>
+      </c>
+      <c r="U92" t="s">
+        <v>680</v>
       </c>
       <c r="W92" t="s">
         <v>36</v>
@@ -8839,40 +8839,37 @@
     </row>
     <row r="93" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>599</v>
+        <v>674</v>
       </c>
       <c r="B93" t="s">
-        <v>660</v>
+        <v>675</v>
       </c>
       <c r="F93" t="s">
-        <v>661</v>
+        <v>94</v>
       </c>
       <c r="G93" t="s">
-        <v>662</v>
+        <v>339</v>
       </c>
       <c r="H93" t="s">
-        <v>68</v>
+        <v>681</v>
+      </c>
+      <c r="I93" t="s">
+        <v>682</v>
       </c>
       <c r="J93" t="s">
-        <v>663</v>
+        <v>683</v>
       </c>
       <c r="M93" t="s">
-        <v>664</v>
+        <v>684</v>
       </c>
       <c r="N93" t="s">
-        <v>665</v>
+        <v>685</v>
       </c>
       <c r="Q93" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="S93" t="s">
-        <v>33</v>
-      </c>
-      <c r="T93" t="s">
-        <v>667</v>
-      </c>
-      <c r="U93" t="s">
-        <v>668</v>
+        <v>217</v>
       </c>
       <c r="W93" t="s">
         <v>36</v>
@@ -8883,40 +8880,49 @@
     </row>
     <row r="94" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>599</v>
+        <v>687</v>
       </c>
       <c r="B94" t="s">
-        <v>660</v>
+        <v>675</v>
+      </c>
+      <c r="D94" t="s">
+        <v>688</v>
+      </c>
+      <c r="E94" t="s">
+        <v>688</v>
       </c>
       <c r="F94" t="s">
-        <v>661</v>
+        <v>689</v>
       </c>
       <c r="G94" t="s">
-        <v>662</v>
+        <v>690</v>
       </c>
       <c r="H94" t="s">
-        <v>377</v>
+        <v>691</v>
       </c>
       <c r="I94" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="J94" t="s">
-        <v>70</v>
+        <v>127</v>
       </c>
       <c r="M94" t="s">
-        <v>669</v>
+        <v>692</v>
       </c>
       <c r="N94" t="s">
-        <v>670</v>
+        <v>693</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>694</v>
       </c>
       <c r="S94" t="s">
-        <v>671</v>
-      </c>
-      <c r="T94" t="s">
-        <v>672</v>
-      </c>
-      <c r="U94" t="s">
-        <v>673</v>
+        <v>695</v>
+      </c>
+      <c r="T94">
+        <v>240</v>
+      </c>
+      <c r="U94">
+        <v>223</v>
       </c>
       <c r="W94" t="s">
         <v>36</v>
@@ -8927,40 +8933,55 @@
     </row>
     <row r="95" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>674</v>
+        <v>687</v>
       </c>
       <c r="B95" t="s">
         <v>675</v>
       </c>
+      <c r="D95" t="s">
+        <v>688</v>
+      </c>
+      <c r="E95" t="s">
+        <v>688</v>
+      </c>
       <c r="F95" t="s">
-        <v>94</v>
+        <v>689</v>
       </c>
       <c r="G95" t="s">
-        <v>339</v>
+        <v>690</v>
       </c>
       <c r="H95" t="s">
-        <v>676</v>
+        <v>696</v>
       </c>
       <c r="I95" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="J95" t="s">
-        <v>70</v>
+        <v>697</v>
+      </c>
+      <c r="L95" t="s">
+        <v>698</v>
       </c>
       <c r="M95" t="s">
-        <v>677</v>
+        <v>699</v>
       </c>
       <c r="N95" t="s">
-        <v>678</v>
+        <v>700</v>
+      </c>
+      <c r="O95" t="s">
+        <v>701</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>702</v>
       </c>
       <c r="S95" t="s">
-        <v>33</v>
-      </c>
-      <c r="T95" t="s">
-        <v>679</v>
-      </c>
-      <c r="U95" t="s">
-        <v>680</v>
+        <v>703</v>
+      </c>
+      <c r="T95">
+        <v>190</v>
+      </c>
+      <c r="U95">
+        <v>122</v>
       </c>
       <c r="W95" t="s">
         <v>36</v>
@@ -8971,38 +8992,47 @@
     </row>
     <row r="96" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>674</v>
+        <v>704</v>
       </c>
       <c r="B96" t="s">
-        <v>675</v>
+        <v>705</v>
+      </c>
+      <c r="D96" t="s">
+        <v>706</v>
+      </c>
+      <c r="E96" t="s">
+        <v>706</v>
       </c>
       <c r="F96" t="s">
-        <v>94</v>
+        <v>707</v>
       </c>
       <c r="G96" t="s">
-        <v>339</v>
+        <v>708</v>
       </c>
       <c r="H96" t="s">
-        <v>681</v>
+        <v>709</v>
       </c>
       <c r="I96" t="s">
-        <v>682</v>
+        <v>29</v>
       </c>
       <c r="J96" t="s">
-        <v>683</v>
+        <v>710</v>
       </c>
       <c r="M96" t="s">
-        <v>684</v>
+        <v>711</v>
       </c>
       <c r="N96" t="s">
-        <v>685</v>
-      </c>
-      <c r="Q96" t="s">
-        <v>686</v>
+        <v>712</v>
       </c>
       <c r="S96" t="s">
         <v>217</v>
       </c>
+      <c r="T96" t="s">
+        <v>713</v>
+      </c>
+      <c r="U96" t="s">
+        <v>714</v>
+      </c>
       <c r="W96" t="s">
         <v>36</v>
       </c>
@@ -9012,49 +9042,49 @@
     </row>
     <row r="97" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>687</v>
+        <v>704</v>
       </c>
       <c r="B97" t="s">
-        <v>675</v>
+        <v>705</v>
       </c>
       <c r="D97" t="s">
-        <v>688</v>
+        <v>706</v>
       </c>
       <c r="E97" t="s">
-        <v>688</v>
+        <v>706</v>
       </c>
       <c r="F97" t="s">
-        <v>689</v>
+        <v>707</v>
       </c>
       <c r="G97" t="s">
-        <v>690</v>
+        <v>708</v>
       </c>
       <c r="H97" t="s">
-        <v>691</v>
+        <v>26</v>
       </c>
       <c r="I97" t="s">
         <v>29</v>
       </c>
       <c r="J97" t="s">
-        <v>127</v>
+        <v>715</v>
+      </c>
+      <c r="L97" t="s">
+        <v>716</v>
       </c>
       <c r="M97" t="s">
-        <v>692</v>
+        <v>717</v>
       </c>
       <c r="N97" t="s">
-        <v>693</v>
-      </c>
-      <c r="Q97" t="s">
-        <v>694</v>
+        <v>718</v>
       </c>
       <c r="S97" t="s">
-        <v>695</v>
-      </c>
-      <c r="T97">
-        <v>240</v>
-      </c>
-      <c r="U97">
-        <v>223</v>
+        <v>217</v>
+      </c>
+      <c r="T97" t="s">
+        <v>719</v>
+      </c>
+      <c r="U97" t="s">
+        <v>720</v>
       </c>
       <c r="W97" t="s">
         <v>36</v>
@@ -9065,164 +9095,173 @@
     </row>
     <row r="98" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>687</v>
+        <v>721</v>
       </c>
       <c r="B98" t="s">
-        <v>675</v>
+        <v>722</v>
       </c>
       <c r="D98" t="s">
-        <v>688</v>
+        <v>723</v>
       </c>
       <c r="E98" t="s">
-        <v>688</v>
+        <v>723</v>
       </c>
       <c r="F98" t="s">
-        <v>689</v>
+        <v>724</v>
       </c>
       <c r="G98" t="s">
-        <v>690</v>
+        <v>725</v>
       </c>
       <c r="H98" t="s">
-        <v>696</v>
+        <v>726</v>
       </c>
       <c r="I98" t="s">
-        <v>29</v>
+        <v>138</v>
       </c>
       <c r="J98" t="s">
-        <v>697</v>
+        <v>139</v>
       </c>
       <c r="L98" t="s">
-        <v>698</v>
+        <v>727</v>
       </c>
       <c r="M98" t="s">
-        <v>699</v>
+        <v>583</v>
       </c>
       <c r="N98" t="s">
-        <v>700</v>
-      </c>
-      <c r="O98" t="s">
-        <v>701</v>
+        <v>728</v>
       </c>
       <c r="Q98" t="s">
-        <v>702</v>
+        <v>729</v>
       </c>
       <c r="S98" t="s">
-        <v>703</v>
-      </c>
-      <c r="T98">
-        <v>190</v>
-      </c>
-      <c r="U98">
-        <v>122</v>
+        <v>380</v>
+      </c>
+      <c r="T98" t="s">
+        <v>730</v>
+      </c>
+      <c r="U98" t="s">
+        <v>730</v>
       </c>
       <c r="W98" t="s">
         <v>36</v>
       </c>
       <c r="X98">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>704</v>
+        <v>721</v>
       </c>
       <c r="B99" t="s">
-        <v>705</v>
+        <v>722</v>
       </c>
       <c r="D99" t="s">
-        <v>706</v>
+        <v>723</v>
       </c>
       <c r="E99" t="s">
-        <v>706</v>
+        <v>723</v>
       </c>
       <c r="F99" t="s">
-        <v>707</v>
+        <v>724</v>
       </c>
       <c r="G99" t="s">
-        <v>708</v>
+        <v>725</v>
       </c>
       <c r="H99" t="s">
-        <v>709</v>
+        <v>731</v>
       </c>
       <c r="I99" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J99" t="s">
-        <v>710</v>
+        <v>39</v>
+      </c>
+      <c r="L99" t="s">
+        <v>732</v>
       </c>
       <c r="M99" t="s">
-        <v>711</v>
+        <v>733</v>
       </c>
       <c r="N99" t="s">
-        <v>712</v>
+        <v>734</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>735</v>
       </c>
       <c r="S99" t="s">
-        <v>217</v>
+        <v>703</v>
       </c>
       <c r="T99" t="s">
-        <v>713</v>
+        <v>736</v>
       </c>
       <c r="U99" t="s">
-        <v>714</v>
+        <v>737</v>
       </c>
       <c r="W99" t="s">
         <v>36</v>
       </c>
       <c r="X99">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>704</v>
+        <v>721</v>
       </c>
       <c r="B100" t="s">
-        <v>705</v>
+        <v>722</v>
       </c>
       <c r="D100" t="s">
-        <v>706</v>
+        <v>723</v>
       </c>
       <c r="E100" t="s">
-        <v>706</v>
+        <v>723</v>
       </c>
       <c r="F100" t="s">
-        <v>707</v>
+        <v>724</v>
       </c>
       <c r="G100" t="s">
-        <v>708</v>
+        <v>725</v>
       </c>
       <c r="H100" t="s">
-        <v>26</v>
+        <v>738</v>
       </c>
       <c r="I100" t="s">
         <v>29</v>
       </c>
       <c r="J100" t="s">
-        <v>715</v>
+        <v>739</v>
       </c>
       <c r="L100" t="s">
-        <v>716</v>
+        <v>740</v>
       </c>
       <c r="M100" t="s">
-        <v>717</v>
+        <v>741</v>
       </c>
       <c r="N100" t="s">
-        <v>718</v>
+        <v>742</v>
+      </c>
+      <c r="O100" t="s">
+        <v>743</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>744</v>
       </c>
       <c r="S100" t="s">
-        <v>217</v>
+        <v>745</v>
       </c>
       <c r="T100" t="s">
-        <v>719</v>
+        <v>746</v>
       </c>
       <c r="U100" t="s">
-        <v>720</v>
+        <v>747</v>
       </c>
       <c r="W100" t="s">
         <v>36</v>
       </c>
       <c r="X100">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9235,9 +9274,6 @@
       <c r="D101" t="s">
         <v>723</v>
       </c>
-      <c r="E101" t="s">
-        <v>723</v>
-      </c>
       <c r="F101" t="s">
         <v>724</v>
       </c>
@@ -9245,34 +9281,28 @@
         <v>725</v>
       </c>
       <c r="H101" t="s">
-        <v>726</v>
+        <v>748</v>
       </c>
       <c r="I101" t="s">
-        <v>138</v>
+        <v>29</v>
       </c>
       <c r="J101" t="s">
-        <v>139</v>
-      </c>
-      <c r="L101" t="s">
-        <v>727</v>
+        <v>749</v>
       </c>
       <c r="M101" t="s">
-        <v>583</v>
+        <v>750</v>
       </c>
       <c r="N101" t="s">
-        <v>728</v>
-      </c>
-      <c r="Q101" t="s">
-        <v>729</v>
+        <v>751</v>
       </c>
       <c r="S101" t="s">
-        <v>380</v>
+        <v>109</v>
       </c>
       <c r="T101" t="s">
-        <v>730</v>
+        <v>752</v>
       </c>
       <c r="U101" t="s">
-        <v>730</v>
+        <v>753</v>
       </c>
       <c r="W101" t="s">
         <v>36</v>
@@ -9291,9 +9321,6 @@
       <c r="D102" t="s">
         <v>723</v>
       </c>
-      <c r="E102" t="s">
-        <v>723</v>
-      </c>
       <c r="F102" t="s">
         <v>724</v>
       </c>
@@ -9301,34 +9328,22 @@
         <v>725</v>
       </c>
       <c r="H102" t="s">
-        <v>731</v>
+        <v>754</v>
       </c>
       <c r="I102" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J102" t="s">
-        <v>39</v>
-      </c>
-      <c r="L102" t="s">
-        <v>732</v>
+        <v>749</v>
       </c>
       <c r="M102" t="s">
-        <v>733</v>
+        <v>755</v>
       </c>
       <c r="N102" t="s">
-        <v>734</v>
-      </c>
-      <c r="Q102" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="S102" t="s">
-        <v>703</v>
-      </c>
-      <c r="T102" t="s">
-        <v>736</v>
-      </c>
-      <c r="U102" t="s">
-        <v>737</v>
+        <v>109</v>
       </c>
       <c r="W102" t="s">
         <v>36</v>
@@ -9357,37 +9372,31 @@
         <v>725</v>
       </c>
       <c r="H103" t="s">
-        <v>738</v>
+        <v>757</v>
       </c>
       <c r="I103" t="s">
         <v>29</v>
       </c>
       <c r="J103" t="s">
-        <v>739</v>
+        <v>749</v>
       </c>
       <c r="L103" t="s">
         <v>740</v>
       </c>
       <c r="M103" t="s">
-        <v>741</v>
+        <v>758</v>
       </c>
       <c r="N103" t="s">
-        <v>742</v>
-      </c>
-      <c r="O103" t="s">
-        <v>743</v>
-      </c>
-      <c r="Q103" t="s">
-        <v>744</v>
+        <v>759</v>
       </c>
       <c r="S103" t="s">
-        <v>745</v>
+        <v>109</v>
       </c>
       <c r="T103" t="s">
-        <v>746</v>
+        <v>760</v>
       </c>
       <c r="U103" t="s">
-        <v>747</v>
+        <v>761</v>
       </c>
       <c r="W103" t="s">
         <v>36</v>
@@ -9406,6 +9415,9 @@
       <c r="D104" t="s">
         <v>723</v>
       </c>
+      <c r="E104" t="s">
+        <v>723</v>
+      </c>
       <c r="F104" t="s">
         <v>724</v>
       </c>
@@ -9413,7 +9425,7 @@
         <v>725</v>
       </c>
       <c r="H104" t="s">
-        <v>748</v>
+        <v>762</v>
       </c>
       <c r="I104" t="s">
         <v>29</v>
@@ -9421,20 +9433,26 @@
       <c r="J104" t="s">
         <v>749</v>
       </c>
+      <c r="L104" t="s">
+        <v>763</v>
+      </c>
       <c r="M104" t="s">
-        <v>750</v>
+        <v>764</v>
       </c>
       <c r="N104" t="s">
-        <v>751</v>
+        <v>765</v>
+      </c>
+      <c r="O104" t="s">
+        <v>766</v>
       </c>
       <c r="S104" t="s">
-        <v>109</v>
-      </c>
-      <c r="T104" t="s">
-        <v>752</v>
-      </c>
-      <c r="U104" t="s">
-        <v>753</v>
+        <v>217</v>
+      </c>
+      <c r="T104">
+        <v>180</v>
+      </c>
+      <c r="U104">
+        <v>139</v>
       </c>
       <c r="W104" t="s">
         <v>36</v>
@@ -9453,6 +9471,9 @@
       <c r="D105" t="s">
         <v>723</v>
       </c>
+      <c r="E105" t="s">
+        <v>723</v>
+      </c>
       <c r="F105" t="s">
         <v>724</v>
       </c>
@@ -9460,7 +9481,7 @@
         <v>725</v>
       </c>
       <c r="H105" t="s">
-        <v>754</v>
+        <v>767</v>
       </c>
       <c r="I105" t="s">
         <v>29</v>
@@ -9468,14 +9489,29 @@
       <c r="J105" t="s">
         <v>749</v>
       </c>
+      <c r="L105" t="s">
+        <v>768</v>
+      </c>
       <c r="M105" t="s">
-        <v>755</v>
+        <v>769</v>
       </c>
       <c r="N105" t="s">
-        <v>756</v>
+        <v>770</v>
+      </c>
+      <c r="O105" t="s">
+        <v>766</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>771</v>
       </c>
       <c r="S105" t="s">
-        <v>109</v>
+        <v>217</v>
+      </c>
+      <c r="T105" t="s">
+        <v>772</v>
+      </c>
+      <c r="U105" t="s">
+        <v>773</v>
       </c>
       <c r="W105" t="s">
         <v>36</v>
@@ -9504,7 +9540,7 @@
         <v>725</v>
       </c>
       <c r="H106" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="I106" t="s">
         <v>29</v>
@@ -9513,22 +9549,25 @@
         <v>749</v>
       </c>
       <c r="L106" t="s">
-        <v>740</v>
+        <v>774</v>
       </c>
       <c r="M106" t="s">
-        <v>758</v>
+        <v>583</v>
       </c>
       <c r="N106" t="s">
-        <v>759</v>
+        <v>775</v>
+      </c>
+      <c r="O106" t="s">
+        <v>766</v>
       </c>
       <c r="S106" t="s">
-        <v>109</v>
+        <v>217</v>
       </c>
       <c r="T106" t="s">
-        <v>760</v>
+        <v>746</v>
       </c>
       <c r="U106" t="s">
-        <v>761</v>
+        <v>227</v>
       </c>
       <c r="W106" t="s">
         <v>36</v>
@@ -9566,13 +9605,13 @@
         <v>749</v>
       </c>
       <c r="L107" t="s">
-        <v>763</v>
+        <v>776</v>
       </c>
       <c r="M107" t="s">
-        <v>764</v>
+        <v>777</v>
       </c>
       <c r="N107" t="s">
-        <v>765</v>
+        <v>778</v>
       </c>
       <c r="O107" t="s">
         <v>766</v>
@@ -9580,11 +9619,11 @@
       <c r="S107" t="s">
         <v>217</v>
       </c>
-      <c r="T107">
-        <v>180</v>
-      </c>
-      <c r="U107">
-        <v>139</v>
+      <c r="T107" t="s">
+        <v>779</v>
+      </c>
+      <c r="U107" t="s">
+        <v>780</v>
       </c>
       <c r="W107" t="s">
         <v>36</v>
@@ -9613,7 +9652,7 @@
         <v>725</v>
       </c>
       <c r="H108" t="s">
-        <v>767</v>
+        <v>781</v>
       </c>
       <c r="I108" t="s">
         <v>29</v>
@@ -9622,28 +9661,25 @@
         <v>749</v>
       </c>
       <c r="L108" t="s">
-        <v>768</v>
+        <v>782</v>
       </c>
       <c r="M108" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
       <c r="N108" t="s">
-        <v>770</v>
+        <v>784</v>
       </c>
       <c r="O108" t="s">
         <v>766</v>
       </c>
-      <c r="Q108" t="s">
-        <v>771</v>
-      </c>
       <c r="S108" t="s">
         <v>217</v>
       </c>
       <c r="T108" t="s">
-        <v>772</v>
+        <v>785</v>
       </c>
       <c r="U108" t="s">
-        <v>773</v>
+        <v>786</v>
       </c>
       <c r="W108" t="s">
         <v>36</v>
@@ -9672,34 +9708,34 @@
         <v>725</v>
       </c>
       <c r="H109" t="s">
-        <v>762</v>
+        <v>787</v>
       </c>
       <c r="I109" t="s">
-        <v>29</v>
+        <v>210</v>
       </c>
       <c r="J109" t="s">
-        <v>749</v>
+        <v>211</v>
       </c>
       <c r="L109" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
       <c r="M109" t="s">
-        <v>583</v>
+        <v>789</v>
       </c>
       <c r="N109" t="s">
-        <v>775</v>
+        <v>790</v>
       </c>
       <c r="O109" t="s">
-        <v>766</v>
+        <v>791</v>
       </c>
       <c r="S109" t="s">
         <v>217</v>
       </c>
       <c r="T109" t="s">
-        <v>746</v>
+        <v>792</v>
       </c>
       <c r="U109" t="s">
-        <v>227</v>
+        <v>793</v>
       </c>
       <c r="W109" t="s">
         <v>36</v>
@@ -9710,164 +9746,131 @@
     </row>
     <row r="110" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>721</v>
+        <v>794</v>
       </c>
       <c r="B110" t="s">
         <v>722</v>
       </c>
       <c r="D110" t="s">
-        <v>723</v>
+        <v>795</v>
       </c>
       <c r="E110" t="s">
-        <v>723</v>
+        <v>795</v>
       </c>
       <c r="F110" t="s">
-        <v>724</v>
+        <v>796</v>
       </c>
       <c r="G110" t="s">
-        <v>725</v>
+        <v>68</v>
       </c>
       <c r="H110" t="s">
-        <v>762</v>
+        <v>797</v>
       </c>
       <c r="I110" t="s">
-        <v>29</v>
+        <v>798</v>
       </c>
       <c r="J110" t="s">
-        <v>749</v>
-      </c>
-      <c r="L110" t="s">
-        <v>776</v>
+        <v>799</v>
       </c>
       <c r="M110" t="s">
-        <v>777</v>
+        <v>677</v>
       </c>
       <c r="N110" t="s">
-        <v>778</v>
-      </c>
-      <c r="O110" t="s">
-        <v>766</v>
+        <v>800</v>
       </c>
       <c r="S110" t="s">
-        <v>217</v>
-      </c>
-      <c r="T110" t="s">
-        <v>779</v>
-      </c>
-      <c r="U110" t="s">
-        <v>780</v>
+        <v>109</v>
       </c>
       <c r="W110" t="s">
         <v>36</v>
       </c>
       <c r="X110">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>721</v>
+        <v>794</v>
       </c>
       <c r="B111" t="s">
         <v>722</v>
       </c>
       <c r="D111" t="s">
-        <v>723</v>
+        <v>795</v>
       </c>
       <c r="E111" t="s">
-        <v>723</v>
+        <v>795</v>
       </c>
       <c r="F111" t="s">
-        <v>724</v>
+        <v>796</v>
       </c>
       <c r="G111" t="s">
-        <v>725</v>
+        <v>68</v>
       </c>
       <c r="H111" t="s">
-        <v>781</v>
+        <v>661</v>
       </c>
       <c r="I111" t="s">
-        <v>29</v>
+        <v>682</v>
       </c>
       <c r="J111" t="s">
-        <v>749</v>
-      </c>
-      <c r="L111" t="s">
-        <v>782</v>
+        <v>801</v>
       </c>
       <c r="M111" t="s">
-        <v>783</v>
+        <v>802</v>
       </c>
       <c r="N111" t="s">
-        <v>784</v>
+        <v>803</v>
       </c>
       <c r="O111" t="s">
-        <v>766</v>
+        <v>804</v>
       </c>
       <c r="S111" t="s">
-        <v>217</v>
-      </c>
-      <c r="T111" t="s">
-        <v>785</v>
-      </c>
-      <c r="U111" t="s">
-        <v>786</v>
+        <v>33</v>
       </c>
       <c r="W111" t="s">
         <v>36</v>
       </c>
       <c r="X111">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>721</v>
+        <v>805</v>
       </c>
       <c r="B112" t="s">
-        <v>722</v>
-      </c>
-      <c r="D112" t="s">
-        <v>723</v>
-      </c>
-      <c r="E112" t="s">
-        <v>723</v>
+        <v>806</v>
       </c>
       <c r="F112" t="s">
-        <v>724</v>
+        <v>807</v>
       </c>
       <c r="G112" t="s">
-        <v>725</v>
+        <v>808</v>
       </c>
       <c r="H112" t="s">
-        <v>787</v>
+        <v>809</v>
       </c>
       <c r="I112" t="s">
-        <v>210</v>
+        <v>810</v>
       </c>
       <c r="J112" t="s">
-        <v>211</v>
-      </c>
-      <c r="L112" t="s">
-        <v>788</v>
+        <v>811</v>
       </c>
       <c r="M112" t="s">
-        <v>789</v>
+        <v>812</v>
       </c>
       <c r="N112" t="s">
-        <v>790</v>
-      </c>
-      <c r="O112" t="s">
-        <v>791</v>
+        <v>813</v>
       </c>
       <c r="S112" t="s">
-        <v>217</v>
+        <v>81</v>
       </c>
       <c r="T112" t="s">
-        <v>792</v>
+        <v>814</v>
       </c>
       <c r="U112" t="s">
-        <v>793</v>
+        <v>815</v>
       </c>
       <c r="W112" t="s">
         <v>36</v>
@@ -9878,40 +9881,37 @@
     </row>
     <row r="113" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>794</v>
+        <v>816</v>
       </c>
       <c r="B113" t="s">
-        <v>722</v>
-      </c>
-      <c r="D113" t="s">
-        <v>795</v>
-      </c>
-      <c r="E113" t="s">
-        <v>795</v>
+        <v>817</v>
       </c>
       <c r="F113" t="s">
-        <v>796</v>
+        <v>818</v>
       </c>
       <c r="G113" t="s">
-        <v>68</v>
+        <v>819</v>
       </c>
       <c r="H113" t="s">
-        <v>797</v>
+        <v>820</v>
       </c>
       <c r="I113" t="s">
-        <v>798</v>
+        <v>104</v>
       </c>
       <c r="J113" t="s">
-        <v>799</v>
+        <v>821</v>
       </c>
       <c r="M113" t="s">
-        <v>677</v>
+        <v>822</v>
       </c>
       <c r="N113" t="s">
-        <v>800</v>
+        <v>823</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>824</v>
       </c>
       <c r="S113" t="s">
-        <v>109</v>
+        <v>217</v>
       </c>
       <c r="W113" t="s">
         <v>36</v>
@@ -9922,134 +9922,134 @@
     </row>
     <row r="114" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>794</v>
+        <v>247</v>
       </c>
       <c r="B114" t="s">
-        <v>722</v>
-      </c>
-      <c r="D114" t="s">
-        <v>795</v>
-      </c>
-      <c r="E114" t="s">
-        <v>795</v>
+        <v>825</v>
       </c>
       <c r="F114" t="s">
-        <v>796</v>
+        <v>826</v>
       </c>
       <c r="G114" t="s">
-        <v>68</v>
+        <v>827</v>
       </c>
       <c r="H114" t="s">
-        <v>661</v>
+        <v>828</v>
       </c>
       <c r="I114" t="s">
-        <v>682</v>
+        <v>38</v>
       </c>
       <c r="J114" t="s">
-        <v>801</v>
+        <v>39</v>
       </c>
       <c r="M114" t="s">
-        <v>802</v>
+        <v>829</v>
       </c>
       <c r="N114" t="s">
-        <v>803</v>
-      </c>
-      <c r="O114" t="s">
-        <v>804</v>
+        <v>830</v>
       </c>
       <c r="S114" t="s">
-        <v>33</v>
+        <v>831</v>
+      </c>
+      <c r="T114">
+        <v>86</v>
+      </c>
+      <c r="U114">
+        <v>71</v>
       </c>
       <c r="W114" t="s">
-        <v>36</v>
+        <v>256</v>
       </c>
       <c r="X114">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>805</v>
+        <v>247</v>
       </c>
       <c r="B115" t="s">
-        <v>806</v>
+        <v>825</v>
       </c>
       <c r="F115" t="s">
-        <v>807</v>
+        <v>826</v>
       </c>
       <c r="G115" t="s">
-        <v>808</v>
+        <v>827</v>
       </c>
       <c r="H115" t="s">
-        <v>809</v>
+        <v>154</v>
       </c>
       <c r="I115" t="s">
-        <v>810</v>
+        <v>38</v>
       </c>
       <c r="J115" t="s">
-        <v>811</v>
+        <v>39</v>
       </c>
       <c r="M115" t="s">
-        <v>812</v>
+        <v>90</v>
       </c>
       <c r="N115" t="s">
-        <v>813</v>
+        <v>832</v>
       </c>
       <c r="S115" t="s">
-        <v>81</v>
+        <v>833</v>
       </c>
       <c r="T115" t="s">
-        <v>814</v>
+        <v>834</v>
       </c>
       <c r="U115" t="s">
-        <v>815</v>
+        <v>835</v>
       </c>
       <c r="W115" t="s">
-        <v>36</v>
+        <v>256</v>
       </c>
       <c r="X115">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>816</v>
+        <v>247</v>
       </c>
       <c r="B116" t="s">
-        <v>817</v>
+        <v>825</v>
       </c>
       <c r="F116" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="G116" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="H116" t="s">
-        <v>820</v>
+        <v>836</v>
       </c>
       <c r="I116" t="s">
-        <v>104</v>
+        <v>837</v>
       </c>
       <c r="J116" t="s">
-        <v>821</v>
+        <v>838</v>
       </c>
       <c r="M116" t="s">
-        <v>822</v>
+        <v>839</v>
       </c>
       <c r="N116" t="s">
-        <v>823</v>
-      </c>
-      <c r="Q116" t="s">
-        <v>824</v>
+        <v>840</v>
       </c>
       <c r="S116" t="s">
-        <v>217</v>
+        <v>81</v>
+      </c>
+      <c r="T116" t="s">
+        <v>841</v>
+      </c>
+      <c r="U116" t="s">
+        <v>842</v>
       </c>
       <c r="W116" t="s">
-        <v>36</v>
+        <v>256</v>
       </c>
       <c r="X116">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10066,28 +10066,31 @@
         <v>827</v>
       </c>
       <c r="H117" t="s">
-        <v>828</v>
+        <v>843</v>
       </c>
       <c r="I117" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="J117" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="M117" t="s">
-        <v>829</v>
+        <v>844</v>
       </c>
       <c r="N117" t="s">
-        <v>830</v>
+        <v>845</v>
+      </c>
+      <c r="O117" t="s">
+        <v>846</v>
       </c>
       <c r="S117" t="s">
-        <v>831</v>
+        <v>847</v>
       </c>
       <c r="T117">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="U117">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="W117" t="s">
         <v>256</v>
@@ -10110,28 +10113,22 @@
         <v>827</v>
       </c>
       <c r="H118" t="s">
-        <v>154</v>
+        <v>614</v>
       </c>
       <c r="I118" t="s">
-        <v>38</v>
+        <v>369</v>
       </c>
       <c r="J118" t="s">
-        <v>39</v>
+        <v>370</v>
       </c>
       <c r="M118" t="s">
-        <v>90</v>
+        <v>848</v>
       </c>
       <c r="N118" t="s">
-        <v>832</v>
+        <v>849</v>
       </c>
       <c r="S118" t="s">
-        <v>833</v>
-      </c>
-      <c r="T118" t="s">
-        <v>834</v>
-      </c>
-      <c r="U118" t="s">
-        <v>835</v>
+        <v>850</v>
       </c>
       <c r="W118" t="s">
         <v>256</v>
@@ -10154,28 +10151,28 @@
         <v>827</v>
       </c>
       <c r="H119" t="s">
-        <v>836</v>
+        <v>851</v>
       </c>
       <c r="I119" t="s">
-        <v>837</v>
+        <v>38</v>
       </c>
       <c r="J119" t="s">
-        <v>838</v>
+        <v>39</v>
       </c>
       <c r="M119" t="s">
-        <v>839</v>
+        <v>852</v>
       </c>
       <c r="N119" t="s">
-        <v>840</v>
+        <v>853</v>
       </c>
       <c r="S119" t="s">
-        <v>81</v>
-      </c>
-      <c r="T119" t="s">
-        <v>841</v>
+        <v>847</v>
+      </c>
+      <c r="T119">
+        <v>93</v>
       </c>
       <c r="U119" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="W119" t="s">
         <v>256</v>
@@ -10198,31 +10195,31 @@
         <v>827</v>
       </c>
       <c r="H120" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="I120" t="s">
-        <v>77</v>
+        <v>855</v>
       </c>
       <c r="J120" t="s">
-        <v>78</v>
+        <v>856</v>
+      </c>
+      <c r="L120" t="s">
+        <v>857</v>
       </c>
       <c r="M120" t="s">
-        <v>844</v>
+        <v>858</v>
       </c>
       <c r="N120" t="s">
-        <v>845</v>
-      </c>
-      <c r="O120" t="s">
-        <v>846</v>
+        <v>859</v>
       </c>
       <c r="S120" t="s">
-        <v>847</v>
+        <v>860</v>
       </c>
       <c r="T120">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="U120">
-        <v>85</v>
+        <v>237</v>
       </c>
       <c r="W120" t="s">
         <v>256</v>
@@ -10245,19 +10242,19 @@
         <v>827</v>
       </c>
       <c r="H121" t="s">
-        <v>614</v>
+        <v>637</v>
       </c>
       <c r="I121" t="s">
-        <v>369</v>
+        <v>810</v>
       </c>
       <c r="J121" t="s">
-        <v>370</v>
+        <v>811</v>
       </c>
       <c r="M121" t="s">
-        <v>848</v>
+        <v>733</v>
       </c>
       <c r="N121" t="s">
-        <v>849</v>
+        <v>861</v>
       </c>
       <c r="S121" t="s">
         <v>850</v>
@@ -10283,28 +10280,22 @@
         <v>827</v>
       </c>
       <c r="H122" t="s">
-        <v>851</v>
+        <v>637</v>
       </c>
       <c r="I122" t="s">
-        <v>38</v>
+        <v>810</v>
       </c>
       <c r="J122" t="s">
-        <v>39</v>
+        <v>811</v>
       </c>
       <c r="M122" t="s">
-        <v>852</v>
+        <v>733</v>
       </c>
       <c r="N122" t="s">
-        <v>853</v>
+        <v>861</v>
       </c>
       <c r="S122" t="s">
-        <v>847</v>
-      </c>
-      <c r="T122">
-        <v>93</v>
-      </c>
-      <c r="U122" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="W122" t="s">
         <v>256</v>
@@ -10315,166 +10306,190 @@
     </row>
     <row r="123" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>247</v>
+        <v>862</v>
       </c>
       <c r="B123" t="s">
-        <v>825</v>
+        <v>863</v>
       </c>
       <c r="F123" t="s">
-        <v>826</v>
+        <v>135</v>
       </c>
       <c r="G123" t="s">
-        <v>827</v>
+        <v>864</v>
       </c>
       <c r="H123" t="s">
-        <v>851</v>
+        <v>103</v>
       </c>
       <c r="I123" t="s">
-        <v>855</v>
+        <v>138</v>
       </c>
       <c r="J123" t="s">
-        <v>856</v>
-      </c>
-      <c r="L123" t="s">
-        <v>857</v>
+        <v>139</v>
       </c>
       <c r="M123" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="N123" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="S123" t="s">
-        <v>860</v>
-      </c>
-      <c r="T123">
-        <v>146</v>
-      </c>
-      <c r="U123">
-        <v>237</v>
+        <v>81</v>
+      </c>
+      <c r="T123" t="s">
+        <v>132</v>
+      </c>
+      <c r="U123" t="s">
+        <v>867</v>
       </c>
       <c r="W123" t="s">
-        <v>256</v>
+        <v>145</v>
       </c>
       <c r="X123">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>247</v>
+        <v>862</v>
       </c>
       <c r="B124" t="s">
-        <v>825</v>
+        <v>863</v>
       </c>
       <c r="F124" t="s">
-        <v>826</v>
+        <v>135</v>
       </c>
       <c r="G124" t="s">
-        <v>827</v>
+        <v>864</v>
       </c>
       <c r="H124" t="s">
-        <v>637</v>
+        <v>868</v>
       </c>
       <c r="I124" t="s">
-        <v>810</v>
+        <v>146</v>
       </c>
       <c r="J124" t="s">
-        <v>811</v>
+        <v>869</v>
       </c>
       <c r="M124" t="s">
-        <v>733</v>
+        <v>870</v>
       </c>
       <c r="N124" t="s">
-        <v>861</v>
+        <v>871</v>
       </c>
       <c r="S124" t="s">
-        <v>850</v>
+        <v>81</v>
+      </c>
+      <c r="T124" t="s">
+        <v>872</v>
+      </c>
+      <c r="U124" t="s">
+        <v>44</v>
       </c>
       <c r="W124" t="s">
-        <v>256</v>
+        <v>145</v>
       </c>
       <c r="X124">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>247</v>
+        <v>873</v>
       </c>
       <c r="B125" t="s">
-        <v>825</v>
+        <v>874</v>
       </c>
       <c r="F125" t="s">
-        <v>826</v>
+        <v>875</v>
       </c>
       <c r="G125" t="s">
-        <v>827</v>
+        <v>421</v>
       </c>
       <c r="H125" t="s">
-        <v>637</v>
+        <v>876</v>
       </c>
       <c r="I125" t="s">
-        <v>810</v>
+        <v>29</v>
       </c>
       <c r="J125" t="s">
-        <v>811</v>
+        <v>710</v>
+      </c>
+      <c r="L125" t="s">
+        <v>877</v>
       </c>
       <c r="M125" t="s">
-        <v>733</v>
+        <v>878</v>
       </c>
       <c r="N125" t="s">
-        <v>861</v>
+        <v>879</v>
+      </c>
+      <c r="O125" t="s">
+        <v>880</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>881</v>
       </c>
       <c r="S125" t="s">
-        <v>850</v>
+        <v>217</v>
+      </c>
+      <c r="T125">
+        <v>450</v>
+      </c>
+      <c r="U125">
+        <v>450</v>
       </c>
       <c r="W125" t="s">
-        <v>256</v>
+        <v>36</v>
       </c>
       <c r="X125">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>862</v>
+        <v>873</v>
       </c>
       <c r="B126" t="s">
-        <v>863</v>
+        <v>874</v>
       </c>
       <c r="F126" t="s">
-        <v>135</v>
+        <v>875</v>
       </c>
       <c r="G126" t="s">
-        <v>864</v>
-      </c>
-      <c r="H126" t="s">
-        <v>103</v>
+        <v>421</v>
+      </c>
+      <c r="H126">
+        <v>1490</v>
       </c>
       <c r="I126" t="s">
-        <v>138</v>
+        <v>38</v>
       </c>
       <c r="J126" t="s">
-        <v>139</v>
+        <v>39</v>
+      </c>
+      <c r="L126" t="s">
+        <v>732</v>
       </c>
       <c r="M126" t="s">
-        <v>865</v>
+        <v>882</v>
       </c>
       <c r="N126" t="s">
-        <v>866</v>
+        <v>883</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>884</v>
       </c>
       <c r="S126" t="s">
-        <v>81</v>
-      </c>
-      <c r="T126" t="s">
-        <v>132</v>
-      </c>
-      <c r="U126" t="s">
-        <v>867</v>
+        <v>100</v>
+      </c>
+      <c r="T126">
+        <v>62</v>
+      </c>
+      <c r="U126">
+        <v>46</v>
       </c>
       <c r="W126" t="s">
-        <v>145</v>
+        <v>36</v>
       </c>
       <c r="X126">
         <v>3</v>
@@ -10482,43 +10497,43 @@
     </row>
     <row r="127" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>862</v>
+        <v>885</v>
       </c>
       <c r="B127" t="s">
-        <v>863</v>
+        <v>886</v>
       </c>
       <c r="F127" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="G127" t="s">
-        <v>864</v>
+        <v>887</v>
       </c>
       <c r="H127" t="s">
-        <v>868</v>
+        <v>637</v>
       </c>
       <c r="I127" t="s">
-        <v>146</v>
+        <v>888</v>
       </c>
       <c r="J127" t="s">
-        <v>869</v>
+        <v>889</v>
       </c>
       <c r="M127" t="s">
-        <v>870</v>
+        <v>890</v>
       </c>
       <c r="N127" t="s">
-        <v>871</v>
+        <v>891</v>
       </c>
       <c r="S127" t="s">
-        <v>81</v>
-      </c>
-      <c r="T127" t="s">
-        <v>872</v>
+        <v>892</v>
+      </c>
+      <c r="T127">
+        <v>206</v>
       </c>
       <c r="U127" t="s">
-        <v>44</v>
+        <v>893</v>
       </c>
       <c r="W127" t="s">
-        <v>145</v>
+        <v>894</v>
       </c>
       <c r="X127">
         <v>3</v>
@@ -10526,49 +10541,43 @@
     </row>
     <row r="128" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="B128" t="s">
-        <v>874</v>
+        <v>886</v>
       </c>
       <c r="F128" t="s">
-        <v>875</v>
+        <v>26</v>
       </c>
       <c r="G128" t="s">
-        <v>421</v>
+        <v>887</v>
       </c>
       <c r="H128" t="s">
-        <v>876</v>
+        <v>637</v>
       </c>
       <c r="I128" t="s">
-        <v>29</v>
+        <v>888</v>
       </c>
       <c r="J128" t="s">
-        <v>710</v>
-      </c>
-      <c r="L128" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="M128" t="s">
-        <v>878</v>
+        <v>895</v>
       </c>
       <c r="N128" t="s">
-        <v>879</v>
-      </c>
-      <c r="O128" t="s">
-        <v>880</v>
+        <v>896</v>
       </c>
       <c r="Q128" t="s">
-        <v>881</v>
+        <v>897</v>
       </c>
       <c r="S128" t="s">
-        <v>217</v>
+        <v>898</v>
       </c>
       <c r="T128">
-        <v>450</v>
+        <v>211</v>
       </c>
       <c r="U128">
-        <v>450</v>
+        <v>91</v>
       </c>
       <c r="W128" t="s">
         <v>36</v>
@@ -10579,46 +10588,46 @@
     </row>
     <row r="129" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>873</v>
+        <v>899</v>
       </c>
       <c r="B129" t="s">
-        <v>874</v>
+        <v>900</v>
       </c>
       <c r="F129" t="s">
-        <v>875</v>
+        <v>901</v>
       </c>
       <c r="G129" t="s">
-        <v>421</v>
+        <v>902</v>
       </c>
       <c r="H129">
-        <v>1490</v>
+        <v>1459</v>
       </c>
       <c r="I129" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J129" t="s">
-        <v>39</v>
+        <v>903</v>
       </c>
       <c r="L129" t="s">
-        <v>732</v>
+        <v>904</v>
       </c>
       <c r="M129" t="s">
-        <v>882</v>
+        <v>905</v>
       </c>
       <c r="N129" t="s">
-        <v>883</v>
+        <v>906</v>
       </c>
       <c r="Q129" t="s">
-        <v>884</v>
+        <v>907</v>
       </c>
       <c r="S129" t="s">
-        <v>100</v>
+        <v>908</v>
       </c>
       <c r="T129">
-        <v>62</v>
+        <v>405</v>
       </c>
       <c r="U129">
-        <v>46</v>
+        <v>516</v>
       </c>
       <c r="W129" t="s">
         <v>36</v>
@@ -10629,43 +10638,46 @@
     </row>
     <row r="130" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>885</v>
+        <v>899</v>
       </c>
       <c r="B130" t="s">
-        <v>886</v>
+        <v>900</v>
       </c>
       <c r="F130" t="s">
-        <v>26</v>
+        <v>901</v>
       </c>
       <c r="G130" t="s">
-        <v>887</v>
-      </c>
-      <c r="H130" t="s">
-        <v>637</v>
+        <v>902</v>
+      </c>
+      <c r="H130">
+        <v>1471</v>
       </c>
       <c r="I130" t="s">
-        <v>888</v>
+        <v>38</v>
       </c>
       <c r="J130" t="s">
-        <v>889</v>
+        <v>39</v>
       </c>
       <c r="M130" t="s">
-        <v>890</v>
+        <v>909</v>
       </c>
       <c r="N130" t="s">
-        <v>891</v>
+        <v>910</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>911</v>
       </c>
       <c r="S130" t="s">
-        <v>892</v>
+        <v>912</v>
       </c>
       <c r="T130">
-        <v>206</v>
-      </c>
-      <c r="U130" t="s">
-        <v>893</v>
+        <v>230</v>
+      </c>
+      <c r="U130">
+        <v>102</v>
       </c>
       <c r="W130" t="s">
-        <v>894</v>
+        <v>36</v>
       </c>
       <c r="X130">
         <v>3</v>
@@ -10673,46 +10685,37 @@
     </row>
     <row r="131" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>885</v>
+        <v>913</v>
       </c>
       <c r="B131" t="s">
-        <v>886</v>
+        <v>914</v>
       </c>
       <c r="F131" t="s">
-        <v>26</v>
+        <v>915</v>
       </c>
       <c r="G131" t="s">
-        <v>887</v>
+        <v>316</v>
       </c>
       <c r="H131" t="s">
-        <v>637</v>
+        <v>63</v>
       </c>
       <c r="I131" t="s">
-        <v>888</v>
+        <v>146</v>
       </c>
       <c r="J131" t="s">
-        <v>889</v>
+        <v>916</v>
       </c>
       <c r="M131" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="N131" t="s">
-        <v>896</v>
-      </c>
-      <c r="Q131" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="S131" t="s">
-        <v>898</v>
-      </c>
-      <c r="T131">
-        <v>211</v>
-      </c>
-      <c r="U131">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="W131" t="s">
-        <v>36</v>
+        <v>145</v>
       </c>
       <c r="X131">
         <v>3</v>
@@ -10720,49 +10723,37 @@
     </row>
     <row r="132" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>899</v>
+        <v>913</v>
       </c>
       <c r="B132" t="s">
-        <v>900</v>
+        <v>914</v>
       </c>
       <c r="F132" t="s">
-        <v>901</v>
+        <v>915</v>
       </c>
       <c r="G132" t="s">
-        <v>902</v>
-      </c>
-      <c r="H132">
-        <v>1459</v>
+        <v>316</v>
+      </c>
+      <c r="H132" t="s">
+        <v>919</v>
       </c>
       <c r="I132" t="s">
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="J132" t="s">
-        <v>903</v>
-      </c>
-      <c r="L132" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
       <c r="M132" t="s">
-        <v>905</v>
+        <v>921</v>
       </c>
       <c r="N132" t="s">
-        <v>906</v>
-      </c>
-      <c r="Q132" t="s">
-        <v>907</v>
+        <v>922</v>
       </c>
       <c r="S132" t="s">
-        <v>908</v>
-      </c>
-      <c r="T132">
-        <v>405</v>
-      </c>
-      <c r="U132">
-        <v>516</v>
+        <v>33</v>
       </c>
       <c r="W132" t="s">
-        <v>36</v>
+        <v>145</v>
       </c>
       <c r="X132">
         <v>3</v>
@@ -10770,43 +10761,43 @@
     </row>
     <row r="133" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>899</v>
+        <v>923</v>
       </c>
       <c r="B133" t="s">
-        <v>900</v>
+        <v>924</v>
       </c>
       <c r="F133" t="s">
-        <v>901</v>
+        <v>558</v>
       </c>
       <c r="G133" t="s">
-        <v>902</v>
-      </c>
-      <c r="H133">
-        <v>1471</v>
+        <v>925</v>
+      </c>
+      <c r="H133" t="s">
+        <v>926</v>
       </c>
       <c r="I133" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J133" t="s">
-        <v>39</v>
+        <v>927</v>
       </c>
       <c r="M133" t="s">
-        <v>909</v>
+        <v>928</v>
       </c>
       <c r="N133" t="s">
-        <v>910</v>
+        <v>929</v>
       </c>
       <c r="Q133" t="s">
-        <v>911</v>
+        <v>930</v>
       </c>
       <c r="S133" t="s">
-        <v>912</v>
-      </c>
-      <c r="T133">
-        <v>230</v>
-      </c>
-      <c r="U133">
-        <v>102</v>
+        <v>33</v>
+      </c>
+      <c r="T133" t="s">
+        <v>753</v>
+      </c>
+      <c r="U133" t="s">
+        <v>931</v>
       </c>
       <c r="W133" t="s">
         <v>36</v>
@@ -10817,37 +10808,43 @@
     </row>
     <row r="134" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>913</v>
+        <v>923</v>
       </c>
       <c r="B134" t="s">
-        <v>914</v>
+        <v>924</v>
       </c>
       <c r="F134" t="s">
-        <v>915</v>
+        <v>558</v>
       </c>
       <c r="G134" t="s">
-        <v>316</v>
+        <v>925</v>
       </c>
       <c r="H134" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="I134" t="s">
-        <v>146</v>
+        <v>29</v>
       </c>
       <c r="J134" t="s">
-        <v>916</v>
+        <v>127</v>
       </c>
       <c r="M134" t="s">
-        <v>917</v>
+        <v>932</v>
       </c>
       <c r="N134" t="s">
-        <v>918</v>
+        <v>933</v>
       </c>
       <c r="S134" t="s">
-        <v>109</v>
+        <v>934</v>
+      </c>
+      <c r="T134" t="s">
+        <v>125</v>
+      </c>
+      <c r="U134" t="s">
+        <v>935</v>
       </c>
       <c r="W134" t="s">
-        <v>145</v>
+        <v>36</v>
       </c>
       <c r="X134">
         <v>3</v>
@@ -10855,37 +10852,43 @@
     </row>
     <row r="135" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>913</v>
+        <v>936</v>
       </c>
       <c r="B135" t="s">
-        <v>914</v>
+        <v>924</v>
       </c>
       <c r="F135" t="s">
-        <v>915</v>
+        <v>937</v>
       </c>
       <c r="G135" t="s">
-        <v>316</v>
+        <v>938</v>
       </c>
       <c r="H135" t="s">
-        <v>919</v>
+        <v>939</v>
       </c>
       <c r="I135" t="s">
-        <v>146</v>
+        <v>29</v>
       </c>
       <c r="J135" t="s">
-        <v>920</v>
+        <v>127</v>
       </c>
       <c r="M135" t="s">
-        <v>921</v>
+        <v>733</v>
       </c>
       <c r="N135" t="s">
-        <v>922</v>
+        <v>940</v>
       </c>
       <c r="S135" t="s">
         <v>33</v>
       </c>
+      <c r="T135" t="s">
+        <v>760</v>
+      </c>
+      <c r="U135" t="s">
+        <v>941</v>
+      </c>
       <c r="W135" t="s">
-        <v>145</v>
+        <v>36</v>
       </c>
       <c r="X135">
         <v>3</v>
@@ -10893,43 +10896,43 @@
     </row>
     <row r="136" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>923</v>
+        <v>936</v>
       </c>
       <c r="B136" t="s">
         <v>924</v>
       </c>
       <c r="F136" t="s">
-        <v>558</v>
+        <v>937</v>
       </c>
       <c r="G136" t="s">
-        <v>925</v>
+        <v>938</v>
       </c>
       <c r="H136" t="s">
-        <v>926</v>
+        <v>942</v>
       </c>
       <c r="I136" t="s">
         <v>29</v>
       </c>
       <c r="J136" t="s">
-        <v>927</v>
+        <v>127</v>
       </c>
       <c r="M136" t="s">
-        <v>928</v>
+        <v>943</v>
       </c>
       <c r="N136" t="s">
-        <v>929</v>
+        <v>944</v>
       </c>
       <c r="Q136" t="s">
-        <v>930</v>
+        <v>945</v>
       </c>
       <c r="S136" t="s">
         <v>33</v>
       </c>
       <c r="T136" t="s">
-        <v>753</v>
+        <v>946</v>
       </c>
       <c r="U136" t="s">
-        <v>931</v>
+        <v>947</v>
       </c>
       <c r="W136" t="s">
         <v>36</v>
@@ -10940,43 +10943,37 @@
     </row>
     <row r="137" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>923</v>
+        <v>948</v>
       </c>
       <c r="B137" t="s">
-        <v>924</v>
+        <v>949</v>
       </c>
       <c r="F137" t="s">
-        <v>558</v>
+        <v>48</v>
       </c>
       <c r="G137" t="s">
-        <v>925</v>
+        <v>950</v>
       </c>
       <c r="H137" t="s">
-        <v>88</v>
+        <v>951</v>
       </c>
       <c r="I137" t="s">
-        <v>29</v>
+        <v>952</v>
       </c>
       <c r="J137" t="s">
-        <v>127</v>
+        <v>953</v>
       </c>
       <c r="M137" t="s">
-        <v>932</v>
+        <v>750</v>
       </c>
       <c r="N137" t="s">
-        <v>933</v>
+        <v>954</v>
       </c>
       <c r="S137" t="s">
-        <v>934</v>
-      </c>
-      <c r="T137" t="s">
-        <v>125</v>
-      </c>
-      <c r="U137" t="s">
-        <v>935</v>
+        <v>745</v>
       </c>
       <c r="W137" t="s">
-        <v>36</v>
+        <v>955</v>
       </c>
       <c r="X137">
         <v>3</v>
@@ -10984,43 +10981,43 @@
     </row>
     <row r="138" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="B138" t="s">
-        <v>924</v>
+        <v>949</v>
       </c>
       <c r="F138" t="s">
-        <v>937</v>
+        <v>48</v>
       </c>
       <c r="G138" t="s">
-        <v>938</v>
+        <v>950</v>
       </c>
       <c r="H138" t="s">
-        <v>939</v>
+        <v>956</v>
       </c>
       <c r="I138" t="s">
-        <v>29</v>
+        <v>952</v>
       </c>
       <c r="J138" t="s">
-        <v>127</v>
+        <v>957</v>
       </c>
       <c r="M138" t="s">
-        <v>733</v>
+        <v>958</v>
       </c>
       <c r="N138" t="s">
-        <v>940</v>
+        <v>959</v>
       </c>
       <c r="S138" t="s">
         <v>33</v>
       </c>
       <c r="T138" t="s">
-        <v>760</v>
+        <v>960</v>
       </c>
       <c r="U138" t="s">
-        <v>941</v>
+        <v>961</v>
       </c>
       <c r="W138" t="s">
-        <v>36</v>
+        <v>955</v>
       </c>
       <c r="X138">
         <v>3</v>
@@ -11028,131 +11025,140 @@
     </row>
     <row r="139" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>936</v>
+        <v>555</v>
       </c>
       <c r="B139" t="s">
-        <v>924</v>
+        <v>962</v>
       </c>
       <c r="F139" t="s">
-        <v>937</v>
+        <v>963</v>
       </c>
       <c r="G139" t="s">
-        <v>938</v>
+        <v>964</v>
       </c>
       <c r="H139" t="s">
-        <v>942</v>
+        <v>965</v>
       </c>
       <c r="I139" t="s">
-        <v>29</v>
+        <v>966</v>
       </c>
       <c r="J139" t="s">
-        <v>127</v>
+        <v>967</v>
+      </c>
+      <c r="L139" t="s">
+        <v>968</v>
       </c>
       <c r="M139" t="s">
-        <v>943</v>
+        <v>969</v>
       </c>
       <c r="N139" t="s">
-        <v>944</v>
+        <v>970</v>
       </c>
       <c r="Q139" t="s">
-        <v>945</v>
+        <v>971</v>
       </c>
       <c r="S139" t="s">
-        <v>33</v>
-      </c>
-      <c r="T139" t="s">
-        <v>946</v>
-      </c>
-      <c r="U139" t="s">
-        <v>947</v>
+        <v>109</v>
+      </c>
+      <c r="T139">
+        <v>480</v>
+      </c>
+      <c r="U139">
+        <v>450</v>
       </c>
       <c r="W139" t="s">
         <v>36</v>
       </c>
       <c r="X139">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>948</v>
+        <v>555</v>
       </c>
       <c r="B140" t="s">
-        <v>949</v>
+        <v>962</v>
       </c>
       <c r="F140" t="s">
-        <v>48</v>
+        <v>963</v>
       </c>
       <c r="G140" t="s">
-        <v>950</v>
+        <v>964</v>
       </c>
       <c r="H140" t="s">
-        <v>951</v>
+        <v>972</v>
       </c>
       <c r="I140" t="s">
-        <v>952</v>
+        <v>69</v>
       </c>
       <c r="J140" t="s">
-        <v>953</v>
+        <v>70</v>
       </c>
       <c r="M140" t="s">
-        <v>750</v>
+        <v>973</v>
       </c>
       <c r="N140" t="s">
-        <v>954</v>
+        <v>974</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>99</v>
       </c>
       <c r="S140" t="s">
-        <v>745</v>
+        <v>100</v>
+      </c>
+      <c r="T140">
+        <v>63</v>
+      </c>
+      <c r="U140">
+        <v>80</v>
       </c>
       <c r="W140" t="s">
-        <v>955</v>
+        <v>36</v>
       </c>
       <c r="X140">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>948</v>
+        <v>555</v>
       </c>
       <c r="B141" t="s">
-        <v>949</v>
+        <v>962</v>
       </c>
       <c r="F141" t="s">
-        <v>48</v>
+        <v>963</v>
       </c>
       <c r="G141" t="s">
-        <v>950</v>
+        <v>964</v>
       </c>
       <c r="H141" t="s">
-        <v>956</v>
+        <v>975</v>
       </c>
       <c r="I141" t="s">
-        <v>952</v>
+        <v>976</v>
       </c>
       <c r="J141" t="s">
-        <v>957</v>
+        <v>977</v>
       </c>
       <c r="M141" t="s">
-        <v>958</v>
+        <v>978</v>
       </c>
       <c r="N141" t="s">
-        <v>959</v>
+        <v>979</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>980</v>
       </c>
       <c r="S141" t="s">
-        <v>33</v>
-      </c>
-      <c r="T141" t="s">
-        <v>960</v>
-      </c>
-      <c r="U141" t="s">
-        <v>961</v>
+        <v>217</v>
       </c>
       <c r="W141" t="s">
-        <v>955</v>
+        <v>36</v>
       </c>
       <c r="X141">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11168,35 +11174,32 @@
       <c r="G142" t="s">
         <v>964</v>
       </c>
-      <c r="H142" t="s">
-        <v>965</v>
+      <c r="H142">
+        <v>1480</v>
       </c>
       <c r="I142" t="s">
-        <v>966</v>
+        <v>38</v>
       </c>
       <c r="J142" t="s">
-        <v>967</v>
-      </c>
-      <c r="L142" t="s">
-        <v>968</v>
+        <v>39</v>
       </c>
       <c r="M142" t="s">
-        <v>969</v>
+        <v>981</v>
       </c>
       <c r="N142" t="s">
-        <v>970</v>
+        <v>982</v>
       </c>
       <c r="Q142" t="s">
-        <v>971</v>
+        <v>983</v>
       </c>
       <c r="S142" t="s">
-        <v>109</v>
+        <v>984</v>
       </c>
       <c r="T142">
-        <v>480</v>
+        <v>255</v>
       </c>
       <c r="U142">
-        <v>450</v>
+        <v>140</v>
       </c>
       <c r="W142" t="s">
         <v>36</v>
@@ -11219,31 +11222,31 @@
         <v>964</v>
       </c>
       <c r="H143" t="s">
-        <v>972</v>
+        <v>985</v>
       </c>
       <c r="I143" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="J143" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="M143" t="s">
-        <v>973</v>
+        <v>986</v>
       </c>
       <c r="N143" t="s">
-        <v>974</v>
+        <v>987</v>
       </c>
       <c r="Q143" t="s">
-        <v>99</v>
+        <v>988</v>
       </c>
       <c r="S143" t="s">
-        <v>100</v>
+        <v>984</v>
       </c>
       <c r="T143">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="U143">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="W143" t="s">
         <v>36</v>
@@ -11266,25 +11269,22 @@
         <v>964</v>
       </c>
       <c r="H144" t="s">
-        <v>975</v>
+        <v>377</v>
       </c>
       <c r="I144" t="s">
-        <v>976</v>
+        <v>38</v>
       </c>
       <c r="J144" t="s">
-        <v>977</v>
+        <v>39</v>
       </c>
       <c r="M144" t="s">
-        <v>978</v>
+        <v>989</v>
       </c>
       <c r="N144" t="s">
-        <v>979</v>
-      </c>
-      <c r="Q144" t="s">
-        <v>980</v>
+        <v>990</v>
       </c>
       <c r="S144" t="s">
-        <v>217</v>
+        <v>85</v>
       </c>
       <c r="W144" t="s">
         <v>36</v>
@@ -11306,32 +11306,29 @@
       <c r="G145" t="s">
         <v>964</v>
       </c>
-      <c r="H145">
-        <v>1480</v>
+      <c r="H145" t="s">
+        <v>88</v>
       </c>
       <c r="I145" t="s">
-        <v>38</v>
+        <v>991</v>
       </c>
       <c r="J145" t="s">
-        <v>39</v>
+        <v>491</v>
       </c>
       <c r="M145" t="s">
-        <v>981</v>
+        <v>992</v>
       </c>
       <c r="N145" t="s">
-        <v>982</v>
-      </c>
-      <c r="Q145" t="s">
-        <v>983</v>
+        <v>993</v>
       </c>
       <c r="S145" t="s">
-        <v>984</v>
-      </c>
-      <c r="T145">
-        <v>255</v>
-      </c>
-      <c r="U145">
-        <v>140</v>
+        <v>85</v>
+      </c>
+      <c r="T145" t="s">
+        <v>309</v>
+      </c>
+      <c r="U145" t="s">
+        <v>994</v>
       </c>
       <c r="W145" t="s">
         <v>36</v>
@@ -11353,32 +11350,35 @@
       <c r="G146" t="s">
         <v>964</v>
       </c>
-      <c r="H146" t="s">
-        <v>985</v>
+      <c r="H146">
+        <v>1497</v>
       </c>
       <c r="I146" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="J146" t="s">
-        <v>105</v>
+        <v>39</v>
       </c>
       <c r="M146" t="s">
-        <v>986</v>
+        <v>995</v>
       </c>
       <c r="N146" t="s">
-        <v>987</v>
+        <v>996</v>
+      </c>
+      <c r="O146" t="s">
+        <v>997</v>
       </c>
       <c r="Q146" t="s">
-        <v>988</v>
+        <v>998</v>
       </c>
       <c r="S146" t="s">
-        <v>984</v>
+        <v>999</v>
       </c>
       <c r="T146">
-        <v>68</v>
+        <v>159</v>
       </c>
       <c r="U146">
-        <v>81</v>
+        <v>192</v>
       </c>
       <c r="W146" t="s">
         <v>36</v>
@@ -11389,131 +11389,134 @@
     </row>
     <row r="147" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>555</v>
+        <v>1000</v>
       </c>
       <c r="B147" t="s">
-        <v>962</v>
+        <v>1001</v>
       </c>
       <c r="F147" t="s">
-        <v>963</v>
+        <v>26</v>
       </c>
       <c r="G147" t="s">
-        <v>964</v>
+        <v>1002</v>
       </c>
       <c r="H147" t="s">
-        <v>377</v>
+        <v>1003</v>
       </c>
       <c r="I147" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="J147" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="M147" t="s">
-        <v>989</v>
+        <v>1004</v>
       </c>
       <c r="N147" t="s">
-        <v>990</v>
+        <v>1005</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>1006</v>
       </c>
       <c r="S147" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="W147" t="s">
-        <v>36</v>
+        <v>256</v>
       </c>
       <c r="X147">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>555</v>
+        <v>1000</v>
       </c>
       <c r="B148" t="s">
-        <v>962</v>
+        <v>1001</v>
       </c>
       <c r="F148" t="s">
-        <v>963</v>
+        <v>26</v>
       </c>
       <c r="G148" t="s">
-        <v>964</v>
+        <v>1002</v>
       </c>
       <c r="H148" t="s">
-        <v>88</v>
+        <v>1007</v>
       </c>
       <c r="I148" t="s">
-        <v>991</v>
+        <v>1008</v>
       </c>
       <c r="J148" t="s">
-        <v>491</v>
+        <v>1009</v>
       </c>
       <c r="M148" t="s">
-        <v>992</v>
+        <v>1010</v>
       </c>
       <c r="N148" t="s">
-        <v>993</v>
+        <v>1011</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>1012</v>
       </c>
       <c r="S148" t="s">
-        <v>85</v>
+        <v>847</v>
       </c>
       <c r="T148" t="s">
-        <v>309</v>
-      </c>
-      <c r="U148" t="s">
-        <v>994</v>
+        <v>1013</v>
+      </c>
+      <c r="U148">
+        <v>27</v>
       </c>
       <c r="W148" t="s">
-        <v>36</v>
+        <v>256</v>
       </c>
       <c r="X148">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>555</v>
+        <v>1014</v>
       </c>
       <c r="B149" t="s">
-        <v>962</v>
+        <v>1015</v>
       </c>
       <c r="F149" t="s">
-        <v>963</v>
+        <v>94</v>
       </c>
       <c r="G149" t="s">
-        <v>964</v>
-      </c>
-      <c r="H149">
-        <v>1497</v>
+        <v>421</v>
+      </c>
+      <c r="H149" t="s">
+        <v>1016</v>
       </c>
       <c r="I149" t="s">
-        <v>38</v>
+        <v>1017</v>
       </c>
       <c r="J149" t="s">
-        <v>39</v>
+        <v>1018</v>
       </c>
       <c r="M149" t="s">
-        <v>995</v>
+        <v>750</v>
       </c>
       <c r="N149" t="s">
-        <v>996</v>
-      </c>
-      <c r="O149" t="s">
-        <v>997</v>
+        <v>1019</v>
       </c>
       <c r="Q149" t="s">
-        <v>998</v>
+        <v>1020</v>
       </c>
       <c r="S149" t="s">
-        <v>999</v>
-      </c>
-      <c r="T149">
-        <v>159</v>
-      </c>
-      <c r="U149">
-        <v>192</v>
+        <v>1021</v>
+      </c>
+      <c r="T149" t="s">
+        <v>1022</v>
+      </c>
+      <c r="U149" t="s">
+        <v>792</v>
       </c>
       <c r="W149" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="X149">
         <v>2</v>
@@ -11521,90 +11524,99 @@
     </row>
     <row r="150" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>1000</v>
+        <v>1014</v>
       </c>
       <c r="B150" t="s">
-        <v>1001</v>
+        <v>1015</v>
       </c>
       <c r="F150" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="G150" t="s">
-        <v>1002</v>
+        <v>421</v>
       </c>
       <c r="H150" t="s">
-        <v>1003</v>
+        <v>1023</v>
       </c>
       <c r="I150" t="s">
-        <v>77</v>
+        <v>460</v>
       </c>
       <c r="J150" t="s">
-        <v>78</v>
+        <v>1024</v>
+      </c>
+      <c r="L150" t="s">
+        <v>1025</v>
       </c>
       <c r="M150" t="s">
-        <v>1004</v>
+        <v>1026</v>
       </c>
       <c r="N150" t="s">
-        <v>1005</v>
+        <v>1027</v>
       </c>
       <c r="Q150" t="s">
-        <v>1006</v>
+        <v>1028</v>
       </c>
       <c r="S150" t="s">
-        <v>81</v>
+        <v>847</v>
+      </c>
+      <c r="T150" t="s">
+        <v>1029</v>
+      </c>
+      <c r="U150" t="s">
+        <v>1030</v>
       </c>
       <c r="W150" t="s">
-        <v>256</v>
+        <v>55</v>
       </c>
       <c r="X150">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>1000</v>
+        <v>1014</v>
       </c>
       <c r="B151" t="s">
-        <v>1001</v>
+        <v>1015</v>
       </c>
       <c r="F151" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="G151" t="s">
-        <v>1002</v>
+        <v>421</v>
       </c>
       <c r="H151" t="s">
-        <v>1007</v>
+        <v>68</v>
       </c>
       <c r="I151" t="s">
-        <v>1008</v>
+        <v>810</v>
       </c>
       <c r="J151" t="s">
-        <v>1009</v>
+        <v>811</v>
       </c>
       <c r="M151" t="s">
-        <v>1010</v>
+        <v>1031</v>
       </c>
       <c r="N151" t="s">
-        <v>1011</v>
+        <v>1032</v>
       </c>
       <c r="Q151" t="s">
-        <v>1012</v>
+        <v>1033</v>
       </c>
       <c r="S151" t="s">
-        <v>847</v>
+        <v>159</v>
       </c>
       <c r="T151" t="s">
-        <v>1013</v>
-      </c>
-      <c r="U151">
-        <v>27</v>
+        <v>101</v>
+      </c>
+      <c r="U151" t="s">
+        <v>1034</v>
       </c>
       <c r="W151" t="s">
-        <v>256</v>
+        <v>55</v>
       </c>
       <c r="X151">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11621,34 +11633,25 @@
         <v>421</v>
       </c>
       <c r="H152" t="s">
-        <v>1016</v>
+        <v>76</v>
       </c>
       <c r="I152" t="s">
-        <v>1017</v>
+        <v>29</v>
       </c>
       <c r="J152" t="s">
-        <v>1018</v>
+        <v>127</v>
       </c>
       <c r="M152" t="s">
-        <v>750</v>
+        <v>1035</v>
       </c>
       <c r="N152" t="s">
-        <v>1019</v>
-      </c>
-      <c r="Q152" t="s">
-        <v>1020</v>
+        <v>1036</v>
       </c>
       <c r="S152" t="s">
-        <v>1021</v>
-      </c>
-      <c r="T152" t="s">
-        <v>1022</v>
-      </c>
-      <c r="U152" t="s">
-        <v>792</v>
+        <v>81</v>
       </c>
       <c r="W152" t="s">
-        <v>55</v>
+        <v>955</v>
       </c>
       <c r="X152">
         <v>2</v>
@@ -11668,37 +11671,25 @@
         <v>421</v>
       </c>
       <c r="H153" t="s">
-        <v>1023</v>
+        <v>1037</v>
       </c>
       <c r="I153" t="s">
         <v>460</v>
       </c>
       <c r="J153" t="s">
-        <v>1024</v>
-      </c>
-      <c r="L153" t="s">
-        <v>1025</v>
+        <v>461</v>
       </c>
       <c r="M153" t="s">
-        <v>1026</v>
+        <v>1038</v>
       </c>
       <c r="N153" t="s">
-        <v>1027</v>
-      </c>
-      <c r="Q153" t="s">
-        <v>1028</v>
+        <v>1039</v>
       </c>
       <c r="S153" t="s">
-        <v>847</v>
-      </c>
-      <c r="T153" t="s">
-        <v>1029</v>
-      </c>
-      <c r="U153" t="s">
-        <v>1030</v>
+        <v>81</v>
       </c>
       <c r="W153" t="s">
-        <v>55</v>
+        <v>955</v>
       </c>
       <c r="X153">
         <v>2</v>
@@ -11718,31 +11709,34 @@
         <v>421</v>
       </c>
       <c r="H154" t="s">
-        <v>68</v>
+        <v>1040</v>
       </c>
       <c r="I154" t="s">
-        <v>810</v>
+        <v>460</v>
       </c>
       <c r="J154" t="s">
-        <v>811</v>
+        <v>1024</v>
+      </c>
+      <c r="L154" t="s">
+        <v>1025</v>
       </c>
       <c r="M154" t="s">
-        <v>1031</v>
+        <v>1041</v>
       </c>
       <c r="N154" t="s">
-        <v>1032</v>
+        <v>1042</v>
       </c>
       <c r="Q154" t="s">
-        <v>1033</v>
+        <v>1043</v>
       </c>
       <c r="S154" t="s">
         <v>159</v>
       </c>
       <c r="T154" t="s">
-        <v>101</v>
+        <v>1044</v>
       </c>
       <c r="U154" t="s">
-        <v>1034</v>
+        <v>1045</v>
       </c>
       <c r="W154" t="s">
         <v>55</v>
@@ -11765,19 +11759,19 @@
         <v>421</v>
       </c>
       <c r="H155" t="s">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="I155" t="s">
-        <v>29</v>
+        <v>837</v>
       </c>
       <c r="J155" t="s">
-        <v>127</v>
+        <v>1046</v>
       </c>
       <c r="M155" t="s">
-        <v>1035</v>
+        <v>1047</v>
       </c>
       <c r="N155" t="s">
-        <v>1036</v>
+        <v>1048</v>
       </c>
       <c r="S155" t="s">
         <v>81</v>
@@ -11803,25 +11797,37 @@
         <v>421</v>
       </c>
       <c r="H156" t="s">
-        <v>1037</v>
+        <v>1002</v>
       </c>
       <c r="I156" t="s">
         <v>460</v>
       </c>
       <c r="J156" t="s">
-        <v>461</v>
+        <v>1024</v>
+      </c>
+      <c r="L156" t="s">
+        <v>1025</v>
       </c>
       <c r="M156" t="s">
-        <v>1038</v>
+        <v>1049</v>
       </c>
       <c r="N156" t="s">
-        <v>1039</v>
+        <v>1050</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>1051</v>
       </c>
       <c r="S156" t="s">
-        <v>81</v>
+        <v>1052</v>
+      </c>
+      <c r="T156" t="s">
+        <v>1053</v>
+      </c>
+      <c r="U156" t="s">
+        <v>1054</v>
       </c>
       <c r="W156" t="s">
-        <v>955</v>
+        <v>55</v>
       </c>
       <c r="X156">
         <v>2</v>
@@ -11829,175 +11835,175 @@
     </row>
     <row r="157" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>1014</v>
+        <v>1055</v>
       </c>
       <c r="B157" t="s">
-        <v>1015</v>
+        <v>1056</v>
       </c>
       <c r="F157" t="s">
-        <v>94</v>
+        <v>951</v>
       </c>
       <c r="G157" t="s">
-        <v>421</v>
+        <v>1057</v>
       </c>
       <c r="H157" t="s">
-        <v>1040</v>
+        <v>1058</v>
       </c>
       <c r="I157" t="s">
-        <v>460</v>
+        <v>1059</v>
       </c>
       <c r="J157" t="s">
-        <v>1024</v>
-      </c>
-      <c r="L157" t="s">
-        <v>1025</v>
+        <v>1060</v>
       </c>
       <c r="M157" t="s">
-        <v>1041</v>
+        <v>1061</v>
       </c>
       <c r="N157" t="s">
-        <v>1042</v>
-      </c>
-      <c r="Q157" t="s">
-        <v>1043</v>
+        <v>1062</v>
       </c>
       <c r="S157" t="s">
-        <v>159</v>
-      </c>
-      <c r="T157" t="s">
-        <v>1044</v>
-      </c>
-      <c r="U157" t="s">
-        <v>1045</v>
+        <v>1063</v>
       </c>
       <c r="W157" t="s">
-        <v>55</v>
+        <v>1064</v>
       </c>
       <c r="X157">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>1014</v>
+        <v>1055</v>
       </c>
       <c r="B158" t="s">
-        <v>1015</v>
+        <v>1056</v>
       </c>
       <c r="F158" t="s">
-        <v>94</v>
+        <v>951</v>
       </c>
       <c r="G158" t="s">
-        <v>421</v>
+        <v>1057</v>
       </c>
       <c r="H158" t="s">
-        <v>119</v>
+        <v>1065</v>
       </c>
       <c r="I158" t="s">
-        <v>837</v>
+        <v>810</v>
       </c>
       <c r="J158" t="s">
-        <v>1046</v>
+        <v>811</v>
       </c>
       <c r="M158" t="s">
-        <v>1047</v>
+        <v>1066</v>
       </c>
       <c r="N158" t="s">
-        <v>1048</v>
+        <v>1067</v>
       </c>
       <c r="S158" t="s">
         <v>81</v>
       </c>
+      <c r="T158" t="s">
+        <v>411</v>
+      </c>
+      <c r="U158" t="s">
+        <v>629</v>
+      </c>
       <c r="W158" t="s">
         <v>955</v>
       </c>
       <c r="X158">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>1014</v>
+        <v>1068</v>
       </c>
       <c r="B159" t="s">
-        <v>1015</v>
+        <v>1069</v>
+      </c>
+      <c r="D159" t="s">
+        <v>1070</v>
       </c>
       <c r="F159" t="s">
-        <v>94</v>
+        <v>1071</v>
       </c>
       <c r="G159" t="s">
-        <v>421</v>
+        <v>458</v>
       </c>
       <c r="H159" t="s">
-        <v>1002</v>
+        <v>205</v>
       </c>
       <c r="I159" t="s">
-        <v>460</v>
+        <v>423</v>
       </c>
       <c r="J159" t="s">
-        <v>1024</v>
-      </c>
-      <c r="L159" t="s">
-        <v>1025</v>
+        <v>212</v>
       </c>
       <c r="M159" t="s">
-        <v>1049</v>
+        <v>1072</v>
       </c>
       <c r="N159" t="s">
-        <v>1050</v>
+        <v>1073</v>
       </c>
       <c r="Q159" t="s">
-        <v>1051</v>
+        <v>1074</v>
       </c>
       <c r="S159" t="s">
-        <v>1052</v>
+        <v>217</v>
       </c>
       <c r="T159" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
       <c r="U159" t="s">
-        <v>1054</v>
+        <v>785</v>
       </c>
       <c r="W159" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="X159">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>1055</v>
+        <v>1068</v>
       </c>
       <c r="B160" t="s">
-        <v>1056</v>
+        <v>1069</v>
       </c>
       <c r="F160" t="s">
-        <v>951</v>
+        <v>1071</v>
       </c>
       <c r="G160" t="s">
-        <v>1057</v>
+        <v>458</v>
       </c>
       <c r="H160" t="s">
-        <v>1058</v>
+        <v>421</v>
       </c>
       <c r="I160" t="s">
-        <v>1059</v>
+        <v>29</v>
       </c>
       <c r="J160" t="s">
-        <v>1060</v>
+        <v>127</v>
       </c>
       <c r="M160" t="s">
-        <v>1061</v>
+        <v>1076</v>
       </c>
       <c r="N160" t="s">
-        <v>1062</v>
+        <v>1077</v>
       </c>
       <c r="S160" t="s">
-        <v>1063</v>
+        <v>81</v>
+      </c>
+      <c r="T160" t="s">
+        <v>1078</v>
+      </c>
+      <c r="U160" t="s">
+        <v>1044</v>
       </c>
       <c r="W160" t="s">
-        <v>1064</v>
+        <v>36</v>
       </c>
       <c r="X160">
         <v>3</v>
@@ -12005,43 +12011,49 @@
     </row>
     <row r="161" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>1055</v>
+        <v>1079</v>
       </c>
       <c r="B161" t="s">
-        <v>1056</v>
+        <v>1080</v>
       </c>
       <c r="F161" t="s">
-        <v>951</v>
+        <v>1081</v>
       </c>
       <c r="G161" t="s">
         <v>1057</v>
       </c>
       <c r="H161" t="s">
-        <v>1065</v>
+        <v>37</v>
       </c>
       <c r="I161" t="s">
-        <v>810</v>
+        <v>29</v>
       </c>
       <c r="J161" t="s">
-        <v>811</v>
+        <v>482</v>
       </c>
       <c r="M161" t="s">
-        <v>1066</v>
+        <v>1082</v>
       </c>
       <c r="N161" t="s">
-        <v>1067</v>
+        <v>1083</v>
+      </c>
+      <c r="O161" t="s">
+        <v>1084</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>1085</v>
       </c>
       <c r="S161" t="s">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="T161" t="s">
-        <v>411</v>
-      </c>
-      <c r="U161" t="s">
-        <v>629</v>
+        <v>395</v>
+      </c>
+      <c r="U161">
+        <v>12</v>
       </c>
       <c r="W161" t="s">
-        <v>955</v>
+        <v>36</v>
       </c>
       <c r="X161">
         <v>3</v>
@@ -12049,46 +12061,43 @@
     </row>
     <row r="162" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>1068</v>
+        <v>1079</v>
       </c>
       <c r="B162" t="s">
-        <v>1069</v>
-      </c>
-      <c r="D162" t="s">
-        <v>1070</v>
+        <v>1080</v>
       </c>
       <c r="F162" t="s">
-        <v>1071</v>
+        <v>1081</v>
       </c>
       <c r="G162" t="s">
-        <v>458</v>
-      </c>
-      <c r="H162" t="s">
-        <v>205</v>
+        <v>1057</v>
+      </c>
+      <c r="H162">
+        <v>1475</v>
       </c>
       <c r="I162" t="s">
-        <v>423</v>
+        <v>69</v>
       </c>
       <c r="J162" t="s">
-        <v>212</v>
+        <v>70</v>
       </c>
       <c r="M162" t="s">
-        <v>1072</v>
+        <v>1086</v>
       </c>
       <c r="N162" t="s">
-        <v>1073</v>
+        <v>1087</v>
       </c>
       <c r="Q162" t="s">
-        <v>1074</v>
+        <v>1088</v>
       </c>
       <c r="S162" t="s">
-        <v>217</v>
+        <v>1089</v>
       </c>
       <c r="T162" t="s">
-        <v>1075</v>
+        <v>1090</v>
       </c>
       <c r="U162" t="s">
-        <v>785</v>
+        <v>1091</v>
       </c>
       <c r="W162" t="s">
         <v>36</v>
@@ -12099,43 +12108,43 @@
     </row>
     <row r="163" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>1068</v>
+        <v>247</v>
       </c>
       <c r="B163" t="s">
-        <v>1069</v>
+        <v>1092</v>
       </c>
       <c r="F163" t="s">
-        <v>1071</v>
+        <v>49</v>
       </c>
       <c r="G163" t="s">
-        <v>458</v>
+        <v>1093</v>
       </c>
       <c r="H163" t="s">
-        <v>421</v>
+        <v>1094</v>
       </c>
       <c r="I163" t="s">
-        <v>29</v>
+        <v>1095</v>
       </c>
       <c r="J163" t="s">
-        <v>127</v>
+        <v>1096</v>
       </c>
       <c r="M163" t="s">
-        <v>1076</v>
+        <v>1097</v>
       </c>
       <c r="N163" t="s">
-        <v>1077</v>
+        <v>1098</v>
       </c>
       <c r="S163" t="s">
-        <v>81</v>
-      </c>
-      <c r="T163" t="s">
-        <v>1078</v>
-      </c>
-      <c r="U163" t="s">
-        <v>1044</v>
+        <v>1099</v>
+      </c>
+      <c r="T163">
+        <v>143</v>
+      </c>
+      <c r="U163">
+        <v>260</v>
       </c>
       <c r="W163" t="s">
-        <v>36</v>
+        <v>256</v>
       </c>
       <c r="X163">
         <v>3</v>
@@ -12143,49 +12152,43 @@
     </row>
     <row r="164" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>1079</v>
+        <v>1100</v>
       </c>
       <c r="B164" t="s">
-        <v>1080</v>
+        <v>1101</v>
       </c>
       <c r="F164" t="s">
-        <v>1081</v>
+        <v>347</v>
       </c>
       <c r="G164" t="s">
-        <v>1057</v>
+        <v>1102</v>
       </c>
       <c r="H164" t="s">
-        <v>37</v>
+        <v>1103</v>
       </c>
       <c r="I164" t="s">
-        <v>29</v>
+        <v>1104</v>
       </c>
       <c r="J164" t="s">
-        <v>482</v>
+        <v>1105</v>
       </c>
       <c r="M164" t="s">
-        <v>1082</v>
+        <v>733</v>
       </c>
       <c r="N164" t="s">
-        <v>1083</v>
-      </c>
-      <c r="O164" t="s">
-        <v>1084</v>
-      </c>
-      <c r="Q164" t="s">
-        <v>1085</v>
+        <v>1106</v>
       </c>
       <c r="S164" t="s">
-        <v>204</v>
+        <v>109</v>
       </c>
       <c r="T164" t="s">
-        <v>395</v>
-      </c>
-      <c r="U164">
-        <v>12</v>
+        <v>1107</v>
+      </c>
+      <c r="U164" t="s">
+        <v>760</v>
       </c>
       <c r="W164" t="s">
-        <v>36</v>
+        <v>256</v>
       </c>
       <c r="X164">
         <v>3</v>
@@ -12193,46 +12196,43 @@
     </row>
     <row r="165" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>1079</v>
+        <v>1100</v>
       </c>
       <c r="B165" t="s">
-        <v>1080</v>
+        <v>1101</v>
       </c>
       <c r="F165" t="s">
-        <v>1081</v>
+        <v>347</v>
       </c>
       <c r="G165" t="s">
-        <v>1057</v>
-      </c>
-      <c r="H165">
-        <v>1475</v>
+        <v>1102</v>
+      </c>
+      <c r="H165" t="s">
+        <v>614</v>
       </c>
       <c r="I165" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="J165" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="M165" t="s">
-        <v>1086</v>
+        <v>1108</v>
       </c>
       <c r="N165" t="s">
-        <v>1087</v>
-      </c>
-      <c r="Q165" t="s">
-        <v>1088</v>
+        <v>1109</v>
       </c>
       <c r="S165" t="s">
-        <v>1089</v>
+        <v>81</v>
       </c>
       <c r="T165" t="s">
-        <v>1090</v>
+        <v>1110</v>
       </c>
       <c r="U165" t="s">
-        <v>1091</v>
+        <v>1111</v>
       </c>
       <c r="W165" t="s">
-        <v>36</v>
+        <v>256</v>
       </c>
       <c r="X165">
         <v>3</v>
@@ -12240,43 +12240,52 @@
     </row>
     <row r="166" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>247</v>
+        <v>1112</v>
       </c>
       <c r="B166" t="s">
-        <v>1092</v>
+        <v>1113</v>
       </c>
       <c r="F166" t="s">
-        <v>49</v>
+        <v>1114</v>
       </c>
       <c r="G166" t="s">
-        <v>1093</v>
+        <v>62</v>
       </c>
       <c r="H166" t="s">
-        <v>1094</v>
+        <v>205</v>
       </c>
       <c r="I166" t="s">
-        <v>1095</v>
+        <v>210</v>
       </c>
       <c r="J166" t="s">
-        <v>1096</v>
+        <v>211</v>
+      </c>
+      <c r="L166" t="s">
+        <v>1115</v>
       </c>
       <c r="M166" t="s">
-        <v>1097</v>
+        <v>1116</v>
       </c>
       <c r="N166" t="s">
-        <v>1098</v>
+        <v>1117</v>
+      </c>
+      <c r="O166" t="s">
+        <v>1118</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>1119</v>
       </c>
       <c r="S166" t="s">
-        <v>1099</v>
+        <v>217</v>
       </c>
       <c r="T166">
-        <v>143</v>
+        <v>349</v>
       </c>
       <c r="U166">
-        <v>260</v>
+        <v>570</v>
       </c>
       <c r="W166" t="s">
-        <v>256</v>
+        <v>36</v>
       </c>
       <c r="X166">
         <v>3</v>
@@ -12284,43 +12293,52 @@
     </row>
     <row r="167" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>1100</v>
+        <v>1112</v>
       </c>
       <c r="B167" t="s">
-        <v>1101</v>
+        <v>1113</v>
       </c>
       <c r="F167" t="s">
-        <v>347</v>
+        <v>1114</v>
       </c>
       <c r="G167" t="s">
-        <v>1102</v>
+        <v>62</v>
       </c>
       <c r="H167" t="s">
-        <v>1103</v>
+        <v>205</v>
       </c>
       <c r="I167" t="s">
-        <v>1104</v>
+        <v>210</v>
       </c>
       <c r="J167" t="s">
-        <v>1105</v>
+        <v>211</v>
+      </c>
+      <c r="L167" t="s">
+        <v>1115</v>
       </c>
       <c r="M167" t="s">
-        <v>733</v>
+        <v>549</v>
       </c>
       <c r="N167" t="s">
-        <v>1106</v>
+        <v>1120</v>
+      </c>
+      <c r="O167" t="s">
+        <v>1118</v>
+      </c>
+      <c r="Q167" t="s">
+        <v>562</v>
       </c>
       <c r="S167" t="s">
-        <v>109</v>
-      </c>
-      <c r="T167" t="s">
-        <v>1107</v>
-      </c>
-      <c r="U167" t="s">
-        <v>760</v>
+        <v>217</v>
+      </c>
+      <c r="T167">
+        <v>349</v>
+      </c>
+      <c r="U167">
+        <v>570</v>
       </c>
       <c r="W167" t="s">
-        <v>256</v>
+        <v>36</v>
       </c>
       <c r="X167">
         <v>3</v>
@@ -12328,43 +12346,43 @@
     </row>
     <row r="168" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>1100</v>
+        <v>1121</v>
       </c>
       <c r="B168" t="s">
-        <v>1101</v>
+        <v>1122</v>
       </c>
       <c r="F168" t="s">
-        <v>347</v>
+        <v>1123</v>
       </c>
       <c r="G168" t="s">
-        <v>1102</v>
+        <v>458</v>
       </c>
       <c r="H168" t="s">
-        <v>614</v>
+        <v>1124</v>
       </c>
       <c r="I168" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="J168" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
       <c r="M168" t="s">
-        <v>1108</v>
+        <v>1125</v>
       </c>
       <c r="N168" t="s">
-        <v>1109</v>
+        <v>1126</v>
       </c>
       <c r="S168" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="T168" t="s">
-        <v>1110</v>
+        <v>1127</v>
       </c>
       <c r="U168" t="s">
-        <v>1111</v>
+        <v>1128</v>
       </c>
       <c r="W168" t="s">
-        <v>256</v>
+        <v>36</v>
       </c>
       <c r="X168">
         <v>3</v>
@@ -12372,49 +12390,46 @@
     </row>
     <row r="169" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>1112</v>
+        <v>1129</v>
       </c>
       <c r="B169" t="s">
-        <v>1113</v>
+        <v>1130</v>
       </c>
       <c r="F169" t="s">
-        <v>1114</v>
+        <v>94</v>
       </c>
       <c r="G169" t="s">
-        <v>62</v>
-      </c>
-      <c r="H169" t="s">
-        <v>205</v>
+        <v>339</v>
+      </c>
+      <c r="H169">
+        <v>1469</v>
       </c>
       <c r="I169" t="s">
-        <v>210</v>
+        <v>575</v>
       </c>
       <c r="J169" t="s">
-        <v>211</v>
-      </c>
-      <c r="L169" t="s">
-        <v>1115</v>
+        <v>1131</v>
       </c>
       <c r="M169" t="s">
-        <v>1116</v>
+        <v>1132</v>
       </c>
       <c r="N169" t="s">
-        <v>1117</v>
+        <v>1133</v>
       </c>
       <c r="O169" t="s">
-        <v>1118</v>
+        <v>1134</v>
       </c>
       <c r="Q169" t="s">
-        <v>1119</v>
+        <v>1135</v>
       </c>
       <c r="S169" t="s">
-        <v>217</v>
+        <v>85</v>
       </c>
       <c r="T169">
         <v>349</v>
       </c>
       <c r="U169">
-        <v>570</v>
+        <v>152</v>
       </c>
       <c r="W169" t="s">
         <v>36</v>
@@ -12425,49 +12440,46 @@
     </row>
     <row r="170" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>1112</v>
+        <v>1129</v>
       </c>
       <c r="B170" t="s">
-        <v>1113</v>
+        <v>1130</v>
       </c>
       <c r="F170" t="s">
-        <v>1114</v>
+        <v>94</v>
       </c>
       <c r="G170" t="s">
-        <v>62</v>
+        <v>339</v>
       </c>
       <c r="H170" t="s">
-        <v>205</v>
+        <v>1136</v>
       </c>
       <c r="I170" t="s">
-        <v>210</v>
+        <v>69</v>
       </c>
       <c r="J170" t="s">
-        <v>211</v>
-      </c>
-      <c r="L170" t="s">
-        <v>1115</v>
+        <v>70</v>
       </c>
       <c r="M170" t="s">
-        <v>549</v>
+        <v>1137</v>
       </c>
       <c r="N170" t="s">
-        <v>1120</v>
+        <v>1138</v>
       </c>
       <c r="O170" t="s">
-        <v>1118</v>
+        <v>1139</v>
       </c>
       <c r="Q170" t="s">
-        <v>562</v>
+        <v>1140</v>
       </c>
       <c r="S170" t="s">
-        <v>217</v>
+        <v>1141</v>
       </c>
       <c r="T170">
-        <v>349</v>
+        <v>239</v>
       </c>
       <c r="U170">
-        <v>570</v>
+        <v>102</v>
       </c>
       <c r="W170" t="s">
         <v>36</v>
@@ -12478,146 +12490,137 @@
     </row>
     <row r="171" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>1121</v>
+        <v>1142</v>
       </c>
       <c r="B171" t="s">
-        <v>1122</v>
+        <v>1143</v>
       </c>
       <c r="F171" t="s">
-        <v>1123</v>
+        <v>1144</v>
       </c>
       <c r="G171" t="s">
-        <v>458</v>
+        <v>196</v>
       </c>
       <c r="H171" t="s">
-        <v>1124</v>
+        <v>1145</v>
       </c>
       <c r="I171" t="s">
-        <v>104</v>
+        <v>29</v>
       </c>
       <c r="J171" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="M171" t="s">
-        <v>1125</v>
+        <v>1146</v>
       </c>
       <c r="N171" t="s">
-        <v>1126</v>
+        <v>1147</v>
+      </c>
+      <c r="Q171" t="s">
+        <v>1148</v>
       </c>
       <c r="S171" t="s">
-        <v>33</v>
-      </c>
-      <c r="T171" t="s">
-        <v>1127</v>
-      </c>
-      <c r="U171" t="s">
-        <v>1128</v>
+        <v>1149</v>
+      </c>
+      <c r="T171">
+        <v>182</v>
+      </c>
+      <c r="U171">
+        <v>323</v>
       </c>
       <c r="W171" t="s">
         <v>36</v>
       </c>
       <c r="X171">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>1129</v>
+        <v>1142</v>
       </c>
       <c r="B172" t="s">
-        <v>1130</v>
+        <v>1143</v>
       </c>
       <c r="F172" t="s">
-        <v>94</v>
+        <v>1144</v>
       </c>
       <c r="G172" t="s">
-        <v>339</v>
-      </c>
-      <c r="H172">
-        <v>1469</v>
+        <v>196</v>
+      </c>
+      <c r="H172" t="s">
+        <v>1150</v>
       </c>
       <c r="I172" t="s">
-        <v>575</v>
+        <v>29</v>
       </c>
       <c r="J172" t="s">
-        <v>1131</v>
+        <v>563</v>
+      </c>
+      <c r="L172" t="s">
+        <v>1151</v>
       </c>
       <c r="M172" t="s">
-        <v>1132</v>
+        <v>1152</v>
       </c>
       <c r="N172" t="s">
-        <v>1133</v>
-      </c>
-      <c r="O172" t="s">
-        <v>1134</v>
+        <v>1153</v>
       </c>
       <c r="Q172" t="s">
-        <v>1135</v>
+        <v>1154</v>
       </c>
       <c r="S172" t="s">
-        <v>85</v>
-      </c>
-      <c r="T172">
-        <v>349</v>
-      </c>
-      <c r="U172">
-        <v>152</v>
+        <v>1155</v>
+      </c>
+      <c r="T172" t="s">
+        <v>1156</v>
+      </c>
+      <c r="U172" t="s">
+        <v>1157</v>
       </c>
       <c r="W172" t="s">
         <v>36</v>
       </c>
       <c r="X172">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>1129</v>
+        <v>1142</v>
       </c>
       <c r="B173" t="s">
-        <v>1130</v>
+        <v>1143</v>
       </c>
       <c r="F173" t="s">
-        <v>94</v>
+        <v>1144</v>
       </c>
       <c r="G173" t="s">
-        <v>339</v>
+        <v>196</v>
       </c>
       <c r="H173" t="s">
-        <v>1136</v>
+        <v>572</v>
       </c>
       <c r="I173" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="J173" t="s">
-        <v>70</v>
+        <v>563</v>
       </c>
       <c r="M173" t="s">
-        <v>1137</v>
+        <v>1158</v>
       </c>
       <c r="N173" t="s">
-        <v>1138</v>
-      </c>
-      <c r="O173" t="s">
-        <v>1139</v>
-      </c>
-      <c r="Q173" t="s">
-        <v>1140</v>
+        <v>1159</v>
       </c>
       <c r="S173" t="s">
-        <v>1141</v>
-      </c>
-      <c r="T173">
-        <v>239</v>
-      </c>
-      <c r="U173">
-        <v>102</v>
+        <v>217</v>
       </c>
       <c r="W173" t="s">
         <v>36</v>
       </c>
       <c r="X173">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12634,31 +12637,22 @@
         <v>196</v>
       </c>
       <c r="H174" t="s">
-        <v>1145</v>
+        <v>572</v>
       </c>
       <c r="I174" t="s">
         <v>29</v>
       </c>
       <c r="J174" t="s">
-        <v>127</v>
+        <v>563</v>
       </c>
       <c r="M174" t="s">
-        <v>1146</v>
+        <v>1158</v>
       </c>
       <c r="N174" t="s">
-        <v>1147</v>
-      </c>
-      <c r="Q174" t="s">
-        <v>1148</v>
+        <v>1159</v>
       </c>
       <c r="S174" t="s">
-        <v>1149</v>
-      </c>
-      <c r="T174">
-        <v>182</v>
-      </c>
-      <c r="U174">
-        <v>323</v>
+        <v>217</v>
       </c>
       <c r="W174" t="s">
         <v>36</v>
@@ -12681,34 +12675,31 @@
         <v>196</v>
       </c>
       <c r="H175" t="s">
-        <v>1150</v>
+        <v>757</v>
       </c>
       <c r="I175" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="J175" t="s">
-        <v>563</v>
-      </c>
-      <c r="L175" t="s">
-        <v>1151</v>
+        <v>70</v>
       </c>
       <c r="M175" t="s">
-        <v>1152</v>
+        <v>1160</v>
       </c>
       <c r="N175" t="s">
-        <v>1153</v>
+        <v>1161</v>
       </c>
       <c r="Q175" t="s">
-        <v>1154</v>
+        <v>1162</v>
       </c>
       <c r="S175" t="s">
-        <v>1155</v>
+        <v>1163</v>
       </c>
       <c r="T175" t="s">
-        <v>1156</v>
-      </c>
-      <c r="U175" t="s">
-        <v>1157</v>
+        <v>1164</v>
+      </c>
+      <c r="U175">
+        <v>322</v>
       </c>
       <c r="W175" t="s">
         <v>36</v>
@@ -12731,22 +12722,31 @@
         <v>196</v>
       </c>
       <c r="H176" t="s">
-        <v>572</v>
+        <v>1165</v>
       </c>
       <c r="I176" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J176" t="s">
-        <v>563</v>
+        <v>39</v>
       </c>
       <c r="M176" t="s">
-        <v>1158</v>
+        <v>1166</v>
       </c>
       <c r="N176" t="s">
-        <v>1159</v>
+        <v>1167</v>
+      </c>
+      <c r="Q176" t="s">
+        <v>1168</v>
       </c>
       <c r="S176" t="s">
-        <v>217</v>
+        <v>1169</v>
+      </c>
+      <c r="T176">
+        <v>182</v>
+      </c>
+      <c r="U176">
+        <v>317</v>
       </c>
       <c r="W176" t="s">
         <v>36</v>
@@ -12769,19 +12769,19 @@
         <v>196</v>
       </c>
       <c r="H177" t="s">
-        <v>572</v>
+        <v>154</v>
       </c>
       <c r="I177" t="s">
         <v>29</v>
       </c>
       <c r="J177" t="s">
-        <v>563</v>
+        <v>1170</v>
       </c>
       <c r="M177" t="s">
-        <v>1158</v>
+        <v>1171</v>
       </c>
       <c r="N177" t="s">
-        <v>1159</v>
+        <v>1172</v>
       </c>
       <c r="S177" t="s">
         <v>217</v>
@@ -12807,31 +12807,22 @@
         <v>196</v>
       </c>
       <c r="H178" t="s">
-        <v>757</v>
+        <v>154</v>
       </c>
       <c r="I178" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="J178" t="s">
-        <v>70</v>
+        <v>1170</v>
       </c>
       <c r="M178" t="s">
-        <v>1160</v>
+        <v>1171</v>
       </c>
       <c r="N178" t="s">
-        <v>1161</v>
-      </c>
-      <c r="Q178" t="s">
-        <v>1162</v>
+        <v>1172</v>
       </c>
       <c r="S178" t="s">
-        <v>1163</v>
-      </c>
-      <c r="T178" t="s">
-        <v>1164</v>
-      </c>
-      <c r="U178">
-        <v>322</v>
+        <v>217</v>
       </c>
       <c r="W178" t="s">
         <v>36</v>
@@ -12854,31 +12845,28 @@
         <v>196</v>
       </c>
       <c r="H179" t="s">
-        <v>1165</v>
+        <v>103</v>
       </c>
       <c r="I179" t="s">
-        <v>38</v>
+        <v>1173</v>
       </c>
       <c r="J179" t="s">
-        <v>39</v>
+        <v>1174</v>
       </c>
       <c r="M179" t="s">
-        <v>1166</v>
+        <v>1175</v>
       </c>
       <c r="N179" t="s">
-        <v>1167</v>
-      </c>
-      <c r="Q179" t="s">
-        <v>1168</v>
+        <v>1176</v>
       </c>
       <c r="S179" t="s">
-        <v>1169</v>
-      </c>
-      <c r="T179">
-        <v>182</v>
-      </c>
-      <c r="U179">
-        <v>317</v>
+        <v>109</v>
+      </c>
+      <c r="T179" t="s">
+        <v>1177</v>
+      </c>
+      <c r="U179" t="s">
+        <v>1178</v>
       </c>
       <c r="W179" t="s">
         <v>36</v>
@@ -12901,22 +12889,28 @@
         <v>196</v>
       </c>
       <c r="H180" t="s">
-        <v>154</v>
+        <v>103</v>
       </c>
       <c r="I180" t="s">
-        <v>29</v>
+        <v>1173</v>
       </c>
       <c r="J180" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="M180" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="N180" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="S180" t="s">
-        <v>217</v>
+        <v>109</v>
+      </c>
+      <c r="T180" t="s">
+        <v>1177</v>
+      </c>
+      <c r="U180" t="s">
+        <v>1178</v>
       </c>
       <c r="W180" t="s">
         <v>36</v>
@@ -12939,22 +12933,31 @@
         <v>196</v>
       </c>
       <c r="H181" t="s">
-        <v>154</v>
+        <v>637</v>
       </c>
       <c r="I181" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="J181" t="s">
-        <v>1170</v>
+        <v>70</v>
       </c>
       <c r="M181" t="s">
-        <v>1171</v>
+        <v>1179</v>
       </c>
       <c r="N181" t="s">
-        <v>1172</v>
+        <v>1180</v>
+      </c>
+      <c r="Q181" t="s">
+        <v>1135</v>
       </c>
       <c r="S181" t="s">
-        <v>217</v>
+        <v>73</v>
+      </c>
+      <c r="T181" t="s">
+        <v>1181</v>
+      </c>
+      <c r="U181" t="s">
+        <v>1182</v>
       </c>
       <c r="W181" t="s">
         <v>36</v>
@@ -12965,43 +12968,49 @@
     </row>
     <row r="182" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>1142</v>
+        <v>1183</v>
       </c>
       <c r="B182" t="s">
-        <v>1143</v>
+        <v>1184</v>
       </c>
       <c r="F182" t="s">
-        <v>1144</v>
+        <v>135</v>
       </c>
       <c r="G182" t="s">
-        <v>196</v>
+        <v>681</v>
       </c>
       <c r="H182" t="s">
-        <v>103</v>
+        <v>637</v>
       </c>
       <c r="I182" t="s">
-        <v>1173</v>
+        <v>77</v>
       </c>
       <c r="J182" t="s">
-        <v>1174</v>
+        <v>78</v>
       </c>
       <c r="M182" t="s">
-        <v>1175</v>
+        <v>1185</v>
       </c>
       <c r="N182" t="s">
-        <v>1176</v>
+        <v>1186</v>
+      </c>
+      <c r="O182" t="s">
+        <v>1187</v>
+      </c>
+      <c r="Q182" t="s">
+        <v>1188</v>
       </c>
       <c r="S182" t="s">
-        <v>109</v>
+        <v>847</v>
       </c>
       <c r="T182" t="s">
-        <v>1177</v>
+        <v>1189</v>
       </c>
       <c r="U182" t="s">
-        <v>1178</v>
+        <v>1190</v>
       </c>
       <c r="W182" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="X182">
         <v>2</v>
@@ -13009,43 +13018,37 @@
     </row>
     <row r="183" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>1142</v>
+        <v>1183</v>
       </c>
       <c r="B183" t="s">
-        <v>1143</v>
+        <v>1184</v>
       </c>
       <c r="F183" t="s">
-        <v>1144</v>
+        <v>135</v>
       </c>
       <c r="G183" t="s">
-        <v>196</v>
+        <v>681</v>
       </c>
       <c r="H183" t="s">
-        <v>103</v>
+        <v>637</v>
       </c>
       <c r="I183" t="s">
-        <v>1173</v>
+        <v>1191</v>
       </c>
       <c r="J183" t="s">
-        <v>1174</v>
+        <v>1192</v>
       </c>
       <c r="M183" t="s">
-        <v>1175</v>
+        <v>1193</v>
       </c>
       <c r="N183" t="s">
-        <v>1176</v>
+        <v>1194</v>
       </c>
       <c r="S183" t="s">
-        <v>109</v>
-      </c>
-      <c r="T183" t="s">
-        <v>1177</v>
-      </c>
-      <c r="U183" t="s">
-        <v>1178</v>
+        <v>81</v>
       </c>
       <c r="W183" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="X183">
         <v>2</v>
@@ -13053,46 +13056,46 @@
     </row>
     <row r="184" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>1142</v>
+        <v>1183</v>
       </c>
       <c r="B184" t="s">
-        <v>1143</v>
+        <v>1184</v>
       </c>
       <c r="F184" t="s">
-        <v>1144</v>
+        <v>135</v>
       </c>
       <c r="G184" t="s">
-        <v>196</v>
+        <v>681</v>
       </c>
       <c r="H184" t="s">
-        <v>637</v>
+        <v>1195</v>
       </c>
       <c r="I184" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="J184" t="s">
-        <v>70</v>
+        <v>127</v>
       </c>
       <c r="M184" t="s">
-        <v>1179</v>
+        <v>1196</v>
       </c>
       <c r="N184" t="s">
-        <v>1180</v>
+        <v>1197</v>
       </c>
       <c r="Q184" t="s">
-        <v>1135</v>
+        <v>1198</v>
       </c>
       <c r="S184" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="T184" t="s">
-        <v>1181</v>
+        <v>310</v>
       </c>
       <c r="U184" t="s">
-        <v>1182</v>
+        <v>1199</v>
       </c>
       <c r="W184" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="X184">
         <v>2</v>
@@ -13112,34 +13115,31 @@
         <v>681</v>
       </c>
       <c r="H185" t="s">
-        <v>637</v>
+        <v>1200</v>
       </c>
       <c r="I185" t="s">
-        <v>77</v>
+        <v>1201</v>
       </c>
       <c r="J185" t="s">
-        <v>78</v>
+        <v>1202</v>
       </c>
       <c r="M185" t="s">
-        <v>1185</v>
+        <v>1203</v>
       </c>
       <c r="N185" t="s">
-        <v>1186</v>
-      </c>
-      <c r="O185" t="s">
-        <v>1187</v>
+        <v>1204</v>
       </c>
       <c r="Q185" t="s">
-        <v>1188</v>
+        <v>1205</v>
       </c>
       <c r="S185" t="s">
-        <v>847</v>
+        <v>159</v>
       </c>
       <c r="T185" t="s">
-        <v>1189</v>
+        <v>464</v>
       </c>
       <c r="U185" t="s">
-        <v>1190</v>
+        <v>117</v>
       </c>
       <c r="W185" t="s">
         <v>55</v>
@@ -13162,19 +13162,19 @@
         <v>681</v>
       </c>
       <c r="H186" t="s">
-        <v>637</v>
+        <v>1206</v>
       </c>
       <c r="I186" t="s">
-        <v>1191</v>
+        <v>1201</v>
       </c>
       <c r="J186" t="s">
-        <v>1192</v>
+        <v>1207</v>
       </c>
       <c r="M186" t="s">
-        <v>1193</v>
+        <v>1208</v>
       </c>
       <c r="N186" t="s">
-        <v>1194</v>
+        <v>1209</v>
       </c>
       <c r="S186" t="s">
         <v>81</v>
@@ -13200,31 +13200,31 @@
         <v>681</v>
       </c>
       <c r="H187" t="s">
-        <v>1195</v>
+        <v>76</v>
       </c>
       <c r="I187" t="s">
-        <v>29</v>
+        <v>460</v>
       </c>
       <c r="J187" t="s">
-        <v>127</v>
+        <v>461</v>
       </c>
       <c r="M187" t="s">
-        <v>1196</v>
+        <v>1210</v>
       </c>
       <c r="N187" t="s">
-        <v>1197</v>
+        <v>1211</v>
       </c>
       <c r="Q187" t="s">
-        <v>1198</v>
+        <v>1212</v>
       </c>
       <c r="S187" t="s">
-        <v>81</v>
+        <v>847</v>
       </c>
       <c r="T187" t="s">
-        <v>310</v>
+        <v>1213</v>
       </c>
       <c r="U187" t="s">
-        <v>1199</v>
+        <v>1214</v>
       </c>
       <c r="W187" t="s">
         <v>55</v>
@@ -13247,31 +13247,31 @@
         <v>681</v>
       </c>
       <c r="H188" t="s">
-        <v>1200</v>
+        <v>76</v>
       </c>
       <c r="I188" t="s">
-        <v>1201</v>
+        <v>77</v>
       </c>
       <c r="J188" t="s">
-        <v>1202</v>
+        <v>78</v>
       </c>
       <c r="M188" t="s">
-        <v>1203</v>
+        <v>1215</v>
       </c>
       <c r="N188" t="s">
-        <v>1204</v>
+        <v>1216</v>
       </c>
       <c r="Q188" t="s">
-        <v>1205</v>
+        <v>1217</v>
       </c>
       <c r="S188" t="s">
         <v>159</v>
       </c>
       <c r="T188" t="s">
-        <v>464</v>
+        <v>1218</v>
       </c>
       <c r="U188" t="s">
-        <v>117</v>
+        <v>1219</v>
       </c>
       <c r="W188" t="s">
         <v>55</v>
@@ -13282,134 +13282,134 @@
     </row>
     <row r="189" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>1183</v>
+        <v>1220</v>
       </c>
       <c r="B189" t="s">
-        <v>1184</v>
+        <v>1221</v>
       </c>
       <c r="F189" t="s">
-        <v>135</v>
+        <v>1222</v>
       </c>
       <c r="G189" t="s">
-        <v>681</v>
+        <v>1223</v>
       </c>
       <c r="H189" t="s">
-        <v>1206</v>
+        <v>951</v>
       </c>
       <c r="I189" t="s">
-        <v>1201</v>
+        <v>138</v>
       </c>
       <c r="J189" t="s">
-        <v>1207</v>
+        <v>139</v>
       </c>
       <c r="M189" t="s">
-        <v>1208</v>
+        <v>741</v>
       </c>
       <c r="N189" t="s">
-        <v>1209</v>
+        <v>1224</v>
       </c>
       <c r="S189" t="s">
         <v>81</v>
       </c>
+      <c r="T189" t="s">
+        <v>760</v>
+      </c>
+      <c r="U189" t="s">
+        <v>1225</v>
+      </c>
       <c r="W189" t="s">
         <v>55</v>
       </c>
       <c r="X189">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>1183</v>
+        <v>1220</v>
       </c>
       <c r="B190" t="s">
-        <v>1184</v>
+        <v>1221</v>
       </c>
       <c r="F190" t="s">
-        <v>135</v>
+        <v>1222</v>
       </c>
       <c r="G190" t="s">
-        <v>681</v>
+        <v>1223</v>
       </c>
       <c r="H190" t="s">
-        <v>76</v>
+        <v>1226</v>
       </c>
       <c r="I190" t="s">
-        <v>460</v>
+        <v>1227</v>
       </c>
       <c r="J190" t="s">
-        <v>461</v>
+        <v>1228</v>
       </c>
       <c r="M190" t="s">
-        <v>1210</v>
+        <v>1229</v>
       </c>
       <c r="N190" t="s">
-        <v>1211</v>
-      </c>
-      <c r="Q190" t="s">
-        <v>1212</v>
+        <v>1230</v>
       </c>
       <c r="S190" t="s">
-        <v>847</v>
+        <v>401</v>
       </c>
       <c r="T190" t="s">
-        <v>1213</v>
+        <v>585</v>
       </c>
       <c r="U190" t="s">
-        <v>1214</v>
+        <v>1231</v>
       </c>
       <c r="W190" t="s">
         <v>55</v>
       </c>
       <c r="X190">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>1183</v>
+        <v>1220</v>
       </c>
       <c r="B191" t="s">
-        <v>1184</v>
+        <v>1221</v>
       </c>
       <c r="F191" t="s">
-        <v>135</v>
+        <v>1222</v>
       </c>
       <c r="G191" t="s">
-        <v>681</v>
+        <v>1223</v>
       </c>
       <c r="H191" t="s">
-        <v>76</v>
+        <v>1232</v>
       </c>
       <c r="I191" t="s">
-        <v>77</v>
+        <v>837</v>
       </c>
       <c r="J191" t="s">
-        <v>78</v>
+        <v>838</v>
       </c>
       <c r="M191" t="s">
-        <v>1215</v>
+        <v>1233</v>
       </c>
       <c r="N191" t="s">
-        <v>1216</v>
-      </c>
-      <c r="Q191" t="s">
-        <v>1217</v>
+        <v>1234</v>
       </c>
       <c r="S191" t="s">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="T191" t="s">
-        <v>1218</v>
+        <v>132</v>
       </c>
       <c r="U191" t="s">
-        <v>1219</v>
+        <v>1235</v>
       </c>
       <c r="W191" t="s">
         <v>55</v>
       </c>
       <c r="X191">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13426,28 +13426,28 @@
         <v>1223</v>
       </c>
       <c r="H192" t="s">
-        <v>951</v>
+        <v>1236</v>
       </c>
       <c r="I192" t="s">
-        <v>138</v>
+        <v>275</v>
       </c>
       <c r="J192" t="s">
-        <v>139</v>
+        <v>276</v>
       </c>
       <c r="M192" t="s">
-        <v>741</v>
+        <v>865</v>
       </c>
       <c r="N192" t="s">
-        <v>1224</v>
+        <v>1237</v>
       </c>
       <c r="S192" t="s">
         <v>81</v>
       </c>
       <c r="T192" t="s">
-        <v>760</v>
+        <v>161</v>
       </c>
       <c r="U192" t="s">
-        <v>1225</v>
+        <v>1044</v>
       </c>
       <c r="W192" t="s">
         <v>55</v>
@@ -13470,28 +13470,28 @@
         <v>1223</v>
       </c>
       <c r="H193" t="s">
-        <v>1226</v>
+        <v>1238</v>
       </c>
       <c r="I193" t="s">
-        <v>1227</v>
+        <v>77</v>
       </c>
       <c r="J193" t="s">
-        <v>1228</v>
+        <v>78</v>
       </c>
       <c r="M193" t="s">
-        <v>1229</v>
+        <v>1239</v>
       </c>
       <c r="N193" t="s">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="S193" t="s">
-        <v>401</v>
+        <v>81</v>
       </c>
       <c r="T193" t="s">
-        <v>585</v>
+        <v>178</v>
       </c>
       <c r="U193" t="s">
-        <v>1231</v>
+        <v>1241</v>
       </c>
       <c r="W193" t="s">
         <v>55</v>
@@ -13514,28 +13514,31 @@
         <v>1223</v>
       </c>
       <c r="H194" t="s">
-        <v>1232</v>
+        <v>1242</v>
       </c>
       <c r="I194" t="s">
-        <v>837</v>
+        <v>1243</v>
       </c>
       <c r="J194" t="s">
-        <v>838</v>
+        <v>1244</v>
       </c>
       <c r="M194" t="s">
-        <v>1233</v>
+        <v>1245</v>
       </c>
       <c r="N194" t="s">
-        <v>1234</v>
+        <v>1246</v>
+      </c>
+      <c r="O194" t="s">
+        <v>1247</v>
       </c>
       <c r="S194" t="s">
-        <v>81</v>
+        <v>1248</v>
       </c>
       <c r="T194" t="s">
-        <v>132</v>
+        <v>760</v>
       </c>
       <c r="U194" t="s">
-        <v>1235</v>
+        <v>1249</v>
       </c>
       <c r="W194" t="s">
         <v>55</v>
@@ -13558,28 +13561,28 @@
         <v>1223</v>
       </c>
       <c r="H195" t="s">
-        <v>1236</v>
+        <v>1250</v>
       </c>
       <c r="I195" t="s">
-        <v>275</v>
+        <v>77</v>
       </c>
       <c r="J195" t="s">
-        <v>276</v>
+        <v>78</v>
       </c>
       <c r="M195" t="s">
-        <v>865</v>
+        <v>1251</v>
       </c>
       <c r="N195" t="s">
-        <v>1237</v>
+        <v>1252</v>
       </c>
       <c r="S195" t="s">
         <v>81</v>
       </c>
       <c r="T195" t="s">
-        <v>161</v>
+        <v>1054</v>
       </c>
       <c r="U195" t="s">
-        <v>1044</v>
+        <v>1253</v>
       </c>
       <c r="W195" t="s">
         <v>55</v>
@@ -13596,34 +13599,28 @@
         <v>1221</v>
       </c>
       <c r="F196" t="s">
-        <v>1222</v>
+        <v>1254</v>
       </c>
       <c r="G196" t="s">
         <v>1223</v>
       </c>
       <c r="H196" t="s">
-        <v>1238</v>
+        <v>154</v>
       </c>
       <c r="I196" t="s">
-        <v>77</v>
+        <v>837</v>
       </c>
       <c r="J196" t="s">
-        <v>78</v>
+        <v>1046</v>
       </c>
       <c r="M196" t="s">
-        <v>1239</v>
+        <v>1255</v>
       </c>
       <c r="N196" t="s">
-        <v>1240</v>
+        <v>1256</v>
       </c>
       <c r="S196" t="s">
         <v>81</v>
-      </c>
-      <c r="T196" t="s">
-        <v>178</v>
-      </c>
-      <c r="U196" t="s">
-        <v>1241</v>
       </c>
       <c r="W196" t="s">
         <v>55</v>
@@ -13646,31 +13643,28 @@
         <v>1223</v>
       </c>
       <c r="H197" t="s">
-        <v>1242</v>
+        <v>1257</v>
       </c>
       <c r="I197" t="s">
-        <v>1243</v>
+        <v>38</v>
       </c>
       <c r="J197" t="s">
-        <v>1244</v>
+        <v>39</v>
       </c>
       <c r="M197" t="s">
-        <v>1245</v>
+        <v>1258</v>
       </c>
       <c r="N197" t="s">
-        <v>1246</v>
-      </c>
-      <c r="O197" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="S197" t="s">
-        <v>1248</v>
+        <v>81</v>
       </c>
       <c r="T197" t="s">
-        <v>760</v>
+        <v>1260</v>
       </c>
       <c r="U197" t="s">
-        <v>1249</v>
+        <v>1261</v>
       </c>
       <c r="W197" t="s">
         <v>55</v>
@@ -13687,34 +13681,28 @@
         <v>1221</v>
       </c>
       <c r="F198" t="s">
-        <v>1222</v>
+        <v>1254</v>
       </c>
       <c r="G198" t="s">
         <v>1223</v>
       </c>
       <c r="H198" t="s">
-        <v>1250</v>
+        <v>614</v>
       </c>
       <c r="I198" t="s">
-        <v>77</v>
+        <v>810</v>
       </c>
       <c r="J198" t="s">
-        <v>78</v>
+        <v>811</v>
       </c>
       <c r="M198" t="s">
-        <v>1251</v>
+        <v>1262</v>
       </c>
       <c r="N198" t="s">
-        <v>1252</v>
+        <v>1263</v>
       </c>
       <c r="S198" t="s">
         <v>81</v>
-      </c>
-      <c r="T198" t="s">
-        <v>1054</v>
-      </c>
-      <c r="U198" t="s">
-        <v>1253</v>
       </c>
       <c r="W198" t="s">
         <v>55</v>
@@ -13731,28 +13719,34 @@
         <v>1221</v>
       </c>
       <c r="F199" t="s">
-        <v>1254</v>
+        <v>1222</v>
       </c>
       <c r="G199" t="s">
         <v>1223</v>
       </c>
       <c r="H199" t="s">
-        <v>154</v>
+        <v>457</v>
       </c>
       <c r="I199" t="s">
-        <v>837</v>
+        <v>490</v>
       </c>
       <c r="J199" t="s">
-        <v>1046</v>
+        <v>491</v>
       </c>
       <c r="M199" t="s">
-        <v>1255</v>
+        <v>1264</v>
       </c>
       <c r="N199" t="s">
-        <v>1256</v>
+        <v>1265</v>
       </c>
       <c r="S199" t="s">
         <v>81</v>
+      </c>
+      <c r="T199" t="s">
+        <v>1266</v>
+      </c>
+      <c r="U199" t="s">
+        <v>1267</v>
       </c>
       <c r="W199" t="s">
         <v>55</v>
@@ -13775,28 +13769,28 @@
         <v>1223</v>
       </c>
       <c r="H200" t="s">
-        <v>1257</v>
+        <v>1268</v>
       </c>
       <c r="I200" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J200" t="s">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="M200" t="s">
-        <v>1258</v>
+        <v>1269</v>
       </c>
       <c r="N200" t="s">
-        <v>1259</v>
+        <v>1270</v>
       </c>
       <c r="S200" t="s">
         <v>81</v>
       </c>
       <c r="T200" t="s">
-        <v>1260</v>
+        <v>1271</v>
       </c>
       <c r="U200" t="s">
-        <v>1261</v>
+        <v>1272</v>
       </c>
       <c r="W200" t="s">
         <v>55</v>
@@ -13807,35 +13801,44 @@
     </row>
     <row r="201" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>1220</v>
+        <v>1273</v>
       </c>
       <c r="B201" t="s">
-        <v>1221</v>
+        <v>1274</v>
       </c>
       <c r="F201" t="s">
-        <v>1254</v>
+        <v>1275</v>
       </c>
       <c r="G201" t="s">
-        <v>1223</v>
+        <v>1276</v>
       </c>
       <c r="H201" t="s">
-        <v>614</v>
+        <v>1277</v>
       </c>
       <c r="I201" t="s">
-        <v>810</v>
+        <v>1278</v>
       </c>
       <c r="J201" t="s">
-        <v>811</v>
+        <v>1279</v>
       </c>
       <c r="M201" t="s">
-        <v>1262</v>
+        <v>1280</v>
       </c>
       <c r="N201" t="s">
-        <v>1263</v>
+        <v>1281</v>
+      </c>
+      <c r="Q201" t="s">
+        <v>1282</v>
       </c>
       <c r="S201" t="s">
         <v>81</v>
       </c>
+      <c r="T201">
+        <v>340</v>
+      </c>
+      <c r="U201">
+        <v>520</v>
+      </c>
       <c r="W201" t="s">
         <v>55</v>
       </c>
@@ -13845,40 +13848,43 @@
     </row>
     <row r="202" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>1220</v>
+        <v>1273</v>
       </c>
       <c r="B202" t="s">
-        <v>1221</v>
+        <v>1274</v>
       </c>
       <c r="F202" t="s">
-        <v>1222</v>
+        <v>1275</v>
       </c>
       <c r="G202" t="s">
-        <v>1223</v>
+        <v>1276</v>
       </c>
       <c r="H202" t="s">
-        <v>457</v>
+        <v>1283</v>
       </c>
       <c r="I202" t="s">
-        <v>490</v>
+        <v>1284</v>
       </c>
       <c r="J202" t="s">
-        <v>491</v>
+        <v>1285</v>
       </c>
       <c r="M202" t="s">
-        <v>1264</v>
+        <v>1286</v>
       </c>
       <c r="N202" t="s">
-        <v>1265</v>
+        <v>1287</v>
+      </c>
+      <c r="Q202" t="s">
+        <v>1288</v>
       </c>
       <c r="S202" t="s">
-        <v>81</v>
-      </c>
-      <c r="T202" t="s">
-        <v>1266</v>
-      </c>
-      <c r="U202" t="s">
-        <v>1267</v>
+        <v>159</v>
+      </c>
+      <c r="T202">
+        <v>22.5</v>
+      </c>
+      <c r="U202">
+        <v>16.600000000000001</v>
       </c>
       <c r="W202" t="s">
         <v>55</v>
@@ -13889,40 +13895,43 @@
     </row>
     <row r="203" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>1220</v>
+        <v>1273</v>
       </c>
       <c r="B203" t="s">
-        <v>1221</v>
+        <v>1274</v>
       </c>
       <c r="F203" t="s">
-        <v>1222</v>
+        <v>1275</v>
       </c>
       <c r="G203" t="s">
-        <v>1223</v>
+        <v>1276</v>
       </c>
       <c r="H203" t="s">
-        <v>1268</v>
+        <v>1289</v>
       </c>
       <c r="I203" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="J203" t="s">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="M203" t="s">
-        <v>1269</v>
+        <v>1290</v>
       </c>
       <c r="N203" t="s">
-        <v>1270</v>
+        <v>1291</v>
+      </c>
+      <c r="Q203" t="s">
+        <v>1292</v>
       </c>
       <c r="S203" t="s">
-        <v>81</v>
-      </c>
-      <c r="T203" t="s">
-        <v>1271</v>
-      </c>
-      <c r="U203" t="s">
-        <v>1272</v>
+        <v>159</v>
+      </c>
+      <c r="T203">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="U203">
+        <v>18.899999999999999</v>
       </c>
       <c r="W203" t="s">
         <v>55</v>
@@ -13945,31 +13954,31 @@
         <v>1276</v>
       </c>
       <c r="H204" t="s">
-        <v>1277</v>
+        <v>754</v>
       </c>
       <c r="I204" t="s">
-        <v>1278</v>
+        <v>69</v>
       </c>
       <c r="J204" t="s">
-        <v>1279</v>
+        <v>70</v>
       </c>
       <c r="M204" t="s">
-        <v>1280</v>
+        <v>1293</v>
       </c>
       <c r="N204" t="s">
-        <v>1281</v>
+        <v>1294</v>
       </c>
       <c r="Q204" t="s">
-        <v>1282</v>
+        <v>1295</v>
       </c>
       <c r="S204" t="s">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="T204">
-        <v>340</v>
+        <v>25.5</v>
       </c>
       <c r="U204">
-        <v>520</v>
+        <v>19</v>
       </c>
       <c r="W204" t="s">
         <v>55</v>
@@ -13992,31 +14001,28 @@
         <v>1276</v>
       </c>
       <c r="H205" t="s">
-        <v>1283</v>
+        <v>1296</v>
       </c>
       <c r="I205" t="s">
-        <v>1284</v>
+        <v>69</v>
       </c>
       <c r="J205" t="s">
-        <v>1285</v>
+        <v>70</v>
       </c>
       <c r="M205" t="s">
-        <v>1286</v>
+        <v>1297</v>
       </c>
       <c r="N205" t="s">
-        <v>1287</v>
-      </c>
-      <c r="Q205" t="s">
-        <v>1288</v>
+        <v>1298</v>
       </c>
       <c r="S205" t="s">
-        <v>159</v>
-      </c>
-      <c r="T205">
-        <v>22.5</v>
-      </c>
-      <c r="U205">
-        <v>16.600000000000001</v>
+        <v>81</v>
+      </c>
+      <c r="T205" t="s">
+        <v>1299</v>
+      </c>
+      <c r="U205" t="s">
+        <v>1300</v>
       </c>
       <c r="W205" t="s">
         <v>55</v>
@@ -14039,31 +14045,31 @@
         <v>1276</v>
       </c>
       <c r="H206" t="s">
-        <v>1289</v>
+        <v>1301</v>
       </c>
       <c r="I206" t="s">
-        <v>69</v>
+        <v>490</v>
       </c>
       <c r="J206" t="s">
-        <v>70</v>
+        <v>491</v>
       </c>
       <c r="M206" t="s">
-        <v>1290</v>
+        <v>483</v>
       </c>
       <c r="N206" t="s">
-        <v>1291</v>
+        <v>1302</v>
       </c>
       <c r="Q206" t="s">
-        <v>1292</v>
+        <v>1303</v>
       </c>
       <c r="S206" t="s">
-        <v>159</v>
+        <v>1304</v>
       </c>
       <c r="T206">
-        <v>33.299999999999997</v>
+        <v>90.2</v>
       </c>
       <c r="U206">
-        <v>18.899999999999999</v>
+        <v>34.1</v>
       </c>
       <c r="W206" t="s">
         <v>55</v>
@@ -14086,31 +14092,31 @@
         <v>1276</v>
       </c>
       <c r="H207" t="s">
-        <v>754</v>
+        <v>1301</v>
       </c>
       <c r="I207" t="s">
-        <v>69</v>
+        <v>460</v>
       </c>
       <c r="J207" t="s">
-        <v>70</v>
+        <v>461</v>
       </c>
       <c r="M207" t="s">
-        <v>1293</v>
+        <v>1305</v>
       </c>
       <c r="N207" t="s">
-        <v>1294</v>
+        <v>1306</v>
       </c>
       <c r="Q207" t="s">
-        <v>1295</v>
+        <v>1307</v>
       </c>
       <c r="S207" t="s">
         <v>159</v>
       </c>
       <c r="T207">
-        <v>25.5</v>
+        <v>122.1</v>
       </c>
       <c r="U207">
-        <v>19</v>
+        <v>157.80000000000001</v>
       </c>
       <c r="W207" t="s">
         <v>55</v>
@@ -14133,28 +14139,31 @@
         <v>1276</v>
       </c>
       <c r="H208" t="s">
-        <v>1296</v>
+        <v>588</v>
       </c>
       <c r="I208" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="J208" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="M208" t="s">
-        <v>1297</v>
+        <v>1308</v>
       </c>
       <c r="N208" t="s">
-        <v>1298</v>
+        <v>1309</v>
+      </c>
+      <c r="Q208" t="s">
+        <v>1310</v>
       </c>
       <c r="S208" t="s">
-        <v>81</v>
-      </c>
-      <c r="T208" t="s">
-        <v>1299</v>
-      </c>
-      <c r="U208" t="s">
-        <v>1300</v>
+        <v>159</v>
+      </c>
+      <c r="T208">
+        <v>66</v>
+      </c>
+      <c r="U208">
+        <v>62</v>
       </c>
       <c r="W208" t="s">
         <v>55</v>
@@ -14177,31 +14186,31 @@
         <v>1276</v>
       </c>
       <c r="H209" t="s">
-        <v>1301</v>
+        <v>1311</v>
       </c>
       <c r="I209" t="s">
-        <v>490</v>
+        <v>581</v>
       </c>
       <c r="J209" t="s">
-        <v>491</v>
+        <v>582</v>
       </c>
       <c r="M209" t="s">
-        <v>483</v>
+        <v>1312</v>
       </c>
       <c r="N209" t="s">
-        <v>1302</v>
+        <v>1313</v>
       </c>
       <c r="Q209" t="s">
-        <v>1303</v>
+        <v>1314</v>
       </c>
       <c r="S209" t="s">
-        <v>1304</v>
+        <v>159</v>
       </c>
       <c r="T209">
-        <v>90.2</v>
+        <v>33.1</v>
       </c>
       <c r="U209">
-        <v>34.1</v>
+        <v>53.8</v>
       </c>
       <c r="W209" t="s">
         <v>55</v>
@@ -14224,31 +14233,22 @@
         <v>1276</v>
       </c>
       <c r="H210" t="s">
-        <v>1301</v>
+        <v>1315</v>
       </c>
       <c r="I210" t="s">
-        <v>460</v>
+        <v>350</v>
       </c>
       <c r="J210" t="s">
-        <v>461</v>
+        <v>351</v>
       </c>
       <c r="M210" t="s">
-        <v>1305</v>
+        <v>1316</v>
       </c>
       <c r="N210" t="s">
-        <v>1306</v>
-      </c>
-      <c r="Q210" t="s">
-        <v>1307</v>
+        <v>1317</v>
       </c>
       <c r="S210" t="s">
-        <v>159</v>
-      </c>
-      <c r="T210">
-        <v>122.1</v>
-      </c>
-      <c r="U210">
-        <v>157.80000000000001</v>
+        <v>81</v>
       </c>
       <c r="W210" t="s">
         <v>55</v>
@@ -14271,31 +14271,31 @@
         <v>1276</v>
       </c>
       <c r="H211" t="s">
-        <v>588</v>
+        <v>1114</v>
       </c>
       <c r="I211" t="s">
-        <v>38</v>
+        <v>460</v>
       </c>
       <c r="J211" t="s">
-        <v>39</v>
+        <v>461</v>
       </c>
       <c r="M211" t="s">
-        <v>1308</v>
+        <v>1318</v>
       </c>
       <c r="N211" t="s">
-        <v>1309</v>
+        <v>1319</v>
       </c>
       <c r="Q211" t="s">
-        <v>1310</v>
+        <v>1320</v>
       </c>
       <c r="S211" t="s">
         <v>159</v>
       </c>
       <c r="T211">
-        <v>66</v>
+        <v>32.5</v>
       </c>
       <c r="U211">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="W211" t="s">
         <v>55</v>
@@ -14306,172 +14306,181 @@
     </row>
     <row r="212" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>1273</v>
+        <v>873</v>
       </c>
       <c r="B212" t="s">
-        <v>1274</v>
+        <v>1321</v>
       </c>
       <c r="F212" t="s">
-        <v>1275</v>
+        <v>347</v>
       </c>
       <c r="G212" t="s">
-        <v>1276</v>
+        <v>1322</v>
       </c>
       <c r="H212" t="s">
-        <v>1311</v>
+        <v>1323</v>
       </c>
       <c r="I212" t="s">
-        <v>581</v>
+        <v>77</v>
       </c>
       <c r="J212" t="s">
-        <v>582</v>
+        <v>78</v>
       </c>
       <c r="M212" t="s">
-        <v>1312</v>
+        <v>932</v>
       </c>
       <c r="N212" t="s">
-        <v>1313</v>
-      </c>
-      <c r="Q212" t="s">
-        <v>1314</v>
+        <v>1324</v>
       </c>
       <c r="S212" t="s">
-        <v>159</v>
-      </c>
-      <c r="T212">
-        <v>33.1</v>
-      </c>
-      <c r="U212">
-        <v>53.8</v>
+        <v>33</v>
+      </c>
+      <c r="T212" t="s">
+        <v>1325</v>
+      </c>
+      <c r="U212" t="s">
+        <v>1326</v>
       </c>
       <c r="W212" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="X212">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="213" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>1273</v>
+        <v>873</v>
       </c>
       <c r="B213" t="s">
-        <v>1274</v>
+        <v>1321</v>
       </c>
       <c r="F213" t="s">
-        <v>1275</v>
+        <v>347</v>
       </c>
       <c r="G213" t="s">
-        <v>1276</v>
+        <v>1322</v>
       </c>
       <c r="H213" t="s">
-        <v>1315</v>
+        <v>1327</v>
       </c>
       <c r="I213" t="s">
-        <v>350</v>
+        <v>29</v>
       </c>
       <c r="J213" t="s">
-        <v>351</v>
+        <v>127</v>
       </c>
       <c r="M213" t="s">
-        <v>1316</v>
+        <v>1328</v>
       </c>
       <c r="N213" t="s">
-        <v>1317</v>
+        <v>1329</v>
       </c>
       <c r="S213" t="s">
-        <v>81</v>
+        <v>33</v>
+      </c>
+      <c r="T213" t="s">
+        <v>753</v>
+      </c>
+      <c r="U213" t="s">
+        <v>1330</v>
       </c>
       <c r="W213" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="X213">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="214" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>1273</v>
+        <v>1331</v>
       </c>
       <c r="B214" t="s">
-        <v>1274</v>
+        <v>1332</v>
       </c>
       <c r="F214" t="s">
-        <v>1275</v>
+        <v>1333</v>
       </c>
       <c r="G214" t="s">
-        <v>1276</v>
-      </c>
-      <c r="H214" t="s">
-        <v>1114</v>
+        <v>1093</v>
+      </c>
+      <c r="H214">
+        <v>1480</v>
       </c>
       <c r="I214" t="s">
-        <v>460</v>
+        <v>64</v>
       </c>
       <c r="J214" t="s">
-        <v>461</v>
+        <v>65</v>
       </c>
       <c r="M214" t="s">
-        <v>1318</v>
+        <v>1334</v>
       </c>
       <c r="N214" t="s">
-        <v>1319</v>
+        <v>1335</v>
       </c>
       <c r="Q214" t="s">
-        <v>1320</v>
+        <v>1336</v>
       </c>
       <c r="S214" t="s">
         <v>159</v>
       </c>
       <c r="T214">
-        <v>32.5</v>
+        <v>120</v>
       </c>
       <c r="U214">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="W214" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="X214">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="215" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>873</v>
+        <v>1331</v>
       </c>
       <c r="B215" t="s">
-        <v>1321</v>
+        <v>1332</v>
       </c>
       <c r="F215" t="s">
-        <v>347</v>
+        <v>1333</v>
       </c>
       <c r="G215" t="s">
-        <v>1322</v>
+        <v>1093</v>
       </c>
       <c r="H215" t="s">
-        <v>1323</v>
+        <v>1337</v>
       </c>
       <c r="I215" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="J215" t="s">
-        <v>78</v>
+        <v>1338</v>
+      </c>
+      <c r="L215" t="s">
+        <v>1339</v>
       </c>
       <c r="M215" t="s">
-        <v>932</v>
+        <v>1340</v>
       </c>
       <c r="N215" t="s">
-        <v>1324</v>
+        <v>1341</v>
+      </c>
+      <c r="Q215" t="s">
+        <v>1342</v>
       </c>
       <c r="S215" t="s">
-        <v>33</v>
-      </c>
-      <c r="T215" t="s">
-        <v>1325</v>
-      </c>
-      <c r="U215" t="s">
-        <v>1326</v>
+        <v>1343</v>
+      </c>
+      <c r="T215">
+        <v>141</v>
+      </c>
+      <c r="U215">
+        <v>100</v>
       </c>
       <c r="W215" t="s">
         <v>36</v>
@@ -14482,40 +14491,46 @@
     </row>
     <row r="216" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>873</v>
+        <v>1079</v>
       </c>
       <c r="B216" t="s">
-        <v>1321</v>
+        <v>1332</v>
       </c>
       <c r="F216" t="s">
-        <v>347</v>
+        <v>266</v>
       </c>
       <c r="G216" t="s">
-        <v>1322</v>
-      </c>
-      <c r="H216" t="s">
-        <v>1327</v>
+        <v>1344</v>
+      </c>
+      <c r="H216">
+        <v>1444</v>
       </c>
       <c r="I216" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="J216" t="s">
-        <v>127</v>
+        <v>1345</v>
+      </c>
+      <c r="L216" t="s">
+        <v>1346</v>
       </c>
       <c r="M216" t="s">
-        <v>1328</v>
+        <v>1347</v>
       </c>
       <c r="N216" t="s">
-        <v>1329</v>
+        <v>1348</v>
+      </c>
+      <c r="Q216" t="s">
+        <v>735</v>
       </c>
       <c r="S216" t="s">
-        <v>33</v>
-      </c>
-      <c r="T216" t="s">
-        <v>753</v>
-      </c>
-      <c r="U216" t="s">
-        <v>1330</v>
+        <v>1349</v>
+      </c>
+      <c r="T216">
+        <v>230</v>
+      </c>
+      <c r="U216">
+        <v>180</v>
       </c>
       <c r="W216" t="s">
         <v>36</v>
@@ -14526,19 +14541,19 @@
     </row>
     <row r="217" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>1331</v>
+        <v>1079</v>
       </c>
       <c r="B217" t="s">
         <v>1332</v>
       </c>
       <c r="F217" t="s">
-        <v>1333</v>
+        <v>266</v>
       </c>
       <c r="G217" t="s">
-        <v>1093</v>
+        <v>1344</v>
       </c>
       <c r="H217">
-        <v>1480</v>
+        <v>1446</v>
       </c>
       <c r="I217" t="s">
         <v>64</v>
@@ -14547,22 +14562,22 @@
         <v>65</v>
       </c>
       <c r="M217" t="s">
-        <v>1334</v>
+        <v>1350</v>
       </c>
       <c r="N217" t="s">
-        <v>1335</v>
+        <v>1351</v>
       </c>
       <c r="Q217" t="s">
-        <v>1336</v>
+        <v>1352</v>
       </c>
       <c r="S217" t="s">
-        <v>159</v>
+        <v>1353</v>
       </c>
       <c r="T217">
-        <v>120</v>
+        <v>292</v>
       </c>
       <c r="U217">
-        <v>170</v>
+        <v>415</v>
       </c>
       <c r="W217" t="s">
         <v>36</v>
@@ -14573,46 +14588,46 @@
     </row>
     <row r="218" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>1331</v>
+        <v>1354</v>
       </c>
       <c r="B218" t="s">
         <v>1332</v>
       </c>
       <c r="F218" t="s">
-        <v>1333</v>
+        <v>1355</v>
       </c>
       <c r="G218" t="s">
-        <v>1093</v>
-      </c>
-      <c r="H218" t="s">
-        <v>1337</v>
+        <v>1356</v>
+      </c>
+      <c r="H218">
+        <v>1474</v>
       </c>
       <c r="I218" t="s">
         <v>64</v>
       </c>
       <c r="J218" t="s">
-        <v>1338</v>
+        <v>1357</v>
       </c>
       <c r="L218" t="s">
-        <v>1339</v>
+        <v>1358</v>
       </c>
       <c r="M218" t="s">
-        <v>1340</v>
+        <v>1359</v>
       </c>
       <c r="N218" t="s">
-        <v>1341</v>
+        <v>1360</v>
       </c>
       <c r="Q218" t="s">
-        <v>1342</v>
+        <v>1361</v>
       </c>
       <c r="S218" t="s">
-        <v>1343</v>
+        <v>109</v>
       </c>
       <c r="T218">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="U218">
-        <v>100</v>
+        <v>185</v>
       </c>
       <c r="W218" t="s">
         <v>36</v>
@@ -14623,43 +14638,43 @@
     </row>
     <row r="219" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>1079</v>
+        <v>1354</v>
       </c>
       <c r="B219" t="s">
         <v>1332</v>
       </c>
       <c r="F219" t="s">
-        <v>266</v>
+        <v>1355</v>
       </c>
       <c r="G219" t="s">
-        <v>1344</v>
+        <v>1356</v>
       </c>
       <c r="H219">
-        <v>1444</v>
+        <v>1482</v>
       </c>
       <c r="I219" t="s">
         <v>64</v>
       </c>
       <c r="J219" t="s">
-        <v>1345</v>
+        <v>1362</v>
       </c>
       <c r="L219" t="s">
-        <v>1346</v>
+        <v>1363</v>
       </c>
       <c r="M219" t="s">
-        <v>1347</v>
+        <v>1364</v>
       </c>
       <c r="N219" t="s">
-        <v>1348</v>
+        <v>1365</v>
       </c>
       <c r="Q219" t="s">
-        <v>735</v>
+        <v>1366</v>
       </c>
       <c r="S219" t="s">
-        <v>1349</v>
+        <v>109</v>
       </c>
       <c r="T219">
-        <v>230</v>
+        <v>143</v>
       </c>
       <c r="U219">
         <v>180</v>
@@ -14673,46 +14688,43 @@
     </row>
     <row r="220" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>1079</v>
+        <v>1367</v>
       </c>
       <c r="B220" t="s">
-        <v>1332</v>
+        <v>1368</v>
       </c>
       <c r="F220" t="s">
-        <v>266</v>
+        <v>48</v>
       </c>
       <c r="G220" t="s">
-        <v>1344</v>
-      </c>
-      <c r="H220">
-        <v>1446</v>
+        <v>49</v>
+      </c>
+      <c r="H220" t="s">
+        <v>951</v>
       </c>
       <c r="I220" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="J220" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="M220" t="s">
-        <v>1350</v>
+        <v>1369</v>
       </c>
       <c r="N220" t="s">
-        <v>1351</v>
-      </c>
-      <c r="Q220" t="s">
-        <v>1352</v>
+        <v>1370</v>
       </c>
       <c r="S220" t="s">
-        <v>1353</v>
-      </c>
-      <c r="T220">
-        <v>292</v>
-      </c>
-      <c r="U220">
-        <v>415</v>
+        <v>109</v>
+      </c>
+      <c r="T220" t="s">
+        <v>1371</v>
+      </c>
+      <c r="U220" t="s">
+        <v>1372</v>
       </c>
       <c r="W220" t="s">
-        <v>36</v>
+        <v>955</v>
       </c>
       <c r="X220">
         <v>3</v>
@@ -14720,189 +14732,45 @@
     </row>
     <row r="221" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>1354</v>
+        <v>1367</v>
       </c>
       <c r="B221" t="s">
-        <v>1332</v>
+        <v>1368</v>
       </c>
       <c r="F221" t="s">
-        <v>1355</v>
+        <v>48</v>
       </c>
       <c r="G221" t="s">
-        <v>1356</v>
-      </c>
-      <c r="H221">
-        <v>1474</v>
+        <v>49</v>
+      </c>
+      <c r="H221" t="s">
+        <v>1373</v>
       </c>
       <c r="I221" t="s">
-        <v>64</v>
+        <v>1374</v>
       </c>
       <c r="J221" t="s">
-        <v>1357</v>
-      </c>
-      <c r="L221" t="s">
-        <v>1358</v>
+        <v>1375</v>
       </c>
       <c r="M221" t="s">
-        <v>1359</v>
+        <v>1376</v>
       </c>
       <c r="N221" t="s">
-        <v>1360</v>
-      </c>
-      <c r="Q221" t="s">
-        <v>1361</v>
+        <v>1377</v>
       </c>
       <c r="S221" t="s">
-        <v>109</v>
-      </c>
-      <c r="T221">
-        <v>165</v>
-      </c>
-      <c r="U221">
-        <v>185</v>
+        <v>81</v>
+      </c>
+      <c r="T221" t="s">
+        <v>1378</v>
+      </c>
+      <c r="U221" t="s">
+        <v>118</v>
       </c>
       <c r="W221" t="s">
-        <v>36</v>
+        <v>955</v>
       </c>
       <c r="X221">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="222" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>1354</v>
-      </c>
-      <c r="B222" t="s">
-        <v>1332</v>
-      </c>
-      <c r="F222" t="s">
-        <v>1355</v>
-      </c>
-      <c r="G222" t="s">
-        <v>1356</v>
-      </c>
-      <c r="H222">
-        <v>1482</v>
-      </c>
-      <c r="I222" t="s">
-        <v>64</v>
-      </c>
-      <c r="J222" t="s">
-        <v>1362</v>
-      </c>
-      <c r="L222" t="s">
-        <v>1363</v>
-      </c>
-      <c r="M222" t="s">
-        <v>1364</v>
-      </c>
-      <c r="N222" t="s">
-        <v>1365</v>
-      </c>
-      <c r="Q222" t="s">
-        <v>1366</v>
-      </c>
-      <c r="S222" t="s">
-        <v>109</v>
-      </c>
-      <c r="T222">
-        <v>143</v>
-      </c>
-      <c r="U222">
-        <v>180</v>
-      </c>
-      <c r="W222" t="s">
-        <v>36</v>
-      </c>
-      <c r="X222">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="223" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>1367</v>
-      </c>
-      <c r="B223" t="s">
-        <v>1368</v>
-      </c>
-      <c r="F223" t="s">
-        <v>48</v>
-      </c>
-      <c r="G223" t="s">
-        <v>49</v>
-      </c>
-      <c r="H223" t="s">
-        <v>951</v>
-      </c>
-      <c r="I223" t="s">
-        <v>77</v>
-      </c>
-      <c r="J223" t="s">
-        <v>78</v>
-      </c>
-      <c r="M223" t="s">
-        <v>1369</v>
-      </c>
-      <c r="N223" t="s">
-        <v>1370</v>
-      </c>
-      <c r="S223" t="s">
-        <v>109</v>
-      </c>
-      <c r="T223" t="s">
-        <v>1371</v>
-      </c>
-      <c r="U223" t="s">
-        <v>1372</v>
-      </c>
-      <c r="W223" t="s">
-        <v>955</v>
-      </c>
-      <c r="X223">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="224" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>1367</v>
-      </c>
-      <c r="B224" t="s">
-        <v>1368</v>
-      </c>
-      <c r="F224" t="s">
-        <v>48</v>
-      </c>
-      <c r="G224" t="s">
-        <v>49</v>
-      </c>
-      <c r="H224" t="s">
-        <v>1373</v>
-      </c>
-      <c r="I224" t="s">
-        <v>1374</v>
-      </c>
-      <c r="J224" t="s">
-        <v>1375</v>
-      </c>
-      <c r="M224" t="s">
-        <v>1376</v>
-      </c>
-      <c r="N224" t="s">
-        <v>1377</v>
-      </c>
-      <c r="S224" t="s">
-        <v>81</v>
-      </c>
-      <c r="T224" t="s">
-        <v>1378</v>
-      </c>
-      <c r="U224" t="s">
-        <v>118</v>
-      </c>
-      <c r="W224" t="s">
-        <v>955</v>
-      </c>
-      <c r="X224">
         <v>3</v>
       </c>
     </row>

--- a/quizzes/peinture-15e.xlsx
+++ b/quizzes/peinture-15e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1760D9-6A5E-498C-98A0-3D8AEDDB9A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB2D713-C36A-4A0A-8A1F-D70807F0B14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2879" uniqueCount="1379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2868" uniqueCount="1379">
   <si>
     <t>Prénom</t>
   </si>
@@ -4496,7 +4496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X221"/>
+  <dimension ref="A1:X220"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -10268,40 +10268,46 @@
     </row>
     <row r="122" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>247</v>
+        <v>862</v>
       </c>
       <c r="B122" t="s">
-        <v>825</v>
+        <v>863</v>
       </c>
       <c r="F122" t="s">
-        <v>826</v>
+        <v>135</v>
       </c>
       <c r="G122" t="s">
-        <v>827</v>
+        <v>864</v>
       </c>
       <c r="H122" t="s">
-        <v>637</v>
+        <v>103</v>
       </c>
       <c r="I122" t="s">
-        <v>810</v>
+        <v>138</v>
       </c>
       <c r="J122" t="s">
-        <v>811</v>
+        <v>139</v>
       </c>
       <c r="M122" t="s">
-        <v>733</v>
+        <v>865</v>
       </c>
       <c r="N122" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="S122" t="s">
-        <v>850</v>
+        <v>81</v>
+      </c>
+      <c r="T122" t="s">
+        <v>132</v>
+      </c>
+      <c r="U122" t="s">
+        <v>867</v>
       </c>
       <c r="W122" t="s">
-        <v>256</v>
+        <v>145</v>
       </c>
       <c r="X122">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10318,28 +10324,28 @@
         <v>864</v>
       </c>
       <c r="H123" t="s">
-        <v>103</v>
+        <v>868</v>
       </c>
       <c r="I123" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="J123" t="s">
-        <v>139</v>
+        <v>869</v>
       </c>
       <c r="M123" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="N123" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="S123" t="s">
         <v>81</v>
       </c>
       <c r="T123" t="s">
-        <v>132</v>
+        <v>872</v>
       </c>
       <c r="U123" t="s">
-        <v>867</v>
+        <v>44</v>
       </c>
       <c r="W123" t="s">
         <v>145</v>
@@ -10350,43 +10356,52 @@
     </row>
     <row r="124" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>862</v>
+        <v>873</v>
       </c>
       <c r="B124" t="s">
-        <v>863</v>
+        <v>874</v>
       </c>
       <c r="F124" t="s">
-        <v>135</v>
+        <v>875</v>
       </c>
       <c r="G124" t="s">
-        <v>864</v>
+        <v>421</v>
       </c>
       <c r="H124" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="I124" t="s">
-        <v>146</v>
+        <v>29</v>
       </c>
       <c r="J124" t="s">
-        <v>869</v>
+        <v>710</v>
+      </c>
+      <c r="L124" t="s">
+        <v>877</v>
       </c>
       <c r="M124" t="s">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="N124" t="s">
-        <v>871</v>
+        <v>879</v>
+      </c>
+      <c r="O124" t="s">
+        <v>880</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>881</v>
       </c>
       <c r="S124" t="s">
-        <v>81</v>
-      </c>
-      <c r="T124" t="s">
-        <v>872</v>
-      </c>
-      <c r="U124" t="s">
-        <v>44</v>
+        <v>217</v>
+      </c>
+      <c r="T124">
+        <v>450</v>
+      </c>
+      <c r="U124">
+        <v>450</v>
       </c>
       <c r="W124" t="s">
-        <v>145</v>
+        <v>36</v>
       </c>
       <c r="X124">
         <v>3</v>
@@ -10405,38 +10420,35 @@
       <c r="G125" t="s">
         <v>421</v>
       </c>
-      <c r="H125" t="s">
-        <v>876</v>
+      <c r="H125">
+        <v>1490</v>
       </c>
       <c r="I125" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J125" t="s">
-        <v>710</v>
+        <v>39</v>
       </c>
       <c r="L125" t="s">
-        <v>877</v>
+        <v>732</v>
       </c>
       <c r="M125" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="N125" t="s">
-        <v>879</v>
-      </c>
-      <c r="O125" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="Q125" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="S125" t="s">
-        <v>217</v>
+        <v>100</v>
       </c>
       <c r="T125">
-        <v>450</v>
+        <v>62</v>
       </c>
       <c r="U125">
-        <v>450</v>
+        <v>46</v>
       </c>
       <c r="W125" t="s">
         <v>36</v>
@@ -10447,49 +10459,43 @@
     </row>
     <row r="126" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="B126" t="s">
-        <v>874</v>
+        <v>886</v>
       </c>
       <c r="F126" t="s">
-        <v>875</v>
+        <v>26</v>
       </c>
       <c r="G126" t="s">
-        <v>421</v>
-      </c>
-      <c r="H126">
-        <v>1490</v>
+        <v>887</v>
+      </c>
+      <c r="H126" t="s">
+        <v>637</v>
       </c>
       <c r="I126" t="s">
-        <v>38</v>
+        <v>888</v>
       </c>
       <c r="J126" t="s">
-        <v>39</v>
-      </c>
-      <c r="L126" t="s">
-        <v>732</v>
+        <v>889</v>
       </c>
       <c r="M126" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="N126" t="s">
-        <v>883</v>
-      </c>
-      <c r="Q126" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
       <c r="S126" t="s">
-        <v>100</v>
+        <v>892</v>
       </c>
       <c r="T126">
-        <v>62</v>
-      </c>
-      <c r="U126">
-        <v>46</v>
+        <v>206</v>
+      </c>
+      <c r="U126" t="s">
+        <v>893</v>
       </c>
       <c r="W126" t="s">
-        <v>36</v>
+        <v>894</v>
       </c>
       <c r="X126">
         <v>3</v>
@@ -10518,22 +10524,25 @@
         <v>889</v>
       </c>
       <c r="M127" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="N127" t="s">
-        <v>891</v>
+        <v>896</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>897</v>
       </c>
       <c r="S127" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="T127">
-        <v>206</v>
-      </c>
-      <c r="U127" t="s">
-        <v>893</v>
+        <v>211</v>
+      </c>
+      <c r="U127">
+        <v>91</v>
       </c>
       <c r="W127" t="s">
-        <v>894</v>
+        <v>36</v>
       </c>
       <c r="X127">
         <v>3</v>
@@ -10541,43 +10550,46 @@
     </row>
     <row r="128" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>885</v>
+        <v>899</v>
       </c>
       <c r="B128" t="s">
-        <v>886</v>
+        <v>900</v>
       </c>
       <c r="F128" t="s">
-        <v>26</v>
+        <v>901</v>
       </c>
       <c r="G128" t="s">
-        <v>887</v>
-      </c>
-      <c r="H128" t="s">
-        <v>637</v>
+        <v>902</v>
+      </c>
+      <c r="H128">
+        <v>1459</v>
       </c>
       <c r="I128" t="s">
-        <v>888</v>
+        <v>29</v>
       </c>
       <c r="J128" t="s">
-        <v>889</v>
+        <v>903</v>
+      </c>
+      <c r="L128" t="s">
+        <v>904</v>
       </c>
       <c r="M128" t="s">
-        <v>895</v>
+        <v>905</v>
       </c>
       <c r="N128" t="s">
-        <v>896</v>
+        <v>906</v>
       </c>
       <c r="Q128" t="s">
-        <v>897</v>
+        <v>907</v>
       </c>
       <c r="S128" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="T128">
-        <v>211</v>
+        <v>405</v>
       </c>
       <c r="U128">
-        <v>91</v>
+        <v>516</v>
       </c>
       <c r="W128" t="s">
         <v>36</v>
@@ -10600,34 +10612,31 @@
         <v>902</v>
       </c>
       <c r="H129">
-        <v>1459</v>
+        <v>1471</v>
       </c>
       <c r="I129" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J129" t="s">
-        <v>903</v>
-      </c>
-      <c r="L129" t="s">
-        <v>904</v>
+        <v>39</v>
       </c>
       <c r="M129" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="N129" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="Q129" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="S129" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="T129">
-        <v>405</v>
+        <v>230</v>
       </c>
       <c r="U129">
-        <v>516</v>
+        <v>102</v>
       </c>
       <c r="W129" t="s">
         <v>36</v>
@@ -10638,46 +10647,37 @@
     </row>
     <row r="130" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>899</v>
+        <v>913</v>
       </c>
       <c r="B130" t="s">
-        <v>900</v>
+        <v>914</v>
       </c>
       <c r="F130" t="s">
-        <v>901</v>
+        <v>915</v>
       </c>
       <c r="G130" t="s">
-        <v>902</v>
-      </c>
-      <c r="H130">
-        <v>1471</v>
+        <v>316</v>
+      </c>
+      <c r="H130" t="s">
+        <v>63</v>
       </c>
       <c r="I130" t="s">
-        <v>38</v>
+        <v>146</v>
       </c>
       <c r="J130" t="s">
-        <v>39</v>
+        <v>916</v>
       </c>
       <c r="M130" t="s">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="N130" t="s">
-        <v>910</v>
-      </c>
-      <c r="Q130" t="s">
-        <v>911</v>
+        <v>918</v>
       </c>
       <c r="S130" t="s">
-        <v>912</v>
-      </c>
-      <c r="T130">
-        <v>230</v>
-      </c>
-      <c r="U130">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="W130" t="s">
-        <v>36</v>
+        <v>145</v>
       </c>
       <c r="X130">
         <v>3</v>
@@ -10697,22 +10697,22 @@
         <v>316</v>
       </c>
       <c r="H131" t="s">
-        <v>63</v>
+        <v>919</v>
       </c>
       <c r="I131" t="s">
         <v>146</v>
       </c>
       <c r="J131" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="M131" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="N131" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="S131" t="s">
-        <v>109</v>
+        <v>33</v>
       </c>
       <c r="W131" t="s">
         <v>145</v>
@@ -10723,37 +10723,46 @@
     </row>
     <row r="132" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>913</v>
+        <v>923</v>
       </c>
       <c r="B132" t="s">
-        <v>914</v>
+        <v>924</v>
       </c>
       <c r="F132" t="s">
-        <v>915</v>
+        <v>558</v>
       </c>
       <c r="G132" t="s">
-        <v>316</v>
+        <v>925</v>
       </c>
       <c r="H132" t="s">
-        <v>919</v>
+        <v>926</v>
       </c>
       <c r="I132" t="s">
-        <v>146</v>
+        <v>29</v>
       </c>
       <c r="J132" t="s">
-        <v>920</v>
+        <v>927</v>
       </c>
       <c r="M132" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
       <c r="N132" t="s">
-        <v>922</v>
+        <v>929</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>930</v>
       </c>
       <c r="S132" t="s">
         <v>33</v>
       </c>
+      <c r="T132" t="s">
+        <v>753</v>
+      </c>
+      <c r="U132" t="s">
+        <v>931</v>
+      </c>
       <c r="W132" t="s">
-        <v>145</v>
+        <v>36</v>
       </c>
       <c r="X132">
         <v>3</v>
@@ -10773,31 +10782,28 @@
         <v>925</v>
       </c>
       <c r="H133" t="s">
-        <v>926</v>
+        <v>88</v>
       </c>
       <c r="I133" t="s">
         <v>29</v>
       </c>
       <c r="J133" t="s">
-        <v>927</v>
+        <v>127</v>
       </c>
       <c r="M133" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="N133" t="s">
-        <v>929</v>
-      </c>
-      <c r="Q133" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="S133" t="s">
-        <v>33</v>
+        <v>934</v>
       </c>
       <c r="T133" t="s">
-        <v>753</v>
+        <v>125</v>
       </c>
       <c r="U133" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="W133" t="s">
         <v>36</v>
@@ -10808,19 +10814,19 @@
     </row>
     <row r="134" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>923</v>
+        <v>936</v>
       </c>
       <c r="B134" t="s">
         <v>924</v>
       </c>
       <c r="F134" t="s">
-        <v>558</v>
+        <v>937</v>
       </c>
       <c r="G134" t="s">
-        <v>925</v>
+        <v>938</v>
       </c>
       <c r="H134" t="s">
-        <v>88</v>
+        <v>939</v>
       </c>
       <c r="I134" t="s">
         <v>29</v>
@@ -10829,19 +10835,19 @@
         <v>127</v>
       </c>
       <c r="M134" t="s">
-        <v>932</v>
+        <v>733</v>
       </c>
       <c r="N134" t="s">
-        <v>933</v>
+        <v>940</v>
       </c>
       <c r="S134" t="s">
-        <v>934</v>
+        <v>33</v>
       </c>
       <c r="T134" t="s">
-        <v>125</v>
+        <v>760</v>
       </c>
       <c r="U134" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="W134" t="s">
         <v>36</v>
@@ -10864,7 +10870,7 @@
         <v>938</v>
       </c>
       <c r="H135" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="I135" t="s">
         <v>29</v>
@@ -10873,19 +10879,22 @@
         <v>127</v>
       </c>
       <c r="M135" t="s">
-        <v>733</v>
+        <v>943</v>
       </c>
       <c r="N135" t="s">
-        <v>940</v>
+        <v>944</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>945</v>
       </c>
       <c r="S135" t="s">
         <v>33</v>
       </c>
       <c r="T135" t="s">
-        <v>760</v>
+        <v>946</v>
       </c>
       <c r="U135" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="W135" t="s">
         <v>36</v>
@@ -10896,46 +10905,37 @@
     </row>
     <row r="136" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="B136" t="s">
-        <v>924</v>
+        <v>949</v>
       </c>
       <c r="F136" t="s">
-        <v>937</v>
+        <v>48</v>
       </c>
       <c r="G136" t="s">
-        <v>938</v>
+        <v>950</v>
       </c>
       <c r="H136" t="s">
-        <v>942</v>
+        <v>951</v>
       </c>
       <c r="I136" t="s">
-        <v>29</v>
+        <v>952</v>
       </c>
       <c r="J136" t="s">
-        <v>127</v>
+        <v>953</v>
       </c>
       <c r="M136" t="s">
-        <v>943</v>
+        <v>750</v>
       </c>
       <c r="N136" t="s">
-        <v>944</v>
-      </c>
-      <c r="Q136" t="s">
-        <v>945</v>
+        <v>954</v>
       </c>
       <c r="S136" t="s">
-        <v>33</v>
-      </c>
-      <c r="T136" t="s">
-        <v>946</v>
-      </c>
-      <c r="U136" t="s">
-        <v>947</v>
+        <v>745</v>
       </c>
       <c r="W136" t="s">
-        <v>36</v>
+        <v>955</v>
       </c>
       <c r="X136">
         <v>3</v>
@@ -10955,22 +10955,28 @@
         <v>950</v>
       </c>
       <c r="H137" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="I137" t="s">
         <v>952</v>
       </c>
       <c r="J137" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="M137" t="s">
-        <v>750</v>
+        <v>958</v>
       </c>
       <c r="N137" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="S137" t="s">
-        <v>745</v>
+        <v>33</v>
+      </c>
+      <c r="T137" t="s">
+        <v>960</v>
+      </c>
+      <c r="U137" t="s">
+        <v>961</v>
       </c>
       <c r="W137" t="s">
         <v>955</v>
@@ -10981,46 +10987,52 @@
     </row>
     <row r="138" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>948</v>
+        <v>555</v>
       </c>
       <c r="B138" t="s">
-        <v>949</v>
+        <v>962</v>
       </c>
       <c r="F138" t="s">
-        <v>48</v>
+        <v>963</v>
       </c>
       <c r="G138" t="s">
-        <v>950</v>
+        <v>964</v>
       </c>
       <c r="H138" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="I138" t="s">
-        <v>952</v>
+        <v>966</v>
       </c>
       <c r="J138" t="s">
-        <v>957</v>
+        <v>967</v>
+      </c>
+      <c r="L138" t="s">
+        <v>968</v>
       </c>
       <c r="M138" t="s">
-        <v>958</v>
+        <v>969</v>
       </c>
       <c r="N138" t="s">
-        <v>959</v>
+        <v>970</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>971</v>
       </c>
       <c r="S138" t="s">
-        <v>33</v>
-      </c>
-      <c r="T138" t="s">
-        <v>960</v>
-      </c>
-      <c r="U138" t="s">
-        <v>961</v>
+        <v>109</v>
+      </c>
+      <c r="T138">
+        <v>480</v>
+      </c>
+      <c r="U138">
+        <v>450</v>
       </c>
       <c r="W138" t="s">
-        <v>955</v>
+        <v>36</v>
       </c>
       <c r="X138">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11037,34 +11049,31 @@
         <v>964</v>
       </c>
       <c r="H139" t="s">
-        <v>965</v>
+        <v>972</v>
       </c>
       <c r="I139" t="s">
-        <v>966</v>
+        <v>69</v>
       </c>
       <c r="J139" t="s">
-        <v>967</v>
-      </c>
-      <c r="L139" t="s">
-        <v>968</v>
+        <v>70</v>
       </c>
       <c r="M139" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="N139" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="Q139" t="s">
-        <v>971</v>
+        <v>99</v>
       </c>
       <c r="S139" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="T139">
-        <v>480</v>
+        <v>63</v>
       </c>
       <c r="U139">
-        <v>450</v>
+        <v>80</v>
       </c>
       <c r="W139" t="s">
         <v>36</v>
@@ -11087,31 +11096,25 @@
         <v>964</v>
       </c>
       <c r="H140" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="I140" t="s">
-        <v>69</v>
+        <v>976</v>
       </c>
       <c r="J140" t="s">
-        <v>70</v>
+        <v>977</v>
       </c>
       <c r="M140" t="s">
-        <v>973</v>
+        <v>978</v>
       </c>
       <c r="N140" t="s">
-        <v>974</v>
+        <v>979</v>
       </c>
       <c r="Q140" t="s">
-        <v>99</v>
+        <v>980</v>
       </c>
       <c r="S140" t="s">
-        <v>100</v>
-      </c>
-      <c r="T140">
-        <v>63</v>
-      </c>
-      <c r="U140">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="W140" t="s">
         <v>36</v>
@@ -11133,26 +11136,32 @@
       <c r="G141" t="s">
         <v>964</v>
       </c>
-      <c r="H141" t="s">
-        <v>975</v>
+      <c r="H141">
+        <v>1480</v>
       </c>
       <c r="I141" t="s">
-        <v>976</v>
+        <v>38</v>
       </c>
       <c r="J141" t="s">
-        <v>977</v>
+        <v>39</v>
       </c>
       <c r="M141" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="N141" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="Q141" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="S141" t="s">
-        <v>217</v>
+        <v>984</v>
+      </c>
+      <c r="T141">
+        <v>255</v>
+      </c>
+      <c r="U141">
+        <v>140</v>
       </c>
       <c r="W141" t="s">
         <v>36</v>
@@ -11174,32 +11183,32 @@
       <c r="G142" t="s">
         <v>964</v>
       </c>
-      <c r="H142">
-        <v>1480</v>
+      <c r="H142" t="s">
+        <v>985</v>
       </c>
       <c r="I142" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="J142" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
       <c r="M142" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="N142" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="Q142" t="s">
-        <v>983</v>
+        <v>988</v>
       </c>
       <c r="S142" t="s">
         <v>984</v>
       </c>
       <c r="T142">
-        <v>255</v>
+        <v>68</v>
       </c>
       <c r="U142">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="W142" t="s">
         <v>36</v>
@@ -11222,31 +11231,22 @@
         <v>964</v>
       </c>
       <c r="H143" t="s">
-        <v>985</v>
+        <v>377</v>
       </c>
       <c r="I143" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="J143" t="s">
-        <v>105</v>
+        <v>39</v>
       </c>
       <c r="M143" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="N143" t="s">
-        <v>987</v>
-      </c>
-      <c r="Q143" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="S143" t="s">
-        <v>984</v>
-      </c>
-      <c r="T143">
-        <v>68</v>
-      </c>
-      <c r="U143">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="W143" t="s">
         <v>36</v>
@@ -11269,22 +11269,28 @@
         <v>964</v>
       </c>
       <c r="H144" t="s">
-        <v>377</v>
+        <v>88</v>
       </c>
       <c r="I144" t="s">
-        <v>38</v>
+        <v>991</v>
       </c>
       <c r="J144" t="s">
-        <v>39</v>
+        <v>491</v>
       </c>
       <c r="M144" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="N144" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="S144" t="s">
         <v>85</v>
+      </c>
+      <c r="T144" t="s">
+        <v>309</v>
+      </c>
+      <c r="U144" t="s">
+        <v>994</v>
       </c>
       <c r="W144" t="s">
         <v>36</v>
@@ -11306,29 +11312,35 @@
       <c r="G145" t="s">
         <v>964</v>
       </c>
-      <c r="H145" t="s">
-        <v>88</v>
+      <c r="H145">
+        <v>1497</v>
       </c>
       <c r="I145" t="s">
-        <v>991</v>
+        <v>38</v>
       </c>
       <c r="J145" t="s">
-        <v>491</v>
+        <v>39</v>
       </c>
       <c r="M145" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="N145" t="s">
-        <v>993</v>
+        <v>996</v>
+      </c>
+      <c r="O145" t="s">
+        <v>997</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>998</v>
       </c>
       <c r="S145" t="s">
-        <v>85</v>
-      </c>
-      <c r="T145" t="s">
-        <v>309</v>
-      </c>
-      <c r="U145" t="s">
-        <v>994</v>
+        <v>999</v>
+      </c>
+      <c r="T145">
+        <v>159</v>
+      </c>
+      <c r="U145">
+        <v>192</v>
       </c>
       <c r="W145" t="s">
         <v>36</v>
@@ -11339,52 +11351,43 @@
     </row>
     <row r="146" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>555</v>
+        <v>1000</v>
       </c>
       <c r="B146" t="s">
-        <v>962</v>
+        <v>1001</v>
       </c>
       <c r="F146" t="s">
-        <v>963</v>
+        <v>26</v>
       </c>
       <c r="G146" t="s">
-        <v>964</v>
-      </c>
-      <c r="H146">
-        <v>1497</v>
+        <v>1002</v>
+      </c>
+      <c r="H146" t="s">
+        <v>1003</v>
       </c>
       <c r="I146" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="J146" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="M146" t="s">
-        <v>995</v>
+        <v>1004</v>
       </c>
       <c r="N146" t="s">
-        <v>996</v>
-      </c>
-      <c r="O146" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
       <c r="Q146" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="S146" t="s">
-        <v>999</v>
-      </c>
-      <c r="T146">
-        <v>159</v>
-      </c>
-      <c r="U146">
-        <v>192</v>
+        <v>81</v>
       </c>
       <c r="W146" t="s">
-        <v>36</v>
+        <v>256</v>
       </c>
       <c r="X146">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11401,25 +11404,31 @@
         <v>1002</v>
       </c>
       <c r="H147" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="I147" t="s">
-        <v>77</v>
+        <v>1008</v>
       </c>
       <c r="J147" t="s">
-        <v>78</v>
+        <v>1009</v>
       </c>
       <c r="M147" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="N147" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="Q147" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
       <c r="S147" t="s">
-        <v>81</v>
+        <v>847</v>
+      </c>
+      <c r="T147" t="s">
+        <v>1013</v>
+      </c>
+      <c r="U147">
+        <v>27</v>
       </c>
       <c r="W147" t="s">
         <v>256</v>
@@ -11430,49 +11439,49 @@
     </row>
     <row r="148" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>1000</v>
+        <v>1014</v>
       </c>
       <c r="B148" t="s">
-        <v>1001</v>
+        <v>1015</v>
       </c>
       <c r="F148" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="G148" t="s">
-        <v>1002</v>
+        <v>421</v>
       </c>
       <c r="H148" t="s">
-        <v>1007</v>
+        <v>1016</v>
       </c>
       <c r="I148" t="s">
-        <v>1008</v>
+        <v>1017</v>
       </c>
       <c r="J148" t="s">
-        <v>1009</v>
+        <v>1018</v>
       </c>
       <c r="M148" t="s">
-        <v>1010</v>
+        <v>750</v>
       </c>
       <c r="N148" t="s">
-        <v>1011</v>
+        <v>1019</v>
       </c>
       <c r="Q148" t="s">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="S148" t="s">
-        <v>847</v>
+        <v>1021</v>
       </c>
       <c r="T148" t="s">
-        <v>1013</v>
-      </c>
-      <c r="U148">
-        <v>27</v>
+        <v>1022</v>
+      </c>
+      <c r="U148" t="s">
+        <v>792</v>
       </c>
       <c r="W148" t="s">
-        <v>256</v>
+        <v>55</v>
       </c>
       <c r="X148">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11489,31 +11498,34 @@
         <v>421</v>
       </c>
       <c r="H149" t="s">
-        <v>1016</v>
+        <v>1023</v>
       </c>
       <c r="I149" t="s">
-        <v>1017</v>
+        <v>460</v>
       </c>
       <c r="J149" t="s">
-        <v>1018</v>
+        <v>1024</v>
+      </c>
+      <c r="L149" t="s">
+        <v>1025</v>
       </c>
       <c r="M149" t="s">
-        <v>750</v>
+        <v>1026</v>
       </c>
       <c r="N149" t="s">
-        <v>1019</v>
+        <v>1027</v>
       </c>
       <c r="Q149" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
       <c r="S149" t="s">
-        <v>1021</v>
+        <v>847</v>
       </c>
       <c r="T149" t="s">
-        <v>1022</v>
+        <v>1029</v>
       </c>
       <c r="U149" t="s">
-        <v>792</v>
+        <v>1030</v>
       </c>
       <c r="W149" t="s">
         <v>55</v>
@@ -11536,34 +11548,31 @@
         <v>421</v>
       </c>
       <c r="H150" t="s">
-        <v>1023</v>
+        <v>68</v>
       </c>
       <c r="I150" t="s">
-        <v>460</v>
+        <v>810</v>
       </c>
       <c r="J150" t="s">
-        <v>1024</v>
-      </c>
-      <c r="L150" t="s">
-        <v>1025</v>
+        <v>811</v>
       </c>
       <c r="M150" t="s">
-        <v>1026</v>
+        <v>1031</v>
       </c>
       <c r="N150" t="s">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="Q150" t="s">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="S150" t="s">
-        <v>847</v>
+        <v>159</v>
       </c>
       <c r="T150" t="s">
-        <v>1029</v>
+        <v>101</v>
       </c>
       <c r="U150" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="W150" t="s">
         <v>55</v>
@@ -11586,34 +11595,25 @@
         <v>421</v>
       </c>
       <c r="H151" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="I151" t="s">
-        <v>810</v>
+        <v>29</v>
       </c>
       <c r="J151" t="s">
-        <v>811</v>
+        <v>127</v>
       </c>
       <c r="M151" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="N151" t="s">
-        <v>1032</v>
-      </c>
-      <c r="Q151" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="S151" t="s">
-        <v>159</v>
-      </c>
-      <c r="T151" t="s">
-        <v>101</v>
-      </c>
-      <c r="U151" t="s">
-        <v>1034</v>
+        <v>81</v>
       </c>
       <c r="W151" t="s">
-        <v>55</v>
+        <v>955</v>
       </c>
       <c r="X151">
         <v>2</v>
@@ -11633,19 +11633,19 @@
         <v>421</v>
       </c>
       <c r="H152" t="s">
-        <v>76</v>
+        <v>1037</v>
       </c>
       <c r="I152" t="s">
-        <v>29</v>
+        <v>460</v>
       </c>
       <c r="J152" t="s">
-        <v>127</v>
+        <v>461</v>
       </c>
       <c r="M152" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="N152" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="S152" t="s">
         <v>81</v>
@@ -11671,25 +11671,37 @@
         <v>421</v>
       </c>
       <c r="H153" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="I153" t="s">
         <v>460</v>
       </c>
       <c r="J153" t="s">
-        <v>461</v>
+        <v>1024</v>
+      </c>
+      <c r="L153" t="s">
+        <v>1025</v>
       </c>
       <c r="M153" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="N153" t="s">
-        <v>1039</v>
+        <v>1042</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>1043</v>
       </c>
       <c r="S153" t="s">
-        <v>81</v>
+        <v>159</v>
+      </c>
+      <c r="T153" t="s">
+        <v>1044</v>
+      </c>
+      <c r="U153" t="s">
+        <v>1045</v>
       </c>
       <c r="W153" t="s">
-        <v>955</v>
+        <v>55</v>
       </c>
       <c r="X153">
         <v>2</v>
@@ -11709,37 +11721,25 @@
         <v>421</v>
       </c>
       <c r="H154" t="s">
-        <v>1040</v>
+        <v>119</v>
       </c>
       <c r="I154" t="s">
-        <v>460</v>
+        <v>837</v>
       </c>
       <c r="J154" t="s">
-        <v>1024</v>
-      </c>
-      <c r="L154" t="s">
-        <v>1025</v>
+        <v>1046</v>
       </c>
       <c r="M154" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="N154" t="s">
-        <v>1042</v>
-      </c>
-      <c r="Q154" t="s">
-        <v>1043</v>
+        <v>1048</v>
       </c>
       <c r="S154" t="s">
-        <v>159</v>
-      </c>
-      <c r="T154" t="s">
-        <v>1044</v>
-      </c>
-      <c r="U154" t="s">
-        <v>1045</v>
+        <v>81</v>
       </c>
       <c r="W154" t="s">
-        <v>55</v>
+        <v>955</v>
       </c>
       <c r="X154">
         <v>2</v>
@@ -11759,25 +11759,37 @@
         <v>421</v>
       </c>
       <c r="H155" t="s">
-        <v>119</v>
+        <v>1002</v>
       </c>
       <c r="I155" t="s">
-        <v>837</v>
+        <v>460</v>
       </c>
       <c r="J155" t="s">
-        <v>1046</v>
+        <v>1024</v>
+      </c>
+      <c r="L155" t="s">
+        <v>1025</v>
       </c>
       <c r="M155" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="N155" t="s">
-        <v>1048</v>
+        <v>1050</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>1051</v>
       </c>
       <c r="S155" t="s">
-        <v>81</v>
+        <v>1052</v>
+      </c>
+      <c r="T155" t="s">
+        <v>1053</v>
+      </c>
+      <c r="U155" t="s">
+        <v>1054</v>
       </c>
       <c r="W155" t="s">
-        <v>955</v>
+        <v>55</v>
       </c>
       <c r="X155">
         <v>2</v>
@@ -11785,52 +11797,40 @@
     </row>
     <row r="156" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>1014</v>
+        <v>1055</v>
       </c>
       <c r="B156" t="s">
-        <v>1015</v>
+        <v>1056</v>
       </c>
       <c r="F156" t="s">
-        <v>94</v>
+        <v>951</v>
       </c>
       <c r="G156" t="s">
-        <v>421</v>
+        <v>1057</v>
       </c>
       <c r="H156" t="s">
-        <v>1002</v>
+        <v>1058</v>
       </c>
       <c r="I156" t="s">
-        <v>460</v>
+        <v>1059</v>
       </c>
       <c r="J156" t="s">
-        <v>1024</v>
-      </c>
-      <c r="L156" t="s">
-        <v>1025</v>
+        <v>1060</v>
       </c>
       <c r="M156" t="s">
-        <v>1049</v>
+        <v>1061</v>
       </c>
       <c r="N156" t="s">
-        <v>1050</v>
-      </c>
-      <c r="Q156" t="s">
-        <v>1051</v>
+        <v>1062</v>
       </c>
       <c r="S156" t="s">
-        <v>1052</v>
-      </c>
-      <c r="T156" t="s">
-        <v>1053</v>
-      </c>
-      <c r="U156" t="s">
-        <v>1054</v>
+        <v>1063</v>
       </c>
       <c r="W156" t="s">
-        <v>55</v>
+        <v>1064</v>
       </c>
       <c r="X156">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11847,25 +11847,31 @@
         <v>1057</v>
       </c>
       <c r="H157" t="s">
-        <v>1058</v>
+        <v>1065</v>
       </c>
       <c r="I157" t="s">
-        <v>1059</v>
+        <v>810</v>
       </c>
       <c r="J157" t="s">
-        <v>1060</v>
+        <v>811</v>
       </c>
       <c r="M157" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="N157" t="s">
-        <v>1062</v>
+        <v>1067</v>
       </c>
       <c r="S157" t="s">
-        <v>1063</v>
+        <v>81</v>
+      </c>
+      <c r="T157" t="s">
+        <v>411</v>
+      </c>
+      <c r="U157" t="s">
+        <v>629</v>
       </c>
       <c r="W157" t="s">
-        <v>1064</v>
+        <v>955</v>
       </c>
       <c r="X157">
         <v>3</v>
@@ -11873,43 +11879,49 @@
     </row>
     <row r="158" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>1055</v>
+        <v>1068</v>
       </c>
       <c r="B158" t="s">
-        <v>1056</v>
+        <v>1069</v>
+      </c>
+      <c r="D158" t="s">
+        <v>1070</v>
       </c>
       <c r="F158" t="s">
-        <v>951</v>
+        <v>1071</v>
       </c>
       <c r="G158" t="s">
-        <v>1057</v>
+        <v>458</v>
       </c>
       <c r="H158" t="s">
-        <v>1065</v>
+        <v>205</v>
       </c>
       <c r="I158" t="s">
-        <v>810</v>
+        <v>423</v>
       </c>
       <c r="J158" t="s">
-        <v>811</v>
+        <v>212</v>
       </c>
       <c r="M158" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
       <c r="N158" t="s">
-        <v>1067</v>
+        <v>1073</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>1074</v>
       </c>
       <c r="S158" t="s">
-        <v>81</v>
+        <v>217</v>
       </c>
       <c r="T158" t="s">
-        <v>411</v>
+        <v>1075</v>
       </c>
       <c r="U158" t="s">
-        <v>629</v>
+        <v>785</v>
       </c>
       <c r="W158" t="s">
-        <v>955</v>
+        <v>36</v>
       </c>
       <c r="X158">
         <v>3</v>
@@ -11922,9 +11934,6 @@
       <c r="B159" t="s">
         <v>1069</v>
       </c>
-      <c r="D159" t="s">
-        <v>1070</v>
-      </c>
       <c r="F159" t="s">
         <v>1071</v>
       </c>
@@ -11932,31 +11941,28 @@
         <v>458</v>
       </c>
       <c r="H159" t="s">
-        <v>205</v>
+        <v>421</v>
       </c>
       <c r="I159" t="s">
-        <v>423</v>
+        <v>29</v>
       </c>
       <c r="J159" t="s">
-        <v>212</v>
+        <v>127</v>
       </c>
       <c r="M159" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="N159" t="s">
-        <v>1073</v>
-      </c>
-      <c r="Q159" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="S159" t="s">
-        <v>217</v>
+        <v>81</v>
       </c>
       <c r="T159" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="U159" t="s">
-        <v>785</v>
+        <v>1044</v>
       </c>
       <c r="W159" t="s">
         <v>36</v>
@@ -11967,40 +11973,46 @@
     </row>
     <row r="160" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>1068</v>
+        <v>1079</v>
       </c>
       <c r="B160" t="s">
-        <v>1069</v>
+        <v>1080</v>
       </c>
       <c r="F160" t="s">
-        <v>1071</v>
+        <v>1081</v>
       </c>
       <c r="G160" t="s">
-        <v>458</v>
+        <v>1057</v>
       </c>
       <c r="H160" t="s">
-        <v>421</v>
+        <v>37</v>
       </c>
       <c r="I160" t="s">
         <v>29</v>
       </c>
       <c r="J160" t="s">
-        <v>127</v>
+        <v>482</v>
       </c>
       <c r="M160" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
       <c r="N160" t="s">
-        <v>1077</v>
+        <v>1083</v>
+      </c>
+      <c r="O160" t="s">
+        <v>1084</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>1085</v>
       </c>
       <c r="S160" t="s">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="T160" t="s">
-        <v>1078</v>
-      </c>
-      <c r="U160" t="s">
-        <v>1044</v>
+        <v>395</v>
+      </c>
+      <c r="U160">
+        <v>12</v>
       </c>
       <c r="W160" t="s">
         <v>36</v>
@@ -12022,35 +12034,32 @@
       <c r="G161" t="s">
         <v>1057</v>
       </c>
-      <c r="H161" t="s">
-        <v>37</v>
+      <c r="H161">
+        <v>1475</v>
       </c>
       <c r="I161" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="J161" t="s">
-        <v>482</v>
+        <v>70</v>
       </c>
       <c r="M161" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="N161" t="s">
-        <v>1083</v>
-      </c>
-      <c r="O161" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="Q161" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="S161" t="s">
-        <v>204</v>
+        <v>1089</v>
       </c>
       <c r="T161" t="s">
-        <v>395</v>
-      </c>
-      <c r="U161">
-        <v>12</v>
+        <v>1090</v>
+      </c>
+      <c r="U161" t="s">
+        <v>1091</v>
       </c>
       <c r="W161" t="s">
         <v>36</v>
@@ -12061,46 +12070,43 @@
     </row>
     <row r="162" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>1079</v>
+        <v>247</v>
       </c>
       <c r="B162" t="s">
-        <v>1080</v>
+        <v>1092</v>
       </c>
       <c r="F162" t="s">
-        <v>1081</v>
+        <v>49</v>
       </c>
       <c r="G162" t="s">
-        <v>1057</v>
-      </c>
-      <c r="H162">
-        <v>1475</v>
+        <v>1093</v>
+      </c>
+      <c r="H162" t="s">
+        <v>1094</v>
       </c>
       <c r="I162" t="s">
-        <v>69</v>
+        <v>1095</v>
       </c>
       <c r="J162" t="s">
-        <v>70</v>
+        <v>1096</v>
       </c>
       <c r="M162" t="s">
-        <v>1086</v>
+        <v>1097</v>
       </c>
       <c r="N162" t="s">
-        <v>1087</v>
-      </c>
-      <c r="Q162" t="s">
-        <v>1088</v>
+        <v>1098</v>
       </c>
       <c r="S162" t="s">
-        <v>1089</v>
-      </c>
-      <c r="T162" t="s">
-        <v>1090</v>
-      </c>
-      <c r="U162" t="s">
-        <v>1091</v>
+        <v>1099</v>
+      </c>
+      <c r="T162">
+        <v>143</v>
+      </c>
+      <c r="U162">
+        <v>260</v>
       </c>
       <c r="W162" t="s">
-        <v>36</v>
+        <v>256</v>
       </c>
       <c r="X162">
         <v>3</v>
@@ -12108,40 +12114,40 @@
     </row>
     <row r="163" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>247</v>
+        <v>1100</v>
       </c>
       <c r="B163" t="s">
-        <v>1092</v>
+        <v>1101</v>
       </c>
       <c r="F163" t="s">
-        <v>49</v>
+        <v>347</v>
       </c>
       <c r="G163" t="s">
-        <v>1093</v>
+        <v>1102</v>
       </c>
       <c r="H163" t="s">
-        <v>1094</v>
+        <v>1103</v>
       </c>
       <c r="I163" t="s">
-        <v>1095</v>
+        <v>1104</v>
       </c>
       <c r="J163" t="s">
-        <v>1096</v>
+        <v>1105</v>
       </c>
       <c r="M163" t="s">
-        <v>1097</v>
+        <v>733</v>
       </c>
       <c r="N163" t="s">
-        <v>1098</v>
+        <v>1106</v>
       </c>
       <c r="S163" t="s">
-        <v>1099</v>
-      </c>
-      <c r="T163">
-        <v>143</v>
-      </c>
-      <c r="U163">
-        <v>260</v>
+        <v>109</v>
+      </c>
+      <c r="T163" t="s">
+        <v>1107</v>
+      </c>
+      <c r="U163" t="s">
+        <v>760</v>
       </c>
       <c r="W163" t="s">
         <v>256</v>
@@ -12164,28 +12170,28 @@
         <v>1102</v>
       </c>
       <c r="H164" t="s">
-        <v>1103</v>
+        <v>614</v>
       </c>
       <c r="I164" t="s">
-        <v>1104</v>
+        <v>38</v>
       </c>
       <c r="J164" t="s">
-        <v>1105</v>
+        <v>39</v>
       </c>
       <c r="M164" t="s">
-        <v>733</v>
+        <v>1108</v>
       </c>
       <c r="N164" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="S164" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="T164" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="U164" t="s">
-        <v>760</v>
+        <v>1111</v>
       </c>
       <c r="W164" t="s">
         <v>256</v>
@@ -12196,43 +12202,52 @@
     </row>
     <row r="165" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>1100</v>
+        <v>1112</v>
       </c>
       <c r="B165" t="s">
-        <v>1101</v>
+        <v>1113</v>
       </c>
       <c r="F165" t="s">
-        <v>347</v>
+        <v>1114</v>
       </c>
       <c r="G165" t="s">
-        <v>1102</v>
+        <v>62</v>
       </c>
       <c r="H165" t="s">
-        <v>614</v>
+        <v>205</v>
       </c>
       <c r="I165" t="s">
-        <v>38</v>
+        <v>210</v>
       </c>
       <c r="J165" t="s">
-        <v>39</v>
+        <v>211</v>
+      </c>
+      <c r="L165" t="s">
+        <v>1115</v>
       </c>
       <c r="M165" t="s">
-        <v>1108</v>
+        <v>1116</v>
       </c>
       <c r="N165" t="s">
-        <v>1109</v>
+        <v>1117</v>
+      </c>
+      <c r="O165" t="s">
+        <v>1118</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>1119</v>
       </c>
       <c r="S165" t="s">
-        <v>81</v>
-      </c>
-      <c r="T165" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U165" t="s">
-        <v>1111</v>
+        <v>217</v>
+      </c>
+      <c r="T165">
+        <v>349</v>
+      </c>
+      <c r="U165">
+        <v>570</v>
       </c>
       <c r="W165" t="s">
-        <v>256</v>
+        <v>36</v>
       </c>
       <c r="X165">
         <v>3</v>
@@ -12264,16 +12279,16 @@
         <v>1115</v>
       </c>
       <c r="M166" t="s">
-        <v>1116</v>
+        <v>549</v>
       </c>
       <c r="N166" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="O166" t="s">
         <v>1118</v>
       </c>
       <c r="Q166" t="s">
-        <v>1119</v>
+        <v>562</v>
       </c>
       <c r="S166" t="s">
         <v>217</v>
@@ -12293,49 +12308,40 @@
     </row>
     <row r="167" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>1112</v>
+        <v>1121</v>
       </c>
       <c r="B167" t="s">
-        <v>1113</v>
+        <v>1122</v>
       </c>
       <c r="F167" t="s">
-        <v>1114</v>
+        <v>1123</v>
       </c>
       <c r="G167" t="s">
-        <v>62</v>
+        <v>458</v>
       </c>
       <c r="H167" t="s">
-        <v>205</v>
+        <v>1124</v>
       </c>
       <c r="I167" t="s">
-        <v>210</v>
+        <v>104</v>
       </c>
       <c r="J167" t="s">
-        <v>211</v>
-      </c>
-      <c r="L167" t="s">
-        <v>1115</v>
+        <v>105</v>
       </c>
       <c r="M167" t="s">
-        <v>549</v>
+        <v>1125</v>
       </c>
       <c r="N167" t="s">
-        <v>1120</v>
-      </c>
-      <c r="O167" t="s">
-        <v>1118</v>
-      </c>
-      <c r="Q167" t="s">
-        <v>562</v>
+        <v>1126</v>
       </c>
       <c r="S167" t="s">
-        <v>217</v>
-      </c>
-      <c r="T167">
-        <v>349</v>
-      </c>
-      <c r="U167">
-        <v>570</v>
+        <v>33</v>
+      </c>
+      <c r="T167" t="s">
+        <v>1127</v>
+      </c>
+      <c r="U167" t="s">
+        <v>1128</v>
       </c>
       <c r="W167" t="s">
         <v>36</v>
@@ -12346,40 +12352,46 @@
     </row>
     <row r="168" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="B168" t="s">
-        <v>1122</v>
+        <v>1130</v>
       </c>
       <c r="F168" t="s">
-        <v>1123</v>
+        <v>94</v>
       </c>
       <c r="G168" t="s">
-        <v>458</v>
-      </c>
-      <c r="H168" t="s">
-        <v>1124</v>
+        <v>339</v>
+      </c>
+      <c r="H168">
+        <v>1469</v>
       </c>
       <c r="I168" t="s">
-        <v>104</v>
+        <v>575</v>
       </c>
       <c r="J168" t="s">
-        <v>105</v>
+        <v>1131</v>
       </c>
       <c r="M168" t="s">
-        <v>1125</v>
+        <v>1132</v>
       </c>
       <c r="N168" t="s">
-        <v>1126</v>
+        <v>1133</v>
+      </c>
+      <c r="O168" t="s">
+        <v>1134</v>
+      </c>
+      <c r="Q168" t="s">
+        <v>1135</v>
       </c>
       <c r="S168" t="s">
-        <v>33</v>
-      </c>
-      <c r="T168" t="s">
-        <v>1127</v>
-      </c>
-      <c r="U168" t="s">
-        <v>1128</v>
+        <v>85</v>
+      </c>
+      <c r="T168">
+        <v>349</v>
+      </c>
+      <c r="U168">
+        <v>152</v>
       </c>
       <c r="W168" t="s">
         <v>36</v>
@@ -12401,35 +12413,35 @@
       <c r="G169" t="s">
         <v>339</v>
       </c>
-      <c r="H169">
-        <v>1469</v>
+      <c r="H169" t="s">
+        <v>1136</v>
       </c>
       <c r="I169" t="s">
-        <v>575</v>
+        <v>69</v>
       </c>
       <c r="J169" t="s">
-        <v>1131</v>
+        <v>70</v>
       </c>
       <c r="M169" t="s">
-        <v>1132</v>
+        <v>1137</v>
       </c>
       <c r="N169" t="s">
-        <v>1133</v>
+        <v>1138</v>
       </c>
       <c r="O169" t="s">
-        <v>1134</v>
+        <v>1139</v>
       </c>
       <c r="Q169" t="s">
-        <v>1135</v>
+        <v>1140</v>
       </c>
       <c r="S169" t="s">
-        <v>85</v>
+        <v>1141</v>
       </c>
       <c r="T169">
-        <v>349</v>
+        <v>239</v>
       </c>
       <c r="U169">
-        <v>152</v>
+        <v>102</v>
       </c>
       <c r="W169" t="s">
         <v>36</v>
@@ -12440,52 +12452,49 @@
     </row>
     <row r="170" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>1129</v>
+        <v>1142</v>
       </c>
       <c r="B170" t="s">
-        <v>1130</v>
+        <v>1143</v>
       </c>
       <c r="F170" t="s">
-        <v>94</v>
+        <v>1144</v>
       </c>
       <c r="G170" t="s">
-        <v>339</v>
+        <v>196</v>
       </c>
       <c r="H170" t="s">
-        <v>1136</v>
+        <v>1145</v>
       </c>
       <c r="I170" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="J170" t="s">
-        <v>70</v>
+        <v>127</v>
       </c>
       <c r="M170" t="s">
-        <v>1137</v>
+        <v>1146</v>
       </c>
       <c r="N170" t="s">
-        <v>1138</v>
-      </c>
-      <c r="O170" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
       <c r="Q170" t="s">
-        <v>1140</v>
+        <v>1148</v>
       </c>
       <c r="S170" t="s">
-        <v>1141</v>
+        <v>1149</v>
       </c>
       <c r="T170">
-        <v>239</v>
+        <v>182</v>
       </c>
       <c r="U170">
-        <v>102</v>
+        <v>323</v>
       </c>
       <c r="W170" t="s">
         <v>36</v>
       </c>
       <c r="X170">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12502,31 +12511,34 @@
         <v>196</v>
       </c>
       <c r="H171" t="s">
-        <v>1145</v>
+        <v>1150</v>
       </c>
       <c r="I171" t="s">
         <v>29</v>
       </c>
       <c r="J171" t="s">
-        <v>127</v>
+        <v>563</v>
+      </c>
+      <c r="L171" t="s">
+        <v>1151</v>
       </c>
       <c r="M171" t="s">
-        <v>1146</v>
+        <v>1152</v>
       </c>
       <c r="N171" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="Q171" t="s">
-        <v>1148</v>
+        <v>1154</v>
       </c>
       <c r="S171" t="s">
-        <v>1149</v>
-      </c>
-      <c r="T171">
-        <v>182</v>
-      </c>
-      <c r="U171">
-        <v>323</v>
+        <v>1155</v>
+      </c>
+      <c r="T171" t="s">
+        <v>1156</v>
+      </c>
+      <c r="U171" t="s">
+        <v>1157</v>
       </c>
       <c r="W171" t="s">
         <v>36</v>
@@ -12549,7 +12561,7 @@
         <v>196</v>
       </c>
       <c r="H172" t="s">
-        <v>1150</v>
+        <v>572</v>
       </c>
       <c r="I172" t="s">
         <v>29</v>
@@ -12557,26 +12569,14 @@
       <c r="J172" t="s">
         <v>563</v>
       </c>
-      <c r="L172" t="s">
-        <v>1151</v>
-      </c>
       <c r="M172" t="s">
-        <v>1152</v>
+        <v>1158</v>
       </c>
       <c r="N172" t="s">
-        <v>1153</v>
-      </c>
-      <c r="Q172" t="s">
-        <v>1154</v>
+        <v>1159</v>
       </c>
       <c r="S172" t="s">
-        <v>1155</v>
-      </c>
-      <c r="T172" t="s">
-        <v>1156</v>
-      </c>
-      <c r="U172" t="s">
-        <v>1157</v>
+        <v>217</v>
       </c>
       <c r="W172" t="s">
         <v>36</v>
@@ -12637,22 +12637,31 @@
         <v>196</v>
       </c>
       <c r="H174" t="s">
-        <v>572</v>
+        <v>757</v>
       </c>
       <c r="I174" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="J174" t="s">
-        <v>563</v>
+        <v>70</v>
       </c>
       <c r="M174" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="N174" t="s">
-        <v>1159</v>
+        <v>1161</v>
+      </c>
+      <c r="Q174" t="s">
+        <v>1162</v>
       </c>
       <c r="S174" t="s">
-        <v>217</v>
+        <v>1163</v>
+      </c>
+      <c r="T174" t="s">
+        <v>1164</v>
+      </c>
+      <c r="U174">
+        <v>322</v>
       </c>
       <c r="W174" t="s">
         <v>36</v>
@@ -12675,31 +12684,31 @@
         <v>196</v>
       </c>
       <c r="H175" t="s">
-        <v>757</v>
+        <v>1165</v>
       </c>
       <c r="I175" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="J175" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="M175" t="s">
-        <v>1160</v>
+        <v>1166</v>
       </c>
       <c r="N175" t="s">
-        <v>1161</v>
+        <v>1167</v>
       </c>
       <c r="Q175" t="s">
-        <v>1162</v>
+        <v>1168</v>
       </c>
       <c r="S175" t="s">
-        <v>1163</v>
-      </c>
-      <c r="T175" t="s">
-        <v>1164</v>
+        <v>1169</v>
+      </c>
+      <c r="T175">
+        <v>182</v>
       </c>
       <c r="U175">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="W175" t="s">
         <v>36</v>
@@ -12722,31 +12731,22 @@
         <v>196</v>
       </c>
       <c r="H176" t="s">
-        <v>1165</v>
+        <v>154</v>
       </c>
       <c r="I176" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J176" t="s">
-        <v>39</v>
+        <v>1170</v>
       </c>
       <c r="M176" t="s">
-        <v>1166</v>
+        <v>1171</v>
       </c>
       <c r="N176" t="s">
-        <v>1167</v>
-      </c>
-      <c r="Q176" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="S176" t="s">
-        <v>1169</v>
-      </c>
-      <c r="T176">
-        <v>182</v>
-      </c>
-      <c r="U176">
-        <v>317</v>
+        <v>217</v>
       </c>
       <c r="W176" t="s">
         <v>36</v>
@@ -12807,22 +12807,28 @@
         <v>196</v>
       </c>
       <c r="H178" t="s">
-        <v>154</v>
+        <v>103</v>
       </c>
       <c r="I178" t="s">
-        <v>29</v>
+        <v>1173</v>
       </c>
       <c r="J178" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="M178" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="N178" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="S178" t="s">
-        <v>217</v>
+        <v>109</v>
+      </c>
+      <c r="T178" t="s">
+        <v>1177</v>
+      </c>
+      <c r="U178" t="s">
+        <v>1178</v>
       </c>
       <c r="W178" t="s">
         <v>36</v>
@@ -12889,28 +12895,31 @@
         <v>196</v>
       </c>
       <c r="H180" t="s">
-        <v>103</v>
+        <v>637</v>
       </c>
       <c r="I180" t="s">
-        <v>1173</v>
+        <v>69</v>
       </c>
       <c r="J180" t="s">
-        <v>1174</v>
+        <v>70</v>
       </c>
       <c r="M180" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="N180" t="s">
-        <v>1176</v>
+        <v>1180</v>
+      </c>
+      <c r="Q180" t="s">
+        <v>1135</v>
       </c>
       <c r="S180" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="T180" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
       <c r="U180" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="W180" t="s">
         <v>36</v>
@@ -12921,46 +12930,49 @@
     </row>
     <row r="181" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>1142</v>
+        <v>1183</v>
       </c>
       <c r="B181" t="s">
-        <v>1143</v>
+        <v>1184</v>
       </c>
       <c r="F181" t="s">
-        <v>1144</v>
+        <v>135</v>
       </c>
       <c r="G181" t="s">
-        <v>196</v>
+        <v>681</v>
       </c>
       <c r="H181" t="s">
         <v>637</v>
       </c>
       <c r="I181" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="J181" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="M181" t="s">
-        <v>1179</v>
+        <v>1185</v>
       </c>
       <c r="N181" t="s">
-        <v>1180</v>
+        <v>1186</v>
+      </c>
+      <c r="O181" t="s">
+        <v>1187</v>
       </c>
       <c r="Q181" t="s">
-        <v>1135</v>
+        <v>1188</v>
       </c>
       <c r="S181" t="s">
-        <v>73</v>
+        <v>847</v>
       </c>
       <c r="T181" t="s">
-        <v>1181</v>
+        <v>1189</v>
       </c>
       <c r="U181" t="s">
-        <v>1182</v>
+        <v>1190</v>
       </c>
       <c r="W181" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="X181">
         <v>2</v>
@@ -12983,31 +12995,19 @@
         <v>637</v>
       </c>
       <c r="I182" t="s">
-        <v>77</v>
+        <v>1191</v>
       </c>
       <c r="J182" t="s">
-        <v>78</v>
+        <v>1192</v>
       </c>
       <c r="M182" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="N182" t="s">
-        <v>1186</v>
-      </c>
-      <c r="O182" t="s">
-        <v>1187</v>
-      </c>
-      <c r="Q182" t="s">
-        <v>1188</v>
+        <v>1194</v>
       </c>
       <c r="S182" t="s">
-        <v>847</v>
-      </c>
-      <c r="T182" t="s">
-        <v>1189</v>
-      </c>
-      <c r="U182" t="s">
-        <v>1190</v>
+        <v>81</v>
       </c>
       <c r="W182" t="s">
         <v>55</v>
@@ -13030,22 +13030,31 @@
         <v>681</v>
       </c>
       <c r="H183" t="s">
-        <v>637</v>
+        <v>1195</v>
       </c>
       <c r="I183" t="s">
-        <v>1191</v>
+        <v>29</v>
       </c>
       <c r="J183" t="s">
-        <v>1192</v>
+        <v>127</v>
       </c>
       <c r="M183" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="N183" t="s">
-        <v>1194</v>
+        <v>1197</v>
+      </c>
+      <c r="Q183" t="s">
+        <v>1198</v>
       </c>
       <c r="S183" t="s">
         <v>81</v>
+      </c>
+      <c r="T183" t="s">
+        <v>310</v>
+      </c>
+      <c r="U183" t="s">
+        <v>1199</v>
       </c>
       <c r="W183" t="s">
         <v>55</v>
@@ -13068,31 +13077,31 @@
         <v>681</v>
       </c>
       <c r="H184" t="s">
-        <v>1195</v>
+        <v>1200</v>
       </c>
       <c r="I184" t="s">
-        <v>29</v>
+        <v>1201</v>
       </c>
       <c r="J184" t="s">
-        <v>127</v>
+        <v>1202</v>
       </c>
       <c r="M184" t="s">
-        <v>1196</v>
+        <v>1203</v>
       </c>
       <c r="N184" t="s">
-        <v>1197</v>
+        <v>1204</v>
       </c>
       <c r="Q184" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="S184" t="s">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="T184" t="s">
-        <v>310</v>
+        <v>464</v>
       </c>
       <c r="U184" t="s">
-        <v>1199</v>
+        <v>117</v>
       </c>
       <c r="W184" t="s">
         <v>55</v>
@@ -13115,31 +13124,22 @@
         <v>681</v>
       </c>
       <c r="H185" t="s">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="I185" t="s">
         <v>1201</v>
       </c>
       <c r="J185" t="s">
-        <v>1202</v>
+        <v>1207</v>
       </c>
       <c r="M185" t="s">
-        <v>1203</v>
+        <v>1208</v>
       </c>
       <c r="N185" t="s">
-        <v>1204</v>
-      </c>
-      <c r="Q185" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="S185" t="s">
-        <v>159</v>
-      </c>
-      <c r="T185" t="s">
-        <v>464</v>
-      </c>
-      <c r="U185" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="W185" t="s">
         <v>55</v>
@@ -13162,22 +13162,31 @@
         <v>681</v>
       </c>
       <c r="H186" t="s">
-        <v>1206</v>
+        <v>76</v>
       </c>
       <c r="I186" t="s">
-        <v>1201</v>
+        <v>460</v>
       </c>
       <c r="J186" t="s">
-        <v>1207</v>
+        <v>461</v>
       </c>
       <c r="M186" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="N186" t="s">
-        <v>1209</v>
+        <v>1211</v>
+      </c>
+      <c r="Q186" t="s">
+        <v>1212</v>
       </c>
       <c r="S186" t="s">
-        <v>81</v>
+        <v>847</v>
+      </c>
+      <c r="T186" t="s">
+        <v>1213</v>
+      </c>
+      <c r="U186" t="s">
+        <v>1214</v>
       </c>
       <c r="W186" t="s">
         <v>55</v>
@@ -13203,28 +13212,28 @@
         <v>76</v>
       </c>
       <c r="I187" t="s">
-        <v>460</v>
+        <v>77</v>
       </c>
       <c r="J187" t="s">
-        <v>461</v>
+        <v>78</v>
       </c>
       <c r="M187" t="s">
-        <v>1210</v>
+        <v>1215</v>
       </c>
       <c r="N187" t="s">
-        <v>1211</v>
+        <v>1216</v>
       </c>
       <c r="Q187" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="S187" t="s">
-        <v>847</v>
+        <v>159</v>
       </c>
       <c r="T187" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="U187" t="s">
-        <v>1214</v>
+        <v>1219</v>
       </c>
       <c r="W187" t="s">
         <v>55</v>
@@ -13235,49 +13244,46 @@
     </row>
     <row r="188" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>1183</v>
+        <v>1220</v>
       </c>
       <c r="B188" t="s">
-        <v>1184</v>
+        <v>1221</v>
       </c>
       <c r="F188" t="s">
-        <v>135</v>
+        <v>1222</v>
       </c>
       <c r="G188" t="s">
-        <v>681</v>
+        <v>1223</v>
       </c>
       <c r="H188" t="s">
-        <v>76</v>
+        <v>951</v>
       </c>
       <c r="I188" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="J188" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="M188" t="s">
-        <v>1215</v>
+        <v>741</v>
       </c>
       <c r="N188" t="s">
-        <v>1216</v>
-      </c>
-      <c r="Q188" t="s">
-        <v>1217</v>
+        <v>1224</v>
       </c>
       <c r="S188" t="s">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="T188" t="s">
-        <v>1218</v>
+        <v>760</v>
       </c>
       <c r="U188" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="W188" t="s">
         <v>55</v>
       </c>
       <c r="X188">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13294,28 +13300,28 @@
         <v>1223</v>
       </c>
       <c r="H189" t="s">
-        <v>951</v>
+        <v>1226</v>
       </c>
       <c r="I189" t="s">
-        <v>138</v>
+        <v>1227</v>
       </c>
       <c r="J189" t="s">
-        <v>139</v>
+        <v>1228</v>
       </c>
       <c r="M189" t="s">
-        <v>741</v>
+        <v>1229</v>
       </c>
       <c r="N189" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="S189" t="s">
-        <v>81</v>
+        <v>401</v>
       </c>
       <c r="T189" t="s">
-        <v>760</v>
+        <v>585</v>
       </c>
       <c r="U189" t="s">
-        <v>1225</v>
+        <v>1231</v>
       </c>
       <c r="W189" t="s">
         <v>55</v>
@@ -13338,28 +13344,28 @@
         <v>1223</v>
       </c>
       <c r="H190" t="s">
-        <v>1226</v>
+        <v>1232</v>
       </c>
       <c r="I190" t="s">
-        <v>1227</v>
+        <v>837</v>
       </c>
       <c r="J190" t="s">
-        <v>1228</v>
+        <v>838</v>
       </c>
       <c r="M190" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="N190" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="S190" t="s">
-        <v>401</v>
+        <v>81</v>
       </c>
       <c r="T190" t="s">
-        <v>585</v>
+        <v>132</v>
       </c>
       <c r="U190" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="W190" t="s">
         <v>55</v>
@@ -13382,28 +13388,28 @@
         <v>1223</v>
       </c>
       <c r="H191" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="I191" t="s">
-        <v>837</v>
+        <v>275</v>
       </c>
       <c r="J191" t="s">
-        <v>838</v>
+        <v>276</v>
       </c>
       <c r="M191" t="s">
-        <v>1233</v>
+        <v>865</v>
       </c>
       <c r="N191" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="S191" t="s">
         <v>81</v>
       </c>
       <c r="T191" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="U191" t="s">
-        <v>1235</v>
+        <v>1044</v>
       </c>
       <c r="W191" t="s">
         <v>55</v>
@@ -13426,28 +13432,28 @@
         <v>1223</v>
       </c>
       <c r="H192" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="I192" t="s">
-        <v>275</v>
+        <v>77</v>
       </c>
       <c r="J192" t="s">
-        <v>276</v>
+        <v>78</v>
       </c>
       <c r="M192" t="s">
-        <v>865</v>
+        <v>1239</v>
       </c>
       <c r="N192" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="S192" t="s">
         <v>81</v>
       </c>
       <c r="T192" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="U192" t="s">
-        <v>1044</v>
+        <v>1241</v>
       </c>
       <c r="W192" t="s">
         <v>55</v>
@@ -13470,28 +13476,31 @@
         <v>1223</v>
       </c>
       <c r="H193" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
       <c r="I193" t="s">
-        <v>77</v>
+        <v>1243</v>
       </c>
       <c r="J193" t="s">
-        <v>78</v>
+        <v>1244</v>
       </c>
       <c r="M193" t="s">
-        <v>1239</v>
+        <v>1245</v>
       </c>
       <c r="N193" t="s">
-        <v>1240</v>
+        <v>1246</v>
+      </c>
+      <c r="O193" t="s">
+        <v>1247</v>
       </c>
       <c r="S193" t="s">
-        <v>81</v>
+        <v>1248</v>
       </c>
       <c r="T193" t="s">
-        <v>178</v>
+        <v>760</v>
       </c>
       <c r="U193" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="W193" t="s">
         <v>55</v>
@@ -13514,31 +13523,28 @@
         <v>1223</v>
       </c>
       <c r="H194" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="I194" t="s">
-        <v>1243</v>
+        <v>77</v>
       </c>
       <c r="J194" t="s">
-        <v>1244</v>
+        <v>78</v>
       </c>
       <c r="M194" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="N194" t="s">
-        <v>1246</v>
-      </c>
-      <c r="O194" t="s">
-        <v>1247</v>
+        <v>1252</v>
       </c>
       <c r="S194" t="s">
-        <v>1248</v>
+        <v>81</v>
       </c>
       <c r="T194" t="s">
-        <v>760</v>
+        <v>1054</v>
       </c>
       <c r="U194" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="W194" t="s">
         <v>55</v>
@@ -13555,34 +13561,28 @@
         <v>1221</v>
       </c>
       <c r="F195" t="s">
-        <v>1222</v>
+        <v>1254</v>
       </c>
       <c r="G195" t="s">
         <v>1223</v>
       </c>
       <c r="H195" t="s">
-        <v>1250</v>
+        <v>154</v>
       </c>
       <c r="I195" t="s">
-        <v>77</v>
+        <v>837</v>
       </c>
       <c r="J195" t="s">
-        <v>78</v>
+        <v>1046</v>
       </c>
       <c r="M195" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="N195" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="S195" t="s">
         <v>81</v>
-      </c>
-      <c r="T195" t="s">
-        <v>1054</v>
-      </c>
-      <c r="U195" t="s">
-        <v>1253</v>
       </c>
       <c r="W195" t="s">
         <v>55</v>
@@ -13599,28 +13599,34 @@
         <v>1221</v>
       </c>
       <c r="F196" t="s">
-        <v>1254</v>
+        <v>1222</v>
       </c>
       <c r="G196" t="s">
         <v>1223</v>
       </c>
       <c r="H196" t="s">
-        <v>154</v>
+        <v>1257</v>
       </c>
       <c r="I196" t="s">
-        <v>837</v>
+        <v>38</v>
       </c>
       <c r="J196" t="s">
-        <v>1046</v>
+        <v>39</v>
       </c>
       <c r="M196" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="N196" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="S196" t="s">
         <v>81</v>
+      </c>
+      <c r="T196" t="s">
+        <v>1260</v>
+      </c>
+      <c r="U196" t="s">
+        <v>1261</v>
       </c>
       <c r="W196" t="s">
         <v>55</v>
@@ -13637,34 +13643,28 @@
         <v>1221</v>
       </c>
       <c r="F197" t="s">
-        <v>1222</v>
+        <v>1254</v>
       </c>
       <c r="G197" t="s">
         <v>1223</v>
       </c>
       <c r="H197" t="s">
-        <v>1257</v>
+        <v>614</v>
       </c>
       <c r="I197" t="s">
-        <v>38</v>
+        <v>810</v>
       </c>
       <c r="J197" t="s">
-        <v>39</v>
+        <v>811</v>
       </c>
       <c r="M197" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="N197" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="S197" t="s">
         <v>81</v>
-      </c>
-      <c r="T197" t="s">
-        <v>1260</v>
-      </c>
-      <c r="U197" t="s">
-        <v>1261</v>
       </c>
       <c r="W197" t="s">
         <v>55</v>
@@ -13681,28 +13681,34 @@
         <v>1221</v>
       </c>
       <c r="F198" t="s">
-        <v>1254</v>
+        <v>1222</v>
       </c>
       <c r="G198" t="s">
         <v>1223</v>
       </c>
       <c r="H198" t="s">
-        <v>614</v>
+        <v>457</v>
       </c>
       <c r="I198" t="s">
-        <v>810</v>
+        <v>490</v>
       </c>
       <c r="J198" t="s">
-        <v>811</v>
+        <v>491</v>
       </c>
       <c r="M198" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="N198" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="S198" t="s">
         <v>81</v>
+      </c>
+      <c r="T198" t="s">
+        <v>1266</v>
+      </c>
+      <c r="U198" t="s">
+        <v>1267</v>
       </c>
       <c r="W198" t="s">
         <v>55</v>
@@ -13725,28 +13731,28 @@
         <v>1223</v>
       </c>
       <c r="H199" t="s">
-        <v>457</v>
+        <v>1268</v>
       </c>
       <c r="I199" t="s">
-        <v>490</v>
+        <v>29</v>
       </c>
       <c r="J199" t="s">
-        <v>491</v>
+        <v>127</v>
       </c>
       <c r="M199" t="s">
-        <v>1264</v>
+        <v>1269</v>
       </c>
       <c r="N199" t="s">
-        <v>1265</v>
+        <v>1270</v>
       </c>
       <c r="S199" t="s">
         <v>81</v>
       </c>
       <c r="T199" t="s">
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="U199" t="s">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="W199" t="s">
         <v>55</v>
@@ -13757,40 +13763,43 @@
     </row>
     <row r="200" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>1220</v>
+        <v>1273</v>
       </c>
       <c r="B200" t="s">
-        <v>1221</v>
+        <v>1274</v>
       </c>
       <c r="F200" t="s">
-        <v>1222</v>
+        <v>1275</v>
       </c>
       <c r="G200" t="s">
-        <v>1223</v>
+        <v>1276</v>
       </c>
       <c r="H200" t="s">
-        <v>1268</v>
+        <v>1277</v>
       </c>
       <c r="I200" t="s">
-        <v>29</v>
+        <v>1278</v>
       </c>
       <c r="J200" t="s">
-        <v>127</v>
+        <v>1279</v>
       </c>
       <c r="M200" t="s">
-        <v>1269</v>
+        <v>1280</v>
       </c>
       <c r="N200" t="s">
-        <v>1270</v>
+        <v>1281</v>
+      </c>
+      <c r="Q200" t="s">
+        <v>1282</v>
       </c>
       <c r="S200" t="s">
         <v>81</v>
       </c>
-      <c r="T200" t="s">
-        <v>1271</v>
-      </c>
-      <c r="U200" t="s">
-        <v>1272</v>
+      <c r="T200">
+        <v>340</v>
+      </c>
+      <c r="U200">
+        <v>520</v>
       </c>
       <c r="W200" t="s">
         <v>55</v>
@@ -13813,31 +13822,31 @@
         <v>1276</v>
       </c>
       <c r="H201" t="s">
-        <v>1277</v>
+        <v>1283</v>
       </c>
       <c r="I201" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
       <c r="J201" t="s">
-        <v>1279</v>
+        <v>1285</v>
       </c>
       <c r="M201" t="s">
-        <v>1280</v>
+        <v>1286</v>
       </c>
       <c r="N201" t="s">
-        <v>1281</v>
+        <v>1287</v>
       </c>
       <c r="Q201" t="s">
-        <v>1282</v>
+        <v>1288</v>
       </c>
       <c r="S201" t="s">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="T201">
-        <v>340</v>
+        <v>22.5</v>
       </c>
       <c r="U201">
-        <v>520</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="W201" t="s">
         <v>55</v>
@@ -13860,31 +13869,31 @@
         <v>1276</v>
       </c>
       <c r="H202" t="s">
-        <v>1283</v>
+        <v>1289</v>
       </c>
       <c r="I202" t="s">
-        <v>1284</v>
+        <v>69</v>
       </c>
       <c r="J202" t="s">
-        <v>1285</v>
+        <v>70</v>
       </c>
       <c r="M202" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="N202" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="Q202" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="S202" t="s">
         <v>159</v>
       </c>
       <c r="T202">
-        <v>22.5</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="U202">
-        <v>16.600000000000001</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="W202" t="s">
         <v>55</v>
@@ -13907,7 +13916,7 @@
         <v>1276</v>
       </c>
       <c r="H203" t="s">
-        <v>1289</v>
+        <v>754</v>
       </c>
       <c r="I203" t="s">
         <v>69</v>
@@ -13916,22 +13925,22 @@
         <v>70</v>
       </c>
       <c r="M203" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="N203" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="Q203" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="S203" t="s">
         <v>159</v>
       </c>
       <c r="T203">
-        <v>33.299999999999997</v>
+        <v>25.5</v>
       </c>
       <c r="U203">
-        <v>18.899999999999999</v>
+        <v>19</v>
       </c>
       <c r="W203" t="s">
         <v>55</v>
@@ -13954,7 +13963,7 @@
         <v>1276</v>
       </c>
       <c r="H204" t="s">
-        <v>754</v>
+        <v>1296</v>
       </c>
       <c r="I204" t="s">
         <v>69</v>
@@ -13963,22 +13972,19 @@
         <v>70</v>
       </c>
       <c r="M204" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="N204" t="s">
-        <v>1294</v>
-      </c>
-      <c r="Q204" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="S204" t="s">
-        <v>159</v>
-      </c>
-      <c r="T204">
-        <v>25.5</v>
-      </c>
-      <c r="U204">
-        <v>19</v>
+        <v>81</v>
+      </c>
+      <c r="T204" t="s">
+        <v>1299</v>
+      </c>
+      <c r="U204" t="s">
+        <v>1300</v>
       </c>
       <c r="W204" t="s">
         <v>55</v>
@@ -14001,28 +14007,31 @@
         <v>1276</v>
       </c>
       <c r="H205" t="s">
-        <v>1296</v>
+        <v>1301</v>
       </c>
       <c r="I205" t="s">
-        <v>69</v>
+        <v>490</v>
       </c>
       <c r="J205" t="s">
-        <v>70</v>
+        <v>491</v>
       </c>
       <c r="M205" t="s">
-        <v>1297</v>
+        <v>483</v>
       </c>
       <c r="N205" t="s">
-        <v>1298</v>
+        <v>1302</v>
+      </c>
+      <c r="Q205" t="s">
+        <v>1303</v>
       </c>
       <c r="S205" t="s">
-        <v>81</v>
-      </c>
-      <c r="T205" t="s">
-        <v>1299</v>
-      </c>
-      <c r="U205" t="s">
-        <v>1300</v>
+        <v>1304</v>
+      </c>
+      <c r="T205">
+        <v>90.2</v>
+      </c>
+      <c r="U205">
+        <v>34.1</v>
       </c>
       <c r="W205" t="s">
         <v>55</v>
@@ -14048,28 +14057,28 @@
         <v>1301</v>
       </c>
       <c r="I206" t="s">
-        <v>490</v>
+        <v>460</v>
       </c>
       <c r="J206" t="s">
-        <v>491</v>
+        <v>461</v>
       </c>
       <c r="M206" t="s">
-        <v>483</v>
+        <v>1305</v>
       </c>
       <c r="N206" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="Q206" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="S206" t="s">
-        <v>1304</v>
+        <v>159</v>
       </c>
       <c r="T206">
-        <v>90.2</v>
+        <v>122.1</v>
       </c>
       <c r="U206">
-        <v>34.1</v>
+        <v>157.80000000000001</v>
       </c>
       <c r="W206" t="s">
         <v>55</v>
@@ -14092,31 +14101,31 @@
         <v>1276</v>
       </c>
       <c r="H207" t="s">
-        <v>1301</v>
+        <v>588</v>
       </c>
       <c r="I207" t="s">
-        <v>460</v>
+        <v>38</v>
       </c>
       <c r="J207" t="s">
-        <v>461</v>
+        <v>39</v>
       </c>
       <c r="M207" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="N207" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="Q207" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="S207" t="s">
         <v>159</v>
       </c>
       <c r="T207">
-        <v>122.1</v>
+        <v>66</v>
       </c>
       <c r="U207">
-        <v>157.80000000000001</v>
+        <v>62</v>
       </c>
       <c r="W207" t="s">
         <v>55</v>
@@ -14139,31 +14148,31 @@
         <v>1276</v>
       </c>
       <c r="H208" t="s">
-        <v>588</v>
+        <v>1311</v>
       </c>
       <c r="I208" t="s">
-        <v>38</v>
+        <v>581</v>
       </c>
       <c r="J208" t="s">
-        <v>39</v>
+        <v>582</v>
       </c>
       <c r="M208" t="s">
-        <v>1308</v>
+        <v>1312</v>
       </c>
       <c r="N208" t="s">
-        <v>1309</v>
+        <v>1313</v>
       </c>
       <c r="Q208" t="s">
-        <v>1310</v>
+        <v>1314</v>
       </c>
       <c r="S208" t="s">
         <v>159</v>
       </c>
       <c r="T208">
-        <v>66</v>
+        <v>33.1</v>
       </c>
       <c r="U208">
-        <v>62</v>
+        <v>53.8</v>
       </c>
       <c r="W208" t="s">
         <v>55</v>
@@ -14186,31 +14195,22 @@
         <v>1276</v>
       </c>
       <c r="H209" t="s">
-        <v>1311</v>
+        <v>1315</v>
       </c>
       <c r="I209" t="s">
-        <v>581</v>
+        <v>350</v>
       </c>
       <c r="J209" t="s">
-        <v>582</v>
+        <v>351</v>
       </c>
       <c r="M209" t="s">
-        <v>1312</v>
+        <v>1316</v>
       </c>
       <c r="N209" t="s">
-        <v>1313</v>
-      </c>
-      <c r="Q209" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="S209" t="s">
-        <v>159</v>
-      </c>
-      <c r="T209">
-        <v>33.1</v>
-      </c>
-      <c r="U209">
-        <v>53.8</v>
+        <v>81</v>
       </c>
       <c r="W209" t="s">
         <v>55</v>
@@ -14233,22 +14233,31 @@
         <v>1276</v>
       </c>
       <c r="H210" t="s">
-        <v>1315</v>
+        <v>1114</v>
       </c>
       <c r="I210" t="s">
-        <v>350</v>
+        <v>460</v>
       </c>
       <c r="J210" t="s">
-        <v>351</v>
+        <v>461</v>
       </c>
       <c r="M210" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="N210" t="s">
-        <v>1317</v>
+        <v>1319</v>
+      </c>
+      <c r="Q210" t="s">
+        <v>1320</v>
       </c>
       <c r="S210" t="s">
-        <v>81</v>
+        <v>159</v>
+      </c>
+      <c r="T210">
+        <v>32.5</v>
+      </c>
+      <c r="U210">
+        <v>26</v>
       </c>
       <c r="W210" t="s">
         <v>55</v>
@@ -14259,49 +14268,46 @@
     </row>
     <row r="211" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>1273</v>
+        <v>873</v>
       </c>
       <c r="B211" t="s">
-        <v>1274</v>
+        <v>1321</v>
       </c>
       <c r="F211" t="s">
-        <v>1275</v>
+        <v>347</v>
       </c>
       <c r="G211" t="s">
-        <v>1276</v>
+        <v>1322</v>
       </c>
       <c r="H211" t="s">
-        <v>1114</v>
+        <v>1323</v>
       </c>
       <c r="I211" t="s">
-        <v>460</v>
+        <v>77</v>
       </c>
       <c r="J211" t="s">
-        <v>461</v>
+        <v>78</v>
       </c>
       <c r="M211" t="s">
-        <v>1318</v>
+        <v>932</v>
       </c>
       <c r="N211" t="s">
-        <v>1319</v>
-      </c>
-      <c r="Q211" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="S211" t="s">
-        <v>159</v>
-      </c>
-      <c r="T211">
-        <v>32.5</v>
-      </c>
-      <c r="U211">
-        <v>26</v>
+        <v>33</v>
+      </c>
+      <c r="T211" t="s">
+        <v>1325</v>
+      </c>
+      <c r="U211" t="s">
+        <v>1326</v>
       </c>
       <c r="W211" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="X211">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="212" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14318,28 +14324,28 @@
         <v>1322</v>
       </c>
       <c r="H212" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
       <c r="I212" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="J212" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="M212" t="s">
-        <v>932</v>
+        <v>1328</v>
       </c>
       <c r="N212" t="s">
-        <v>1324</v>
+        <v>1329</v>
       </c>
       <c r="S212" t="s">
         <v>33</v>
       </c>
       <c r="T212" t="s">
-        <v>1325</v>
+        <v>753</v>
       </c>
       <c r="U212" t="s">
-        <v>1326</v>
+        <v>1330</v>
       </c>
       <c r="W212" t="s">
         <v>36</v>
@@ -14350,40 +14356,43 @@
     </row>
     <row r="213" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>873</v>
+        <v>1331</v>
       </c>
       <c r="B213" t="s">
-        <v>1321</v>
+        <v>1332</v>
       </c>
       <c r="F213" t="s">
-        <v>347</v>
+        <v>1333</v>
       </c>
       <c r="G213" t="s">
-        <v>1322</v>
-      </c>
-      <c r="H213" t="s">
-        <v>1327</v>
+        <v>1093</v>
+      </c>
+      <c r="H213">
+        <v>1480</v>
       </c>
       <c r="I213" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="J213" t="s">
-        <v>127</v>
+        <v>65</v>
       </c>
       <c r="M213" t="s">
-        <v>1328</v>
+        <v>1334</v>
       </c>
       <c r="N213" t="s">
-        <v>1329</v>
+        <v>1335</v>
+      </c>
+      <c r="Q213" t="s">
+        <v>1336</v>
       </c>
       <c r="S213" t="s">
-        <v>33</v>
-      </c>
-      <c r="T213" t="s">
-        <v>753</v>
-      </c>
-      <c r="U213" t="s">
-        <v>1330</v>
+        <v>159</v>
+      </c>
+      <c r="T213">
+        <v>120</v>
+      </c>
+      <c r="U213">
+        <v>170</v>
       </c>
       <c r="W213" t="s">
         <v>36</v>
@@ -14405,32 +14414,35 @@
       <c r="G214" t="s">
         <v>1093</v>
       </c>
-      <c r="H214">
-        <v>1480</v>
+      <c r="H214" t="s">
+        <v>1337</v>
       </c>
       <c r="I214" t="s">
         <v>64</v>
       </c>
       <c r="J214" t="s">
-        <v>65</v>
+        <v>1338</v>
+      </c>
+      <c r="L214" t="s">
+        <v>1339</v>
       </c>
       <c r="M214" t="s">
-        <v>1334</v>
+        <v>1340</v>
       </c>
       <c r="N214" t="s">
-        <v>1335</v>
+        <v>1341</v>
       </c>
       <c r="Q214" t="s">
-        <v>1336</v>
+        <v>1342</v>
       </c>
       <c r="S214" t="s">
-        <v>159</v>
+        <v>1343</v>
       </c>
       <c r="T214">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="U214">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="W214" t="s">
         <v>36</v>
@@ -14441,46 +14453,46 @@
     </row>
     <row r="215" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>1331</v>
+        <v>1079</v>
       </c>
       <c r="B215" t="s">
         <v>1332</v>
       </c>
       <c r="F215" t="s">
-        <v>1333</v>
+        <v>266</v>
       </c>
       <c r="G215" t="s">
-        <v>1093</v>
-      </c>
-      <c r="H215" t="s">
-        <v>1337</v>
+        <v>1344</v>
+      </c>
+      <c r="H215">
+        <v>1444</v>
       </c>
       <c r="I215" t="s">
         <v>64</v>
       </c>
       <c r="J215" t="s">
-        <v>1338</v>
+        <v>1345</v>
       </c>
       <c r="L215" t="s">
-        <v>1339</v>
+        <v>1346</v>
       </c>
       <c r="M215" t="s">
-        <v>1340</v>
+        <v>1347</v>
       </c>
       <c r="N215" t="s">
-        <v>1341</v>
+        <v>1348</v>
       </c>
       <c r="Q215" t="s">
-        <v>1342</v>
+        <v>735</v>
       </c>
       <c r="S215" t="s">
-        <v>1343</v>
+        <v>1349</v>
       </c>
       <c r="T215">
-        <v>141</v>
+        <v>230</v>
       </c>
       <c r="U215">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="W215" t="s">
         <v>36</v>
@@ -14503,34 +14515,31 @@
         <v>1344</v>
       </c>
       <c r="H216">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="I216" t="s">
         <v>64</v>
       </c>
       <c r="J216" t="s">
-        <v>1345</v>
-      </c>
-      <c r="L216" t="s">
-        <v>1346</v>
+        <v>65</v>
       </c>
       <c r="M216" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="N216" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="Q216" t="s">
-        <v>735</v>
+        <v>1352</v>
       </c>
       <c r="S216" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
       <c r="T216">
-        <v>230</v>
+        <v>292</v>
       </c>
       <c r="U216">
-        <v>180</v>
+        <v>415</v>
       </c>
       <c r="W216" t="s">
         <v>36</v>
@@ -14541,43 +14550,46 @@
     </row>
     <row r="217" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>1079</v>
+        <v>1354</v>
       </c>
       <c r="B217" t="s">
         <v>1332</v>
       </c>
       <c r="F217" t="s">
-        <v>266</v>
+        <v>1355</v>
       </c>
       <c r="G217" t="s">
-        <v>1344</v>
+        <v>1356</v>
       </c>
       <c r="H217">
-        <v>1446</v>
+        <v>1474</v>
       </c>
       <c r="I217" t="s">
         <v>64</v>
       </c>
       <c r="J217" t="s">
-        <v>65</v>
+        <v>1357</v>
+      </c>
+      <c r="L217" t="s">
+        <v>1358</v>
       </c>
       <c r="M217" t="s">
-        <v>1350</v>
+        <v>1359</v>
       </c>
       <c r="N217" t="s">
-        <v>1351</v>
+        <v>1360</v>
       </c>
       <c r="Q217" t="s">
-        <v>1352</v>
+        <v>1361</v>
       </c>
       <c r="S217" t="s">
-        <v>1353</v>
+        <v>109</v>
       </c>
       <c r="T217">
-        <v>292</v>
+        <v>165</v>
       </c>
       <c r="U217">
-        <v>415</v>
+        <v>185</v>
       </c>
       <c r="W217" t="s">
         <v>36</v>
@@ -14600,34 +14612,34 @@
         <v>1356</v>
       </c>
       <c r="H218">
-        <v>1474</v>
+        <v>1482</v>
       </c>
       <c r="I218" t="s">
         <v>64</v>
       </c>
       <c r="J218" t="s">
-        <v>1357</v>
+        <v>1362</v>
       </c>
       <c r="L218" t="s">
-        <v>1358</v>
+        <v>1363</v>
       </c>
       <c r="M218" t="s">
-        <v>1359</v>
+        <v>1364</v>
       </c>
       <c r="N218" t="s">
-        <v>1360</v>
+        <v>1365</v>
       </c>
       <c r="Q218" t="s">
-        <v>1361</v>
+        <v>1366</v>
       </c>
       <c r="S218" t="s">
         <v>109</v>
       </c>
       <c r="T218">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="U218">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="W218" t="s">
         <v>36</v>
@@ -14638,49 +14650,43 @@
     </row>
     <row r="219" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>1354</v>
+        <v>1367</v>
       </c>
       <c r="B219" t="s">
-        <v>1332</v>
+        <v>1368</v>
       </c>
       <c r="F219" t="s">
-        <v>1355</v>
+        <v>48</v>
       </c>
       <c r="G219" t="s">
-        <v>1356</v>
-      </c>
-      <c r="H219">
-        <v>1482</v>
+        <v>49</v>
+      </c>
+      <c r="H219" t="s">
+        <v>951</v>
       </c>
       <c r="I219" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="J219" t="s">
-        <v>1362</v>
-      </c>
-      <c r="L219" t="s">
-        <v>1363</v>
+        <v>78</v>
       </c>
       <c r="M219" t="s">
-        <v>1364</v>
+        <v>1369</v>
       </c>
       <c r="N219" t="s">
-        <v>1365</v>
-      </c>
-      <c r="Q219" t="s">
-        <v>1366</v>
+        <v>1370</v>
       </c>
       <c r="S219" t="s">
         <v>109</v>
       </c>
-      <c r="T219">
-        <v>143</v>
-      </c>
-      <c r="U219">
-        <v>180</v>
+      <c r="T219" t="s">
+        <v>1371</v>
+      </c>
+      <c r="U219" t="s">
+        <v>1372</v>
       </c>
       <c r="W219" t="s">
-        <v>36</v>
+        <v>955</v>
       </c>
       <c r="X219">
         <v>3</v>
@@ -14700,77 +14706,33 @@
         <v>49</v>
       </c>
       <c r="H220" t="s">
-        <v>951</v>
+        <v>1373</v>
       </c>
       <c r="I220" t="s">
-        <v>77</v>
+        <v>1374</v>
       </c>
       <c r="J220" t="s">
-        <v>78</v>
+        <v>1375</v>
       </c>
       <c r="M220" t="s">
-        <v>1369</v>
+        <v>1376</v>
       </c>
       <c r="N220" t="s">
-        <v>1370</v>
+        <v>1377</v>
       </c>
       <c r="S220" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="T220" t="s">
-        <v>1371</v>
+        <v>1378</v>
       </c>
       <c r="U220" t="s">
-        <v>1372</v>
+        <v>118</v>
       </c>
       <c r="W220" t="s">
         <v>955</v>
       </c>
       <c r="X220">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="221" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>1367</v>
-      </c>
-      <c r="B221" t="s">
-        <v>1368</v>
-      </c>
-      <c r="F221" t="s">
-        <v>48</v>
-      </c>
-      <c r="G221" t="s">
-        <v>49</v>
-      </c>
-      <c r="H221" t="s">
-        <v>1373</v>
-      </c>
-      <c r="I221" t="s">
-        <v>1374</v>
-      </c>
-      <c r="J221" t="s">
-        <v>1375</v>
-      </c>
-      <c r="M221" t="s">
-        <v>1376</v>
-      </c>
-      <c r="N221" t="s">
-        <v>1377</v>
-      </c>
-      <c r="S221" t="s">
-        <v>81</v>
-      </c>
-      <c r="T221" t="s">
-        <v>1378</v>
-      </c>
-      <c r="U221" t="s">
-        <v>118</v>
-      </c>
-      <c r="W221" t="s">
-        <v>955</v>
-      </c>
-      <c r="X221">
         <v>3</v>
       </c>
     </row>

--- a/quizzes/peinture-15e.xlsx
+++ b/quizzes/peinture-15e.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2DF62B7-6D6D-42B4-9E5C-A3A78AD1F04F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C19285-8E3C-4FA1-BC34-281BC619664E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2884" uniqueCount="1380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2886" uniqueCount="1390">
   <si>
     <t>Prénom</t>
   </si>
@@ -2530,9 +2530,6 @@
     <t>6,8 cm</t>
   </si>
   <si>
-    <t>8,5 cm</t>
-  </si>
-  <si>
     <t>1452-1458</t>
   </si>
   <si>
@@ -2551,9 +2548,6 @@
     <t>94,5 cm</t>
   </si>
   <si>
-    <t>85,5 cm</t>
-  </si>
-  <si>
     <t>1452-1458 environ</t>
   </si>
   <si>
@@ -2587,9 +2581,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/e/e7/Jean_Fouquet_-_Portrait_of_Guillaume_Jouvenel_des_Ursins_-_Louvre.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>73.2</t>
-  </si>
-  <si>
     <t>Nouans-les-Fontaines</t>
   </si>
   <si>
@@ -4160,6 +4151,45 @@
   </si>
   <si>
     <t>132 cm</t>
+  </si>
+  <si>
+    <t>16,5cm</t>
+  </si>
+  <si>
+    <t>12cm</t>
+  </si>
+  <si>
+    <t>93 cm</t>
+  </si>
+  <si>
+    <t>"Heures d'Etienne Chevalier"</t>
+  </si>
+  <si>
+    <t>93cm</t>
+  </si>
+  <si>
+    <t>146cm</t>
+  </si>
+  <si>
+    <t>73.2cm</t>
+  </si>
+  <si>
+    <t>237cm</t>
+  </si>
+  <si>
+    <t>85cm</t>
+  </si>
+  <si>
+    <t>85,5cm</t>
+  </si>
+  <si>
+    <t>8,5cm</t>
+  </si>
+  <si>
+    <t>86cm</t>
+  </si>
+  <si>
+    <t>71cm</t>
   </si>
 </sst>
 </file>
@@ -4175,12 +4205,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -4195,8 +4231,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4499,7 +4548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X221"/>
+  <dimension ref="A1:X220"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -4515,15 +4564,15 @@
     <col min="11" max="11" width="11.42578125" customWidth="1"/>
     <col min="12" max="12" width="12.7109375" customWidth="1"/>
     <col min="13" max="13" width="25.140625" customWidth="1"/>
-    <col min="14" max="14" width="16.28515625" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="16.28515625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" style="2" customWidth="1"/>
     <col min="16" max="16" width="17.140625" customWidth="1"/>
     <col min="17" max="17" width="11.85546875" customWidth="1"/>
-    <col min="18" max="18" width="7.5703125" customWidth="1"/>
-    <col min="19" max="19" width="9.140625" customWidth="1"/>
-    <col min="20" max="20" width="7.140625" customWidth="1"/>
-    <col min="21" max="21" width="7" customWidth="1"/>
-    <col min="22" max="22" width="3.28515625" customWidth="1"/>
+    <col min="18" max="18" width="14.140625" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="12.5703125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="7" style="1" customWidth="1"/>
+    <col min="22" max="22" width="3.28515625" style="1" customWidth="1"/>
     <col min="23" max="23" width="4.7109375" customWidth="1"/>
     <col min="24" max="24" width="5.5703125" customWidth="1"/>
   </cols>
@@ -4568,10 +4617,10 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P1" t="s">
@@ -4583,16 +4632,16 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="W1" t="s">
@@ -4627,16 +4676,16 @@
       <c r="M2" t="s">
         <v>31</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" s="1" t="s">
         <v>35</v>
       </c>
       <c r="W2" t="s">
@@ -4671,19 +4720,19 @@
       <c r="M3" t="s">
         <v>40</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="2" t="s">
         <v>41</v>
       </c>
       <c r="Q3" t="s">
         <v>42</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="T3" t="s">
+      <c r="T3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="U3" t="s">
+      <c r="U3" s="1" t="s">
         <v>45</v>
       </c>
       <c r="W3" t="s">
@@ -4718,16 +4767,16 @@
       <c r="M4" t="s">
         <v>52</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="S4" t="s">
+      <c r="S4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="1">
         <v>162</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="1">
         <v>211</v>
       </c>
       <c r="W4" t="s">
@@ -4762,16 +4811,16 @@
       <c r="M5" t="s">
         <v>56</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="S5" t="s">
+      <c r="S5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="1">
         <v>162</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="1">
         <v>211</v>
       </c>
       <c r="W5" t="s">
@@ -4806,10 +4855,10 @@
       <c r="M6" t="s">
         <v>66</v>
       </c>
-      <c r="N6" t="s">
+      <c r="N6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="S6" t="s">
+      <c r="S6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="W6" t="s">
@@ -4844,16 +4893,16 @@
       <c r="M7" t="s">
         <v>71</v>
       </c>
-      <c r="N7" t="s">
+      <c r="N7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="S7" t="s">
+      <c r="S7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="T7" t="s">
+      <c r="T7" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="U7" t="s">
+      <c r="U7" s="1" t="s">
         <v>75</v>
       </c>
       <c r="W7" t="s">
@@ -4888,10 +4937,10 @@
       <c r="M8" t="s">
         <v>79</v>
       </c>
-      <c r="N8" t="s">
+      <c r="N8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="S8" t="s">
+      <c r="S8" s="2" t="s">
         <v>81</v>
       </c>
       <c r="W8" t="s">
@@ -4926,16 +4975,16 @@
       <c r="M9" t="s">
         <v>83</v>
       </c>
-      <c r="N9" t="s">
+      <c r="N9" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="S9" t="s">
+      <c r="S9" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="T9" t="s">
+      <c r="T9" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="U9" t="s">
+      <c r="U9" s="1" t="s">
         <v>87</v>
       </c>
       <c r="W9" t="s">
@@ -4970,10 +5019,10 @@
       <c r="M10" t="s">
         <v>90</v>
       </c>
-      <c r="N10" t="s">
+      <c r="N10" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="S10" t="s">
+      <c r="S10" s="2" t="s">
         <v>92</v>
       </c>
       <c r="W10" t="s">
@@ -5008,19 +5057,19 @@
       <c r="M11" t="s">
         <v>97</v>
       </c>
-      <c r="N11" t="s">
+      <c r="N11" s="2" t="s">
         <v>98</v>
       </c>
       <c r="Q11" t="s">
         <v>99</v>
       </c>
-      <c r="S11" t="s">
+      <c r="S11" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T11" t="s">
+      <c r="T11" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="U11" t="s">
+      <c r="U11" s="1" t="s">
         <v>102</v>
       </c>
       <c r="W11" t="s">
@@ -5055,19 +5104,19 @@
       <c r="M12" t="s">
         <v>106</v>
       </c>
-      <c r="N12" t="s">
+      <c r="N12" s="2" t="s">
         <v>107</v>
       </c>
       <c r="Q12" t="s">
         <v>108</v>
       </c>
-      <c r="S12" t="s">
+      <c r="S12" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T12" t="s">
+      <c r="T12" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="U12" t="s">
+      <c r="U12" s="1" t="s">
         <v>111</v>
       </c>
       <c r="W12" t="s">
@@ -5102,19 +5151,19 @@
       <c r="M13" t="s">
         <v>114</v>
       </c>
-      <c r="N13" t="s">
+      <c r="N13" s="2" t="s">
         <v>115</v>
       </c>
       <c r="Q13" t="s">
         <v>116</v>
       </c>
-      <c r="S13" t="s">
+      <c r="S13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="T13" t="s">
+      <c r="T13" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="U13" t="s">
+      <c r="U13" s="1" t="s">
         <v>118</v>
       </c>
       <c r="W13" t="s">
@@ -5149,19 +5198,19 @@
       <c r="M14" t="s">
         <v>120</v>
       </c>
-      <c r="N14" t="s">
+      <c r="N14" s="2" t="s">
         <v>121</v>
       </c>
       <c r="Q14" t="s">
         <v>122</v>
       </c>
-      <c r="S14" t="s">
+      <c r="S14" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="T14" t="s">
+      <c r="T14" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="U14" t="s">
+      <c r="U14" s="1" t="s">
         <v>125</v>
       </c>
       <c r="W14" t="s">
@@ -5196,19 +5245,19 @@
       <c r="M15" t="s">
         <v>128</v>
       </c>
-      <c r="N15" t="s">
+      <c r="N15" s="2" t="s">
         <v>129</v>
       </c>
       <c r="Q15" t="s">
         <v>130</v>
       </c>
-      <c r="S15" t="s">
+      <c r="S15" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="T15" t="s">
+      <c r="T15" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="U15" t="s">
+      <c r="U15" s="1" t="s">
         <v>132</v>
       </c>
       <c r="W15" t="s">
@@ -5243,22 +5292,22 @@
       <c r="M16" t="s">
         <v>140</v>
       </c>
-      <c r="N16" t="s">
+      <c r="N16" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="O16" t="s">
+      <c r="O16" s="2" t="s">
         <v>142</v>
       </c>
       <c r="Q16" t="s">
         <v>143</v>
       </c>
-      <c r="S16" t="s">
+      <c r="S16" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="1">
         <v>242</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="1">
         <v>130</v>
       </c>
       <c r="W16" t="s">
@@ -5293,19 +5342,19 @@
       <c r="M17" t="s">
         <v>148</v>
       </c>
-      <c r="N17" t="s">
+      <c r="N17" s="2" t="s">
         <v>149</v>
       </c>
       <c r="Q17" t="s">
         <v>150</v>
       </c>
-      <c r="S17" t="s">
+      <c r="S17" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="1">
         <v>175</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="1">
         <v>189</v>
       </c>
       <c r="W17" t="s">
@@ -5340,19 +5389,19 @@
       <c r="M18" t="s">
         <v>156</v>
       </c>
-      <c r="N18" t="s">
+      <c r="N18" s="2" t="s">
         <v>157</v>
       </c>
       <c r="Q18" t="s">
         <v>158</v>
       </c>
-      <c r="S18" t="s">
+      <c r="S18" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="T18" t="s">
+      <c r="T18" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="U18" t="s">
+      <c r="U18" s="1" t="s">
         <v>161</v>
       </c>
       <c r="W18" t="s">
@@ -5387,19 +5436,19 @@
       <c r="M19" t="s">
         <v>164</v>
       </c>
-      <c r="N19" t="s">
+      <c r="N19" s="2" t="s">
         <v>165</v>
       </c>
       <c r="Q19" t="s">
         <v>166</v>
       </c>
-      <c r="S19" t="s">
+      <c r="S19" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="T19" t="s">
+      <c r="T19" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="U19" t="s">
+      <c r="U19" s="1" t="s">
         <v>168</v>
       </c>
       <c r="W19" t="s">
@@ -5434,10 +5483,10 @@
       <c r="M20" t="s">
         <v>169</v>
       </c>
-      <c r="N20" t="s">
+      <c r="N20" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="S20" t="s">
+      <c r="S20" s="2" t="s">
         <v>81</v>
       </c>
       <c r="W20" t="s">
@@ -5472,19 +5521,19 @@
       <c r="M21" t="s">
         <v>174</v>
       </c>
-      <c r="N21" t="s">
+      <c r="N21" s="2" t="s">
         <v>175</v>
       </c>
       <c r="Q21" t="s">
         <v>176</v>
       </c>
-      <c r="S21" t="s">
+      <c r="S21" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="T21" t="s">
+      <c r="T21" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="U21" t="s">
+      <c r="U21" s="1" t="s">
         <v>179</v>
       </c>
       <c r="W21" t="s">
@@ -5519,19 +5568,19 @@
       <c r="M22" t="s">
         <v>183</v>
       </c>
-      <c r="N22" t="s">
+      <c r="N22" s="2" t="s">
         <v>184</v>
       </c>
       <c r="Q22" t="s">
         <v>185</v>
       </c>
-      <c r="S22" t="s">
+      <c r="S22" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="T22" t="s">
+      <c r="T22" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="U22" t="s">
+      <c r="U22" s="1" t="s">
         <v>186</v>
       </c>
       <c r="W22" t="s">
@@ -5566,22 +5615,22 @@
       <c r="M23" t="s">
         <v>192</v>
       </c>
-      <c r="N23" t="s">
+      <c r="N23" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="O23" t="s">
+      <c r="O23" s="2" t="s">
         <v>194</v>
       </c>
       <c r="Q23" t="s">
         <v>195</v>
       </c>
-      <c r="S23" t="s">
+      <c r="S23" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T23">
+      <c r="T23" s="1">
         <v>167</v>
       </c>
-      <c r="U23">
+      <c r="U23" s="1">
         <v>87</v>
       </c>
       <c r="W23" t="s">
@@ -5616,19 +5665,19 @@
       <c r="M24" t="s">
         <v>197</v>
       </c>
-      <c r="N24" t="s">
+      <c r="N24" s="2" t="s">
         <v>198</v>
       </c>
       <c r="Q24" t="s">
         <v>199</v>
       </c>
-      <c r="S24" t="s">
+      <c r="S24" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T24">
+      <c r="T24" s="1">
         <v>111</v>
       </c>
-      <c r="U24">
+      <c r="U24" s="1">
         <v>134</v>
       </c>
       <c r="W24" t="s">
@@ -5663,19 +5712,19 @@
       <c r="M25" t="s">
         <v>201</v>
       </c>
-      <c r="N25" t="s">
+      <c r="N25" s="2" t="s">
         <v>202</v>
       </c>
       <c r="Q25" t="s">
         <v>203</v>
       </c>
-      <c r="S25" t="s">
+      <c r="S25" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="T25">
+      <c r="T25" s="1">
         <v>203</v>
       </c>
-      <c r="U25">
+      <c r="U25" s="1">
         <v>314</v>
       </c>
       <c r="W25" t="s">
@@ -5710,19 +5759,19 @@
       <c r="M26" t="s">
         <v>206</v>
       </c>
-      <c r="N26" t="s">
+      <c r="N26" s="2" t="s">
         <v>207</v>
       </c>
       <c r="Q26" t="s">
         <v>208</v>
       </c>
-      <c r="S26" t="s">
+      <c r="S26" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="T26">
+      <c r="T26" s="1">
         <v>118</v>
       </c>
-      <c r="U26">
+      <c r="U26" s="1">
         <v>118</v>
       </c>
       <c r="W26" t="s">
@@ -5760,22 +5809,22 @@
       <c r="M27" t="s">
         <v>213</v>
       </c>
-      <c r="N27" t="s">
+      <c r="N27" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="O27" t="s">
+      <c r="O27" s="2" t="s">
         <v>215</v>
       </c>
       <c r="Q27" t="s">
         <v>216</v>
       </c>
-      <c r="S27" t="s">
+      <c r="S27" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="T27">
+      <c r="T27" s="1">
         <v>348</v>
       </c>
-      <c r="U27">
+      <c r="U27" s="1">
         <v>558</v>
       </c>
       <c r="W27" t="s">
@@ -5810,19 +5859,19 @@
       <c r="M28" t="s">
         <v>219</v>
       </c>
-      <c r="N28" t="s">
+      <c r="N28" s="2" t="s">
         <v>220</v>
       </c>
       <c r="Q28" t="s">
         <v>221</v>
       </c>
-      <c r="S28" t="s">
+      <c r="S28" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="T28">
+      <c r="T28" s="1">
         <v>69</v>
       </c>
-      <c r="U28">
+      <c r="U28" s="1">
         <v>173</v>
       </c>
       <c r="W28" t="s">
@@ -5857,16 +5906,16 @@
       <c r="M29" t="s">
         <v>224</v>
       </c>
-      <c r="N29" t="s">
+      <c r="N29" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="S29" t="s">
+      <c r="S29" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="T29" t="s">
+      <c r="T29" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="U29" t="s">
+      <c r="U29" s="1" t="s">
         <v>227</v>
       </c>
       <c r="W29" t="s">
@@ -5901,19 +5950,19 @@
       <c r="M30" t="s">
         <v>229</v>
       </c>
-      <c r="N30" t="s">
+      <c r="N30" s="2" t="s">
         <v>230</v>
       </c>
       <c r="Q30" t="s">
         <v>231</v>
       </c>
-      <c r="S30" t="s">
+      <c r="S30" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="T30" t="s">
+      <c r="T30" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="U30" t="s">
+      <c r="U30" s="1" t="s">
         <v>234</v>
       </c>
       <c r="W30" t="s">
@@ -5948,19 +5997,19 @@
       <c r="M31" t="s">
         <v>235</v>
       </c>
-      <c r="N31" t="s">
+      <c r="N31" s="2" t="s">
         <v>236</v>
       </c>
       <c r="Q31" t="s">
         <v>237</v>
       </c>
-      <c r="S31" t="s">
+      <c r="S31" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="T31" t="s">
+      <c r="T31" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="U31" t="s">
+      <c r="U31" s="1" t="s">
         <v>238</v>
       </c>
       <c r="W31" t="s">
@@ -5995,19 +6044,19 @@
       <c r="M32" t="s">
         <v>240</v>
       </c>
-      <c r="N32" t="s">
+      <c r="N32" s="2" t="s">
         <v>241</v>
       </c>
       <c r="Q32" t="s">
         <v>242</v>
       </c>
-      <c r="S32" t="s">
+      <c r="S32" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T32">
+      <c r="T32" s="1">
         <v>150</v>
       </c>
-      <c r="U32">
+      <c r="U32" s="1">
         <v>156</v>
       </c>
       <c r="W32" t="s">
@@ -6042,19 +6091,19 @@
       <c r="M33" t="s">
         <v>244</v>
       </c>
-      <c r="N33" t="s">
+      <c r="N33" s="2" t="s">
         <v>245</v>
       </c>
       <c r="Q33" t="s">
         <v>246</v>
       </c>
-      <c r="S33" t="s">
+      <c r="S33" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T33">
+      <c r="T33" s="1">
         <v>62</v>
       </c>
-      <c r="U33">
+      <c r="U33" s="1">
         <v>91</v>
       </c>
       <c r="W33" t="s">
@@ -6092,19 +6141,19 @@
       <c r="M34" t="s">
         <v>253</v>
       </c>
-      <c r="N34" t="s">
+      <c r="N34" s="2" t="s">
         <v>254</v>
       </c>
       <c r="Q34" t="s">
         <v>255</v>
       </c>
-      <c r="S34" t="s">
+      <c r="S34" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="T34">
+      <c r="T34" s="1">
         <v>116</v>
       </c>
-      <c r="U34">
+      <c r="U34" s="1">
         <v>138</v>
       </c>
       <c r="W34" t="s">
@@ -6139,19 +6188,19 @@
       <c r="M35" t="s">
         <v>260</v>
       </c>
-      <c r="N35" t="s">
+      <c r="N35" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="O35" t="s">
+      <c r="O35" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="S35" t="s">
+      <c r="S35" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="T35">
+      <c r="T35" s="1">
         <v>24.1</v>
       </c>
-      <c r="U35">
+      <c r="U35" s="1">
         <v>17</v>
       </c>
       <c r="W35" t="s">
@@ -6189,19 +6238,19 @@
       <c r="M36" t="s">
         <v>271</v>
       </c>
-      <c r="N36" t="s">
+      <c r="N36" s="2" t="s">
         <v>272</v>
       </c>
       <c r="Q36" t="s">
         <v>273</v>
       </c>
-      <c r="S36" t="s">
+      <c r="S36" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="T36">
+      <c r="T36" s="1">
         <v>185</v>
       </c>
-      <c r="U36">
+      <c r="U36" s="1">
         <v>294</v>
       </c>
       <c r="W36" t="s">
@@ -6236,22 +6285,22 @@
       <c r="M37" t="s">
         <v>277</v>
       </c>
-      <c r="N37" t="s">
+      <c r="N37" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="O37" t="s">
+      <c r="O37" s="2" t="s">
         <v>279</v>
       </c>
       <c r="Q37" t="s">
         <v>280</v>
       </c>
-      <c r="S37" t="s">
+      <c r="S37" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="T37">
+      <c r="T37" s="1">
         <v>324</v>
       </c>
-      <c r="U37">
+      <c r="U37" s="1">
         <v>364</v>
       </c>
       <c r="W37" t="s">
@@ -6286,22 +6335,22 @@
       <c r="M38" t="s">
         <v>287</v>
       </c>
-      <c r="N38" t="s">
+      <c r="N38" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="O38" t="s">
+      <c r="O38" s="2" t="s">
         <v>289</v>
       </c>
       <c r="Q38" t="s">
         <v>290</v>
       </c>
-      <c r="S38" t="s">
+      <c r="S38" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="T38" t="s">
+      <c r="T38" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="U38" t="s">
+      <c r="U38" s="1" t="s">
         <v>292</v>
       </c>
       <c r="W38" t="s">
@@ -6336,19 +6385,19 @@
       <c r="M39" t="s">
         <v>294</v>
       </c>
-      <c r="N39" t="s">
+      <c r="N39" s="2" t="s">
         <v>295</v>
       </c>
       <c r="Q39" t="s">
         <v>296</v>
       </c>
-      <c r="S39" t="s">
+      <c r="S39" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="T39" t="s">
+      <c r="T39" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="U39" t="s">
+      <c r="U39" s="1" t="s">
         <v>298</v>
       </c>
       <c r="W39" t="s">
@@ -6383,19 +6432,19 @@
       <c r="M40" t="s">
         <v>300</v>
       </c>
-      <c r="N40" t="s">
+      <c r="N40" s="2" t="s">
         <v>301</v>
       </c>
       <c r="Q40" t="s">
         <v>302</v>
       </c>
-      <c r="S40" t="s">
+      <c r="S40" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="T40" t="s">
+      <c r="T40" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="U40" t="s">
+      <c r="U40" s="1" t="s">
         <v>304</v>
       </c>
       <c r="W40" t="s">
@@ -6430,22 +6479,22 @@
       <c r="M41" t="s">
         <v>306</v>
       </c>
-      <c r="N41" t="s">
+      <c r="N41" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="O41" t="s">
+      <c r="O41" s="2" t="s">
         <v>289</v>
       </c>
       <c r="Q41" t="s">
         <v>308</v>
       </c>
-      <c r="S41" t="s">
+      <c r="S41" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="T41" t="s">
+      <c r="T41" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="U41" t="s">
+      <c r="U41" s="1" t="s">
         <v>310</v>
       </c>
       <c r="W41" t="s">
@@ -6480,22 +6529,22 @@
       <c r="M42" t="s">
         <v>311</v>
       </c>
-      <c r="N42" t="s">
+      <c r="N42" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="O42" t="s">
+      <c r="O42" s="2" t="s">
         <v>289</v>
       </c>
       <c r="Q42" t="s">
         <v>313</v>
       </c>
-      <c r="S42" t="s">
+      <c r="S42" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="T42" t="s">
+      <c r="T42" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="U42" t="s">
+      <c r="U42" s="1" t="s">
         <v>315</v>
       </c>
       <c r="W42" t="s">
@@ -6530,22 +6579,22 @@
       <c r="M43" t="s">
         <v>317</v>
       </c>
-      <c r="N43" t="s">
+      <c r="N43" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="O43" t="s">
+      <c r="O43" s="2" t="s">
         <v>289</v>
       </c>
       <c r="Q43" t="s">
         <v>319</v>
       </c>
-      <c r="S43" t="s">
+      <c r="S43" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="T43" t="s">
+      <c r="T43" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="U43" t="s">
+      <c r="U43" s="1" t="s">
         <v>321</v>
       </c>
       <c r="W43" t="s">
@@ -6580,22 +6629,22 @@
       <c r="M44" t="s">
         <v>323</v>
       </c>
-      <c r="N44" t="s">
+      <c r="N44" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="O44" t="s">
+      <c r="O44" s="2" t="s">
         <v>289</v>
       </c>
       <c r="Q44" t="s">
         <v>325</v>
       </c>
-      <c r="S44" t="s">
+      <c r="S44" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="T44" t="s">
+      <c r="T44" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="U44" t="s">
+      <c r="U44" s="1" t="s">
         <v>326</v>
       </c>
       <c r="W44" t="s">
@@ -6630,22 +6679,22 @@
       <c r="M45" t="s">
         <v>327</v>
       </c>
-      <c r="N45" t="s">
+      <c r="N45" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="O45" t="s">
+      <c r="O45" s="2" t="s">
         <v>289</v>
       </c>
       <c r="Q45" t="s">
         <v>329</v>
       </c>
-      <c r="S45" t="s">
+      <c r="S45" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="T45" t="s">
+      <c r="T45" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="U45" t="s">
+      <c r="U45" s="1" t="s">
         <v>331</v>
       </c>
       <c r="W45" t="s">
@@ -6680,22 +6729,22 @@
       <c r="M46" t="s">
         <v>333</v>
       </c>
-      <c r="N46" t="s">
+      <c r="N46" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="O46" t="s">
+      <c r="O46" s="2" t="s">
         <v>335</v>
       </c>
       <c r="Q46" t="s">
         <v>336</v>
       </c>
-      <c r="S46" t="s">
+      <c r="S46" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="T46" t="s">
+      <c r="T46" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="U46" t="s">
+      <c r="U46" s="1" t="s">
         <v>338</v>
       </c>
       <c r="W46" t="s">
@@ -6730,22 +6779,22 @@
       <c r="M47" t="s">
         <v>340</v>
       </c>
-      <c r="N47" t="s">
+      <c r="N47" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="O47" t="s">
+      <c r="O47" s="2" t="s">
         <v>289</v>
       </c>
       <c r="Q47" t="s">
         <v>342</v>
       </c>
-      <c r="S47" t="s">
+      <c r="S47" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="T47" t="s">
+      <c r="T47" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="U47" t="s">
+      <c r="U47" s="1" t="s">
         <v>344</v>
       </c>
       <c r="W47" t="s">
@@ -6780,10 +6829,10 @@
       <c r="M48" t="s">
         <v>352</v>
       </c>
-      <c r="N48" t="s">
+      <c r="N48" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="S48" t="s">
+      <c r="S48" s="2" t="s">
         <v>81</v>
       </c>
       <c r="W48" t="s">
@@ -6818,19 +6867,19 @@
       <c r="M49" t="s">
         <v>354</v>
       </c>
-      <c r="N49" t="s">
+      <c r="N49" s="2" t="s">
         <v>355</v>
       </c>
       <c r="Q49" t="s">
         <v>356</v>
       </c>
-      <c r="S49" t="s">
+      <c r="S49" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="T49" t="s">
+      <c r="T49" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="U49" t="s">
+      <c r="U49" s="1" t="s">
         <v>358</v>
       </c>
       <c r="W49" t="s">
@@ -6865,16 +6914,16 @@
       <c r="M50" t="s">
         <v>363</v>
       </c>
-      <c r="N50" t="s">
+      <c r="N50" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="S50" t="s">
+      <c r="S50" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="T50" t="s">
+      <c r="T50" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="U50" t="s">
+      <c r="U50" s="1" t="s">
         <v>367</v>
       </c>
       <c r="W50" t="s">
@@ -6909,19 +6958,19 @@
       <c r="M51" t="s">
         <v>371</v>
       </c>
-      <c r="N51" t="s">
+      <c r="N51" s="2" t="s">
         <v>372</v>
       </c>
       <c r="Q51" t="s">
         <v>373</v>
       </c>
-      <c r="S51" t="s">
+      <c r="S51" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="T51" t="s">
+      <c r="T51" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="U51">
+      <c r="U51" s="1">
         <v>21</v>
       </c>
       <c r="W51" t="s">
@@ -6956,19 +7005,19 @@
       <c r="M52" t="s">
         <v>378</v>
       </c>
-      <c r="N52" t="s">
+      <c r="N52" s="2" t="s">
         <v>379</v>
       </c>
       <c r="Q52" t="s">
         <v>42</v>
       </c>
-      <c r="S52" t="s">
+      <c r="S52" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="T52" t="s">
+      <c r="T52" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="U52" t="s">
+      <c r="U52" s="1" t="s">
         <v>382</v>
       </c>
       <c r="W52" t="s">
@@ -7003,19 +7052,19 @@
       <c r="M53" t="s">
         <v>383</v>
       </c>
-      <c r="N53" t="s">
+      <c r="N53" s="2" t="s">
         <v>384</v>
       </c>
       <c r="Q53" t="s">
         <v>385</v>
       </c>
-      <c r="S53" t="s">
+      <c r="S53" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="T53">
+      <c r="T53" s="1">
         <v>207</v>
       </c>
-      <c r="U53" t="s">
+      <c r="U53" s="1" t="s">
         <v>387</v>
       </c>
       <c r="W53" t="s">
@@ -7050,19 +7099,19 @@
       <c r="M54" t="s">
         <v>391</v>
       </c>
-      <c r="N54" t="s">
+      <c r="N54" s="2" t="s">
         <v>392</v>
       </c>
       <c r="Q54" t="s">
         <v>393</v>
       </c>
-      <c r="S54" t="s">
+      <c r="S54" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="T54">
+      <c r="T54" s="1">
         <v>25</v>
       </c>
-      <c r="U54" t="s">
+      <c r="U54" s="1" t="s">
         <v>395</v>
       </c>
       <c r="W54" t="s">
@@ -7097,16 +7146,16 @@
       <c r="M55" t="s">
         <v>399</v>
       </c>
-      <c r="N55" t="s">
+      <c r="N55" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="S55" t="s">
+      <c r="S55" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="T55" t="s">
+      <c r="T55" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="U55" t="s">
+      <c r="U55" s="1" t="s">
         <v>403</v>
       </c>
       <c r="W55" t="s">
@@ -7141,16 +7190,16 @@
       <c r="M56" t="s">
         <v>408</v>
       </c>
-      <c r="N56" t="s">
+      <c r="N56" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="S56" t="s">
+      <c r="S56" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="T56" t="s">
+      <c r="T56" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="U56" t="s">
+      <c r="U56" s="1" t="s">
         <v>411</v>
       </c>
       <c r="W56" t="s">
@@ -7185,19 +7234,19 @@
       <c r="M57" t="s">
         <v>413</v>
       </c>
-      <c r="N57" t="s">
+      <c r="N57" s="2" t="s">
         <v>414</v>
       </c>
       <c r="Q57" t="s">
         <v>415</v>
       </c>
-      <c r="S57" t="s">
+      <c r="S57" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="T57" t="s">
+      <c r="T57" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="U57" t="s">
+      <c r="U57" s="1" t="s">
         <v>417</v>
       </c>
       <c r="W57" t="s">
@@ -7232,19 +7281,19 @@
       <c r="M58" t="s">
         <v>425</v>
       </c>
-      <c r="N58" t="s">
+      <c r="N58" s="2" t="s">
         <v>426</v>
       </c>
       <c r="Q58" t="s">
         <v>427</v>
       </c>
-      <c r="S58" t="s">
+      <c r="S58" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="T58" t="s">
+      <c r="T58" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="U58" t="s">
+      <c r="U58" s="1" t="s">
         <v>430</v>
       </c>
       <c r="W58" t="s">
@@ -7282,19 +7331,19 @@
       <c r="M59" t="s">
         <v>435</v>
       </c>
-      <c r="N59" t="s">
+      <c r="N59" s="2" t="s">
         <v>436</v>
       </c>
       <c r="Q59" t="s">
         <v>437</v>
       </c>
-      <c r="S59" t="s">
+      <c r="S59" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="T59">
+      <c r="T59" s="1">
         <v>800</v>
       </c>
-      <c r="U59" t="s">
+      <c r="U59" s="1" t="s">
         <v>439</v>
       </c>
       <c r="W59" t="s">
@@ -7329,19 +7378,19 @@
       <c r="M60" t="s">
         <v>443</v>
       </c>
-      <c r="N60" t="s">
+      <c r="N60" s="2" t="s">
         <v>444</v>
       </c>
       <c r="Q60" t="s">
         <v>445</v>
       </c>
-      <c r="S60" t="s">
+      <c r="S60" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="T60" t="s">
+      <c r="T60" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="U60">
+      <c r="U60" s="1">
         <v>30</v>
       </c>
       <c r="W60" t="s">
@@ -7376,19 +7425,19 @@
       <c r="M61" t="s">
         <v>450</v>
       </c>
-      <c r="N61" t="s">
+      <c r="N61" s="2" t="s">
         <v>451</v>
       </c>
       <c r="Q61" t="s">
         <v>452</v>
       </c>
-      <c r="S61" t="s">
+      <c r="S61" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="T61">
+      <c r="T61" s="1">
         <v>45</v>
       </c>
-      <c r="U61" t="s">
+      <c r="U61" s="1" t="s">
         <v>454</v>
       </c>
       <c r="W61" t="s">
@@ -7423,16 +7472,16 @@
       <c r="M62" t="s">
         <v>462</v>
       </c>
-      <c r="N62" t="s">
+      <c r="N62" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="S62" t="s">
+      <c r="S62" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="T62" t="s">
+      <c r="T62" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="U62" t="s">
+      <c r="U62" s="1" t="s">
         <v>465</v>
       </c>
       <c r="W62" t="s">
@@ -7467,16 +7516,16 @@
       <c r="M63" t="s">
         <v>469</v>
       </c>
-      <c r="N63" t="s">
+      <c r="N63" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="S63" t="s">
+      <c r="S63" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="T63" t="s">
+      <c r="T63" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="U63" t="s">
+      <c r="U63" s="1" t="s">
         <v>472</v>
       </c>
       <c r="W63" t="s">
@@ -7511,19 +7560,19 @@
       <c r="M64" t="s">
         <v>474</v>
       </c>
-      <c r="N64" t="s">
+      <c r="N64" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="O64" t="s">
+      <c r="O64" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="S64" t="s">
+      <c r="S64" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="T64" t="s">
+      <c r="T64" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="U64" t="s">
+      <c r="U64" s="1" t="s">
         <v>478</v>
       </c>
       <c r="W64" t="s">
@@ -7558,19 +7607,19 @@
       <c r="M65" t="s">
         <v>483</v>
       </c>
-      <c r="N65" t="s">
+      <c r="N65" s="2" t="s">
         <v>484</v>
       </c>
       <c r="Q65" t="s">
         <v>485</v>
       </c>
-      <c r="S65" t="s">
+      <c r="S65" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="T65" t="s">
+      <c r="T65" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="U65" t="s">
+      <c r="U65" s="1" t="s">
         <v>488</v>
       </c>
       <c r="W65" t="s">
@@ -7605,19 +7654,19 @@
       <c r="M66" t="s">
         <v>492</v>
       </c>
-      <c r="N66" t="s">
+      <c r="N66" s="2" t="s">
         <v>493</v>
       </c>
       <c r="Q66" t="s">
         <v>494</v>
       </c>
-      <c r="S66" t="s">
+      <c r="S66" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="T66" t="s">
+      <c r="T66" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="U66" t="s">
+      <c r="U66" s="1" t="s">
         <v>497</v>
       </c>
       <c r="W66" t="s">
@@ -7652,19 +7701,19 @@
       <c r="M67" t="s">
         <v>501</v>
       </c>
-      <c r="N67" t="s">
+      <c r="N67" s="2" t="s">
         <v>502</v>
       </c>
       <c r="Q67" t="s">
         <v>503</v>
       </c>
-      <c r="S67" t="s">
+      <c r="S67" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="T67" t="s">
+      <c r="T67" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="U67" t="s">
+      <c r="U67" s="1" t="s">
         <v>506</v>
       </c>
       <c r="W67" t="s">
@@ -7702,19 +7751,19 @@
       <c r="M68" t="s">
         <v>510</v>
       </c>
-      <c r="N68" t="s">
+      <c r="N68" s="2" t="s">
         <v>511</v>
       </c>
       <c r="Q68" t="s">
         <v>512</v>
       </c>
-      <c r="S68" t="s">
+      <c r="S68" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="T68" t="s">
+      <c r="T68" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="U68" t="s">
+      <c r="U68" s="1" t="s">
         <v>515</v>
       </c>
       <c r="W68" t="s">
@@ -7749,19 +7798,19 @@
       <c r="M69" t="s">
         <v>197</v>
       </c>
-      <c r="N69" t="s">
+      <c r="N69" s="2" t="s">
         <v>517</v>
       </c>
       <c r="Q69" t="s">
         <v>199</v>
       </c>
-      <c r="S69" t="s">
+      <c r="S69" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="T69" t="s">
+      <c r="T69" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="U69" t="s">
+      <c r="U69" s="1" t="s">
         <v>519</v>
       </c>
       <c r="W69" t="s">
@@ -7796,19 +7845,19 @@
       <c r="M70" t="s">
         <v>521</v>
       </c>
-      <c r="N70" t="s">
+      <c r="N70" s="2" t="s">
         <v>522</v>
       </c>
       <c r="Q70" t="s">
         <v>523</v>
       </c>
-      <c r="S70" t="s">
+      <c r="S70" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="T70" t="s">
+      <c r="T70" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="U70" t="s">
+      <c r="U70" s="1" t="s">
         <v>526</v>
       </c>
       <c r="W70" t="s">
@@ -7843,19 +7892,19 @@
       <c r="M71" t="s">
         <v>528</v>
       </c>
-      <c r="N71" t="s">
+      <c r="N71" s="2" t="s">
         <v>529</v>
       </c>
       <c r="Q71" t="s">
         <v>530</v>
       </c>
-      <c r="S71" t="s">
+      <c r="S71" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="T71" t="s">
+      <c r="T71" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="U71">
+      <c r="U71" s="1">
         <v>32</v>
       </c>
       <c r="W71" t="s">
@@ -7890,19 +7939,19 @@
       <c r="M72" t="s">
         <v>536</v>
       </c>
-      <c r="N72" t="s">
+      <c r="N72" s="2" t="s">
         <v>537</v>
       </c>
       <c r="Q72" t="s">
         <v>538</v>
       </c>
-      <c r="S72" t="s">
+      <c r="S72" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="T72" t="s">
+      <c r="T72" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="U72" t="s">
+      <c r="U72" s="1" t="s">
         <v>366</v>
       </c>
       <c r="W72" t="s">
@@ -7937,19 +7986,19 @@
       <c r="M73" t="s">
         <v>542</v>
       </c>
-      <c r="N73" t="s">
+      <c r="N73" s="2" t="s">
         <v>543</v>
       </c>
       <c r="Q73" t="s">
         <v>542</v>
       </c>
-      <c r="S73" t="s">
+      <c r="S73" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="T73" t="s">
+      <c r="T73" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="U73" t="s">
+      <c r="U73" s="1" t="s">
         <v>545</v>
       </c>
       <c r="W73" t="s">
@@ -7987,19 +8036,19 @@
       <c r="M74" t="s">
         <v>549</v>
       </c>
-      <c r="N74" t="s">
+      <c r="N74" s="2" t="s">
         <v>550</v>
       </c>
       <c r="Q74" t="s">
         <v>551</v>
       </c>
-      <c r="S74" t="s">
+      <c r="S74" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="T74" t="s">
+      <c r="T74" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="U74" t="s">
+      <c r="U74" s="1" t="s">
         <v>554</v>
       </c>
       <c r="W74" t="s">
@@ -8037,19 +8086,19 @@
       <c r="M75" t="s">
         <v>549</v>
       </c>
-      <c r="N75" t="s">
+      <c r="N75" s="2" t="s">
         <v>561</v>
       </c>
       <c r="Q75" t="s">
         <v>562</v>
       </c>
-      <c r="S75" t="s">
+      <c r="S75" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="T75">
+      <c r="T75" s="1">
         <v>453</v>
       </c>
-      <c r="U75">
+      <c r="U75" s="1">
         <v>975</v>
       </c>
       <c r="W75" t="s">
@@ -8087,22 +8136,22 @@
       <c r="M76" t="s">
         <v>565</v>
       </c>
-      <c r="N76" t="s">
+      <c r="N76" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="O76" t="s">
+      <c r="O76" s="2" t="s">
         <v>567</v>
       </c>
       <c r="Q76" t="s">
         <v>568</v>
       </c>
-      <c r="S76" t="s">
+      <c r="S76" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="T76">
+      <c r="T76" s="1">
         <v>833</v>
       </c>
-      <c r="U76">
+      <c r="U76" s="1">
         <v>512</v>
       </c>
       <c r="W76" t="s">
@@ -8137,13 +8186,13 @@
       <c r="M77" t="s">
         <v>577</v>
       </c>
-      <c r="N77" t="s">
+      <c r="N77" s="2" t="s">
         <v>578</v>
       </c>
       <c r="Q77" t="s">
         <v>579</v>
       </c>
-      <c r="S77" t="s">
+      <c r="S77" s="2" t="s">
         <v>217</v>
       </c>
       <c r="W77" t="s">
@@ -8178,16 +8227,16 @@
       <c r="M78" t="s">
         <v>583</v>
       </c>
-      <c r="N78" t="s">
+      <c r="N78" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="S78" t="s">
+      <c r="S78" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="T78" t="s">
+      <c r="T78" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="U78" t="s">
+      <c r="U78" s="1" t="s">
         <v>586</v>
       </c>
       <c r="W78" t="s">
@@ -8222,19 +8271,19 @@
       <c r="M79" t="s">
         <v>589</v>
       </c>
-      <c r="N79" t="s">
+      <c r="N79" s="2" t="s">
         <v>590</v>
       </c>
       <c r="Q79" t="s">
         <v>591</v>
       </c>
-      <c r="S79" t="s">
+      <c r="S79" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="T79" t="s">
+      <c r="T79" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="U79">
+      <c r="U79" s="1">
         <v>66</v>
       </c>
       <c r="W79" t="s">
@@ -8269,19 +8318,19 @@
       <c r="M80" t="s">
         <v>595</v>
       </c>
-      <c r="N80" t="s">
+      <c r="N80" s="2" t="s">
         <v>596</v>
       </c>
       <c r="Q80" t="s">
         <v>597</v>
       </c>
-      <c r="S80" t="s">
+      <c r="S80" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="T80">
+      <c r="T80" s="1">
         <v>177</v>
       </c>
-      <c r="U80">
+      <c r="U80" s="1">
         <v>151</v>
       </c>
       <c r="W80" t="s">
@@ -8316,19 +8365,19 @@
       <c r="M81" t="s">
         <v>602</v>
       </c>
-      <c r="N81" t="s">
+      <c r="N81" s="2" t="s">
         <v>603</v>
       </c>
       <c r="Q81" t="s">
         <v>597</v>
       </c>
-      <c r="S81" t="s">
+      <c r="S81" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T81" t="s">
+      <c r="T81" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="U81" t="s">
+      <c r="U81" s="1" t="s">
         <v>605</v>
       </c>
       <c r="W81" t="s">
@@ -8366,19 +8415,19 @@
       <c r="M82" t="s">
         <v>610</v>
       </c>
-      <c r="N82" t="s">
+      <c r="N82" s="2" t="s">
         <v>611</v>
       </c>
       <c r="Q82" t="s">
         <v>612</v>
       </c>
-      <c r="S82" t="s">
+      <c r="S82" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="T82" t="s">
+      <c r="T82" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="U82" t="s">
+      <c r="U82" s="1" t="s">
         <v>613</v>
       </c>
       <c r="W82" t="s">
@@ -8416,19 +8465,19 @@
       <c r="M83" t="s">
         <v>618</v>
       </c>
-      <c r="N83" t="s">
+      <c r="N83" s="2" t="s">
         <v>619</v>
       </c>
       <c r="Q83" t="s">
         <v>620</v>
       </c>
-      <c r="S83" t="s">
+      <c r="S83" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T83" t="s">
+      <c r="T83" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="U83" t="s">
+      <c r="U83" s="1" t="s">
         <v>622</v>
       </c>
       <c r="W83" t="s">
@@ -8463,16 +8512,16 @@
       <c r="M84" t="s">
         <v>626</v>
       </c>
-      <c r="N84" t="s">
+      <c r="N84" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="S84" t="s">
+      <c r="S84" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="T84" t="s">
+      <c r="T84" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="U84" t="s">
+      <c r="U84" s="1" t="s">
         <v>629</v>
       </c>
       <c r="W84" t="s">
@@ -8507,16 +8556,16 @@
       <c r="M85" t="s">
         <v>626</v>
       </c>
-      <c r="N85" t="s">
+      <c r="N85" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="S85" t="s">
+      <c r="S85" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="T85" t="s">
+      <c r="T85" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="U85" t="s">
+      <c r="U85" s="1" t="s">
         <v>629</v>
       </c>
       <c r="W85" t="s">
@@ -8551,19 +8600,19 @@
       <c r="M86" t="s">
         <v>631</v>
       </c>
-      <c r="N86" t="s">
+      <c r="N86" s="2" t="s">
         <v>632</v>
       </c>
       <c r="Q86" t="s">
         <v>633</v>
       </c>
-      <c r="S86" t="s">
+      <c r="S86" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="T86" t="s">
+      <c r="T86" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="U86" t="s">
+      <c r="U86" s="1" t="s">
         <v>636</v>
       </c>
       <c r="W86" t="s">
@@ -8598,16 +8647,16 @@
       <c r="M87" t="s">
         <v>638</v>
       </c>
-      <c r="N87" t="s">
+      <c r="N87" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="S87" t="s">
+      <c r="S87" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T87" t="s">
+      <c r="T87" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="U87" t="s">
+      <c r="U87" s="1" t="s">
         <v>640</v>
       </c>
       <c r="W87" t="s">
@@ -8642,16 +8691,16 @@
       <c r="M88" t="s">
         <v>641</v>
       </c>
-      <c r="N88" t="s">
+      <c r="N88" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="S88" t="s">
+      <c r="S88" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="T88" t="s">
+      <c r="T88" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="U88" t="s">
+      <c r="U88" s="1" t="s">
         <v>644</v>
       </c>
       <c r="W88" t="s">
@@ -8686,16 +8735,16 @@
       <c r="M89" t="s">
         <v>638</v>
       </c>
-      <c r="N89" t="s">
+      <c r="N89" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="S89" t="s">
+      <c r="S89" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T89" t="s">
+      <c r="T89" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="U89" t="s">
+      <c r="U89" s="1" t="s">
         <v>640</v>
       </c>
       <c r="W89" t="s">
@@ -8730,16 +8779,16 @@
       <c r="M90" t="s">
         <v>641</v>
       </c>
-      <c r="N90" t="s">
+      <c r="N90" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="S90" t="s">
+      <c r="S90" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="T90" t="s">
+      <c r="T90" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="U90" t="s">
+      <c r="U90" s="1" t="s">
         <v>644</v>
       </c>
       <c r="W90" t="s">
@@ -8774,19 +8823,19 @@
       <c r="M91" t="s">
         <v>646</v>
       </c>
-      <c r="N91" t="s">
+      <c r="N91" s="2" t="s">
         <v>647</v>
       </c>
       <c r="Q91" t="s">
         <v>648</v>
       </c>
-      <c r="S91" t="s">
+      <c r="S91" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="T91" t="s">
+      <c r="T91" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="U91" t="s">
+      <c r="U91" s="1" t="s">
         <v>650</v>
       </c>
       <c r="W91" t="s">
@@ -8827,10 +8876,10 @@
       <c r="M92" t="s">
         <v>658</v>
       </c>
-      <c r="N92" t="s">
+      <c r="N92" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="S92" t="s">
+      <c r="S92" s="2" t="s">
         <v>217</v>
       </c>
       <c r="W92" t="s">
@@ -8862,19 +8911,19 @@
       <c r="M93" t="s">
         <v>664</v>
       </c>
-      <c r="N93" t="s">
+      <c r="N93" s="2" t="s">
         <v>665</v>
       </c>
       <c r="Q93" t="s">
         <v>666</v>
       </c>
-      <c r="S93" t="s">
+      <c r="S93" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="T93" t="s">
+      <c r="T93" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="U93" t="s">
+      <c r="U93" s="1" t="s">
         <v>668</v>
       </c>
       <c r="W93" t="s">
@@ -8909,16 +8958,16 @@
       <c r="M94" t="s">
         <v>669</v>
       </c>
-      <c r="N94" t="s">
+      <c r="N94" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="S94" t="s">
+      <c r="S94" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="T94" t="s">
+      <c r="T94" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="U94" t="s">
+      <c r="U94" s="1" t="s">
         <v>673</v>
       </c>
       <c r="W94" t="s">
@@ -8953,16 +9002,16 @@
       <c r="M95" t="s">
         <v>677</v>
       </c>
-      <c r="N95" t="s">
+      <c r="N95" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="S95" t="s">
+      <c r="S95" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="T95" t="s">
+      <c r="T95" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="U95" t="s">
+      <c r="U95" s="1" t="s">
         <v>680</v>
       </c>
       <c r="W95" t="s">
@@ -8997,13 +9046,13 @@
       <c r="M96" t="s">
         <v>684</v>
       </c>
-      <c r="N96" t="s">
+      <c r="N96" s="2" t="s">
         <v>685</v>
       </c>
       <c r="Q96" t="s">
         <v>686</v>
       </c>
-      <c r="S96" t="s">
+      <c r="S96" s="2" t="s">
         <v>217</v>
       </c>
       <c r="W96" t="s">
@@ -9047,19 +9096,19 @@
       <c r="M97" t="s">
         <v>693</v>
       </c>
-      <c r="N97" t="s">
+      <c r="N97" s="2" t="s">
         <v>694</v>
       </c>
       <c r="Q97" t="s">
         <v>695</v>
       </c>
-      <c r="S97" t="s">
+      <c r="S97" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="T97">
+      <c r="T97" s="1">
         <v>240</v>
       </c>
-      <c r="U97">
+      <c r="U97" s="1">
         <v>223</v>
       </c>
       <c r="W97" t="s">
@@ -9103,22 +9152,22 @@
       <c r="M98" t="s">
         <v>700</v>
       </c>
-      <c r="N98" t="s">
+      <c r="N98" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="O98" t="s">
+      <c r="O98" s="2" t="s">
         <v>702</v>
       </c>
       <c r="Q98" t="s">
         <v>703</v>
       </c>
-      <c r="S98" t="s">
+      <c r="S98" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="T98">
+      <c r="T98" s="1">
         <v>190</v>
       </c>
-      <c r="U98">
+      <c r="U98" s="1">
         <v>122</v>
       </c>
       <c r="W98" t="s">
@@ -9159,16 +9208,16 @@
       <c r="M99" t="s">
         <v>712</v>
       </c>
-      <c r="N99" t="s">
+      <c r="N99" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="S99" t="s">
+      <c r="S99" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="T99" t="s">
+      <c r="T99" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="U99" t="s">
+      <c r="U99" s="1" t="s">
         <v>715</v>
       </c>
       <c r="W99" t="s">
@@ -9212,16 +9261,16 @@
       <c r="M100" t="s">
         <v>718</v>
       </c>
-      <c r="N100" t="s">
+      <c r="N100" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="S100" t="s">
+      <c r="S100" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="T100" t="s">
+      <c r="T100" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="U100" t="s">
+      <c r="U100" s="1" t="s">
         <v>721</v>
       </c>
       <c r="W100" t="s">
@@ -9265,19 +9314,19 @@
       <c r="M101" t="s">
         <v>583</v>
       </c>
-      <c r="N101" t="s">
+      <c r="N101" s="2" t="s">
         <v>729</v>
       </c>
       <c r="Q101" t="s">
         <v>730</v>
       </c>
-      <c r="S101" t="s">
+      <c r="S101" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="T101" t="s">
+      <c r="T101" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="U101" t="s">
+      <c r="U101" s="1" t="s">
         <v>731</v>
       </c>
       <c r="W101" t="s">
@@ -9321,19 +9370,19 @@
       <c r="M102" t="s">
         <v>734</v>
       </c>
-      <c r="N102" t="s">
+      <c r="N102" s="2" t="s">
         <v>735</v>
       </c>
       <c r="Q102" t="s">
         <v>736</v>
       </c>
-      <c r="S102" t="s">
+      <c r="S102" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="T102" t="s">
+      <c r="T102" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="U102" t="s">
+      <c r="U102" s="1" t="s">
         <v>738</v>
       </c>
       <c r="W102" t="s">
@@ -9377,22 +9426,22 @@
       <c r="M103" t="s">
         <v>742</v>
       </c>
-      <c r="N103" t="s">
+      <c r="N103" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="O103" t="s">
+      <c r="O103" s="2" t="s">
         <v>744</v>
       </c>
       <c r="Q103" t="s">
         <v>745</v>
       </c>
-      <c r="S103" t="s">
+      <c r="S103" s="2" t="s">
         <v>746</v>
       </c>
-      <c r="T103" t="s">
+      <c r="T103" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="U103" t="s">
+      <c r="U103" s="1" t="s">
         <v>748</v>
       </c>
       <c r="W103" t="s">
@@ -9430,16 +9479,16 @@
       <c r="M104" t="s">
         <v>751</v>
       </c>
-      <c r="N104" t="s">
+      <c r="N104" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="S104" t="s">
+      <c r="S104" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T104" t="s">
+      <c r="T104" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="U104" t="s">
+      <c r="U104" s="1" t="s">
         <v>754</v>
       </c>
       <c r="W104" t="s">
@@ -9477,10 +9526,10 @@
       <c r="M105" t="s">
         <v>756</v>
       </c>
-      <c r="N105" t="s">
+      <c r="N105" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="S105" t="s">
+      <c r="S105" s="2" t="s">
         <v>109</v>
       </c>
       <c r="W105" t="s">
@@ -9524,16 +9573,16 @@
       <c r="M106" t="s">
         <v>759</v>
       </c>
-      <c r="N106" t="s">
+      <c r="N106" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="S106" t="s">
+      <c r="S106" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T106" t="s">
+      <c r="T106" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="U106" t="s">
+      <c r="U106" s="1" t="s">
         <v>762</v>
       </c>
       <c r="W106" t="s">
@@ -9577,19 +9626,19 @@
       <c r="M107" t="s">
         <v>765</v>
       </c>
-      <c r="N107" t="s">
+      <c r="N107" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="O107" t="s">
+      <c r="O107" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="S107" t="s">
+      <c r="S107" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="T107">
+      <c r="T107" s="1">
         <v>180</v>
       </c>
-      <c r="U107">
+      <c r="U107" s="1">
         <v>139</v>
       </c>
       <c r="W107" t="s">
@@ -9633,22 +9682,22 @@
       <c r="M108" t="s">
         <v>770</v>
       </c>
-      <c r="N108" t="s">
+      <c r="N108" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="O108" t="s">
+      <c r="O108" s="2" t="s">
         <v>767</v>
       </c>
       <c r="Q108" t="s">
         <v>772</v>
       </c>
-      <c r="S108" t="s">
+      <c r="S108" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="T108" t="s">
+      <c r="T108" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="U108" t="s">
+      <c r="U108" s="1" t="s">
         <v>774</v>
       </c>
       <c r="W108" t="s">
@@ -9692,19 +9741,19 @@
       <c r="M109" t="s">
         <v>583</v>
       </c>
-      <c r="N109" t="s">
+      <c r="N109" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="O109" t="s">
+      <c r="O109" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="S109" t="s">
+      <c r="S109" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="T109" t="s">
+      <c r="T109" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="U109" t="s">
+      <c r="U109" s="1" t="s">
         <v>227</v>
       </c>
       <c r="W109" t="s">
@@ -9748,19 +9797,19 @@
       <c r="M110" t="s">
         <v>778</v>
       </c>
-      <c r="N110" t="s">
+      <c r="N110" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="O110" t="s">
+      <c r="O110" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="S110" t="s">
+      <c r="S110" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="T110" t="s">
+      <c r="T110" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="U110" t="s">
+      <c r="U110" s="1" t="s">
         <v>781</v>
       </c>
       <c r="W110" t="s">
@@ -9804,19 +9853,19 @@
       <c r="M111" t="s">
         <v>784</v>
       </c>
-      <c r="N111" t="s">
+      <c r="N111" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="O111" t="s">
+      <c r="O111" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="S111" t="s">
+      <c r="S111" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="T111" t="s">
+      <c r="T111" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="U111" t="s">
+      <c r="U111" s="1" t="s">
         <v>787</v>
       </c>
       <c r="W111" t="s">
@@ -9860,19 +9909,19 @@
       <c r="M112" t="s">
         <v>790</v>
       </c>
-      <c r="N112" t="s">
+      <c r="N112" s="2" t="s">
         <v>791</v>
       </c>
-      <c r="O112" t="s">
+      <c r="O112" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="S112" t="s">
+      <c r="S112" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="T112" t="s">
+      <c r="T112" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="U112" t="s">
+      <c r="U112" s="1" t="s">
         <v>794</v>
       </c>
       <c r="W112" t="s">
@@ -9913,10 +9962,10 @@
       <c r="M113" t="s">
         <v>677</v>
       </c>
-      <c r="N113" t="s">
+      <c r="N113" s="2" t="s">
         <v>801</v>
       </c>
-      <c r="S113" t="s">
+      <c r="S113" s="2" t="s">
         <v>109</v>
       </c>
       <c r="W113" t="s">
@@ -9957,13 +10006,13 @@
       <c r="M114" t="s">
         <v>803</v>
       </c>
-      <c r="N114" t="s">
+      <c r="N114" s="2" t="s">
         <v>804</v>
       </c>
-      <c r="O114" t="s">
+      <c r="O114" s="2" t="s">
         <v>805</v>
       </c>
-      <c r="S114" t="s">
+      <c r="S114" s="2" t="s">
         <v>33</v>
       </c>
       <c r="W114" t="s">
@@ -9998,16 +10047,16 @@
       <c r="M115" t="s">
         <v>813</v>
       </c>
-      <c r="N115" t="s">
+      <c r="N115" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="S115" t="s">
+      <c r="S115" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="T115" t="s">
+      <c r="T115" s="1" t="s">
         <v>815</v>
       </c>
-      <c r="U115" t="s">
+      <c r="U115" s="1" t="s">
         <v>816</v>
       </c>
       <c r="W115" t="s">
@@ -10042,13 +10091,13 @@
       <c r="M116" t="s">
         <v>823</v>
       </c>
-      <c r="N116" t="s">
+      <c r="N116" s="2" t="s">
         <v>824</v>
       </c>
       <c r="Q116" t="s">
         <v>825</v>
       </c>
-      <c r="S116" t="s">
+      <c r="S116" s="2" t="s">
         <v>217</v>
       </c>
       <c r="W116" t="s">
@@ -10058,426 +10107,463 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
+    <row r="117" spans="1:24" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="3" t="s">
         <v>826</v>
       </c>
-      <c r="F117" t="s">
+      <c r="F117" s="3" t="s">
         <v>827</v>
       </c>
-      <c r="G117" t="s">
+      <c r="G117" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="H117" t="s">
+      <c r="H117" s="3" t="s">
         <v>829</v>
       </c>
-      <c r="I117" t="s">
+      <c r="I117" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="J117" t="s">
+      <c r="J117" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="M117" t="s">
+      <c r="M117" s="3" t="s">
         <v>830</v>
       </c>
-      <c r="N117" t="s">
+      <c r="N117" s="4" t="s">
         <v>831</v>
       </c>
-      <c r="S117" t="s">
+      <c r="O117" s="4"/>
+      <c r="S117" s="4" t="s">
         <v>832</v>
       </c>
-      <c r="T117">
-        <v>86</v>
-      </c>
-      <c r="U117">
-        <v>71</v>
-      </c>
-      <c r="W117" t="s">
+      <c r="T117" s="5" t="s">
+        <v>1388</v>
+      </c>
+      <c r="U117" s="5" t="s">
+        <v>1389</v>
+      </c>
+      <c r="V117" s="5"/>
+      <c r="W117" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="X117">
+      <c r="X117" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
+    <row r="118" spans="1:24" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="3" t="s">
         <v>826</v>
       </c>
-      <c r="F118" t="s">
+      <c r="F118" s="3" t="s">
         <v>827</v>
       </c>
-      <c r="G118" t="s">
+      <c r="G118" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="H118" t="s">
+      <c r="H118" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="I118" t="s">
+      <c r="I118" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="J118" t="s">
+      <c r="J118" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="M118" t="s">
+      <c r="M118" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="N118" t="s">
+      <c r="N118" s="4" t="s">
         <v>833</v>
       </c>
-      <c r="S118" t="s">
+      <c r="O118" s="4"/>
+      <c r="S118" s="4" t="s">
         <v>834</v>
       </c>
-      <c r="T118" t="s">
+      <c r="T118" s="5" t="s">
         <v>835</v>
       </c>
-      <c r="U118" t="s">
+      <c r="U118" s="5" t="s">
+        <v>1387</v>
+      </c>
+      <c r="V118" s="5"/>
+      <c r="W118" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="X118" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:24" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="H119" s="3" t="s">
         <v>836</v>
       </c>
-      <c r="W118" t="s">
+      <c r="I119" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="J119" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="M119" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="N119" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="O119" s="4"/>
+      <c r="S119" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="T119" s="5" t="s">
+        <v>841</v>
+      </c>
+      <c r="U119" s="5" t="s">
+        <v>1386</v>
+      </c>
+      <c r="V119" s="5"/>
+      <c r="W119" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="X118">
+      <c r="X119" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
+    <row r="120" spans="1:24" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B120" s="3" t="s">
         <v>826</v>
       </c>
-      <c r="F119" t="s">
+      <c r="F120" s="3" t="s">
         <v>827</v>
       </c>
-      <c r="G119" t="s">
+      <c r="G120" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="H119" t="s">
-        <v>837</v>
-      </c>
-      <c r="I119" t="s">
-        <v>838</v>
-      </c>
-      <c r="J119" t="s">
-        <v>839</v>
-      </c>
-      <c r="M119" t="s">
-        <v>840</v>
-      </c>
-      <c r="N119" t="s">
-        <v>841</v>
-      </c>
-      <c r="S119" t="s">
-        <v>81</v>
-      </c>
-      <c r="T119" t="s">
+      <c r="H120" s="3" t="s">
         <v>842</v>
       </c>
-      <c r="U119" t="s">
+      <c r="I120" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J120" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M120" s="3" t="s">
         <v>843</v>
       </c>
-      <c r="W119" t="s">
+      <c r="N120" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="O120" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="S120" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="T120" s="5" t="s">
+        <v>1379</v>
+      </c>
+      <c r="U120" s="5" t="s">
+        <v>1385</v>
+      </c>
+      <c r="V120" s="5"/>
+      <c r="W120" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="X119">
+      <c r="X120" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
+    <row r="121" spans="1:24" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B121" s="3" t="s">
         <v>826</v>
       </c>
-      <c r="F120" t="s">
+      <c r="F121" s="3" t="s">
         <v>827</v>
       </c>
-      <c r="G120" t="s">
+      <c r="G121" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="H120" t="s">
-        <v>844</v>
-      </c>
-      <c r="I120" t="s">
-        <v>77</v>
-      </c>
-      <c r="J120" t="s">
-        <v>78</v>
-      </c>
-      <c r="M120" t="s">
-        <v>845</v>
-      </c>
-      <c r="N120" t="s">
+      <c r="H121" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="J121" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="M121" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="N121" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="O121" s="4" t="s">
+        <v>1380</v>
+      </c>
+      <c r="S121" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="T121" s="5" t="s">
+        <v>1377</v>
+      </c>
+      <c r="U121" s="5" t="s">
+        <v>1378</v>
+      </c>
+      <c r="V121" s="5"/>
+      <c r="W121" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="X121" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:24" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J122" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M122" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="N122" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="O122" s="4"/>
+      <c r="S122" s="4" t="s">
         <v>846</v>
       </c>
-      <c r="O120" t="s">
-        <v>847</v>
-      </c>
-      <c r="S120" t="s">
-        <v>848</v>
-      </c>
-      <c r="T120">
-        <v>93</v>
-      </c>
-      <c r="U120">
-        <v>85</v>
-      </c>
-      <c r="W120" t="s">
+      <c r="T122" s="5" t="s">
+        <v>1381</v>
+      </c>
+      <c r="U122" s="5" t="s">
+        <v>1383</v>
+      </c>
+      <c r="V122" s="5"/>
+      <c r="W122" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="X120">
+      <c r="X122" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
+    <row r="123" spans="1:24" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B123" s="3" t="s">
         <v>826</v>
       </c>
-      <c r="F121" t="s">
+      <c r="F123" s="3" t="s">
         <v>827</v>
       </c>
-      <c r="G121" t="s">
+      <c r="G123" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="H121" t="s">
-        <v>614</v>
-      </c>
-      <c r="I121" t="s">
+      <c r="H123" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="J123" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="L123" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="M123" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="N123" s="4" t="s">
+        <v>857</v>
+      </c>
+      <c r="O123" s="4"/>
+      <c r="S123" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="T123" s="5" t="s">
+        <v>1382</v>
+      </c>
+      <c r="U123" s="5" t="s">
+        <v>1384</v>
+      </c>
+      <c r="V123" s="5"/>
+      <c r="W123" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="X123" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:24" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="I124" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="J121" t="s">
+      <c r="J124" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="M121" t="s">
+      <c r="M124" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="N124" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="O124" s="4" t="s">
+        <v>1380</v>
+      </c>
+      <c r="S124" s="4" t="s">
         <v>849</v>
       </c>
-      <c r="N121" t="s">
-        <v>850</v>
-      </c>
-      <c r="S121" t="s">
-        <v>851</v>
-      </c>
-      <c r="W121" t="s">
+      <c r="T124" s="5" t="s">
+        <v>1377</v>
+      </c>
+      <c r="U124" s="5" t="s">
+        <v>1378</v>
+      </c>
+      <c r="V124" s="5"/>
+      <c r="W124" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="X121">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="122" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>247</v>
-      </c>
-      <c r="B122" t="s">
-        <v>826</v>
-      </c>
-      <c r="F122" t="s">
-        <v>827</v>
-      </c>
-      <c r="G122" t="s">
-        <v>828</v>
-      </c>
-      <c r="H122" t="s">
-        <v>852</v>
-      </c>
-      <c r="I122" t="s">
-        <v>38</v>
-      </c>
-      <c r="J122" t="s">
-        <v>39</v>
-      </c>
-      <c r="M122" t="s">
-        <v>853</v>
-      </c>
-      <c r="N122" t="s">
-        <v>854</v>
-      </c>
-      <c r="S122" t="s">
-        <v>848</v>
-      </c>
-      <c r="T122">
-        <v>93</v>
-      </c>
-      <c r="U122" t="s">
-        <v>855</v>
-      </c>
-      <c r="W122" t="s">
-        <v>256</v>
-      </c>
-      <c r="X122">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="123" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>247</v>
-      </c>
-      <c r="B123" t="s">
-        <v>826</v>
-      </c>
-      <c r="F123" t="s">
-        <v>827</v>
-      </c>
-      <c r="G123" t="s">
-        <v>828</v>
-      </c>
-      <c r="H123" t="s">
-        <v>852</v>
-      </c>
-      <c r="I123" t="s">
-        <v>856</v>
-      </c>
-      <c r="J123" t="s">
-        <v>857</v>
-      </c>
-      <c r="L123" t="s">
-        <v>858</v>
-      </c>
-      <c r="M123" t="s">
-        <v>859</v>
-      </c>
-      <c r="N123" t="s">
-        <v>860</v>
-      </c>
-      <c r="S123" t="s">
-        <v>861</v>
-      </c>
-      <c r="T123">
-        <v>146</v>
-      </c>
-      <c r="U123">
-        <v>237</v>
-      </c>
-      <c r="W123" t="s">
-        <v>256</v>
-      </c>
-      <c r="X123">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="124" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>247</v>
-      </c>
-      <c r="B124" t="s">
-        <v>826</v>
-      </c>
-      <c r="F124" t="s">
-        <v>827</v>
-      </c>
-      <c r="G124" t="s">
-        <v>828</v>
-      </c>
-      <c r="H124" t="s">
-        <v>637</v>
-      </c>
-      <c r="I124" t="s">
-        <v>811</v>
-      </c>
-      <c r="J124" t="s">
-        <v>812</v>
-      </c>
-      <c r="M124" t="s">
-        <v>734</v>
-      </c>
-      <c r="N124" t="s">
-        <v>862</v>
-      </c>
-      <c r="S124" t="s">
-        <v>851</v>
-      </c>
-      <c r="W124" t="s">
-        <v>256</v>
-      </c>
-      <c r="X124">
+      <c r="X124" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>247</v>
+        <v>860</v>
       </c>
       <c r="B125" t="s">
-        <v>826</v>
+        <v>861</v>
       </c>
       <c r="F125" t="s">
-        <v>827</v>
+        <v>135</v>
       </c>
       <c r="G125" t="s">
-        <v>828</v>
+        <v>862</v>
       </c>
       <c r="H125" t="s">
-        <v>637</v>
+        <v>103</v>
       </c>
       <c r="I125" t="s">
-        <v>811</v>
+        <v>138</v>
       </c>
       <c r="J125" t="s">
-        <v>812</v>
+        <v>139</v>
       </c>
       <c r="M125" t="s">
-        <v>734</v>
-      </c>
-      <c r="N125" t="s">
-        <v>862</v>
-      </c>
-      <c r="S125" t="s">
-        <v>851</v>
+        <v>863</v>
+      </c>
+      <c r="N125" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="S125" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="T125" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U125" s="1" t="s">
+        <v>865</v>
       </c>
       <c r="W125" t="s">
-        <v>256</v>
+        <v>145</v>
       </c>
       <c r="X125">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B126" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="F126" t="s">
         <v>135</v>
       </c>
       <c r="G126" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="H126" t="s">
-        <v>103</v>
+        <v>866</v>
       </c>
       <c r="I126" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="J126" t="s">
-        <v>139</v>
+        <v>867</v>
       </c>
       <c r="M126" t="s">
-        <v>866</v>
-      </c>
-      <c r="N126" t="s">
-        <v>867</v>
-      </c>
-      <c r="S126" t="s">
+        <v>868</v>
+      </c>
+      <c r="N126" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="S126" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="T126" t="s">
-        <v>132</v>
-      </c>
-      <c r="U126" t="s">
-        <v>868</v>
+      <c r="T126" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="U126" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="W126" t="s">
         <v>145</v>
@@ -10488,43 +10574,52 @@
     </row>
     <row r="127" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="B127" t="s">
-        <v>864</v>
+        <v>872</v>
       </c>
       <c r="F127" t="s">
-        <v>135</v>
+        <v>873</v>
       </c>
       <c r="G127" t="s">
-        <v>865</v>
+        <v>421</v>
       </c>
       <c r="H127" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="I127" t="s">
-        <v>146</v>
+        <v>29</v>
       </c>
       <c r="J127" t="s">
-        <v>870</v>
+        <v>711</v>
+      </c>
+      <c r="L127" t="s">
+        <v>875</v>
       </c>
       <c r="M127" t="s">
-        <v>871</v>
-      </c>
-      <c r="N127" t="s">
-        <v>872</v>
-      </c>
-      <c r="S127" t="s">
-        <v>81</v>
-      </c>
-      <c r="T127" t="s">
-        <v>873</v>
-      </c>
-      <c r="U127" t="s">
-        <v>44</v>
+        <v>876</v>
+      </c>
+      <c r="N127" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="O127" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>879</v>
+      </c>
+      <c r="S127" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="T127" s="1">
+        <v>450</v>
+      </c>
+      <c r="U127" s="1">
+        <v>450</v>
       </c>
       <c r="W127" t="s">
-        <v>145</v>
+        <v>36</v>
       </c>
       <c r="X127">
         <v>3</v>
@@ -10532,49 +10627,46 @@
     </row>
     <row r="128" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="B128" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="F128" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G128" t="s">
         <v>421</v>
       </c>
-      <c r="H128" t="s">
-        <v>877</v>
+      <c r="H128">
+        <v>1490</v>
       </c>
       <c r="I128" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J128" t="s">
-        <v>711</v>
+        <v>39</v>
       </c>
       <c r="L128" t="s">
-        <v>878</v>
+        <v>733</v>
       </c>
       <c r="M128" t="s">
-        <v>879</v>
-      </c>
-      <c r="N128" t="s">
         <v>880</v>
       </c>
-      <c r="O128" t="s">
+      <c r="N128" s="2" t="s">
         <v>881</v>
       </c>
       <c r="Q128" t="s">
         <v>882</v>
       </c>
-      <c r="S128" t="s">
-        <v>217</v>
-      </c>
-      <c r="T128">
-        <v>450</v>
-      </c>
-      <c r="U128">
-        <v>450</v>
+      <c r="S128" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="T128" s="1">
+        <v>62</v>
+      </c>
+      <c r="U128" s="1">
+        <v>46</v>
       </c>
       <c r="W128" t="s">
         <v>36</v>
@@ -10585,49 +10677,43 @@
     </row>
     <row r="129" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>874</v>
+        <v>883</v>
       </c>
       <c r="B129" t="s">
-        <v>875</v>
+        <v>884</v>
       </c>
       <c r="F129" t="s">
-        <v>876</v>
+        <v>26</v>
       </c>
       <c r="G129" t="s">
-        <v>421</v>
-      </c>
-      <c r="H129">
-        <v>1490</v>
+        <v>885</v>
+      </c>
+      <c r="H129" t="s">
+        <v>637</v>
       </c>
       <c r="I129" t="s">
-        <v>38</v>
+        <v>886</v>
       </c>
       <c r="J129" t="s">
-        <v>39</v>
-      </c>
-      <c r="L129" t="s">
-        <v>733</v>
+        <v>887</v>
       </c>
       <c r="M129" t="s">
-        <v>883</v>
-      </c>
-      <c r="N129" t="s">
-        <v>884</v>
-      </c>
-      <c r="Q129" t="s">
-        <v>885</v>
-      </c>
-      <c r="S129" t="s">
-        <v>100</v>
-      </c>
-      <c r="T129">
-        <v>62</v>
-      </c>
-      <c r="U129">
-        <v>46</v>
+        <v>888</v>
+      </c>
+      <c r="N129" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="S129" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="T129" s="1">
+        <v>206</v>
+      </c>
+      <c r="U129" s="1" t="s">
+        <v>891</v>
       </c>
       <c r="W129" t="s">
-        <v>36</v>
+        <v>892</v>
       </c>
       <c r="X129">
         <v>3</v>
@@ -10635,43 +10721,46 @@
     </row>
     <row r="130" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="B130" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="F130" t="s">
         <v>26</v>
       </c>
       <c r="G130" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="H130" t="s">
         <v>637</v>
       </c>
       <c r="I130" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="J130" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="M130" t="s">
-        <v>891</v>
-      </c>
-      <c r="N130" t="s">
-        <v>892</v>
-      </c>
-      <c r="S130" t="s">
         <v>893</v>
       </c>
-      <c r="T130">
-        <v>206</v>
-      </c>
-      <c r="U130" t="s">
+      <c r="N130" s="2" t="s">
         <v>894</v>
       </c>
+      <c r="Q130" t="s">
+        <v>895</v>
+      </c>
+      <c r="S130" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="T130" s="1">
+        <v>211</v>
+      </c>
+      <c r="U130" s="1">
+        <v>91</v>
+      </c>
       <c r="W130" t="s">
-        <v>895</v>
+        <v>36</v>
       </c>
       <c r="X130">
         <v>3</v>
@@ -10679,43 +10768,46 @@
     </row>
     <row r="131" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="B131" t="s">
-        <v>887</v>
+        <v>898</v>
       </c>
       <c r="F131" t="s">
-        <v>26</v>
+        <v>899</v>
       </c>
       <c r="G131" t="s">
-        <v>888</v>
-      </c>
-      <c r="H131" t="s">
-        <v>637</v>
+        <v>900</v>
+      </c>
+      <c r="H131">
+        <v>1459</v>
       </c>
       <c r="I131" t="s">
-        <v>889</v>
+        <v>29</v>
       </c>
       <c r="J131" t="s">
-        <v>890</v>
+        <v>901</v>
+      </c>
+      <c r="L131" t="s">
+        <v>902</v>
       </c>
       <c r="M131" t="s">
-        <v>896</v>
-      </c>
-      <c r="N131" t="s">
-        <v>897</v>
+        <v>903</v>
+      </c>
+      <c r="N131" s="2" t="s">
+        <v>904</v>
       </c>
       <c r="Q131" t="s">
-        <v>898</v>
-      </c>
-      <c r="S131" t="s">
-        <v>899</v>
-      </c>
-      <c r="T131">
-        <v>211</v>
-      </c>
-      <c r="U131">
-        <v>91</v>
+        <v>905</v>
+      </c>
+      <c r="S131" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="T131" s="1">
+        <v>405</v>
+      </c>
+      <c r="U131" s="1">
+        <v>516</v>
       </c>
       <c r="W131" t="s">
         <v>36</v>
@@ -10726,46 +10818,43 @@
     </row>
     <row r="132" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>897</v>
+      </c>
+      <c r="B132" t="s">
+        <v>898</v>
+      </c>
+      <c r="F132" t="s">
+        <v>899</v>
+      </c>
+      <c r="G132" t="s">
         <v>900</v>
       </c>
-      <c r="B132" t="s">
-        <v>901</v>
-      </c>
-      <c r="F132" t="s">
-        <v>902</v>
-      </c>
-      <c r="G132" t="s">
-        <v>903</v>
-      </c>
       <c r="H132">
-        <v>1459</v>
+        <v>1471</v>
       </c>
       <c r="I132" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J132" t="s">
-        <v>904</v>
-      </c>
-      <c r="L132" t="s">
-        <v>905</v>
+        <v>39</v>
       </c>
       <c r="M132" t="s">
-        <v>906</v>
-      </c>
-      <c r="N132" t="s">
         <v>907</v>
       </c>
+      <c r="N132" s="2" t="s">
+        <v>908</v>
+      </c>
       <c r="Q132" t="s">
-        <v>908</v>
-      </c>
-      <c r="S132" t="s">
         <v>909</v>
       </c>
-      <c r="T132">
-        <v>405</v>
-      </c>
-      <c r="U132">
-        <v>516</v>
+      <c r="S132" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="T132" s="1">
+        <v>230</v>
+      </c>
+      <c r="U132" s="1">
+        <v>102</v>
       </c>
       <c r="W132" t="s">
         <v>36</v>
@@ -10776,46 +10865,37 @@
     </row>
     <row r="133" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>900</v>
+        <v>911</v>
       </c>
       <c r="B133" t="s">
-        <v>901</v>
+        <v>912</v>
       </c>
       <c r="F133" t="s">
-        <v>902</v>
+        <v>913</v>
       </c>
       <c r="G133" t="s">
-        <v>903</v>
-      </c>
-      <c r="H133">
-        <v>1471</v>
+        <v>316</v>
+      </c>
+      <c r="H133" t="s">
+        <v>63</v>
       </c>
       <c r="I133" t="s">
-        <v>38</v>
+        <v>146</v>
       </c>
       <c r="J133" t="s">
-        <v>39</v>
+        <v>914</v>
       </c>
       <c r="M133" t="s">
-        <v>910</v>
-      </c>
-      <c r="N133" t="s">
-        <v>911</v>
-      </c>
-      <c r="Q133" t="s">
-        <v>912</v>
-      </c>
-      <c r="S133" t="s">
-        <v>913</v>
-      </c>
-      <c r="T133">
-        <v>230</v>
-      </c>
-      <c r="U133">
-        <v>102</v>
+        <v>915</v>
+      </c>
+      <c r="N133" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="S133" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="W133" t="s">
-        <v>36</v>
+        <v>145</v>
       </c>
       <c r="X133">
         <v>3</v>
@@ -10823,34 +10903,34 @@
     </row>
     <row r="134" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="B134" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="F134" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="G134" t="s">
         <v>316</v>
       </c>
       <c r="H134" t="s">
-        <v>63</v>
+        <v>917</v>
       </c>
       <c r="I134" t="s">
         <v>146</v>
       </c>
       <c r="J134" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="M134" t="s">
-        <v>918</v>
-      </c>
-      <c r="N134" t="s">
         <v>919</v>
       </c>
-      <c r="S134" t="s">
-        <v>109</v>
+      <c r="N134" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="S134" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="W134" t="s">
         <v>145</v>
@@ -10861,37 +10941,46 @@
     </row>
     <row r="135" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="B135" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
       <c r="F135" t="s">
-        <v>916</v>
+        <v>558</v>
       </c>
       <c r="G135" t="s">
-        <v>316</v>
+        <v>923</v>
       </c>
       <c r="H135" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="I135" t="s">
-        <v>146</v>
+        <v>29</v>
       </c>
       <c r="J135" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="M135" t="s">
-        <v>922</v>
-      </c>
-      <c r="N135" t="s">
-        <v>923</v>
-      </c>
-      <c r="S135" t="s">
+        <v>926</v>
+      </c>
+      <c r="N135" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>928</v>
+      </c>
+      <c r="S135" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="T135" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="U135" s="1" t="s">
+        <v>929</v>
+      </c>
       <c r="W135" t="s">
-        <v>145</v>
+        <v>36</v>
       </c>
       <c r="X135">
         <v>3</v>
@@ -10899,43 +10988,40 @@
     </row>
     <row r="136" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="B136" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="F136" t="s">
         <v>558</v>
       </c>
       <c r="G136" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="H136" t="s">
-        <v>927</v>
+        <v>88</v>
       </c>
       <c r="I136" t="s">
         <v>29</v>
       </c>
       <c r="J136" t="s">
-        <v>928</v>
+        <v>127</v>
       </c>
       <c r="M136" t="s">
-        <v>929</v>
-      </c>
-      <c r="N136" t="s">
         <v>930</v>
       </c>
-      <c r="Q136" t="s">
+      <c r="N136" s="2" t="s">
         <v>931</v>
       </c>
-      <c r="S136" t="s">
-        <v>33</v>
-      </c>
-      <c r="T136" t="s">
-        <v>754</v>
-      </c>
-      <c r="U136" t="s">
+      <c r="S136" s="2" t="s">
         <v>932</v>
+      </c>
+      <c r="T136" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="U136" s="1" t="s">
+        <v>933</v>
       </c>
       <c r="W136" t="s">
         <v>36</v>
@@ -10946,19 +11032,19 @@
     </row>
     <row r="137" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>924</v>
+        <v>934</v>
       </c>
       <c r="B137" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="F137" t="s">
-        <v>558</v>
+        <v>935</v>
       </c>
       <c r="G137" t="s">
-        <v>926</v>
+        <v>936</v>
       </c>
       <c r="H137" t="s">
-        <v>88</v>
+        <v>937</v>
       </c>
       <c r="I137" t="s">
         <v>29</v>
@@ -10967,19 +11053,19 @@
         <v>127</v>
       </c>
       <c r="M137" t="s">
-        <v>933</v>
-      </c>
-      <c r="N137" t="s">
-        <v>934</v>
-      </c>
-      <c r="S137" t="s">
-        <v>935</v>
-      </c>
-      <c r="T137" t="s">
-        <v>125</v>
-      </c>
-      <c r="U137" t="s">
-        <v>936</v>
+        <v>734</v>
+      </c>
+      <c r="N137" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="S137" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T137" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="U137" s="1" t="s">
+        <v>939</v>
       </c>
       <c r="W137" t="s">
         <v>36</v>
@@ -10990,16 +11076,16 @@
     </row>
     <row r="138" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="B138" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="F138" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="G138" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="H138" t="s">
         <v>940</v>
@@ -11011,19 +11097,22 @@
         <v>127</v>
       </c>
       <c r="M138" t="s">
-        <v>734</v>
-      </c>
-      <c r="N138" t="s">
         <v>941</v>
       </c>
-      <c r="S138" t="s">
+      <c r="N138" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>943</v>
+      </c>
+      <c r="S138" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="T138" t="s">
-        <v>761</v>
-      </c>
-      <c r="U138" t="s">
-        <v>942</v>
+      <c r="T138" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="U138" s="1" t="s">
+        <v>945</v>
       </c>
       <c r="W138" t="s">
         <v>36</v>
@@ -11034,46 +11123,37 @@
     </row>
     <row r="139" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>937</v>
+        <v>946</v>
       </c>
       <c r="B139" t="s">
-        <v>925</v>
+        <v>947</v>
       </c>
       <c r="F139" t="s">
-        <v>938</v>
+        <v>48</v>
       </c>
       <c r="G139" t="s">
-        <v>939</v>
+        <v>948</v>
       </c>
       <c r="H139" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="I139" t="s">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="J139" t="s">
-        <v>127</v>
+        <v>951</v>
       </c>
       <c r="M139" t="s">
-        <v>944</v>
-      </c>
-      <c r="N139" t="s">
-        <v>945</v>
-      </c>
-      <c r="Q139" t="s">
-        <v>946</v>
-      </c>
-      <c r="S139" t="s">
-        <v>33</v>
-      </c>
-      <c r="T139" t="s">
-        <v>947</v>
-      </c>
-      <c r="U139" t="s">
-        <v>948</v>
+        <v>751</v>
+      </c>
+      <c r="N139" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="S139" s="2" t="s">
+        <v>746</v>
       </c>
       <c r="W139" t="s">
-        <v>36</v>
+        <v>953</v>
       </c>
       <c r="X139">
         <v>3</v>
@@ -11081,37 +11161,43 @@
     </row>
     <row r="140" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="B140" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="F140" t="s">
         <v>48</v>
       </c>
       <c r="G140" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="H140" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="I140" t="s">
+        <v>950</v>
+      </c>
+      <c r="J140" t="s">
+        <v>955</v>
+      </c>
+      <c r="M140" t="s">
+        <v>956</v>
+      </c>
+      <c r="N140" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="S140" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T140" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="U140" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="W140" t="s">
         <v>953</v>
-      </c>
-      <c r="J140" t="s">
-        <v>954</v>
-      </c>
-      <c r="M140" t="s">
-        <v>751</v>
-      </c>
-      <c r="N140" t="s">
-        <v>955</v>
-      </c>
-      <c r="S140" t="s">
-        <v>746</v>
-      </c>
-      <c r="W140" t="s">
-        <v>956</v>
       </c>
       <c r="X140">
         <v>3</v>
@@ -11119,46 +11205,52 @@
     </row>
     <row r="141" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>949</v>
+        <v>555</v>
       </c>
       <c r="B141" t="s">
-        <v>950</v>
+        <v>960</v>
       </c>
       <c r="F141" t="s">
-        <v>48</v>
+        <v>961</v>
       </c>
       <c r="G141" t="s">
-        <v>951</v>
+        <v>962</v>
       </c>
       <c r="H141" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="I141" t="s">
-        <v>953</v>
+        <v>964</v>
       </c>
       <c r="J141" t="s">
-        <v>958</v>
+        <v>965</v>
+      </c>
+      <c r="L141" t="s">
+        <v>966</v>
       </c>
       <c r="M141" t="s">
-        <v>959</v>
-      </c>
-      <c r="N141" t="s">
-        <v>960</v>
-      </c>
-      <c r="S141" t="s">
-        <v>33</v>
-      </c>
-      <c r="T141" t="s">
-        <v>961</v>
-      </c>
-      <c r="U141" t="s">
-        <v>962</v>
+        <v>967</v>
+      </c>
+      <c r="N141" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>969</v>
+      </c>
+      <c r="S141" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="T141" s="1">
+        <v>480</v>
+      </c>
+      <c r="U141" s="1">
+        <v>450</v>
       </c>
       <c r="W141" t="s">
-        <v>956</v>
+        <v>36</v>
       </c>
       <c r="X141">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11166,43 +11258,40 @@
         <v>555</v>
       </c>
       <c r="B142" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="F142" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G142" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="H142" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="I142" t="s">
-        <v>967</v>
+        <v>69</v>
       </c>
       <c r="J142" t="s">
-        <v>968</v>
-      </c>
-      <c r="L142" t="s">
-        <v>969</v>
+        <v>70</v>
       </c>
       <c r="M142" t="s">
-        <v>970</v>
-      </c>
-      <c r="N142" t="s">
         <v>971</v>
       </c>
+      <c r="N142" s="2" t="s">
+        <v>972</v>
+      </c>
       <c r="Q142" t="s">
-        <v>972</v>
-      </c>
-      <c r="S142" t="s">
-        <v>109</v>
-      </c>
-      <c r="T142">
-        <v>480</v>
-      </c>
-      <c r="U142">
-        <v>450</v>
+        <v>99</v>
+      </c>
+      <c r="S142" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="T142" s="1">
+        <v>63</v>
+      </c>
+      <c r="U142" s="1">
+        <v>80</v>
       </c>
       <c r="W142" t="s">
         <v>36</v>
@@ -11216,40 +11305,34 @@
         <v>555</v>
       </c>
       <c r="B143" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="F143" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G143" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="H143" t="s">
         <v>973</v>
       </c>
       <c r="I143" t="s">
-        <v>69</v>
+        <v>974</v>
       </c>
       <c r="J143" t="s">
-        <v>70</v>
+        <v>975</v>
       </c>
       <c r="M143" t="s">
-        <v>974</v>
-      </c>
-      <c r="N143" t="s">
-        <v>975</v>
+        <v>976</v>
+      </c>
+      <c r="N143" s="2" t="s">
+        <v>977</v>
       </c>
       <c r="Q143" t="s">
-        <v>99</v>
-      </c>
-      <c r="S143" t="s">
-        <v>100</v>
-      </c>
-      <c r="T143">
-        <v>63</v>
-      </c>
-      <c r="U143">
-        <v>80</v>
+        <v>978</v>
+      </c>
+      <c r="S143" s="2" t="s">
+        <v>217</v>
       </c>
       <c r="W143" t="s">
         <v>36</v>
@@ -11263,34 +11346,40 @@
         <v>555</v>
       </c>
       <c r="B144" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="F144" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G144" t="s">
-        <v>965</v>
-      </c>
-      <c r="H144" t="s">
-        <v>976</v>
+        <v>962</v>
+      </c>
+      <c r="H144">
+        <v>1480</v>
       </c>
       <c r="I144" t="s">
-        <v>977</v>
+        <v>38</v>
       </c>
       <c r="J144" t="s">
-        <v>978</v>
+        <v>39</v>
       </c>
       <c r="M144" t="s">
         <v>979</v>
       </c>
-      <c r="N144" t="s">
+      <c r="N144" s="2" t="s">
         <v>980</v>
       </c>
       <c r="Q144" t="s">
         <v>981</v>
       </c>
-      <c r="S144" t="s">
-        <v>217</v>
+      <c r="S144" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="T144" s="1">
+        <v>255</v>
+      </c>
+      <c r="U144" s="1">
+        <v>140</v>
       </c>
       <c r="W144" t="s">
         <v>36</v>
@@ -11304,40 +11393,40 @@
         <v>555</v>
       </c>
       <c r="B145" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="F145" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G145" t="s">
-        <v>965</v>
-      </c>
-      <c r="H145">
-        <v>1480</v>
+        <v>962</v>
+      </c>
+      <c r="H145" t="s">
+        <v>983</v>
       </c>
       <c r="I145" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="J145" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
       <c r="M145" t="s">
+        <v>984</v>
+      </c>
+      <c r="N145" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>986</v>
+      </c>
+      <c r="S145" s="2" t="s">
         <v>982</v>
       </c>
-      <c r="N145" t="s">
-        <v>983</v>
-      </c>
-      <c r="Q145" t="s">
-        <v>984</v>
-      </c>
-      <c r="S145" t="s">
-        <v>985</v>
-      </c>
-      <c r="T145">
-        <v>255</v>
-      </c>
-      <c r="U145">
-        <v>140</v>
+      <c r="T145" s="1">
+        <v>68</v>
+      </c>
+      <c r="U145" s="1">
+        <v>81</v>
       </c>
       <c r="W145" t="s">
         <v>36</v>
@@ -11351,40 +11440,31 @@
         <v>555</v>
       </c>
       <c r="B146" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="F146" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G146" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="H146" t="s">
-        <v>986</v>
+        <v>377</v>
       </c>
       <c r="I146" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="J146" t="s">
-        <v>105</v>
+        <v>39</v>
       </c>
       <c r="M146" t="s">
         <v>987</v>
       </c>
-      <c r="N146" t="s">
+      <c r="N146" s="2" t="s">
         <v>988</v>
       </c>
-      <c r="Q146" t="s">
-        <v>989</v>
-      </c>
-      <c r="S146" t="s">
-        <v>985</v>
-      </c>
-      <c r="T146">
-        <v>68</v>
-      </c>
-      <c r="U146">
-        <v>81</v>
+      <c r="S146" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="W146" t="s">
         <v>36</v>
@@ -11398,31 +11478,37 @@
         <v>555</v>
       </c>
       <c r="B147" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="F147" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G147" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="H147" t="s">
-        <v>377</v>
+        <v>88</v>
       </c>
       <c r="I147" t="s">
-        <v>38</v>
+        <v>989</v>
       </c>
       <c r="J147" t="s">
-        <v>39</v>
+        <v>491</v>
       </c>
       <c r="M147" t="s">
         <v>990</v>
       </c>
-      <c r="N147" t="s">
+      <c r="N147" s="2" t="s">
         <v>991</v>
       </c>
-      <c r="S147" t="s">
+      <c r="S147" s="2" t="s">
         <v>85</v>
+      </c>
+      <c r="T147" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="U147" s="1" t="s">
+        <v>992</v>
       </c>
       <c r="W147" t="s">
         <v>36</v>
@@ -11436,37 +11522,43 @@
         <v>555</v>
       </c>
       <c r="B148" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="F148" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G148" t="s">
-        <v>965</v>
-      </c>
-      <c r="H148" t="s">
-        <v>88</v>
+        <v>962</v>
+      </c>
+      <c r="H148">
+        <v>1497</v>
       </c>
       <c r="I148" t="s">
-        <v>992</v>
+        <v>38</v>
       </c>
       <c r="J148" t="s">
-        <v>491</v>
+        <v>39</v>
       </c>
       <c r="M148" t="s">
         <v>993</v>
       </c>
-      <c r="N148" t="s">
+      <c r="N148" s="2" t="s">
         <v>994</v>
       </c>
-      <c r="S148" t="s">
-        <v>85</v>
-      </c>
-      <c r="T148" t="s">
-        <v>309</v>
-      </c>
-      <c r="U148" t="s">
+      <c r="O148" s="2" t="s">
         <v>995</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>996</v>
+      </c>
+      <c r="S148" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="T148" s="1">
+        <v>159</v>
+      </c>
+      <c r="U148" s="1">
+        <v>192</v>
       </c>
       <c r="W148" t="s">
         <v>36</v>
@@ -11477,87 +11569,84 @@
     </row>
     <row r="149" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>555</v>
+        <v>998</v>
       </c>
       <c r="B149" t="s">
-        <v>963</v>
+        <v>999</v>
       </c>
       <c r="F149" t="s">
-        <v>964</v>
+        <v>26</v>
       </c>
       <c r="G149" t="s">
-        <v>965</v>
-      </c>
-      <c r="H149">
-        <v>1497</v>
+        <v>1000</v>
+      </c>
+      <c r="H149" t="s">
+        <v>1001</v>
       </c>
       <c r="I149" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="J149" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="M149" t="s">
-        <v>996</v>
-      </c>
-      <c r="N149" t="s">
-        <v>997</v>
-      </c>
-      <c r="O149" t="s">
-        <v>998</v>
+        <v>1002</v>
+      </c>
+      <c r="N149" s="2" t="s">
+        <v>1003</v>
       </c>
       <c r="Q149" t="s">
-        <v>999</v>
-      </c>
-      <c r="S149" t="s">
-        <v>1000</v>
-      </c>
-      <c r="T149">
-        <v>159</v>
-      </c>
-      <c r="U149">
-        <v>192</v>
+        <v>1004</v>
+      </c>
+      <c r="S149" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="W149" t="s">
-        <v>36</v>
+        <v>256</v>
       </c>
       <c r="X149">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="B150" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="F150" t="s">
         <v>26</v>
       </c>
       <c r="G150" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="H150" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="I150" t="s">
-        <v>77</v>
+        <v>1006</v>
       </c>
       <c r="J150" t="s">
-        <v>78</v>
+        <v>1007</v>
       </c>
       <c r="M150" t="s">
-        <v>1005</v>
-      </c>
-      <c r="N150" t="s">
-        <v>1006</v>
+        <v>1008</v>
+      </c>
+      <c r="N150" s="2" t="s">
+        <v>1009</v>
       </c>
       <c r="Q150" t="s">
-        <v>1007</v>
-      </c>
-      <c r="S150" t="s">
-        <v>81</v>
+        <v>1010</v>
+      </c>
+      <c r="S150" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="T150" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="U150" s="1">
+        <v>27</v>
       </c>
       <c r="W150" t="s">
         <v>256</v>
@@ -11568,57 +11657,57 @@
     </row>
     <row r="151" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>1001</v>
+        <v>1012</v>
       </c>
       <c r="B151" t="s">
-        <v>1002</v>
+        <v>1013</v>
       </c>
       <c r="F151" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="G151" t="s">
-        <v>1003</v>
+        <v>421</v>
       </c>
       <c r="H151" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="I151" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
       <c r="J151" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="M151" t="s">
-        <v>1011</v>
-      </c>
-      <c r="N151" t="s">
-        <v>1012</v>
+        <v>751</v>
+      </c>
+      <c r="N151" s="2" t="s">
+        <v>1017</v>
       </c>
       <c r="Q151" t="s">
-        <v>1013</v>
-      </c>
-      <c r="S151" t="s">
-        <v>848</v>
-      </c>
-      <c r="T151" t="s">
-        <v>1014</v>
-      </c>
-      <c r="U151">
-        <v>27</v>
+        <v>1018</v>
+      </c>
+      <c r="S151" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="T151" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="U151" s="1" t="s">
+        <v>793</v>
       </c>
       <c r="W151" t="s">
-        <v>256</v>
+        <v>55</v>
       </c>
       <c r="X151">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="B152" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="F152" t="s">
         <v>94</v>
@@ -11627,31 +11716,34 @@
         <v>421</v>
       </c>
       <c r="H152" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="I152" t="s">
-        <v>1018</v>
+        <v>460</v>
       </c>
       <c r="J152" t="s">
-        <v>1019</v>
+        <v>1022</v>
+      </c>
+      <c r="L152" t="s">
+        <v>1023</v>
       </c>
       <c r="M152" t="s">
-        <v>751</v>
-      </c>
-      <c r="N152" t="s">
-        <v>1020</v>
+        <v>1024</v>
+      </c>
+      <c r="N152" s="2" t="s">
+        <v>1025</v>
       </c>
       <c r="Q152" t="s">
-        <v>1021</v>
-      </c>
-      <c r="S152" t="s">
-        <v>1022</v>
-      </c>
-      <c r="T152" t="s">
-        <v>1023</v>
-      </c>
-      <c r="U152" t="s">
-        <v>793</v>
+        <v>1026</v>
+      </c>
+      <c r="S152" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="T152" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="U152" s="1" t="s">
+        <v>1028</v>
       </c>
       <c r="W152" t="s">
         <v>55</v>
@@ -11662,10 +11754,10 @@
     </row>
     <row r="153" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="B153" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="F153" t="s">
         <v>94</v>
@@ -11674,34 +11766,31 @@
         <v>421</v>
       </c>
       <c r="H153" t="s">
-        <v>1024</v>
+        <v>68</v>
       </c>
       <c r="I153" t="s">
-        <v>460</v>
+        <v>811</v>
       </c>
       <c r="J153" t="s">
-        <v>1025</v>
-      </c>
-      <c r="L153" t="s">
-        <v>1026</v>
+        <v>812</v>
       </c>
       <c r="M153" t="s">
-        <v>1027</v>
-      </c>
-      <c r="N153" t="s">
-        <v>1028</v>
+        <v>1029</v>
+      </c>
+      <c r="N153" s="2" t="s">
+        <v>1030</v>
       </c>
       <c r="Q153" t="s">
-        <v>1029</v>
-      </c>
-      <c r="S153" t="s">
-        <v>848</v>
-      </c>
-      <c r="T153" t="s">
-        <v>1030</v>
-      </c>
-      <c r="U153" t="s">
         <v>1031</v>
+      </c>
+      <c r="S153" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="T153" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="U153" s="1" t="s">
+        <v>1032</v>
       </c>
       <c r="W153" t="s">
         <v>55</v>
@@ -11712,10 +11801,10 @@
     </row>
     <row r="154" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="B154" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="F154" t="s">
         <v>94</v>
@@ -11724,34 +11813,25 @@
         <v>421</v>
       </c>
       <c r="H154" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="I154" t="s">
-        <v>811</v>
+        <v>29</v>
       </c>
       <c r="J154" t="s">
-        <v>812</v>
+        <v>127</v>
       </c>
       <c r="M154" t="s">
-        <v>1032</v>
-      </c>
-      <c r="N154" t="s">
         <v>1033</v>
       </c>
-      <c r="Q154" t="s">
+      <c r="N154" s="2" t="s">
         <v>1034</v>
       </c>
-      <c r="S154" t="s">
-        <v>159</v>
-      </c>
-      <c r="T154" t="s">
-        <v>101</v>
-      </c>
-      <c r="U154" t="s">
-        <v>1035</v>
+      <c r="S154" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="W154" t="s">
-        <v>55</v>
+        <v>953</v>
       </c>
       <c r="X154">
         <v>2</v>
@@ -11759,10 +11839,10 @@
     </row>
     <row r="155" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="B155" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="F155" t="s">
         <v>94</v>
@@ -11771,25 +11851,25 @@
         <v>421</v>
       </c>
       <c r="H155" t="s">
-        <v>76</v>
+        <v>1035</v>
       </c>
       <c r="I155" t="s">
-        <v>29</v>
+        <v>460</v>
       </c>
       <c r="J155" t="s">
-        <v>127</v>
+        <v>461</v>
       </c>
       <c r="M155" t="s">
         <v>1036</v>
       </c>
-      <c r="N155" t="s">
+      <c r="N155" s="2" t="s">
         <v>1037</v>
       </c>
-      <c r="S155" t="s">
+      <c r="S155" s="2" t="s">
         <v>81</v>
       </c>
       <c r="W155" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="X155">
         <v>2</v>
@@ -11797,10 +11877,10 @@
     </row>
     <row r="156" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="B156" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="F156" t="s">
         <v>94</v>
@@ -11815,19 +11895,31 @@
         <v>460</v>
       </c>
       <c r="J156" t="s">
-        <v>461</v>
+        <v>1022</v>
+      </c>
+      <c r="L156" t="s">
+        <v>1023</v>
       </c>
       <c r="M156" t="s">
         <v>1039</v>
       </c>
-      <c r="N156" t="s">
+      <c r="N156" s="2" t="s">
         <v>1040</v>
       </c>
-      <c r="S156" t="s">
-        <v>81</v>
+      <c r="Q156" t="s">
+        <v>1041</v>
+      </c>
+      <c r="S156" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="T156" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="U156" s="1" t="s">
+        <v>1043</v>
       </c>
       <c r="W156" t="s">
-        <v>956</v>
+        <v>55</v>
       </c>
       <c r="X156">
         <v>2</v>
@@ -11835,10 +11927,10 @@
     </row>
     <row r="157" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="B157" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="F157" t="s">
         <v>94</v>
@@ -11847,37 +11939,25 @@
         <v>421</v>
       </c>
       <c r="H157" t="s">
-        <v>1041</v>
+        <v>119</v>
       </c>
       <c r="I157" t="s">
-        <v>460</v>
+        <v>837</v>
       </c>
       <c r="J157" t="s">
-        <v>1025</v>
-      </c>
-      <c r="L157" t="s">
-        <v>1026</v>
+        <v>1044</v>
       </c>
       <c r="M157" t="s">
-        <v>1042</v>
-      </c>
-      <c r="N157" t="s">
-        <v>1043</v>
-      </c>
-      <c r="Q157" t="s">
-        <v>1044</v>
-      </c>
-      <c r="S157" t="s">
-        <v>159</v>
-      </c>
-      <c r="T157" t="s">
         <v>1045</v>
       </c>
-      <c r="U157" t="s">
+      <c r="N157" s="2" t="s">
         <v>1046</v>
       </c>
+      <c r="S157" s="2" t="s">
+        <v>81</v>
+      </c>
       <c r="W157" t="s">
-        <v>55</v>
+        <v>953</v>
       </c>
       <c r="X157">
         <v>2</v>
@@ -11885,10 +11965,10 @@
     </row>
     <row r="158" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="B158" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="F158" t="s">
         <v>94</v>
@@ -11897,25 +11977,37 @@
         <v>421</v>
       </c>
       <c r="H158" t="s">
-        <v>119</v>
+        <v>1000</v>
       </c>
       <c r="I158" t="s">
-        <v>838</v>
+        <v>460</v>
       </c>
       <c r="J158" t="s">
+        <v>1022</v>
+      </c>
+      <c r="L158" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M158" t="s">
         <v>1047</v>
       </c>
-      <c r="M158" t="s">
+      <c r="N158" s="2" t="s">
         <v>1048</v>
       </c>
-      <c r="N158" t="s">
+      <c r="Q158" t="s">
         <v>1049</v>
       </c>
-      <c r="S158" t="s">
-        <v>81</v>
+      <c r="S158" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="T158" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="U158" s="1" t="s">
+        <v>1052</v>
       </c>
       <c r="W158" t="s">
-        <v>956</v>
+        <v>55</v>
       </c>
       <c r="X158">
         <v>2</v>
@@ -11923,87 +12015,81 @@
     </row>
     <row r="159" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>1015</v>
+        <v>1053</v>
       </c>
       <c r="B159" t="s">
-        <v>1016</v>
+        <v>1054</v>
       </c>
       <c r="F159" t="s">
-        <v>94</v>
+        <v>949</v>
       </c>
       <c r="G159" t="s">
-        <v>421</v>
+        <v>1055</v>
       </c>
       <c r="H159" t="s">
-        <v>1003</v>
+        <v>1056</v>
       </c>
       <c r="I159" t="s">
-        <v>460</v>
+        <v>1057</v>
       </c>
       <c r="J159" t="s">
-        <v>1025</v>
-      </c>
-      <c r="L159" t="s">
-        <v>1026</v>
+        <v>1058</v>
       </c>
       <c r="M159" t="s">
-        <v>1050</v>
-      </c>
-      <c r="N159" t="s">
-        <v>1051</v>
-      </c>
-      <c r="Q159" t="s">
-        <v>1052</v>
-      </c>
-      <c r="S159" t="s">
-        <v>1053</v>
-      </c>
-      <c r="T159" t="s">
-        <v>1054</v>
-      </c>
-      <c r="U159" t="s">
-        <v>1055</v>
+        <v>1059</v>
+      </c>
+      <c r="N159" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="S159" s="2" t="s">
+        <v>1061</v>
       </c>
       <c r="W159" t="s">
-        <v>55</v>
+        <v>1062</v>
       </c>
       <c r="X159">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="B160" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="F160" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="G160" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="H160" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="I160" t="s">
-        <v>1060</v>
+        <v>811</v>
       </c>
       <c r="J160" t="s">
-        <v>1061</v>
+        <v>812</v>
       </c>
       <c r="M160" t="s">
-        <v>1062</v>
-      </c>
-      <c r="N160" t="s">
-        <v>1063</v>
-      </c>
-      <c r="S160" t="s">
         <v>1064</v>
       </c>
+      <c r="N160" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="S160" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="T160" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="U160" s="1" t="s">
+        <v>629</v>
+      </c>
       <c r="W160" t="s">
-        <v>1065</v>
+        <v>953</v>
       </c>
       <c r="X160">
         <v>3</v>
@@ -12011,43 +12097,49 @@
     </row>
     <row r="161" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B161" t="s">
-        <v>1057</v>
+        <v>1067</v>
+      </c>
+      <c r="D161" t="s">
+        <v>1068</v>
       </c>
       <c r="F161" t="s">
-        <v>952</v>
+        <v>1069</v>
       </c>
       <c r="G161" t="s">
-        <v>1058</v>
+        <v>458</v>
       </c>
       <c r="H161" t="s">
-        <v>1066</v>
+        <v>205</v>
       </c>
       <c r="I161" t="s">
-        <v>811</v>
+        <v>423</v>
       </c>
       <c r="J161" t="s">
-        <v>812</v>
+        <v>212</v>
       </c>
       <c r="M161" t="s">
-        <v>1067</v>
-      </c>
-      <c r="N161" t="s">
-        <v>1068</v>
-      </c>
-      <c r="S161" t="s">
-        <v>81</v>
-      </c>
-      <c r="T161" t="s">
-        <v>411</v>
-      </c>
-      <c r="U161" t="s">
-        <v>629</v>
+        <v>1070</v>
+      </c>
+      <c r="N161" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>1072</v>
+      </c>
+      <c r="S161" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="T161" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="U161" s="1" t="s">
+        <v>786</v>
       </c>
       <c r="W161" t="s">
-        <v>956</v>
+        <v>36</v>
       </c>
       <c r="X161">
         <v>3</v>
@@ -12055,46 +12147,40 @@
     </row>
     <row r="162" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B162" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F162" t="s">
         <v>1069</v>
-      </c>
-      <c r="B162" t="s">
-        <v>1070</v>
-      </c>
-      <c r="D162" t="s">
-        <v>1071</v>
-      </c>
-      <c r="F162" t="s">
-        <v>1072</v>
       </c>
       <c r="G162" t="s">
         <v>458</v>
       </c>
       <c r="H162" t="s">
-        <v>205</v>
+        <v>421</v>
       </c>
       <c r="I162" t="s">
-        <v>423</v>
+        <v>29</v>
       </c>
       <c r="J162" t="s">
-        <v>212</v>
+        <v>127</v>
       </c>
       <c r="M162" t="s">
-        <v>1073</v>
-      </c>
-      <c r="N162" t="s">
         <v>1074</v>
       </c>
-      <c r="Q162" t="s">
+      <c r="N162" s="2" t="s">
         <v>1075</v>
       </c>
-      <c r="S162" t="s">
-        <v>217</v>
-      </c>
-      <c r="T162" t="s">
+      <c r="S162" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="T162" s="1" t="s">
         <v>1076</v>
       </c>
-      <c r="U162" t="s">
-        <v>786</v>
+      <c r="U162" s="1" t="s">
+        <v>1042</v>
       </c>
       <c r="W162" t="s">
         <v>36</v>
@@ -12105,40 +12191,46 @@
     </row>
     <row r="163" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>1069</v>
+        <v>1077</v>
       </c>
       <c r="B163" t="s">
-        <v>1070</v>
+        <v>1078</v>
       </c>
       <c r="F163" t="s">
-        <v>1072</v>
+        <v>1079</v>
       </c>
       <c r="G163" t="s">
-        <v>458</v>
+        <v>1055</v>
       </c>
       <c r="H163" t="s">
-        <v>421</v>
+        <v>37</v>
       </c>
       <c r="I163" t="s">
         <v>29</v>
       </c>
       <c r="J163" t="s">
-        <v>127</v>
+        <v>482</v>
       </c>
       <c r="M163" t="s">
-        <v>1077</v>
-      </c>
-      <c r="N163" t="s">
-        <v>1078</v>
-      </c>
-      <c r="S163" t="s">
-        <v>81</v>
-      </c>
-      <c r="T163" t="s">
-        <v>1079</v>
-      </c>
-      <c r="U163" t="s">
-        <v>1045</v>
+        <v>1080</v>
+      </c>
+      <c r="N163" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="O163" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>1083</v>
+      </c>
+      <c r="S163" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="T163" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="U163" s="1">
+        <v>12</v>
       </c>
       <c r="W163" t="s">
         <v>36</v>
@@ -12149,46 +12241,43 @@
     </row>
     <row r="164" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="B164" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="F164" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="G164" t="s">
-        <v>1058</v>
-      </c>
-      <c r="H164" t="s">
-        <v>37</v>
+        <v>1055</v>
+      </c>
+      <c r="H164">
+        <v>1475</v>
       </c>
       <c r="I164" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="J164" t="s">
-        <v>482</v>
+        <v>70</v>
       </c>
       <c r="M164" t="s">
-        <v>1083</v>
-      </c>
-      <c r="N164" t="s">
         <v>1084</v>
       </c>
-      <c r="O164" t="s">
+      <c r="N164" s="2" t="s">
         <v>1085</v>
       </c>
       <c r="Q164" t="s">
         <v>1086</v>
       </c>
-      <c r="S164" t="s">
-        <v>204</v>
-      </c>
-      <c r="T164" t="s">
-        <v>395</v>
-      </c>
-      <c r="U164">
-        <v>12</v>
+      <c r="S164" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="T164" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U164" s="1" t="s">
+        <v>1089</v>
       </c>
       <c r="W164" t="s">
         <v>36</v>
@@ -12199,46 +12288,43 @@
     </row>
     <row r="165" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>1080</v>
+        <v>247</v>
       </c>
       <c r="B165" t="s">
-        <v>1081</v>
+        <v>1090</v>
       </c>
       <c r="F165" t="s">
-        <v>1082</v>
+        <v>49</v>
       </c>
       <c r="G165" t="s">
-        <v>1058</v>
-      </c>
-      <c r="H165">
-        <v>1475</v>
+        <v>1091</v>
+      </c>
+      <c r="H165" t="s">
+        <v>1092</v>
       </c>
       <c r="I165" t="s">
-        <v>69</v>
+        <v>1093</v>
       </c>
       <c r="J165" t="s">
-        <v>70</v>
+        <v>1094</v>
       </c>
       <c r="M165" t="s">
-        <v>1087</v>
-      </c>
-      <c r="N165" t="s">
-        <v>1088</v>
-      </c>
-      <c r="Q165" t="s">
-        <v>1089</v>
-      </c>
-      <c r="S165" t="s">
-        <v>1090</v>
-      </c>
-      <c r="T165" t="s">
-        <v>1091</v>
-      </c>
-      <c r="U165" t="s">
-        <v>1092</v>
+        <v>1095</v>
+      </c>
+      <c r="N165" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="S165" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="T165" s="1">
+        <v>143</v>
+      </c>
+      <c r="U165" s="1">
+        <v>260</v>
       </c>
       <c r="W165" t="s">
-        <v>36</v>
+        <v>256</v>
       </c>
       <c r="X165">
         <v>3</v>
@@ -12246,40 +12332,40 @@
     </row>
     <row r="166" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>247</v>
+        <v>1098</v>
       </c>
       <c r="B166" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="F166" t="s">
-        <v>49</v>
+        <v>347</v>
       </c>
       <c r="G166" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="H166" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="I166" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="J166" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="M166" t="s">
-        <v>1098</v>
-      </c>
-      <c r="N166" t="s">
-        <v>1099</v>
-      </c>
-      <c r="S166" t="s">
-        <v>1100</v>
-      </c>
-      <c r="T166">
-        <v>143</v>
-      </c>
-      <c r="U166">
-        <v>260</v>
+        <v>734</v>
+      </c>
+      <c r="N166" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="S166" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="T166" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="U166" s="1" t="s">
+        <v>761</v>
       </c>
       <c r="W166" t="s">
         <v>256</v>
@@ -12290,40 +12376,40 @@
     </row>
     <row r="167" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="B167" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="F167" t="s">
         <v>347</v>
       </c>
       <c r="G167" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="H167" t="s">
-        <v>1104</v>
+        <v>614</v>
       </c>
       <c r="I167" t="s">
-        <v>1105</v>
+        <v>38</v>
       </c>
       <c r="J167" t="s">
+        <v>39</v>
+      </c>
+      <c r="M167" t="s">
         <v>1106</v>
       </c>
-      <c r="M167" t="s">
-        <v>734</v>
-      </c>
-      <c r="N167" t="s">
+      <c r="N167" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="S167" t="s">
-        <v>109</v>
-      </c>
-      <c r="T167" t="s">
+      <c r="S167" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="T167" s="1" t="s">
         <v>1108</v>
       </c>
-      <c r="U167" t="s">
-        <v>761</v>
+      <c r="U167" s="1" t="s">
+        <v>1109</v>
       </c>
       <c r="W167" t="s">
         <v>256</v>
@@ -12334,43 +12420,52 @@
     </row>
     <row r="168" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>1101</v>
+        <v>1110</v>
       </c>
       <c r="B168" t="s">
-        <v>1102</v>
+        <v>1111</v>
       </c>
       <c r="F168" t="s">
-        <v>347</v>
+        <v>1112</v>
       </c>
       <c r="G168" t="s">
-        <v>1103</v>
+        <v>62</v>
       </c>
       <c r="H168" t="s">
-        <v>614</v>
+        <v>205</v>
       </c>
       <c r="I168" t="s">
-        <v>38</v>
+        <v>210</v>
       </c>
       <c r="J168" t="s">
-        <v>39</v>
+        <v>211</v>
+      </c>
+      <c r="L168" t="s">
+        <v>1113</v>
       </c>
       <c r="M168" t="s">
-        <v>1109</v>
-      </c>
-      <c r="N168" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S168" t="s">
-        <v>81</v>
-      </c>
-      <c r="T168" t="s">
-        <v>1111</v>
-      </c>
-      <c r="U168" t="s">
-        <v>1112</v>
+        <v>1114</v>
+      </c>
+      <c r="N168" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="O168" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="Q168" t="s">
+        <v>1117</v>
+      </c>
+      <c r="S168" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="T168" s="1">
+        <v>349</v>
+      </c>
+      <c r="U168" s="1">
+        <v>570</v>
       </c>
       <c r="W168" t="s">
-        <v>256</v>
+        <v>36</v>
       </c>
       <c r="X168">
         <v>3</v>
@@ -12378,13 +12473,13 @@
     </row>
     <row r="169" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="B169" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="F169" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="G169" t="s">
         <v>62</v>
@@ -12399,27 +12494,27 @@
         <v>211</v>
       </c>
       <c r="L169" t="s">
+        <v>1113</v>
+      </c>
+      <c r="M169" t="s">
+        <v>549</v>
+      </c>
+      <c r="N169" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="O169" s="2" t="s">
         <v>1116</v>
       </c>
-      <c r="M169" t="s">
-        <v>1117</v>
-      </c>
-      <c r="N169" t="s">
-        <v>1118</v>
-      </c>
-      <c r="O169" t="s">
-        <v>1119</v>
-      </c>
       <c r="Q169" t="s">
-        <v>1120</v>
-      </c>
-      <c r="S169" t="s">
+        <v>562</v>
+      </c>
+      <c r="S169" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="T169">
+      <c r="T169" s="1">
         <v>349</v>
       </c>
-      <c r="U169">
+      <c r="U169" s="1">
         <v>570</v>
       </c>
       <c r="W169" t="s">
@@ -12431,49 +12526,40 @@
     </row>
     <row r="170" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="B170" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="F170" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="G170" t="s">
-        <v>62</v>
+        <v>458</v>
       </c>
       <c r="H170" t="s">
-        <v>205</v>
+        <v>1122</v>
       </c>
       <c r="I170" t="s">
-        <v>210</v>
+        <v>104</v>
       </c>
       <c r="J170" t="s">
-        <v>211</v>
-      </c>
-      <c r="L170" t="s">
-        <v>1116</v>
+        <v>105</v>
       </c>
       <c r="M170" t="s">
-        <v>549</v>
-      </c>
-      <c r="N170" t="s">
-        <v>1121</v>
-      </c>
-      <c r="O170" t="s">
-        <v>1119</v>
-      </c>
-      <c r="Q170" t="s">
-        <v>562</v>
-      </c>
-      <c r="S170" t="s">
-        <v>217</v>
-      </c>
-      <c r="T170">
-        <v>349</v>
-      </c>
-      <c r="U170">
-        <v>570</v>
+        <v>1123</v>
+      </c>
+      <c r="N170" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="S170" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T170" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="U170" s="1" t="s">
+        <v>1126</v>
       </c>
       <c r="W170" t="s">
         <v>36</v>
@@ -12484,40 +12570,46 @@
     </row>
     <row r="171" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="B171" t="s">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="F171" t="s">
-        <v>1124</v>
+        <v>94</v>
       </c>
       <c r="G171" t="s">
-        <v>458</v>
-      </c>
-      <c r="H171" t="s">
-        <v>1125</v>
+        <v>339</v>
+      </c>
+      <c r="H171">
+        <v>1469</v>
       </c>
       <c r="I171" t="s">
-        <v>104</v>
+        <v>575</v>
       </c>
       <c r="J171" t="s">
-        <v>105</v>
+        <v>1129</v>
       </c>
       <c r="M171" t="s">
-        <v>1126</v>
-      </c>
-      <c r="N171" t="s">
-        <v>1127</v>
-      </c>
-      <c r="S171" t="s">
-        <v>33</v>
-      </c>
-      <c r="T171" t="s">
-        <v>1128</v>
-      </c>
-      <c r="U171" t="s">
-        <v>1129</v>
+        <v>1130</v>
+      </c>
+      <c r="N171" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="O171" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="Q171" t="s">
+        <v>1133</v>
+      </c>
+      <c r="S171" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="T171" s="1">
+        <v>349</v>
+      </c>
+      <c r="U171" s="1">
+        <v>152</v>
       </c>
       <c r="W171" t="s">
         <v>36</v>
@@ -12528,10 +12620,10 @@
     </row>
     <row r="172" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="B172" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="F172" t="s">
         <v>94</v>
@@ -12539,35 +12631,35 @@
       <c r="G172" t="s">
         <v>339</v>
       </c>
-      <c r="H172">
-        <v>1469</v>
+      <c r="H172" t="s">
+        <v>1134</v>
       </c>
       <c r="I172" t="s">
-        <v>575</v>
+        <v>69</v>
       </c>
       <c r="J172" t="s">
-        <v>1132</v>
+        <v>70</v>
       </c>
       <c r="M172" t="s">
-        <v>1133</v>
-      </c>
-      <c r="N172" t="s">
-        <v>1134</v>
-      </c>
-      <c r="O172" t="s">
         <v>1135</v>
       </c>
+      <c r="N172" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="O172" s="2" t="s">
+        <v>1137</v>
+      </c>
       <c r="Q172" t="s">
-        <v>1136</v>
-      </c>
-      <c r="S172" t="s">
-        <v>85</v>
-      </c>
-      <c r="T172">
-        <v>349</v>
-      </c>
-      <c r="U172">
-        <v>152</v>
+        <v>1138</v>
+      </c>
+      <c r="S172" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="T172" s="1">
+        <v>239</v>
+      </c>
+      <c r="U172" s="1">
+        <v>102</v>
       </c>
       <c r="W172" t="s">
         <v>36</v>
@@ -12578,93 +12670,93 @@
     </row>
     <row r="173" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>1130</v>
+        <v>1140</v>
       </c>
       <c r="B173" t="s">
-        <v>1131</v>
+        <v>1141</v>
       </c>
       <c r="F173" t="s">
-        <v>94</v>
+        <v>1142</v>
       </c>
       <c r="G173" t="s">
-        <v>339</v>
+        <v>196</v>
       </c>
       <c r="H173" t="s">
-        <v>1137</v>
+        <v>1143</v>
       </c>
       <c r="I173" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="J173" t="s">
-        <v>70</v>
+        <v>127</v>
       </c>
       <c r="M173" t="s">
-        <v>1138</v>
-      </c>
-      <c r="N173" t="s">
-        <v>1139</v>
-      </c>
-      <c r="O173" t="s">
-        <v>1140</v>
+        <v>1144</v>
+      </c>
+      <c r="N173" s="2" t="s">
+        <v>1145</v>
       </c>
       <c r="Q173" t="s">
-        <v>1141</v>
-      </c>
-      <c r="S173" t="s">
-        <v>1142</v>
-      </c>
-      <c r="T173">
-        <v>239</v>
-      </c>
-      <c r="U173">
-        <v>102</v>
+        <v>1146</v>
+      </c>
+      <c r="S173" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="T173" s="1">
+        <v>182</v>
+      </c>
+      <c r="U173" s="1">
+        <v>323</v>
       </c>
       <c r="W173" t="s">
         <v>36</v>
       </c>
       <c r="X173">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="B174" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="F174" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="G174" t="s">
         <v>196</v>
       </c>
       <c r="H174" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="I174" t="s">
         <v>29</v>
       </c>
       <c r="J174" t="s">
-        <v>127</v>
+        <v>563</v>
+      </c>
+      <c r="L174" t="s">
+        <v>1149</v>
       </c>
       <c r="M174" t="s">
-        <v>1147</v>
-      </c>
-      <c r="N174" t="s">
-        <v>1148</v>
+        <v>1150</v>
+      </c>
+      <c r="N174" s="2" t="s">
+        <v>1151</v>
       </c>
       <c r="Q174" t="s">
-        <v>1149</v>
-      </c>
-      <c r="S174" t="s">
-        <v>1150</v>
-      </c>
-      <c r="T174">
-        <v>182</v>
-      </c>
-      <c r="U174">
-        <v>323</v>
+        <v>1152</v>
+      </c>
+      <c r="S174" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="T174" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="U174" s="1" t="s">
+        <v>1155</v>
       </c>
       <c r="W174" t="s">
         <v>36</v>
@@ -12675,19 +12767,19 @@
     </row>
     <row r="175" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="B175" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="F175" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="G175" t="s">
         <v>196</v>
       </c>
       <c r="H175" t="s">
-        <v>1151</v>
+        <v>572</v>
       </c>
       <c r="I175" t="s">
         <v>29</v>
@@ -12695,26 +12787,14 @@
       <c r="J175" t="s">
         <v>563</v>
       </c>
-      <c r="L175" t="s">
-        <v>1152</v>
-      </c>
       <c r="M175" t="s">
-        <v>1153</v>
-      </c>
-      <c r="N175" t="s">
-        <v>1154</v>
-      </c>
-      <c r="Q175" t="s">
-        <v>1155</v>
-      </c>
-      <c r="S175" t="s">
         <v>1156</v>
       </c>
-      <c r="T175" t="s">
+      <c r="N175" s="2" t="s">
         <v>1157</v>
       </c>
-      <c r="U175" t="s">
-        <v>1158</v>
+      <c r="S175" s="2" t="s">
+        <v>217</v>
       </c>
       <c r="W175" t="s">
         <v>36</v>
@@ -12725,34 +12805,43 @@
     </row>
     <row r="176" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="B176" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="F176" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="G176" t="s">
         <v>196</v>
       </c>
       <c r="H176" t="s">
-        <v>572</v>
+        <v>758</v>
       </c>
       <c r="I176" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="J176" t="s">
-        <v>563</v>
+        <v>70</v>
       </c>
       <c r="M176" t="s">
+        <v>1158</v>
+      </c>
+      <c r="N176" s="2" t="s">
         <v>1159</v>
       </c>
-      <c r="N176" t="s">
+      <c r="Q176" t="s">
         <v>1160</v>
       </c>
-      <c r="S176" t="s">
-        <v>217</v>
+      <c r="S176" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="T176" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="U176" s="1">
+        <v>322</v>
       </c>
       <c r="W176" t="s">
         <v>36</v>
@@ -12763,43 +12852,43 @@
     </row>
     <row r="177" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="B177" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="F177" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="G177" t="s">
         <v>196</v>
       </c>
       <c r="H177" t="s">
-        <v>758</v>
+        <v>1163</v>
       </c>
       <c r="I177" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="J177" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="M177" t="s">
-        <v>1161</v>
-      </c>
-      <c r="N177" t="s">
-        <v>1162</v>
+        <v>1164</v>
+      </c>
+      <c r="N177" s="2" t="s">
+        <v>1165</v>
       </c>
       <c r="Q177" t="s">
-        <v>1163</v>
-      </c>
-      <c r="S177" t="s">
-        <v>1164</v>
-      </c>
-      <c r="T177" t="s">
-        <v>1165</v>
-      </c>
-      <c r="U177">
-        <v>322</v>
+        <v>1166</v>
+      </c>
+      <c r="S177" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="T177" s="1">
+        <v>182</v>
+      </c>
+      <c r="U177" s="1">
+        <v>317</v>
       </c>
       <c r="W177" t="s">
         <v>36</v>
@@ -12810,43 +12899,34 @@
     </row>
     <row r="178" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="B178" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="F178" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="G178" t="s">
         <v>196</v>
       </c>
       <c r="H178" t="s">
-        <v>1166</v>
+        <v>154</v>
       </c>
       <c r="I178" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J178" t="s">
-        <v>39</v>
+        <v>1168</v>
       </c>
       <c r="M178" t="s">
-        <v>1167</v>
-      </c>
-      <c r="N178" t="s">
-        <v>1168</v>
-      </c>
-      <c r="Q178" t="s">
         <v>1169</v>
       </c>
-      <c r="S178" t="s">
+      <c r="N178" s="2" t="s">
         <v>1170</v>
       </c>
-      <c r="T178">
-        <v>182</v>
-      </c>
-      <c r="U178">
-        <v>317</v>
+      <c r="S178" s="2" t="s">
+        <v>217</v>
       </c>
       <c r="W178" t="s">
         <v>36</v>
@@ -12857,34 +12937,40 @@
     </row>
     <row r="179" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="B179" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="F179" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="G179" t="s">
         <v>196</v>
       </c>
       <c r="H179" t="s">
-        <v>154</v>
+        <v>103</v>
       </c>
       <c r="I179" t="s">
-        <v>29</v>
+        <v>1171</v>
       </c>
       <c r="J179" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="M179" t="s">
-        <v>1172</v>
-      </c>
-      <c r="N179" t="s">
         <v>1173</v>
       </c>
-      <c r="S179" t="s">
-        <v>217</v>
+      <c r="N179" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="S179" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="T179" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="U179" s="1" t="s">
+        <v>1176</v>
       </c>
       <c r="W179" t="s">
         <v>36</v>
@@ -12895,40 +12981,43 @@
     </row>
     <row r="180" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="B180" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="F180" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="G180" t="s">
         <v>196</v>
       </c>
       <c r="H180" t="s">
-        <v>103</v>
+        <v>637</v>
       </c>
       <c r="I180" t="s">
-        <v>1174</v>
+        <v>69</v>
       </c>
       <c r="J180" t="s">
-        <v>1175</v>
+        <v>70</v>
       </c>
       <c r="M180" t="s">
-        <v>1176</v>
-      </c>
-      <c r="N180" t="s">
         <v>1177</v>
       </c>
-      <c r="S180" t="s">
-        <v>109</v>
-      </c>
-      <c r="T180" t="s">
+      <c r="N180" s="2" t="s">
         <v>1178</v>
       </c>
-      <c r="U180" t="s">
+      <c r="Q180" t="s">
+        <v>1133</v>
+      </c>
+      <c r="S180" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="T180" s="1" t="s">
         <v>1179</v>
+      </c>
+      <c r="U180" s="1" t="s">
+        <v>1180</v>
       </c>
       <c r="W180" t="s">
         <v>36</v>
@@ -12939,46 +13028,49 @@
     </row>
     <row r="181" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>1143</v>
+        <v>1181</v>
       </c>
       <c r="B181" t="s">
-        <v>1144</v>
+        <v>1182</v>
       </c>
       <c r="F181" t="s">
-        <v>1145</v>
+        <v>135</v>
       </c>
       <c r="G181" t="s">
-        <v>196</v>
+        <v>681</v>
       </c>
       <c r="H181" t="s">
         <v>637</v>
       </c>
       <c r="I181" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="J181" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="M181" t="s">
-        <v>1180</v>
-      </c>
-      <c r="N181" t="s">
-        <v>1181</v>
+        <v>1183</v>
+      </c>
+      <c r="N181" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="O181" s="2" t="s">
+        <v>1185</v>
       </c>
       <c r="Q181" t="s">
-        <v>1136</v>
-      </c>
-      <c r="S181" t="s">
-        <v>73</v>
-      </c>
-      <c r="T181" t="s">
-        <v>1182</v>
-      </c>
-      <c r="U181" t="s">
-        <v>1183</v>
+        <v>1186</v>
+      </c>
+      <c r="S181" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="T181" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="U181" s="1" t="s">
+        <v>1188</v>
       </c>
       <c r="W181" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="X181">
         <v>2</v>
@@ -12986,10 +13078,10 @@
     </row>
     <row r="182" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="B182" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="F182" t="s">
         <v>135</v>
@@ -13001,31 +13093,19 @@
         <v>637</v>
       </c>
       <c r="I182" t="s">
-        <v>77</v>
+        <v>1189</v>
       </c>
       <c r="J182" t="s">
-        <v>78</v>
+        <v>1190</v>
       </c>
       <c r="M182" t="s">
-        <v>1186</v>
-      </c>
-      <c r="N182" t="s">
-        <v>1187</v>
-      </c>
-      <c r="O182" t="s">
-        <v>1188</v>
-      </c>
-      <c r="Q182" t="s">
-        <v>1189</v>
-      </c>
-      <c r="S182" t="s">
-        <v>848</v>
-      </c>
-      <c r="T182" t="s">
-        <v>1190</v>
-      </c>
-      <c r="U182" t="s">
         <v>1191</v>
+      </c>
+      <c r="N182" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="S182" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="W182" t="s">
         <v>55</v>
@@ -13036,10 +13116,10 @@
     </row>
     <row r="183" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="B183" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="F183" t="s">
         <v>135</v>
@@ -13048,22 +13128,31 @@
         <v>681</v>
       </c>
       <c r="H183" t="s">
-        <v>637</v>
+        <v>1193</v>
       </c>
       <c r="I183" t="s">
-        <v>1192</v>
+        <v>29</v>
       </c>
       <c r="J183" t="s">
-        <v>1193</v>
+        <v>127</v>
       </c>
       <c r="M183" t="s">
         <v>1194</v>
       </c>
-      <c r="N183" t="s">
+      <c r="N183" s="2" t="s">
         <v>1195</v>
       </c>
-      <c r="S183" t="s">
+      <c r="Q183" t="s">
+        <v>1196</v>
+      </c>
+      <c r="S183" s="2" t="s">
         <v>81</v>
+      </c>
+      <c r="T183" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="U183" s="1" t="s">
+        <v>1197</v>
       </c>
       <c r="W183" t="s">
         <v>55</v>
@@ -13074,10 +13163,10 @@
     </row>
     <row r="184" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="B184" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="F184" t="s">
         <v>135</v>
@@ -13086,31 +13175,31 @@
         <v>681</v>
       </c>
       <c r="H184" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="I184" t="s">
-        <v>29</v>
+        <v>1199</v>
       </c>
       <c r="J184" t="s">
-        <v>127</v>
+        <v>1200</v>
       </c>
       <c r="M184" t="s">
-        <v>1197</v>
-      </c>
-      <c r="N184" t="s">
-        <v>1198</v>
+        <v>1201</v>
+      </c>
+      <c r="N184" s="2" t="s">
+        <v>1202</v>
       </c>
       <c r="Q184" t="s">
-        <v>1199</v>
-      </c>
-      <c r="S184" t="s">
-        <v>81</v>
-      </c>
-      <c r="T184" t="s">
-        <v>310</v>
-      </c>
-      <c r="U184" t="s">
-        <v>1200</v>
+        <v>1203</v>
+      </c>
+      <c r="S184" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="T184" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="U184" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="W184" t="s">
         <v>55</v>
@@ -13121,10 +13210,10 @@
     </row>
     <row r="185" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="B185" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="F185" t="s">
         <v>135</v>
@@ -13133,31 +13222,22 @@
         <v>681</v>
       </c>
       <c r="H185" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="I185" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="J185" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="M185" t="s">
-        <v>1204</v>
-      </c>
-      <c r="N185" t="s">
-        <v>1205</v>
-      </c>
-      <c r="Q185" t="s">
         <v>1206</v>
       </c>
-      <c r="S185" t="s">
-        <v>159</v>
-      </c>
-      <c r="T185" t="s">
-        <v>464</v>
-      </c>
-      <c r="U185" t="s">
-        <v>117</v>
+      <c r="N185" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="S185" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="W185" t="s">
         <v>55</v>
@@ -13168,10 +13248,10 @@
     </row>
     <row r="186" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="B186" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="F186" t="s">
         <v>135</v>
@@ -13180,22 +13260,31 @@
         <v>681</v>
       </c>
       <c r="H186" t="s">
-        <v>1207</v>
+        <v>76</v>
       </c>
       <c r="I186" t="s">
-        <v>1202</v>
+        <v>460</v>
       </c>
       <c r="J186" t="s">
+        <v>461</v>
+      </c>
+      <c r="M186" t="s">
         <v>1208</v>
       </c>
-      <c r="M186" t="s">
+      <c r="N186" s="2" t="s">
         <v>1209</v>
       </c>
-      <c r="N186" t="s">
+      <c r="Q186" t="s">
         <v>1210</v>
       </c>
-      <c r="S186" t="s">
-        <v>81</v>
+      <c r="S186" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="T186" s="1" t="s">
+        <v>1211</v>
+      </c>
+      <c r="U186" s="1" t="s">
+        <v>1212</v>
       </c>
       <c r="W186" t="s">
         <v>55</v>
@@ -13206,10 +13295,10 @@
     </row>
     <row r="187" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="B187" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="F187" t="s">
         <v>135</v>
@@ -13221,28 +13310,28 @@
         <v>76</v>
       </c>
       <c r="I187" t="s">
-        <v>460</v>
+        <v>77</v>
       </c>
       <c r="J187" t="s">
-        <v>461</v>
+        <v>78</v>
       </c>
       <c r="M187" t="s">
-        <v>1211</v>
-      </c>
-      <c r="N187" t="s">
-        <v>1212</v>
+        <v>1213</v>
+      </c>
+      <c r="N187" s="2" t="s">
+        <v>1214</v>
       </c>
       <c r="Q187" t="s">
-        <v>1213</v>
-      </c>
-      <c r="S187" t="s">
-        <v>848</v>
-      </c>
-      <c r="T187" t="s">
-        <v>1214</v>
-      </c>
-      <c r="U187" t="s">
         <v>1215</v>
+      </c>
+      <c r="S187" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="T187" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="U187" s="1" t="s">
+        <v>1217</v>
       </c>
       <c r="W187" t="s">
         <v>55</v>
@@ -13253,87 +13342,84 @@
     </row>
     <row r="188" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>1184</v>
+        <v>1218</v>
       </c>
       <c r="B188" t="s">
-        <v>1185</v>
+        <v>1219</v>
       </c>
       <c r="F188" t="s">
-        <v>135</v>
+        <v>1220</v>
       </c>
       <c r="G188" t="s">
-        <v>681</v>
+        <v>1221</v>
       </c>
       <c r="H188" t="s">
-        <v>76</v>
+        <v>949</v>
       </c>
       <c r="I188" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="J188" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="M188" t="s">
-        <v>1216</v>
-      </c>
-      <c r="N188" t="s">
-        <v>1217</v>
-      </c>
-      <c r="Q188" t="s">
-        <v>1218</v>
-      </c>
-      <c r="S188" t="s">
-        <v>159</v>
-      </c>
-      <c r="T188" t="s">
-        <v>1219</v>
-      </c>
-      <c r="U188" t="s">
-        <v>1220</v>
+        <v>742</v>
+      </c>
+      <c r="N188" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="S188" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="T188" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="U188" s="1" t="s">
+        <v>1223</v>
       </c>
       <c r="W188" t="s">
         <v>55</v>
       </c>
       <c r="X188">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B189" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F189" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G189" t="s">
         <v>1221</v>
       </c>
-      <c r="B189" t="s">
-        <v>1222</v>
-      </c>
-      <c r="F189" t="s">
-        <v>1223</v>
-      </c>
-      <c r="G189" t="s">
+      <c r="H189" t="s">
         <v>1224</v>
       </c>
-      <c r="H189" t="s">
-        <v>952</v>
-      </c>
       <c r="I189" t="s">
-        <v>138</v>
+        <v>1225</v>
       </c>
       <c r="J189" t="s">
-        <v>139</v>
+        <v>1226</v>
       </c>
       <c r="M189" t="s">
-        <v>742</v>
-      </c>
-      <c r="N189" t="s">
-        <v>1225</v>
-      </c>
-      <c r="S189" t="s">
-        <v>81</v>
-      </c>
-      <c r="T189" t="s">
-        <v>761</v>
-      </c>
-      <c r="U189" t="s">
-        <v>1226</v>
+        <v>1227</v>
+      </c>
+      <c r="N189" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="S189" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="T189" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="U189" s="1" t="s">
+        <v>1229</v>
       </c>
       <c r="W189" t="s">
         <v>55</v>
@@ -13344,40 +13430,40 @@
     </row>
     <row r="190" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B190" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F190" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G190" t="s">
         <v>1221</v>
       </c>
-      <c r="B190" t="s">
-        <v>1222</v>
-      </c>
-      <c r="F190" t="s">
-        <v>1223</v>
-      </c>
-      <c r="G190" t="s">
-        <v>1224</v>
-      </c>
       <c r="H190" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="I190" t="s">
-        <v>1228</v>
+        <v>837</v>
       </c>
       <c r="J190" t="s">
-        <v>1229</v>
+        <v>838</v>
       </c>
       <c r="M190" t="s">
-        <v>1230</v>
-      </c>
-      <c r="N190" t="s">
         <v>1231</v>
       </c>
-      <c r="S190" t="s">
-        <v>401</v>
-      </c>
-      <c r="T190" t="s">
-        <v>585</v>
-      </c>
-      <c r="U190" t="s">
+      <c r="N190" s="2" t="s">
         <v>1232</v>
+      </c>
+      <c r="S190" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="T190" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U190" s="1" t="s">
+        <v>1233</v>
       </c>
       <c r="W190" t="s">
         <v>55</v>
@@ -13388,40 +13474,40 @@
     </row>
     <row r="191" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B191" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F191" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G191" t="s">
         <v>1221</v>
       </c>
-      <c r="B191" t="s">
-        <v>1222</v>
-      </c>
-      <c r="F191" t="s">
-        <v>1223</v>
-      </c>
-      <c r="G191" t="s">
-        <v>1224</v>
-      </c>
       <c r="H191" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="I191" t="s">
-        <v>838</v>
+        <v>275</v>
       </c>
       <c r="J191" t="s">
-        <v>839</v>
+        <v>276</v>
       </c>
       <c r="M191" t="s">
-        <v>1234</v>
-      </c>
-      <c r="N191" t="s">
+        <v>863</v>
+      </c>
+      <c r="N191" s="2" t="s">
         <v>1235</v>
       </c>
-      <c r="S191" t="s">
+      <c r="S191" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="T191" t="s">
-        <v>132</v>
-      </c>
-      <c r="U191" t="s">
-        <v>1236</v>
+      <c r="T191" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="U191" s="1" t="s">
+        <v>1042</v>
       </c>
       <c r="W191" t="s">
         <v>55</v>
@@ -13432,40 +13518,40 @@
     </row>
     <row r="192" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B192" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F192" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G192" t="s">
         <v>1221</v>
       </c>
-      <c r="B192" t="s">
-        <v>1222</v>
-      </c>
-      <c r="F192" t="s">
-        <v>1223</v>
-      </c>
-      <c r="G192" t="s">
-        <v>1224</v>
-      </c>
       <c r="H192" t="s">
+        <v>1236</v>
+      </c>
+      <c r="I192" t="s">
+        <v>77</v>
+      </c>
+      <c r="J192" t="s">
+        <v>78</v>
+      </c>
+      <c r="M192" t="s">
         <v>1237</v>
       </c>
-      <c r="I192" t="s">
-        <v>275</v>
-      </c>
-      <c r="J192" t="s">
-        <v>276</v>
-      </c>
-      <c r="M192" t="s">
-        <v>866</v>
-      </c>
-      <c r="N192" t="s">
+      <c r="N192" s="2" t="s">
         <v>1238</v>
       </c>
-      <c r="S192" t="s">
+      <c r="S192" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="T192" t="s">
-        <v>161</v>
-      </c>
-      <c r="U192" t="s">
-        <v>1045</v>
+      <c r="T192" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="U192" s="1" t="s">
+        <v>1239</v>
       </c>
       <c r="W192" t="s">
         <v>55</v>
@@ -13476,40 +13562,43 @@
     </row>
     <row r="193" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B193" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F193" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G193" t="s">
         <v>1221</v>
       </c>
-      <c r="B193" t="s">
-        <v>1222</v>
-      </c>
-      <c r="F193" t="s">
-        <v>1223</v>
-      </c>
-      <c r="G193" t="s">
-        <v>1224</v>
-      </c>
       <c r="H193" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="I193" t="s">
-        <v>77</v>
+        <v>1241</v>
       </c>
       <c r="J193" t="s">
-        <v>78</v>
+        <v>1242</v>
       </c>
       <c r="M193" t="s">
-        <v>1240</v>
-      </c>
-      <c r="N193" t="s">
-        <v>1241</v>
-      </c>
-      <c r="S193" t="s">
-        <v>81</v>
-      </c>
-      <c r="T193" t="s">
-        <v>178</v>
-      </c>
-      <c r="U193" t="s">
-        <v>1242</v>
+        <v>1243</v>
+      </c>
+      <c r="N193" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="O193" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="S193" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="T193" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="U193" s="1" t="s">
+        <v>1247</v>
       </c>
       <c r="W193" t="s">
         <v>55</v>
@@ -13520,43 +13609,40 @@
     </row>
     <row r="194" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B194" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F194" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G194" t="s">
         <v>1221</v>
       </c>
-      <c r="B194" t="s">
-        <v>1222</v>
-      </c>
-      <c r="F194" t="s">
-        <v>1223</v>
-      </c>
-      <c r="G194" t="s">
-        <v>1224</v>
-      </c>
       <c r="H194" t="s">
-        <v>1243</v>
+        <v>1248</v>
       </c>
       <c r="I194" t="s">
-        <v>1244</v>
+        <v>77</v>
       </c>
       <c r="J194" t="s">
-        <v>1245</v>
+        <v>78</v>
       </c>
       <c r="M194" t="s">
-        <v>1246</v>
-      </c>
-      <c r="N194" t="s">
-        <v>1247</v>
-      </c>
-      <c r="O194" t="s">
-        <v>1248</v>
-      </c>
-      <c r="S194" t="s">
         <v>1249</v>
       </c>
-      <c r="T194" t="s">
-        <v>761</v>
-      </c>
-      <c r="U194" t="s">
+      <c r="N194" s="2" t="s">
         <v>1250</v>
+      </c>
+      <c r="S194" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="T194" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="U194" s="1" t="s">
+        <v>1251</v>
       </c>
       <c r="W194" t="s">
         <v>55</v>
@@ -13567,40 +13653,34 @@
     </row>
     <row r="195" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B195" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F195" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G195" t="s">
         <v>1221</v>
       </c>
-      <c r="B195" t="s">
-        <v>1222</v>
-      </c>
-      <c r="F195" t="s">
-        <v>1223</v>
-      </c>
-      <c r="G195" t="s">
-        <v>1224</v>
-      </c>
       <c r="H195" t="s">
-        <v>1251</v>
+        <v>154</v>
       </c>
       <c r="I195" t="s">
-        <v>77</v>
+        <v>837</v>
       </c>
       <c r="J195" t="s">
-        <v>78</v>
+        <v>1044</v>
       </c>
       <c r="M195" t="s">
-        <v>1252</v>
-      </c>
-      <c r="N195" t="s">
         <v>1253</v>
       </c>
-      <c r="S195" t="s">
+      <c r="N195" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="S195" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="T195" t="s">
-        <v>1055</v>
-      </c>
-      <c r="U195" t="s">
-        <v>1254</v>
       </c>
       <c r="W195" t="s">
         <v>55</v>
@@ -13611,34 +13691,40 @@
     </row>
     <row r="196" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B196" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F196" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G196" t="s">
         <v>1221</v>
       </c>
-      <c r="B196" t="s">
-        <v>1222</v>
-      </c>
-      <c r="F196" t="s">
+      <c r="H196" t="s">
         <v>1255</v>
       </c>
-      <c r="G196" t="s">
-        <v>1224</v>
-      </c>
-      <c r="H196" t="s">
-        <v>154</v>
-      </c>
       <c r="I196" t="s">
-        <v>838</v>
+        <v>38</v>
       </c>
       <c r="J196" t="s">
-        <v>1047</v>
+        <v>39</v>
       </c>
       <c r="M196" t="s">
         <v>1256</v>
       </c>
-      <c r="N196" t="s">
+      <c r="N196" s="2" t="s">
         <v>1257</v>
       </c>
-      <c r="S196" t="s">
+      <c r="S196" s="2" t="s">
         <v>81</v>
+      </c>
+      <c r="T196" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="U196" s="1" t="s">
+        <v>1259</v>
       </c>
       <c r="W196" t="s">
         <v>55</v>
@@ -13649,40 +13735,34 @@
     </row>
     <row r="197" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B197" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F197" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G197" t="s">
         <v>1221</v>
       </c>
-      <c r="B197" t="s">
-        <v>1222</v>
-      </c>
-      <c r="F197" t="s">
-        <v>1223</v>
-      </c>
-      <c r="G197" t="s">
-        <v>1224</v>
-      </c>
       <c r="H197" t="s">
-        <v>1258</v>
+        <v>614</v>
       </c>
       <c r="I197" t="s">
-        <v>38</v>
+        <v>811</v>
       </c>
       <c r="J197" t="s">
-        <v>39</v>
+        <v>812</v>
       </c>
       <c r="M197" t="s">
-        <v>1259</v>
-      </c>
-      <c r="N197" t="s">
         <v>1260</v>
       </c>
-      <c r="S197" t="s">
+      <c r="N197" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="S197" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="T197" t="s">
-        <v>1261</v>
-      </c>
-      <c r="U197" t="s">
-        <v>1262</v>
       </c>
       <c r="W197" t="s">
         <v>55</v>
@@ -13693,34 +13773,40 @@
     </row>
     <row r="198" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B198" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F198" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G198" t="s">
         <v>1221</v>
       </c>
-      <c r="B198" t="s">
-        <v>1222</v>
-      </c>
-      <c r="F198" t="s">
-        <v>1255</v>
-      </c>
-      <c r="G198" t="s">
-        <v>1224</v>
-      </c>
       <c r="H198" t="s">
-        <v>614</v>
+        <v>457</v>
       </c>
       <c r="I198" t="s">
-        <v>811</v>
+        <v>490</v>
       </c>
       <c r="J198" t="s">
-        <v>812</v>
+        <v>491</v>
       </c>
       <c r="M198" t="s">
+        <v>1262</v>
+      </c>
+      <c r="N198" s="2" t="s">
         <v>1263</v>
       </c>
-      <c r="N198" t="s">
+      <c r="S198" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="T198" s="1" t="s">
         <v>1264</v>
       </c>
-      <c r="S198" t="s">
-        <v>81</v>
+      <c r="U198" s="1" t="s">
+        <v>1265</v>
       </c>
       <c r="W198" t="s">
         <v>55</v>
@@ -13731,40 +13817,40 @@
     </row>
     <row r="199" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B199" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F199" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G199" t="s">
         <v>1221</v>
       </c>
-      <c r="B199" t="s">
-        <v>1222</v>
-      </c>
-      <c r="F199" t="s">
-        <v>1223</v>
-      </c>
-      <c r="G199" t="s">
-        <v>1224</v>
-      </c>
       <c r="H199" t="s">
-        <v>457</v>
+        <v>1266</v>
       </c>
       <c r="I199" t="s">
-        <v>490</v>
+        <v>29</v>
       </c>
       <c r="J199" t="s">
-        <v>491</v>
+        <v>127</v>
       </c>
       <c r="M199" t="s">
-        <v>1265</v>
-      </c>
-      <c r="N199" t="s">
-        <v>1266</v>
-      </c>
-      <c r="S199" t="s">
+        <v>1267</v>
+      </c>
+      <c r="N199" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="S199" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="T199" t="s">
-        <v>1267</v>
-      </c>
-      <c r="U199" t="s">
-        <v>1268</v>
+      <c r="T199" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="U199" s="1" t="s">
+        <v>1270</v>
       </c>
       <c r="W199" t="s">
         <v>55</v>
@@ -13775,40 +13861,43 @@
     </row>
     <row r="200" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>1221</v>
+        <v>1271</v>
       </c>
       <c r="B200" t="s">
-        <v>1222</v>
+        <v>1272</v>
       </c>
       <c r="F200" t="s">
-        <v>1223</v>
+        <v>1273</v>
       </c>
       <c r="G200" t="s">
-        <v>1224</v>
+        <v>1274</v>
       </c>
       <c r="H200" t="s">
-        <v>1269</v>
+        <v>1275</v>
       </c>
       <c r="I200" t="s">
-        <v>29</v>
+        <v>1276</v>
       </c>
       <c r="J200" t="s">
-        <v>127</v>
+        <v>1277</v>
       </c>
       <c r="M200" t="s">
-        <v>1270</v>
-      </c>
-      <c r="N200" t="s">
-        <v>1271</v>
-      </c>
-      <c r="S200" t="s">
+        <v>1278</v>
+      </c>
+      <c r="N200" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="Q200" t="s">
+        <v>1280</v>
+      </c>
+      <c r="S200" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="T200" t="s">
-        <v>1272</v>
-      </c>
-      <c r="U200" t="s">
-        <v>1273</v>
+      <c r="T200" s="1">
+        <v>340</v>
+      </c>
+      <c r="U200" s="1">
+        <v>520</v>
       </c>
       <c r="W200" t="s">
         <v>55</v>
@@ -13819,43 +13908,43 @@
     </row>
     <row r="201" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B201" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F201" t="s">
+        <v>1273</v>
+      </c>
+      <c r="G201" t="s">
         <v>1274</v>
       </c>
-      <c r="B201" t="s">
-        <v>1275</v>
-      </c>
-      <c r="F201" t="s">
-        <v>1276</v>
-      </c>
-      <c r="G201" t="s">
-        <v>1277</v>
-      </c>
       <c r="H201" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="I201" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="J201" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="M201" t="s">
-        <v>1281</v>
-      </c>
-      <c r="N201" t="s">
-        <v>1282</v>
+        <v>1284</v>
+      </c>
+      <c r="N201" s="2" t="s">
+        <v>1285</v>
       </c>
       <c r="Q201" t="s">
-        <v>1283</v>
-      </c>
-      <c r="S201" t="s">
-        <v>81</v>
-      </c>
-      <c r="T201">
-        <v>340</v>
-      </c>
-      <c r="U201">
-        <v>520</v>
+        <v>1286</v>
+      </c>
+      <c r="S201" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="T201" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="U201" s="1">
+        <v>16.600000000000001</v>
       </c>
       <c r="W201" t="s">
         <v>55</v>
@@ -13866,43 +13955,43 @@
     </row>
     <row r="202" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B202" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F202" t="s">
+        <v>1273</v>
+      </c>
+      <c r="G202" t="s">
         <v>1274</v>
       </c>
-      <c r="B202" t="s">
-        <v>1275</v>
-      </c>
-      <c r="F202" t="s">
-        <v>1276</v>
-      </c>
-      <c r="G202" t="s">
-        <v>1277</v>
-      </c>
       <c r="H202" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="I202" t="s">
-        <v>1285</v>
+        <v>69</v>
       </c>
       <c r="J202" t="s">
-        <v>1286</v>
+        <v>70</v>
       </c>
       <c r="M202" t="s">
-        <v>1287</v>
-      </c>
-      <c r="N202" t="s">
         <v>1288</v>
       </c>
+      <c r="N202" s="2" t="s">
+        <v>1289</v>
+      </c>
       <c r="Q202" t="s">
-        <v>1289</v>
-      </c>
-      <c r="S202" t="s">
+        <v>1290</v>
+      </c>
+      <c r="S202" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="T202">
-        <v>22.5</v>
-      </c>
-      <c r="U202">
-        <v>16.600000000000001</v>
+      <c r="T202" s="1">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="U202" s="1">
+        <v>18.899999999999999</v>
       </c>
       <c r="W202" t="s">
         <v>55</v>
@@ -13913,19 +14002,19 @@
     </row>
     <row r="203" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B203" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F203" t="s">
+        <v>1273</v>
+      </c>
+      <c r="G203" t="s">
         <v>1274</v>
       </c>
-      <c r="B203" t="s">
-        <v>1275</v>
-      </c>
-      <c r="F203" t="s">
-        <v>1276</v>
-      </c>
-      <c r="G203" t="s">
-        <v>1277</v>
-      </c>
       <c r="H203" t="s">
-        <v>1290</v>
+        <v>755</v>
       </c>
       <c r="I203" t="s">
         <v>69</v>
@@ -13936,20 +14025,20 @@
       <c r="M203" t="s">
         <v>1291</v>
       </c>
-      <c r="N203" t="s">
+      <c r="N203" s="2" t="s">
         <v>1292</v>
       </c>
       <c r="Q203" t="s">
         <v>1293</v>
       </c>
-      <c r="S203" t="s">
+      <c r="S203" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="T203">
-        <v>33.299999999999997</v>
-      </c>
-      <c r="U203">
-        <v>18.899999999999999</v>
+      <c r="T203" s="1">
+        <v>25.5</v>
+      </c>
+      <c r="U203" s="1">
+        <v>19</v>
       </c>
       <c r="W203" t="s">
         <v>55</v>
@@ -13960,19 +14049,19 @@
     </row>
     <row r="204" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B204" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F204" t="s">
+        <v>1273</v>
+      </c>
+      <c r="G204" t="s">
         <v>1274</v>
       </c>
-      <c r="B204" t="s">
-        <v>1275</v>
-      </c>
-      <c r="F204" t="s">
-        <v>1276</v>
-      </c>
-      <c r="G204" t="s">
-        <v>1277</v>
-      </c>
       <c r="H204" t="s">
-        <v>755</v>
+        <v>1294</v>
       </c>
       <c r="I204" t="s">
         <v>69</v>
@@ -13981,22 +14070,19 @@
         <v>70</v>
       </c>
       <c r="M204" t="s">
-        <v>1294</v>
-      </c>
-      <c r="N204" t="s">
         <v>1295</v>
       </c>
-      <c r="Q204" t="s">
+      <c r="N204" s="2" t="s">
         <v>1296</v>
       </c>
-      <c r="S204" t="s">
-        <v>159</v>
-      </c>
-      <c r="T204">
-        <v>25.5</v>
-      </c>
-      <c r="U204">
-        <v>19</v>
+      <c r="S204" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="T204" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="U204" s="1" t="s">
+        <v>1298</v>
       </c>
       <c r="W204" t="s">
         <v>55</v>
@@ -14007,40 +14093,43 @@
     </row>
     <row r="205" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B205" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F205" t="s">
+        <v>1273</v>
+      </c>
+      <c r="G205" t="s">
         <v>1274</v>
       </c>
-      <c r="B205" t="s">
-        <v>1275</v>
-      </c>
-      <c r="F205" t="s">
-        <v>1276</v>
-      </c>
-      <c r="G205" t="s">
-        <v>1277</v>
-      </c>
       <c r="H205" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="I205" t="s">
-        <v>69</v>
+        <v>490</v>
       </c>
       <c r="J205" t="s">
-        <v>70</v>
+        <v>491</v>
       </c>
       <c r="M205" t="s">
-        <v>1298</v>
-      </c>
-      <c r="N205" t="s">
-        <v>1299</v>
-      </c>
-      <c r="S205" t="s">
-        <v>81</v>
-      </c>
-      <c r="T205" t="s">
+        <v>483</v>
+      </c>
+      <c r="N205" s="2" t="s">
         <v>1300</v>
       </c>
-      <c r="U205" t="s">
+      <c r="Q205" t="s">
         <v>1301</v>
+      </c>
+      <c r="S205" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="T205" s="1">
+        <v>90.2</v>
+      </c>
+      <c r="U205" s="1">
+        <v>34.1</v>
       </c>
       <c r="W205" t="s">
         <v>55</v>
@@ -14051,43 +14140,43 @@
     </row>
     <row r="206" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B206" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F206" t="s">
+        <v>1273</v>
+      </c>
+      <c r="G206" t="s">
         <v>1274</v>
       </c>
-      <c r="B206" t="s">
-        <v>1275</v>
-      </c>
-      <c r="F206" t="s">
-        <v>1276</v>
-      </c>
-      <c r="G206" t="s">
-        <v>1277</v>
-      </c>
       <c r="H206" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="I206" t="s">
-        <v>490</v>
+        <v>460</v>
       </c>
       <c r="J206" t="s">
-        <v>491</v>
+        <v>461</v>
       </c>
       <c r="M206" t="s">
-        <v>483</v>
-      </c>
-      <c r="N206" t="s">
         <v>1303</v>
       </c>
+      <c r="N206" s="2" t="s">
+        <v>1304</v>
+      </c>
       <c r="Q206" t="s">
-        <v>1304</v>
-      </c>
-      <c r="S206" t="s">
         <v>1305</v>
       </c>
-      <c r="T206">
-        <v>90.2</v>
-      </c>
-      <c r="U206">
-        <v>34.1</v>
+      <c r="S206" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="T206" s="1">
+        <v>122.1</v>
+      </c>
+      <c r="U206" s="1">
+        <v>157.80000000000001</v>
       </c>
       <c r="W206" t="s">
         <v>55</v>
@@ -14098,43 +14187,43 @@
     </row>
     <row r="207" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B207" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F207" t="s">
+        <v>1273</v>
+      </c>
+      <c r="G207" t="s">
         <v>1274</v>
       </c>
-      <c r="B207" t="s">
-        <v>1275</v>
-      </c>
-      <c r="F207" t="s">
-        <v>1276</v>
-      </c>
-      <c r="G207" t="s">
-        <v>1277</v>
-      </c>
       <c r="H207" t="s">
-        <v>1302</v>
+        <v>588</v>
       </c>
       <c r="I207" t="s">
-        <v>460</v>
+        <v>38</v>
       </c>
       <c r="J207" t="s">
-        <v>461</v>
+        <v>39</v>
       </c>
       <c r="M207" t="s">
         <v>1306</v>
       </c>
-      <c r="N207" t="s">
+      <c r="N207" s="2" t="s">
         <v>1307</v>
       </c>
       <c r="Q207" t="s">
         <v>1308</v>
       </c>
-      <c r="S207" t="s">
+      <c r="S207" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="T207">
-        <v>122.1</v>
-      </c>
-      <c r="U207">
-        <v>157.80000000000001</v>
+      <c r="T207" s="1">
+        <v>66</v>
+      </c>
+      <c r="U207" s="1">
+        <v>62</v>
       </c>
       <c r="W207" t="s">
         <v>55</v>
@@ -14145,43 +14234,43 @@
     </row>
     <row r="208" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B208" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F208" t="s">
+        <v>1273</v>
+      </c>
+      <c r="G208" t="s">
         <v>1274</v>
       </c>
-      <c r="B208" t="s">
-        <v>1275</v>
-      </c>
-      <c r="F208" t="s">
-        <v>1276</v>
-      </c>
-      <c r="G208" t="s">
-        <v>1277</v>
-      </c>
       <c r="H208" t="s">
-        <v>588</v>
+        <v>1309</v>
       </c>
       <c r="I208" t="s">
-        <v>38</v>
+        <v>581</v>
       </c>
       <c r="J208" t="s">
-        <v>39</v>
+        <v>582</v>
       </c>
       <c r="M208" t="s">
-        <v>1309</v>
-      </c>
-      <c r="N208" t="s">
         <v>1310</v>
       </c>
+      <c r="N208" s="2" t="s">
+        <v>1311</v>
+      </c>
       <c r="Q208" t="s">
-        <v>1311</v>
-      </c>
-      <c r="S208" t="s">
+        <v>1312</v>
+      </c>
+      <c r="S208" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="T208">
-        <v>66</v>
-      </c>
-      <c r="U208">
-        <v>62</v>
+      <c r="T208" s="1">
+        <v>33.1</v>
+      </c>
+      <c r="U208" s="1">
+        <v>53.8</v>
       </c>
       <c r="W208" t="s">
         <v>55</v>
@@ -14192,43 +14281,34 @@
     </row>
     <row r="209" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B209" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F209" t="s">
+        <v>1273</v>
+      </c>
+      <c r="G209" t="s">
         <v>1274</v>
       </c>
-      <c r="B209" t="s">
-        <v>1275</v>
-      </c>
-      <c r="F209" t="s">
-        <v>1276</v>
-      </c>
-      <c r="G209" t="s">
-        <v>1277</v>
-      </c>
       <c r="H209" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="I209" t="s">
-        <v>581</v>
+        <v>350</v>
       </c>
       <c r="J209" t="s">
-        <v>582</v>
+        <v>351</v>
       </c>
       <c r="M209" t="s">
-        <v>1313</v>
-      </c>
-      <c r="N209" t="s">
         <v>1314</v>
       </c>
-      <c r="Q209" t="s">
+      <c r="N209" s="2" t="s">
         <v>1315</v>
       </c>
-      <c r="S209" t="s">
-        <v>159</v>
-      </c>
-      <c r="T209">
-        <v>33.1</v>
-      </c>
-      <c r="U209">
-        <v>53.8</v>
+      <c r="S209" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="W209" t="s">
         <v>55</v>
@@ -14239,34 +14319,43 @@
     </row>
     <row r="210" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B210" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F210" t="s">
+        <v>1273</v>
+      </c>
+      <c r="G210" t="s">
         <v>1274</v>
       </c>
-      <c r="B210" t="s">
-        <v>1275</v>
-      </c>
-      <c r="F210" t="s">
-        <v>1276</v>
-      </c>
-      <c r="G210" t="s">
-        <v>1277</v>
-      </c>
       <c r="H210" t="s">
+        <v>1112</v>
+      </c>
+      <c r="I210" t="s">
+        <v>460</v>
+      </c>
+      <c r="J210" t="s">
+        <v>461</v>
+      </c>
+      <c r="M210" t="s">
         <v>1316</v>
       </c>
-      <c r="I210" t="s">
-        <v>350</v>
-      </c>
-      <c r="J210" t="s">
-        <v>351</v>
-      </c>
-      <c r="M210" t="s">
+      <c r="N210" s="2" t="s">
         <v>1317</v>
       </c>
-      <c r="N210" t="s">
+      <c r="Q210" t="s">
         <v>1318</v>
       </c>
-      <c r="S210" t="s">
-        <v>81</v>
+      <c r="S210" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="T210" s="1">
+        <v>32.5</v>
+      </c>
+      <c r="U210" s="1">
+        <v>26</v>
       </c>
       <c r="W210" t="s">
         <v>55</v>
@@ -14277,87 +14366,84 @@
     </row>
     <row r="211" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>1274</v>
+        <v>871</v>
       </c>
       <c r="B211" t="s">
-        <v>1275</v>
+        <v>1319</v>
       </c>
       <c r="F211" t="s">
-        <v>1276</v>
+        <v>347</v>
       </c>
       <c r="G211" t="s">
-        <v>1277</v>
+        <v>1320</v>
       </c>
       <c r="H211" t="s">
-        <v>1115</v>
+        <v>1321</v>
       </c>
       <c r="I211" t="s">
-        <v>460</v>
+        <v>77</v>
       </c>
       <c r="J211" t="s">
-        <v>461</v>
+        <v>78</v>
       </c>
       <c r="M211" t="s">
-        <v>1319</v>
-      </c>
-      <c r="N211" t="s">
-        <v>1320</v>
-      </c>
-      <c r="Q211" t="s">
-        <v>1321</v>
-      </c>
-      <c r="S211" t="s">
-        <v>159</v>
-      </c>
-      <c r="T211">
-        <v>32.5</v>
-      </c>
-      <c r="U211">
-        <v>26</v>
+        <v>930</v>
+      </c>
+      <c r="N211" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="S211" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T211" s="1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="U211" s="1" t="s">
+        <v>1324</v>
       </c>
       <c r="W211" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="X211">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="212" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="B212" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="F212" t="s">
         <v>347</v>
       </c>
       <c r="G212" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="H212" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="I212" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="J212" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="M212" t="s">
-        <v>933</v>
-      </c>
-      <c r="N212" t="s">
-        <v>1325</v>
-      </c>
-      <c r="S212" t="s">
+        <v>1326</v>
+      </c>
+      <c r="N212" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="S212" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="T212" t="s">
-        <v>1326</v>
-      </c>
-      <c r="U212" t="s">
-        <v>1327</v>
+      <c r="T212" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="U212" s="1" t="s">
+        <v>1328</v>
       </c>
       <c r="W212" t="s">
         <v>36</v>
@@ -14368,40 +14454,43 @@
     </row>
     <row r="213" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>874</v>
+        <v>1329</v>
       </c>
       <c r="B213" t="s">
-        <v>1322</v>
+        <v>1330</v>
       </c>
       <c r="F213" t="s">
-        <v>347</v>
+        <v>1331</v>
       </c>
       <c r="G213" t="s">
-        <v>1323</v>
-      </c>
-      <c r="H213" t="s">
-        <v>1328</v>
+        <v>1091</v>
+      </c>
+      <c r="H213">
+        <v>1480</v>
       </c>
       <c r="I213" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="J213" t="s">
-        <v>127</v>
+        <v>65</v>
       </c>
       <c r="M213" t="s">
-        <v>1329</v>
-      </c>
-      <c r="N213" t="s">
-        <v>1330</v>
-      </c>
-      <c r="S213" t="s">
-        <v>33</v>
-      </c>
-      <c r="T213" t="s">
-        <v>754</v>
-      </c>
-      <c r="U213" t="s">
-        <v>1331</v>
+        <v>1332</v>
+      </c>
+      <c r="N213" s="2" t="s">
+        <v>1333</v>
+      </c>
+      <c r="Q213" t="s">
+        <v>1334</v>
+      </c>
+      <c r="S213" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="T213" s="1">
+        <v>120</v>
+      </c>
+      <c r="U213" s="1">
+        <v>170</v>
       </c>
       <c r="W213" t="s">
         <v>36</v>
@@ -14412,43 +14501,46 @@
     </row>
     <row r="214" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
       <c r="B214" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="F214" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="G214" t="s">
-        <v>1094</v>
-      </c>
-      <c r="H214">
-        <v>1480</v>
+        <v>1091</v>
+      </c>
+      <c r="H214" t="s">
+        <v>1335</v>
       </c>
       <c r="I214" t="s">
         <v>64</v>
       </c>
       <c r="J214" t="s">
-        <v>65</v>
+        <v>1336</v>
+      </c>
+      <c r="L214" t="s">
+        <v>1337</v>
       </c>
       <c r="M214" t="s">
-        <v>1335</v>
-      </c>
-      <c r="N214" t="s">
-        <v>1336</v>
+        <v>1338</v>
+      </c>
+      <c r="N214" s="2" t="s">
+        <v>1339</v>
       </c>
       <c r="Q214" t="s">
-        <v>1337</v>
-      </c>
-      <c r="S214" t="s">
-        <v>159</v>
-      </c>
-      <c r="T214">
-        <v>120</v>
-      </c>
-      <c r="U214">
-        <v>170</v>
+        <v>1340</v>
+      </c>
+      <c r="S214" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="T214" s="1">
+        <v>141</v>
+      </c>
+      <c r="U214" s="1">
+        <v>100</v>
       </c>
       <c r="W214" t="s">
         <v>36</v>
@@ -14459,46 +14551,46 @@
     </row>
     <row r="215" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>1332</v>
+        <v>1077</v>
       </c>
       <c r="B215" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="F215" t="s">
-        <v>1334</v>
+        <v>266</v>
       </c>
       <c r="G215" t="s">
-        <v>1094</v>
-      </c>
-      <c r="H215" t="s">
-        <v>1338</v>
+        <v>1342</v>
+      </c>
+      <c r="H215">
+        <v>1444</v>
       </c>
       <c r="I215" t="s">
         <v>64</v>
       </c>
       <c r="J215" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="L215" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
       <c r="M215" t="s">
-        <v>1341</v>
-      </c>
-      <c r="N215" t="s">
-        <v>1342</v>
+        <v>1345</v>
+      </c>
+      <c r="N215" s="2" t="s">
+        <v>1346</v>
       </c>
       <c r="Q215" t="s">
-        <v>1343</v>
-      </c>
-      <c r="S215" t="s">
-        <v>1344</v>
-      </c>
-      <c r="T215">
-        <v>141</v>
-      </c>
-      <c r="U215">
-        <v>100</v>
+        <v>736</v>
+      </c>
+      <c r="S215" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="T215" s="1">
+        <v>230</v>
+      </c>
+      <c r="U215" s="1">
+        <v>180</v>
       </c>
       <c r="W215" t="s">
         <v>36</v>
@@ -14509,46 +14601,43 @@
     </row>
     <row r="216" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="B216" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="F216" t="s">
         <v>266</v>
       </c>
       <c r="G216" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
       <c r="H216">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="I216" t="s">
         <v>64</v>
       </c>
       <c r="J216" t="s">
-        <v>1346</v>
-      </c>
-      <c r="L216" t="s">
-        <v>1347</v>
+        <v>65</v>
       </c>
       <c r="M216" t="s">
         <v>1348</v>
       </c>
-      <c r="N216" t="s">
+      <c r="N216" s="2" t="s">
         <v>1349</v>
       </c>
       <c r="Q216" t="s">
-        <v>736</v>
-      </c>
-      <c r="S216" t="s">
         <v>1350</v>
       </c>
-      <c r="T216">
-        <v>230</v>
-      </c>
-      <c r="U216">
-        <v>180</v>
+      <c r="S216" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="T216" s="1">
+        <v>292</v>
+      </c>
+      <c r="U216" s="1">
+        <v>415</v>
       </c>
       <c r="W216" t="s">
         <v>36</v>
@@ -14559,43 +14648,46 @@
     </row>
     <row r="217" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>1080</v>
+        <v>1352</v>
       </c>
       <c r="B217" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="F217" t="s">
-        <v>266</v>
+        <v>1353</v>
       </c>
       <c r="G217" t="s">
-        <v>1345</v>
+        <v>1354</v>
       </c>
       <c r="H217">
-        <v>1446</v>
+        <v>1474</v>
       </c>
       <c r="I217" t="s">
         <v>64</v>
       </c>
       <c r="J217" t="s">
-        <v>65</v>
+        <v>1355</v>
+      </c>
+      <c r="L217" t="s">
+        <v>1356</v>
       </c>
       <c r="M217" t="s">
-        <v>1351</v>
-      </c>
-      <c r="N217" t="s">
-        <v>1352</v>
+        <v>1357</v>
+      </c>
+      <c r="N217" s="2" t="s">
+        <v>1358</v>
       </c>
       <c r="Q217" t="s">
-        <v>1353</v>
-      </c>
-      <c r="S217" t="s">
-        <v>1354</v>
-      </c>
-      <c r="T217">
-        <v>292</v>
-      </c>
-      <c r="U217">
-        <v>415</v>
+        <v>1359</v>
+      </c>
+      <c r="S217" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="T217" s="1">
+        <v>165</v>
+      </c>
+      <c r="U217" s="1">
+        <v>185</v>
       </c>
       <c r="W217" t="s">
         <v>36</v>
@@ -14606,46 +14698,46 @@
     </row>
     <row r="218" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
       <c r="B218" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="F218" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
       <c r="G218" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
       <c r="H218">
-        <v>1474</v>
+        <v>1482</v>
       </c>
       <c r="I218" t="s">
         <v>64</v>
       </c>
       <c r="J218" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="L218" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="M218" t="s">
-        <v>1360</v>
-      </c>
-      <c r="N218" t="s">
-        <v>1361</v>
+        <v>1362</v>
+      </c>
+      <c r="N218" s="2" t="s">
+        <v>1363</v>
       </c>
       <c r="Q218" t="s">
-        <v>1362</v>
-      </c>
-      <c r="S218" t="s">
+        <v>1364</v>
+      </c>
+      <c r="S218" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T218">
-        <v>165</v>
-      </c>
-      <c r="U218">
-        <v>185</v>
+      <c r="T218" s="1">
+        <v>143</v>
+      </c>
+      <c r="U218" s="1">
+        <v>180</v>
       </c>
       <c r="W218" t="s">
         <v>36</v>
@@ -14656,49 +14748,43 @@
     </row>
     <row r="219" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>1355</v>
+        <v>1365</v>
       </c>
       <c r="B219" t="s">
-        <v>1333</v>
+        <v>1366</v>
       </c>
       <c r="F219" t="s">
-        <v>1356</v>
+        <v>48</v>
       </c>
       <c r="G219" t="s">
-        <v>1357</v>
-      </c>
-      <c r="H219">
-        <v>1482</v>
+        <v>49</v>
+      </c>
+      <c r="H219" t="s">
+        <v>949</v>
       </c>
       <c r="I219" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="J219" t="s">
-        <v>1363</v>
-      </c>
-      <c r="L219" t="s">
-        <v>1364</v>
+        <v>78</v>
       </c>
       <c r="M219" t="s">
-        <v>1365</v>
-      </c>
-      <c r="N219" t="s">
-        <v>1366</v>
-      </c>
-      <c r="Q219" t="s">
         <v>1367</v>
       </c>
-      <c r="S219" t="s">
+      <c r="N219" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="S219" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T219">
-        <v>143</v>
-      </c>
-      <c r="U219">
-        <v>180</v>
+      <c r="T219" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="U219" s="1" t="s">
+        <v>1370</v>
       </c>
       <c r="W219" t="s">
-        <v>36</v>
+        <v>953</v>
       </c>
       <c r="X219">
         <v>3</v>
@@ -14706,10 +14792,10 @@
     </row>
     <row r="220" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>1368</v>
+        <v>1365</v>
       </c>
       <c r="B220" t="s">
-        <v>1369</v>
+        <v>1366</v>
       </c>
       <c r="F220" t="s">
         <v>48</v>
@@ -14718,77 +14804,33 @@
         <v>49</v>
       </c>
       <c r="H220" t="s">
-        <v>952</v>
+        <v>1371</v>
       </c>
       <c r="I220" t="s">
-        <v>77</v>
+        <v>1372</v>
       </c>
       <c r="J220" t="s">
-        <v>78</v>
+        <v>1373</v>
       </c>
       <c r="M220" t="s">
-        <v>1370</v>
-      </c>
-      <c r="N220" t="s">
-        <v>1371</v>
-      </c>
-      <c r="S220" t="s">
-        <v>109</v>
-      </c>
-      <c r="T220" t="s">
-        <v>1372</v>
-      </c>
-      <c r="U220" t="s">
-        <v>1373</v>
+        <v>1374</v>
+      </c>
+      <c r="N220" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="S220" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="T220" s="1" t="s">
+        <v>1376</v>
+      </c>
+      <c r="U220" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="W220" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="X220">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="221" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>1368</v>
-      </c>
-      <c r="B221" t="s">
-        <v>1369</v>
-      </c>
-      <c r="F221" t="s">
-        <v>48</v>
-      </c>
-      <c r="G221" t="s">
-        <v>49</v>
-      </c>
-      <c r="H221" t="s">
-        <v>1374</v>
-      </c>
-      <c r="I221" t="s">
-        <v>1375</v>
-      </c>
-      <c r="J221" t="s">
-        <v>1376</v>
-      </c>
-      <c r="M221" t="s">
-        <v>1377</v>
-      </c>
-      <c r="N221" t="s">
-        <v>1378</v>
-      </c>
-      <c r="S221" t="s">
-        <v>81</v>
-      </c>
-      <c r="T221" t="s">
-        <v>1379</v>
-      </c>
-      <c r="U221" t="s">
-        <v>118</v>
-      </c>
-      <c r="W221" t="s">
-        <v>956</v>
-      </c>
-      <c r="X221">
         <v>3</v>
       </c>
     </row>
